--- a/data/default/CattleHerd.xlsx
+++ b/data/default/CattleHerd.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jnka0003\Documents\#1 Projekt\MISTRA Food Futures WP5\CIBUSmod Food Systems Model\CIBUSmod\data\prod_parameters\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jnka0003\Documents\#1 Projekt\MISTRA Food Futures WP5\CIBUSmod Food Systems Model\CIBUSmod\data\default\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19020" windowHeight="6705" tabRatio="846" activeTab="4"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19020" windowHeight="6705" tabRatio="846" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="references" sheetId="13" r:id="rId1"/>
@@ -3307,12 +3307,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="38" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="40" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="40" fillId="41" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -3324,6 +3318,12 @@
     </xf>
     <xf numFmtId="0" fontId="40" fillId="40" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="38" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="40" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="43">
@@ -36050,49 +36050,49 @@
       </c>
       <c r="AB3" s="202"/>
       <c r="AC3" s="202"/>
-      <c r="AD3" s="261" t="s">
+      <c r="AD3" s="259" t="s">
         <v>543</v>
       </c>
-      <c r="AE3" s="262" t="s">
+      <c r="AE3" s="260" t="s">
         <v>545</v>
       </c>
-      <c r="AF3" s="261" t="s">
+      <c r="AF3" s="259" t="s">
         <v>547</v>
       </c>
-      <c r="AG3" s="262" t="s">
+      <c r="AG3" s="260" t="s">
         <v>549</v>
       </c>
-      <c r="AH3" s="261" t="s">
+      <c r="AH3" s="259" t="s">
         <v>550</v>
       </c>
-      <c r="AI3" s="262" t="s">
+      <c r="AI3" s="260" t="s">
         <v>552</v>
       </c>
-      <c r="AJ3" s="261" t="s">
+      <c r="AJ3" s="259" t="s">
         <v>553</v>
       </c>
-      <c r="AK3" s="262" t="s">
+      <c r="AK3" s="260" t="s">
         <v>554</v>
       </c>
-      <c r="AL3" s="261" t="s">
+      <c r="AL3" s="259" t="s">
         <v>556</v>
       </c>
-      <c r="AM3" s="262" t="s">
+      <c r="AM3" s="260" t="s">
         <v>557</v>
       </c>
-      <c r="AN3" s="261" t="s">
+      <c r="AN3" s="259" t="s">
         <v>577</v>
       </c>
-      <c r="AO3" s="262" t="s">
+      <c r="AO3" s="260" t="s">
         <v>559</v>
       </c>
-      <c r="AP3" s="261" t="s">
+      <c r="AP3" s="259" t="s">
         <v>560</v>
       </c>
-      <c r="AQ3" s="260" t="s">
+      <c r="AQ3" s="258" t="s">
         <v>581</v>
       </c>
-      <c r="AR3" s="259" t="s">
+      <c r="AR3" s="257" t="s">
         <v>576</v>
       </c>
     </row>
@@ -36143,21 +36143,21 @@
       <c r="AA4" s="201"/>
       <c r="AB4" s="202"/>
       <c r="AC4" s="202"/>
-      <c r="AD4" s="261"/>
-      <c r="AE4" s="262"/>
-      <c r="AF4" s="261"/>
-      <c r="AG4" s="262"/>
-      <c r="AH4" s="261"/>
-      <c r="AI4" s="262"/>
-      <c r="AJ4" s="261"/>
-      <c r="AK4" s="262"/>
-      <c r="AL4" s="261"/>
-      <c r="AM4" s="262"/>
-      <c r="AN4" s="261"/>
-      <c r="AO4" s="262"/>
-      <c r="AP4" s="261"/>
-      <c r="AQ4" s="260"/>
-      <c r="AR4" s="259"/>
+      <c r="AD4" s="259"/>
+      <c r="AE4" s="260"/>
+      <c r="AF4" s="259"/>
+      <c r="AG4" s="260"/>
+      <c r="AH4" s="259"/>
+      <c r="AI4" s="260"/>
+      <c r="AJ4" s="259"/>
+      <c r="AK4" s="260"/>
+      <c r="AL4" s="259"/>
+      <c r="AM4" s="260"/>
+      <c r="AN4" s="259"/>
+      <c r="AO4" s="260"/>
+      <c r="AP4" s="259"/>
+      <c r="AQ4" s="258"/>
+      <c r="AR4" s="257"/>
     </row>
     <row r="5" spans="2:44" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="209" t="s">
@@ -36238,21 +36238,21 @@
       <c r="AA5" s="201"/>
       <c r="AB5" s="202"/>
       <c r="AC5" s="202"/>
-      <c r="AD5" s="261"/>
-      <c r="AE5" s="262"/>
-      <c r="AF5" s="261"/>
-      <c r="AG5" s="262"/>
-      <c r="AH5" s="261"/>
-      <c r="AI5" s="262"/>
-      <c r="AJ5" s="261"/>
-      <c r="AK5" s="262"/>
-      <c r="AL5" s="261"/>
-      <c r="AM5" s="262"/>
-      <c r="AN5" s="261"/>
-      <c r="AO5" s="262"/>
-      <c r="AP5" s="261"/>
-      <c r="AQ5" s="260"/>
-      <c r="AR5" s="259" t="s">
+      <c r="AD5" s="259"/>
+      <c r="AE5" s="260"/>
+      <c r="AF5" s="259"/>
+      <c r="AG5" s="260"/>
+      <c r="AH5" s="259"/>
+      <c r="AI5" s="260"/>
+      <c r="AJ5" s="259"/>
+      <c r="AK5" s="260"/>
+      <c r="AL5" s="259"/>
+      <c r="AM5" s="260"/>
+      <c r="AN5" s="259"/>
+      <c r="AO5" s="260"/>
+      <c r="AP5" s="259"/>
+      <c r="AQ5" s="258"/>
+      <c r="AR5" s="257" t="s">
         <v>575</v>
       </c>
     </row>
@@ -37687,23 +37687,23 @@
       <c r="N23" s="169"/>
       <c r="O23" s="169"/>
       <c r="P23" s="169"/>
-      <c r="Q23" s="258" t="s">
+      <c r="Q23" s="262" t="s">
         <v>596</v>
       </c>
-      <c r="R23" s="258" t="s">
+      <c r="R23" s="262" t="s">
         <v>597</v>
       </c>
-      <c r="S23" s="258" t="s">
+      <c r="S23" s="262" t="s">
         <v>584</v>
       </c>
-      <c r="T23" s="257" t="s">
+      <c r="T23" s="261" t="s">
         <v>303</v>
       </c>
-      <c r="U23" s="257"/>
-      <c r="V23" s="257" t="s">
+      <c r="U23" s="261"/>
+      <c r="V23" s="261" t="s">
         <v>304</v>
       </c>
-      <c r="W23" s="257"/>
+      <c r="W23" s="261"/>
       <c r="X23" s="168" t="s">
         <v>482</v>
       </c>
@@ -37728,9 +37728,9 @@
       <c r="P24" s="170" t="s">
         <v>483</v>
       </c>
-      <c r="Q24" s="258"/>
-      <c r="R24" s="258"/>
-      <c r="S24" s="258"/>
+      <c r="Q24" s="262"/>
+      <c r="R24" s="262"/>
+      <c r="S24" s="262"/>
       <c r="T24" s="244" t="s">
         <v>483</v>
       </c>
@@ -44348,6 +44348,11 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="V23:W23"/>
+    <mergeCell ref="T23:U23"/>
+    <mergeCell ref="Q23:Q24"/>
+    <mergeCell ref="R23:R24"/>
+    <mergeCell ref="S23:S24"/>
     <mergeCell ref="AR3:AR5"/>
     <mergeCell ref="AQ3:AQ5"/>
     <mergeCell ref="AD3:AD5"/>
@@ -44363,11 +44368,6 @@
     <mergeCell ref="AN3:AN5"/>
     <mergeCell ref="AO3:AO5"/>
     <mergeCell ref="AP3:AP5"/>
-    <mergeCell ref="V23:W23"/>
-    <mergeCell ref="T23:U23"/>
-    <mergeCell ref="Q23:Q24"/>
-    <mergeCell ref="R23:R24"/>
-    <mergeCell ref="S23:S24"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/data/default/CattleHerd.xlsx
+++ b/data/default/CattleHerd.xlsx
@@ -145,7 +145,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4043" uniqueCount="601">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4041" uniqueCount="601">
   <si>
     <t>value</t>
   </si>
@@ -3301,12 +3301,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="38" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="40" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="40" fillId="41" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -3318,6 +3312,12 @@
     </xf>
     <xf numFmtId="0" fontId="40" fillId="40" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="38" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="40" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="43">
@@ -3995,6 +3995,7 @@
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout/>
       <c:overlay val="0"/>
     </c:title>
     <c:autoTitleDeleted val="0"/>
@@ -4397,6 +4398,7 @@
               </a:p>
             </c:rich>
           </c:tx>
+          <c:layout/>
           <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="0" sourceLinked="1"/>
@@ -4430,6 +4432,7 @@
               </a:p>
             </c:rich>
           </c:tx>
+          <c:layout/>
           <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="0.0" sourceLinked="1"/>
@@ -4443,6 +4446,7 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
+      <c:layout/>
       <c:overlay val="0"/>
     </c:legend>
     <c:plotVisOnly val="1"/>
@@ -4472,6 +4476,7 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -5473,6 +5478,7 @@
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout/>
       <c:overlay val="0"/>
     </c:title>
     <c:autoTitleDeleted val="0"/>
@@ -5692,6 +5698,7 @@
               </a:p>
             </c:rich>
           </c:tx>
+          <c:layout/>
           <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="0" sourceLinked="1"/>
@@ -5725,6 +5732,7 @@
               </a:p>
             </c:rich>
           </c:tx>
+          <c:layout/>
           <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
@@ -5778,6 +5786,7 @@
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout/>
       <c:overlay val="0"/>
     </c:title>
     <c:autoTitleDeleted val="0"/>
@@ -5997,6 +6006,7 @@
               </a:p>
             </c:rich>
           </c:tx>
+          <c:layout/>
           <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="0" sourceLinked="1"/>
@@ -6030,6 +6040,7 @@
               </a:p>
             </c:rich>
           </c:tx>
+          <c:layout/>
           <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
@@ -6083,6 +6094,7 @@
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout/>
       <c:overlay val="0"/>
     </c:title>
     <c:autoTitleDeleted val="0"/>
@@ -6485,6 +6497,7 @@
               </a:p>
             </c:rich>
           </c:tx>
+          <c:layout/>
           <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="0" sourceLinked="1"/>
@@ -6518,6 +6531,7 @@
               </a:p>
             </c:rich>
           </c:tx>
+          <c:layout/>
           <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="0.0" sourceLinked="1"/>
@@ -6531,6 +6545,7 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
+      <c:layout/>
       <c:overlay val="0"/>
     </c:legend>
     <c:plotVisOnly val="1"/>
@@ -6575,6 +6590,7 @@
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout/>
       <c:overlay val="0"/>
     </c:title>
     <c:autoTitleDeleted val="0"/>
@@ -6977,6 +6993,7 @@
               </a:p>
             </c:rich>
           </c:tx>
+          <c:layout/>
           <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="0" sourceLinked="1"/>
@@ -7010,6 +7027,7 @@
               </a:p>
             </c:rich>
           </c:tx>
+          <c:layout/>
           <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="0.0" sourceLinked="1"/>
@@ -7023,6 +7041,7 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
+      <c:layout/>
       <c:overlay val="0"/>
     </c:legend>
     <c:plotVisOnly val="1"/>
@@ -7067,6 +7086,7 @@
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout/>
       <c:overlay val="0"/>
     </c:title>
     <c:autoTitleDeleted val="0"/>
@@ -7286,6 +7306,7 @@
               </a:p>
             </c:rich>
           </c:tx>
+          <c:layout/>
           <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="0" sourceLinked="1"/>
@@ -7319,6 +7340,7 @@
               </a:p>
             </c:rich>
           </c:tx>
+          <c:layout/>
           <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
@@ -7372,6 +7394,7 @@
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout/>
       <c:overlay val="0"/>
     </c:title>
     <c:autoTitleDeleted val="0"/>
@@ -7591,6 +7614,7 @@
               </a:p>
             </c:rich>
           </c:tx>
+          <c:layout/>
           <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="0" sourceLinked="1"/>
@@ -7624,6 +7648,7 @@
               </a:p>
             </c:rich>
           </c:tx>
+          <c:layout/>
           <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
@@ -7677,6 +7702,7 @@
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout/>
       <c:overlay val="0"/>
     </c:title>
     <c:autoTitleDeleted val="0"/>
@@ -8079,6 +8105,7 @@
               </a:p>
             </c:rich>
           </c:tx>
+          <c:layout/>
           <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="0" sourceLinked="1"/>
@@ -8112,6 +8139,7 @@
               </a:p>
             </c:rich>
           </c:tx>
+          <c:layout/>
           <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="0.0" sourceLinked="1"/>
@@ -8125,6 +8153,7 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
+      <c:layout/>
       <c:overlay val="0"/>
     </c:legend>
     <c:plotVisOnly val="1"/>
@@ -17660,7 +17689,7 @@
   <sheetPr>
     <tabColor theme="4"/>
   </sheetPr>
-  <dimension ref="A1:O601"/>
+  <dimension ref="A1:O599"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" bestFit="1" customWidth="1"/>
@@ -20316,120 +20345,133 @@
       </c>
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A140" s="97" t="s">
+      <c r="I140" s="13"/>
+    </row>
+    <row r="141" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A141" s="94" t="s">
+        <v>404</v>
+      </c>
+      <c r="B141" s="94"/>
+      <c r="C141" s="94"/>
+      <c r="D141" s="95"/>
+      <c r="E141" s="95"/>
+      <c r="F141" s="95"/>
+      <c r="G141" s="95"/>
+      <c r="H141" s="95"/>
+      <c r="I141" s="95"/>
+      <c r="J141" s="95" t="s">
+        <v>327</v>
+      </c>
+      <c r="K141" s="95"/>
+      <c r="L141" s="95"/>
+    </row>
+    <row r="142" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H142" s="159" t="s">
+        <v>326</v>
+      </c>
+      <c r="I142" s="159">
+        <v>0</v>
+      </c>
+      <c r="J142" s="159"/>
+      <c r="K142" s="159" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="143" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A143" s="97" t="s">
         <v>303</v>
       </c>
-      <c r="B140" s="97"/>
-      <c r="C140" s="97"/>
-      <c r="D140" s="98"/>
-      <c r="E140" s="98"/>
-      <c r="F140" s="98"/>
-      <c r="G140" s="98"/>
-      <c r="H140" s="98"/>
-      <c r="I140" s="99"/>
-      <c r="J140" s="98"/>
-      <c r="K140" s="98"/>
-      <c r="L140" s="98"/>
-    </row>
-    <row r="141" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A141" s="100" t="s">
-        <v>304</v>
-      </c>
-      <c r="B141" s="100"/>
-      <c r="C141" s="100"/>
-      <c r="D141" s="101"/>
-      <c r="E141" s="101"/>
-      <c r="F141" s="101"/>
-      <c r="G141" s="101"/>
-      <c r="H141" s="101"/>
-      <c r="I141" s="101"/>
-      <c r="J141" s="101"/>
-      <c r="K141" s="101"/>
-      <c r="L141" s="101"/>
-    </row>
-    <row r="143" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A143" s="94" t="s">
-        <v>404</v>
-      </c>
-      <c r="B143" s="94"/>
-      <c r="C143" s="94"/>
-      <c r="D143" s="95"/>
-      <c r="E143" s="95"/>
-      <c r="F143" s="95"/>
-      <c r="G143" s="95"/>
-      <c r="H143" s="95"/>
-      <c r="I143" s="95"/>
-      <c r="J143" s="95" t="s">
-        <v>327</v>
-      </c>
-      <c r="K143" s="95"/>
-      <c r="L143" s="95"/>
+      <c r="B143" s="97"/>
+      <c r="C143" s="97"/>
+      <c r="D143" s="98"/>
+      <c r="E143" s="98"/>
+      <c r="F143" s="98"/>
+      <c r="G143" s="98"/>
+      <c r="H143" s="98"/>
+      <c r="I143" s="99"/>
+      <c r="J143" s="98"/>
+      <c r="K143" s="98"/>
+      <c r="L143" s="98"/>
     </row>
     <row r="144" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="H144" s="159" t="s">
+      <c r="A144" s="81" t="s">
+        <v>74</v>
+      </c>
+      <c r="B144" s="48"/>
+      <c r="C144" s="48"/>
+      <c r="D144" s="49"/>
+      <c r="E144" s="49"/>
+      <c r="F144" s="49"/>
+      <c r="G144" s="49"/>
+      <c r="H144" s="49"/>
+      <c r="I144" s="162"/>
+      <c r="J144" s="49"/>
+      <c r="K144" s="49"/>
+      <c r="L144" s="49"/>
+    </row>
+    <row r="145" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A145" s="159" t="s">
+        <v>2</v>
+      </c>
+      <c r="B145" s="159"/>
+      <c r="C145" s="159"/>
+      <c r="D145" s="159" t="s">
+        <v>18</v>
+      </c>
+      <c r="H145" s="159" t="s">
         <v>326</v>
       </c>
-      <c r="I144" s="159">
+      <c r="I145" s="159">
         <v>0</v>
       </c>
-      <c r="J144" s="159"/>
-      <c r="K144" s="159" t="s">
+      <c r="J145" s="159"/>
+      <c r="K145" s="159" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="145" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A145" s="97" t="s">
-        <v>303</v>
-      </c>
-      <c r="B145" s="97"/>
-      <c r="C145" s="97"/>
-      <c r="D145" s="98"/>
-      <c r="E145" s="98"/>
-      <c r="F145" s="98"/>
-      <c r="G145" s="98"/>
-      <c r="H145" s="98"/>
-      <c r="I145" s="99"/>
-      <c r="J145" s="98"/>
-      <c r="K145" s="98"/>
-      <c r="L145" s="98"/>
-    </row>
-    <row r="146" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A146" s="81" t="s">
-        <v>74</v>
-      </c>
-      <c r="B146" s="48"/>
-      <c r="C146" s="48"/>
-      <c r="D146" s="49"/>
-      <c r="E146" s="49"/>
-      <c r="F146" s="49"/>
-      <c r="G146" s="49"/>
-      <c r="H146" s="49"/>
-      <c r="I146" s="162"/>
-      <c r="J146" s="49"/>
-      <c r="K146" s="49"/>
-      <c r="L146" s="49"/>
-    </row>
-    <row r="147" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A147" s="159" t="s">
+    <row r="146" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
         <v>2</v>
       </c>
-      <c r="B147" s="159"/>
-      <c r="C147" s="159"/>
-      <c r="D147" s="159" t="s">
+      <c r="D146" t="s">
         <v>18</v>
       </c>
-      <c r="H147" s="159" t="s">
+      <c r="E146" t="str">
+        <f>Foderstater!U$63</f>
+        <v>ley silage, 1st cut</v>
+      </c>
+      <c r="H146" t="s">
         <v>326</v>
       </c>
-      <c r="I147" s="159">
-        <v>0</v>
+      <c r="I146" s="13">
+        <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E146,Foderstater!$U$63:$U$100,0),MATCH(A146&amp;C146&amp;D146,Foderstater!$X$62:$AI$62,0))</f>
+        <v>38.609681277854051</v>
+      </c>
+      <c r="J146" s="159"/>
+      <c r="K146" s="159"/>
+    </row>
+    <row r="147" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>2</v>
+      </c>
+      <c r="D147" t="s">
+        <v>18</v>
+      </c>
+      <c r="E147" t="str">
+        <f>Foderstater!U$64</f>
+        <v>ley silage, regrowth</v>
+      </c>
+      <c r="H147" t="s">
+        <v>326</v>
+      </c>
+      <c r="I147" s="13">
+        <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E147,Foderstater!$U$63:$U$100,0),MATCH(A147&amp;C147&amp;D147,Foderstater!$X$62:$AI$62,0))</f>
+        <v>9.2377598080515053</v>
       </c>
       <c r="J147" s="159"/>
-      <c r="K147" s="159" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="148" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K147" s="159"/>
+    </row>
+    <row r="148" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>2</v>
       </c>
@@ -20437,20 +20479,20 @@
         <v>18</v>
       </c>
       <c r="E148" t="str">
-        <f>Foderstater!U$63</f>
-        <v>ley silage, 1st cut</v>
+        <f>Foderstater!U$65</f>
+        <v>other silage</v>
       </c>
       <c r="H148" t="s">
         <v>326</v>
       </c>
       <c r="I148" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E148,Foderstater!$U$63:$U$100,0),MATCH(A148&amp;C148&amp;D148,Foderstater!$X$62:$AI$62,0))</f>
-        <v>38.609681277854051</v>
+        <v>0</v>
       </c>
       <c r="J148" s="159"/>
       <c r="K148" s="159"/>
     </row>
-    <row r="149" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>2</v>
       </c>
@@ -20458,20 +20500,20 @@
         <v>18</v>
       </c>
       <c r="E149" t="str">
-        <f>Foderstater!U$64</f>
-        <v>ley silage, regrowth</v>
+        <f>Foderstater!U$66</f>
+        <v>maize silage</v>
       </c>
       <c r="H149" t="s">
         <v>326</v>
       </c>
       <c r="I149" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E149,Foderstater!$U$63:$U$100,0),MATCH(A149&amp;C149&amp;D149,Foderstater!$X$62:$AI$62,0))</f>
-        <v>9.2377598080515053</v>
+        <v>0</v>
       </c>
       <c r="J149" s="159"/>
       <c r="K149" s="159"/>
     </row>
-    <row r="150" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>2</v>
       </c>
@@ -20479,20 +20521,20 @@
         <v>18</v>
       </c>
       <c r="E150" t="str">
-        <f>Foderstater!U$65</f>
-        <v>other silage</v>
+        <f>Foderstater!U$67</f>
+        <v>straw</v>
       </c>
       <c r="H150" t="s">
         <v>326</v>
       </c>
       <c r="I150" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E150,Foderstater!$U$63:$U$100,0),MATCH(A150&amp;C150&amp;D150,Foderstater!$X$62:$AI$62,0))</f>
-        <v>0</v>
+        <v>3.1679738484393072</v>
       </c>
       <c r="J150" s="159"/>
       <c r="K150" s="159"/>
     </row>
-    <row r="151" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>2</v>
       </c>
@@ -20500,20 +20542,20 @@
         <v>18</v>
       </c>
       <c r="E151" t="str">
-        <f>Foderstater!U$66</f>
-        <v>maize silage</v>
+        <f>Foderstater!U$68</f>
+        <v>grazing</v>
       </c>
       <c r="H151" t="s">
         <v>326</v>
       </c>
       <c r="I151" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E151,Foderstater!$U$63:$U$100,0),MATCH(A151&amp;C151&amp;D151,Foderstater!$X$62:$AI$62,0))</f>
-        <v>0</v>
+        <v>10.166080013639251</v>
       </c>
       <c r="J151" s="159"/>
       <c r="K151" s="159"/>
     </row>
-    <row r="152" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>2</v>
       </c>
@@ -20521,20 +20563,20 @@
         <v>18</v>
       </c>
       <c r="E152" t="str">
-        <f>Foderstater!U$67</f>
-        <v>straw</v>
+        <f>Foderstater!U$69</f>
+        <v>wheat</v>
       </c>
       <c r="H152" t="s">
         <v>326</v>
       </c>
       <c r="I152" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E152,Foderstater!$U$63:$U$100,0),MATCH(A152&amp;C152&amp;D152,Foderstater!$X$62:$AI$62,0))</f>
-        <v>3.1679738484393072</v>
+        <v>6.1497391870569844</v>
       </c>
       <c r="J152" s="159"/>
       <c r="K152" s="159"/>
     </row>
-    <row r="153" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>2</v>
       </c>
@@ -20542,20 +20584,20 @@
         <v>18</v>
       </c>
       <c r="E153" t="str">
-        <f>Foderstater!U$68</f>
-        <v>grazing</v>
+        <f>Foderstater!U$70</f>
+        <v>barley</v>
       </c>
       <c r="H153" t="s">
         <v>326</v>
       </c>
       <c r="I153" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E153,Foderstater!$U$63:$U$100,0),MATCH(A153&amp;C153&amp;D153,Foderstater!$X$62:$AI$62,0))</f>
-        <v>10.166080013639251</v>
+        <v>11.290606059990822</v>
       </c>
       <c r="J153" s="159"/>
       <c r="K153" s="159"/>
     </row>
-    <row r="154" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>2</v>
       </c>
@@ -20563,20 +20605,20 @@
         <v>18</v>
       </c>
       <c r="E154" t="str">
-        <f>Foderstater!U$69</f>
-        <v>wheat</v>
+        <f>Foderstater!U$71</f>
+        <v>oats</v>
       </c>
       <c r="H154" t="s">
         <v>326</v>
       </c>
       <c r="I154" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E154,Foderstater!$U$63:$U$100,0),MATCH(A154&amp;C154&amp;D154,Foderstater!$X$62:$AI$62,0))</f>
-        <v>6.1497391870569844</v>
+        <v>2.5305995086863016</v>
       </c>
       <c r="J154" s="159"/>
       <c r="K154" s="159"/>
     </row>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>2</v>
       </c>
@@ -20584,20 +20626,20 @@
         <v>18</v>
       </c>
       <c r="E155" t="str">
-        <f>Foderstater!U$70</f>
-        <v>barley</v>
+        <f>Foderstater!U$72</f>
+        <v>triticale</v>
       </c>
       <c r="H155" t="s">
         <v>326</v>
       </c>
       <c r="I155" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E155,Foderstater!$U$63:$U$100,0),MATCH(A155&amp;C155&amp;D155,Foderstater!$X$62:$AI$62,0))</f>
-        <v>11.290606059990822</v>
+        <v>3.9696382637077976</v>
       </c>
       <c r="J155" s="159"/>
       <c r="K155" s="159"/>
     </row>
-    <row r="156" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>2</v>
       </c>
@@ -20605,20 +20647,20 @@
         <v>18</v>
       </c>
       <c r="E156" t="str">
-        <f>Foderstater!U$71</f>
-        <v>oats</v>
+        <f>Foderstater!U$73</f>
+        <v>rye</v>
       </c>
       <c r="H156" t="s">
         <v>326</v>
       </c>
       <c r="I156" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E156,Foderstater!$U$63:$U$100,0),MATCH(A156&amp;C156&amp;D156,Foderstater!$X$62:$AI$62,0))</f>
-        <v>2.5305995086863016</v>
+        <v>1.1272622080408017E-2</v>
       </c>
       <c r="J156" s="159"/>
       <c r="K156" s="159"/>
     </row>
-    <row r="157" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>2</v>
       </c>
@@ -20626,20 +20668,20 @@
         <v>18</v>
       </c>
       <c r="E157" t="str">
-        <f>Foderstater!U$72</f>
-        <v>triticale</v>
+        <f>Foderstater!U$74</f>
+        <v>maize</v>
       </c>
       <c r="H157" t="s">
         <v>326</v>
       </c>
       <c r="I157" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E157,Foderstater!$U$63:$U$100,0),MATCH(A157&amp;C157&amp;D157,Foderstater!$X$62:$AI$62,0))</f>
-        <v>3.9696382637077976</v>
+        <v>0.39798335104430993</v>
       </c>
       <c r="J157" s="159"/>
       <c r="K157" s="159"/>
     </row>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>2</v>
       </c>
@@ -20647,20 +20689,20 @@
         <v>18</v>
       </c>
       <c r="E158" t="str">
-        <f>Foderstater!U$73</f>
-        <v>rye</v>
+        <f>Foderstater!U$75</f>
+        <v>peas</v>
       </c>
       <c r="H158" t="s">
         <v>326</v>
       </c>
       <c r="I158" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E158,Foderstater!$U$63:$U$100,0),MATCH(A158&amp;C158&amp;D158,Foderstater!$X$62:$AI$62,0))</f>
-        <v>1.1272622080408017E-2</v>
+        <v>6.2198540886316538E-2</v>
       </c>
       <c r="J158" s="159"/>
       <c r="K158" s="159"/>
     </row>
-    <row r="159" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>2</v>
       </c>
@@ -20668,20 +20710,20 @@
         <v>18</v>
       </c>
       <c r="E159" t="str">
-        <f>Foderstater!U$74</f>
-        <v>maize</v>
+        <f>Foderstater!U$76</f>
+        <v>broad beans</v>
       </c>
       <c r="H159" t="s">
         <v>326</v>
       </c>
       <c r="I159" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E159,Foderstater!$U$63:$U$100,0),MATCH(A159&amp;C159&amp;D159,Foderstater!$X$62:$AI$62,0))</f>
-        <v>0.39798335104430993</v>
+        <v>0.21373263842786655</v>
       </c>
       <c r="J159" s="159"/>
       <c r="K159" s="159"/>
     </row>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>2</v>
       </c>
@@ -20689,15 +20731,15 @@
         <v>18</v>
       </c>
       <c r="E160" t="str">
-        <f>Foderstater!U$75</f>
-        <v>peas</v>
+        <f>Foderstater!U$77</f>
+        <v>rapeseed</v>
       </c>
       <c r="H160" t="s">
         <v>326</v>
       </c>
       <c r="I160" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E160,Foderstater!$U$63:$U$100,0),MATCH(A160&amp;C160&amp;D160,Foderstater!$X$62:$AI$62,0))</f>
-        <v>6.2198540886316538E-2</v>
+        <v>3.3834826631664936</v>
       </c>
       <c r="J160" s="159"/>
       <c r="K160" s="159"/>
@@ -20710,15 +20752,15 @@
         <v>18</v>
       </c>
       <c r="E161" t="str">
-        <f>Foderstater!U$76</f>
-        <v>broad beans</v>
+        <f>Foderstater!U$78</f>
+        <v>linseed</v>
       </c>
       <c r="H161" t="s">
         <v>326</v>
       </c>
       <c r="I161" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E161,Foderstater!$U$63:$U$100,0),MATCH(A161&amp;C161&amp;D161,Foderstater!$X$62:$AI$62,0))</f>
-        <v>0.21373263842786655</v>
+        <v>2.4958557242137649E-3</v>
       </c>
       <c r="J161" s="159"/>
       <c r="K161" s="159"/>
@@ -20731,15 +20773,15 @@
         <v>18</v>
       </c>
       <c r="E162" t="str">
-        <f>Foderstater!U$77</f>
-        <v>rapeseed</v>
+        <f>Foderstater!U$79</f>
+        <v>vegetable oils</v>
       </c>
       <c r="H162" t="s">
         <v>326</v>
       </c>
       <c r="I162" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E162,Foderstater!$U$63:$U$100,0),MATCH(A162&amp;C162&amp;D162,Foderstater!$X$62:$AI$62,0))</f>
-        <v>3.3834826631664936</v>
+        <v>6.4435354702415792E-2</v>
       </c>
       <c r="J162" s="159"/>
       <c r="K162" s="159"/>
@@ -20752,15 +20794,15 @@
         <v>18</v>
       </c>
       <c r="E163" t="str">
-        <f>Foderstater!U$78</f>
-        <v>linseed</v>
+        <f>Foderstater!U$80</f>
+        <v>soybeans</v>
       </c>
       <c r="H163" t="s">
         <v>326</v>
       </c>
       <c r="I163" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E163,Foderstater!$U$63:$U$100,0),MATCH(A163&amp;C163&amp;D163,Foderstater!$X$62:$AI$62,0))</f>
-        <v>2.4958557242137649E-3</v>
+        <v>6.2968191575980506E-2</v>
       </c>
       <c r="J163" s="159"/>
       <c r="K163" s="159"/>
@@ -20773,15 +20815,15 @@
         <v>18</v>
       </c>
       <c r="E164" t="str">
-        <f>Foderstater!U$79</f>
-        <v>vegetable oils</v>
+        <f>Foderstater!U$81</f>
+        <v>soybean meal</v>
       </c>
       <c r="H164" t="s">
         <v>326</v>
       </c>
       <c r="I164" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E164,Foderstater!$U$63:$U$100,0),MATCH(A164&amp;C164&amp;D164,Foderstater!$X$62:$AI$62,0))</f>
-        <v>6.4435354702415792E-2</v>
+        <v>0.57519106653391427</v>
       </c>
       <c r="J164" s="159"/>
       <c r="K164" s="159"/>
@@ -20794,15 +20836,15 @@
         <v>18</v>
       </c>
       <c r="E165" t="str">
-        <f>Foderstater!U$80</f>
-        <v>soybeans</v>
+        <f>Foderstater!U$82</f>
+        <v>soybean protein concentrate</v>
       </c>
       <c r="H165" t="s">
         <v>326</v>
       </c>
       <c r="I165" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E165,Foderstater!$U$63:$U$100,0),MATCH(A165&amp;C165&amp;D165,Foderstater!$X$62:$AI$62,0))</f>
-        <v>6.2968191575980506E-2</v>
+        <v>0</v>
       </c>
       <c r="J165" s="159"/>
       <c r="K165" s="159"/>
@@ -20815,15 +20857,15 @@
         <v>18</v>
       </c>
       <c r="E166" t="str">
-        <f>Foderstater!U$81</f>
-        <v>soybean meal</v>
+        <f>Foderstater!U$83</f>
+        <v>rapeseed meal</v>
       </c>
       <c r="H166" t="s">
         <v>326</v>
       </c>
       <c r="I166" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E166,Foderstater!$U$63:$U$100,0),MATCH(A166&amp;C166&amp;D166,Foderstater!$X$62:$AI$62,0))</f>
-        <v>0.57519106653391427</v>
+        <v>4.4425645420347344</v>
       </c>
       <c r="J166" s="159"/>
       <c r="K166" s="159"/>
@@ -20836,18 +20878,16 @@
         <v>18</v>
       </c>
       <c r="E167" t="str">
-        <f>Foderstater!U$82</f>
-        <v>soybean protein concentrate</v>
+        <f>Foderstater!U$84</f>
+        <v>sunflower seed meal</v>
       </c>
       <c r="H167" t="s">
         <v>326</v>
       </c>
       <c r="I167" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E167,Foderstater!$U$63:$U$100,0),MATCH(A167&amp;C167&amp;D167,Foderstater!$X$62:$AI$62,0))</f>
-        <v>0</v>
-      </c>
-      <c r="J167" s="159"/>
-      <c r="K167" s="159"/>
+        <v>6.136972904857535E-2</v>
+      </c>
     </row>
     <row r="168" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
@@ -20857,18 +20897,16 @@
         <v>18</v>
       </c>
       <c r="E168" t="str">
-        <f>Foderstater!U$83</f>
-        <v>rapeseed meal</v>
+        <f>Foderstater!U$85</f>
+        <v>palm kernel expeller</v>
       </c>
       <c r="H168" t="s">
         <v>326</v>
       </c>
       <c r="I168" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E168,Foderstater!$U$63:$U$100,0),MATCH(A168&amp;C168&amp;D168,Foderstater!$X$62:$AI$62,0))</f>
-        <v>4.4425645420347344</v>
-      </c>
-      <c r="J168" s="159"/>
-      <c r="K168" s="159"/>
+        <v>0.39877553799094467</v>
+      </c>
     </row>
     <row r="169" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
@@ -20878,15 +20916,15 @@
         <v>18</v>
       </c>
       <c r="E169" t="str">
-        <f>Foderstater!U$84</f>
-        <v>sunflower seed meal</v>
+        <f>Foderstater!U$86</f>
+        <v>luzern meal</v>
       </c>
       <c r="H169" t="s">
         <v>326</v>
       </c>
       <c r="I169" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E169,Foderstater!$U$63:$U$100,0),MATCH(A169&amp;C169&amp;D169,Foderstater!$X$62:$AI$62,0))</f>
-        <v>6.136972904857535E-2</v>
+        <v>0.12130313990935594</v>
       </c>
     </row>
     <row r="170" spans="1:11" x14ac:dyDescent="0.25">
@@ -20897,15 +20935,15 @@
         <v>18</v>
       </c>
       <c r="E170" t="str">
-        <f>Foderstater!U$85</f>
-        <v>palm kernel expeller</v>
+        <f>Foderstater!U$87</f>
+        <v>wheat bran</v>
       </c>
       <c r="H170" t="s">
         <v>326</v>
       </c>
       <c r="I170" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E170,Foderstater!$U$63:$U$100,0),MATCH(A170&amp;C170&amp;D170,Foderstater!$X$62:$AI$62,0))</f>
-        <v>0.39877553799094467</v>
+        <v>1.321614002942858</v>
       </c>
     </row>
     <row r="171" spans="1:11" x14ac:dyDescent="0.25">
@@ -20916,15 +20954,15 @@
         <v>18</v>
       </c>
       <c r="E171" t="str">
-        <f>Foderstater!U$86</f>
-        <v>luzern meal</v>
+        <f>Foderstater!U$88</f>
+        <v>wheat bran, fine</v>
       </c>
       <c r="H171" t="s">
         <v>326</v>
       </c>
       <c r="I171" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E171,Foderstater!$U$63:$U$100,0),MATCH(A171&amp;C171&amp;D171,Foderstater!$X$62:$AI$62,0))</f>
-        <v>0.12130313990935594</v>
+        <v>3.4645257386917328E-3</v>
       </c>
     </row>
     <row r="172" spans="1:11" x14ac:dyDescent="0.25">
@@ -20935,15 +20973,15 @@
         <v>18</v>
       </c>
       <c r="E172" t="str">
-        <f>Foderstater!U$87</f>
-        <v>wheat bran</v>
+        <f>Foderstater!U$89</f>
+        <v>oat hulls</v>
       </c>
       <c r="H172" t="s">
         <v>326</v>
       </c>
       <c r="I172" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E172,Foderstater!$U$63:$U$100,0),MATCH(A172&amp;C172&amp;D172,Foderstater!$X$62:$AI$62,0))</f>
-        <v>1.321614002942858</v>
+        <v>0.15917555594859789</v>
       </c>
     </row>
     <row r="173" spans="1:11" x14ac:dyDescent="0.25">
@@ -20954,15 +20992,15 @@
         <v>18</v>
       </c>
       <c r="E173" t="str">
-        <f>Foderstater!U$88</f>
-        <v>wheat bran, fine</v>
+        <f>Foderstater!U$90</f>
+        <v>oat bran</v>
       </c>
       <c r="H173" t="s">
         <v>326</v>
       </c>
       <c r="I173" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E173,Foderstater!$U$63:$U$100,0),MATCH(A173&amp;C173&amp;D173,Foderstater!$X$62:$AI$62,0))</f>
-        <v>3.4645257386917328E-3</v>
+        <v>1.7964759181842063E-2</v>
       </c>
     </row>
     <row r="174" spans="1:11" x14ac:dyDescent="0.25">
@@ -20973,15 +21011,15 @@
         <v>18</v>
       </c>
       <c r="E174" t="str">
-        <f>Foderstater!U$89</f>
-        <v>oat hulls</v>
+        <f>Foderstater!U$91</f>
+        <v>rye bran</v>
       </c>
       <c r="H174" t="s">
         <v>326</v>
       </c>
       <c r="I174" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E174,Foderstater!$U$63:$U$100,0),MATCH(A174&amp;C174&amp;D174,Foderstater!$X$62:$AI$62,0))</f>
-        <v>0.15917555594859789</v>
+        <v>5.5403512056737859E-2</v>
       </c>
     </row>
     <row r="175" spans="1:11" x14ac:dyDescent="0.25">
@@ -20992,15 +21030,15 @@
         <v>18</v>
       </c>
       <c r="E175" t="str">
-        <f>Foderstater!U$90</f>
-        <v>oat bran</v>
+        <f>Foderstater!U$92</f>
+        <v>wheat distillers grain, dry</v>
       </c>
       <c r="H175" t="s">
         <v>326</v>
       </c>
       <c r="I175" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E175,Foderstater!$U$63:$U$100,0),MATCH(A175&amp;C175&amp;D175,Foderstater!$X$62:$AI$62,0))</f>
-        <v>1.7964759181842063E-2</v>
+        <v>1.4206094996744831</v>
       </c>
     </row>
     <row r="176" spans="1:11" x14ac:dyDescent="0.25">
@@ -21011,15 +21049,15 @@
         <v>18</v>
       </c>
       <c r="E176" t="str">
-        <f>Foderstater!U$91</f>
-        <v>rye bran</v>
+        <f>Foderstater!U$93</f>
+        <v>barley brewers grain</v>
       </c>
       <c r="H176" t="s">
         <v>326</v>
       </c>
       <c r="I176" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E176,Foderstater!$U$63:$U$100,0),MATCH(A176&amp;C176&amp;D176,Foderstater!$X$62:$AI$62,0))</f>
-        <v>5.5403512056737859E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="177" spans="1:11" x14ac:dyDescent="0.25">
@@ -21030,15 +21068,15 @@
         <v>18</v>
       </c>
       <c r="E177" t="str">
-        <f>Foderstater!U$92</f>
-        <v>wheat distillers grain, dry</v>
+        <f>Foderstater!U$94</f>
+        <v>maize gluten meal</v>
       </c>
       <c r="H177" t="s">
         <v>326</v>
       </c>
       <c r="I177" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E177,Foderstater!$U$63:$U$100,0),MATCH(A177&amp;C177&amp;D177,Foderstater!$X$62:$AI$62,0))</f>
-        <v>1.4206094996744831</v>
+        <v>4.2926359235494246E-2</v>
       </c>
     </row>
     <row r="178" spans="1:11" x14ac:dyDescent="0.25">
@@ -21049,15 +21087,15 @@
         <v>18</v>
       </c>
       <c r="E178" t="str">
-        <f>Foderstater!U$93</f>
-        <v>barley brewers grain</v>
+        <f>Foderstater!U$95</f>
+        <v>sugar beet molasses</v>
       </c>
       <c r="H178" t="s">
         <v>326</v>
       </c>
       <c r="I178" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E178,Foderstater!$U$63:$U$100,0),MATCH(A178&amp;C178&amp;D178,Foderstater!$X$62:$AI$62,0))</f>
-        <v>0</v>
+        <v>0.47602729121024218</v>
       </c>
     </row>
     <row r="179" spans="1:11" x14ac:dyDescent="0.25">
@@ -21068,15 +21106,15 @@
         <v>18</v>
       </c>
       <c r="E179" t="str">
-        <f>Foderstater!U$94</f>
-        <v>maize gluten meal</v>
+        <f>Foderstater!U$96</f>
+        <v>sugar beet pulp</v>
       </c>
       <c r="H179" t="s">
         <v>326</v>
       </c>
       <c r="I179" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E179,Foderstater!$U$63:$U$100,0),MATCH(A179&amp;C179&amp;D179,Foderstater!$X$62:$AI$62,0))</f>
-        <v>4.2926359235494246E-2</v>
+        <v>0.91853231005300495</v>
       </c>
     </row>
     <row r="180" spans="1:11" x14ac:dyDescent="0.25">
@@ -21087,15 +21125,15 @@
         <v>18</v>
       </c>
       <c r="E180" t="str">
-        <f>Foderstater!U$95</f>
-        <v>sugar beet molasses</v>
+        <f>Foderstater!U$97</f>
+        <v>whey powder</v>
       </c>
       <c r="H180" t="s">
         <v>326</v>
       </c>
       <c r="I180" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E180,Foderstater!$U$63:$U$100,0),MATCH(A180&amp;C180&amp;D180,Foderstater!$X$62:$AI$62,0))</f>
-        <v>0.47602729121024218</v>
+        <v>0</v>
       </c>
     </row>
     <row r="181" spans="1:11" x14ac:dyDescent="0.25">
@@ -21106,15 +21144,15 @@
         <v>18</v>
       </c>
       <c r="E181" t="str">
-        <f>Foderstater!U$96</f>
-        <v>sugar beet pulp</v>
+        <f>Foderstater!U$98</f>
+        <v>potatoe protein</v>
       </c>
       <c r="H181" t="s">
         <v>326</v>
       </c>
       <c r="I181" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E181,Foderstater!$U$63:$U$100,0),MATCH(A181&amp;C181&amp;D181,Foderstater!$X$62:$AI$62,0))</f>
-        <v>0.91853231005300495</v>
+        <v>4.2052766660258274E-3</v>
       </c>
     </row>
     <row r="182" spans="1:11" x14ac:dyDescent="0.25">
@@ -21125,8 +21163,8 @@
         <v>18</v>
       </c>
       <c r="E182" t="str">
-        <f>Foderstater!U$97</f>
-        <v>whey powder</v>
+        <f>Foderstater!U$99</f>
+        <v>fish meal</v>
       </c>
       <c r="H182" t="s">
         <v>326</v>
@@ -21144,78 +21182,94 @@
         <v>18</v>
       </c>
       <c r="E183" t="str">
-        <f>Foderstater!U$98</f>
-        <v>potatoe protein</v>
+        <f>Foderstater!U$100</f>
+        <v>minerals</v>
       </c>
       <c r="H183" t="s">
         <v>326</v>
       </c>
       <c r="I183" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E183,Foderstater!$U$63:$U$100,0),MATCH(A183&amp;C183&amp;D183,Foderstater!$X$62:$AI$62,0))</f>
-        <v>4.2052766660258274E-3</v>
-      </c>
-    </row>
-    <row r="184" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A184" t="s">
+        <v>0.66022570674046432</v>
+      </c>
+    </row>
+    <row r="185" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A185" s="159" t="s">
         <v>2</v>
       </c>
-      <c r="D184" t="s">
+      <c r="B185" s="159" t="s">
+        <v>1</v>
+      </c>
+      <c r="C185" s="159" t="s">
+        <v>430</v>
+      </c>
+      <c r="D185" s="159" t="s">
         <v>18</v>
       </c>
-      <c r="E184" t="str">
-        <f>Foderstater!U$99</f>
-        <v>fish meal</v>
-      </c>
-      <c r="H184" t="s">
+      <c r="H185" s="159" t="s">
         <v>326</v>
       </c>
-      <c r="I184" s="13">
-        <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E184,Foderstater!$U$63:$U$100,0),MATCH(A184&amp;C184&amp;D184,Foderstater!$X$62:$AI$62,0))</f>
+      <c r="I185" s="159">
         <v>0</v>
       </c>
-    </row>
-    <row r="185" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A185" t="s">
+      <c r="J185" s="159"/>
+      <c r="K185" s="159" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="186" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
         <v>2</v>
       </c>
-      <c r="D185" t="s">
+      <c r="B186" t="s">
+        <v>1</v>
+      </c>
+      <c r="C186" t="s">
+        <v>430</v>
+      </c>
+      <c r="D186" t="s">
         <v>18</v>
       </c>
-      <c r="E185" t="str">
-        <f>Foderstater!U$100</f>
-        <v>minerals</v>
-      </c>
-      <c r="H185" t="s">
+      <c r="E186" t="str">
+        <f>Foderstater!U$63</f>
+        <v>ley silage, 1st cut</v>
+      </c>
+      <c r="H186" t="s">
         <v>326</v>
       </c>
-      <c r="I185" s="13">
-        <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E185,Foderstater!$U$63:$U$100,0),MATCH(A185&amp;C185&amp;D185,Foderstater!$X$62:$AI$62,0))</f>
-        <v>0.66022570674046432</v>
-      </c>
+      <c r="I186" s="13">
+        <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E186,Foderstater!$U$63:$U$100,0),MATCH(A186&amp;C186&amp;D186,Foderstater!$X$62:$AI$62,0))</f>
+        <v>20.561419371957058</v>
+      </c>
+      <c r="J186" s="159"/>
+      <c r="K186" s="159"/>
     </row>
     <row r="187" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A187" s="159" t="s">
+      <c r="A187" t="s">
         <v>2</v>
       </c>
-      <c r="B187" s="159" t="s">
+      <c r="B187" t="s">
         <v>1</v>
       </c>
-      <c r="C187" s="159" t="s">
+      <c r="C187" t="s">
         <v>430</v>
       </c>
-      <c r="D187" s="159" t="s">
+      <c r="D187" t="s">
         <v>18</v>
       </c>
-      <c r="H187" s="159" t="s">
+      <c r="E187" t="str">
+        <f>Foderstater!U$64</f>
+        <v>ley silage, regrowth</v>
+      </c>
+      <c r="H187" t="s">
         <v>326</v>
       </c>
-      <c r="I187" s="159">
-        <v>0</v>
+      <c r="I187" s="13">
+        <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E187,Foderstater!$U$63:$U$100,0),MATCH(A187&amp;C187&amp;D187,Foderstater!$X$62:$AI$62,0))</f>
+        <v>9.5364207102254017</v>
       </c>
       <c r="J187" s="159"/>
-      <c r="K187" s="159" t="s">
-        <v>424</v>
-      </c>
+      <c r="K187" s="159"/>
     </row>
     <row r="188" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
@@ -21231,15 +21285,15 @@
         <v>18</v>
       </c>
       <c r="E188" t="str">
-        <f>Foderstater!U$63</f>
-        <v>ley silage, 1st cut</v>
+        <f>Foderstater!U$65</f>
+        <v>other silage</v>
       </c>
       <c r="H188" t="s">
         <v>326</v>
       </c>
       <c r="I188" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E188,Foderstater!$U$63:$U$100,0),MATCH(A188&amp;C188&amp;D188,Foderstater!$X$62:$AI$62,0))</f>
-        <v>20.561419371957058</v>
+        <v>0</v>
       </c>
       <c r="J188" s="159"/>
       <c r="K188" s="159"/>
@@ -21258,15 +21312,15 @@
         <v>18</v>
       </c>
       <c r="E189" t="str">
-        <f>Foderstater!U$64</f>
-        <v>ley silage, regrowth</v>
+        <f>Foderstater!U$66</f>
+        <v>maize silage</v>
       </c>
       <c r="H189" t="s">
         <v>326</v>
       </c>
       <c r="I189" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E189,Foderstater!$U$63:$U$100,0),MATCH(A189&amp;C189&amp;D189,Foderstater!$X$62:$AI$62,0))</f>
-        <v>9.5364207102254017</v>
+        <v>15.876048855936714</v>
       </c>
       <c r="J189" s="159"/>
       <c r="K189" s="159"/>
@@ -21285,15 +21339,15 @@
         <v>18</v>
       </c>
       <c r="E190" t="str">
-        <f>Foderstater!U$65</f>
-        <v>other silage</v>
+        <f>Foderstater!U$67</f>
+        <v>straw</v>
       </c>
       <c r="H190" t="s">
         <v>326</v>
       </c>
       <c r="I190" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E190,Foderstater!$U$63:$U$100,0),MATCH(A190&amp;C190&amp;D190,Foderstater!$X$62:$AI$62,0))</f>
-        <v>0</v>
+        <v>3.0977656304266756</v>
       </c>
       <c r="J190" s="159"/>
       <c r="K190" s="159"/>
@@ -21312,15 +21366,15 @@
         <v>18</v>
       </c>
       <c r="E191" t="str">
-        <f>Foderstater!U$66</f>
-        <v>maize silage</v>
+        <f>Foderstater!U$68</f>
+        <v>grazing</v>
       </c>
       <c r="H191" t="s">
         <v>326</v>
       </c>
       <c r="I191" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E191,Foderstater!$U$63:$U$100,0),MATCH(A191&amp;C191&amp;D191,Foderstater!$X$62:$AI$62,0))</f>
-        <v>15.876048855936714</v>
+        <v>9.9407806910823222</v>
       </c>
       <c r="J191" s="159"/>
       <c r="K191" s="159"/>
@@ -21339,15 +21393,15 @@
         <v>18</v>
       </c>
       <c r="E192" t="str">
-        <f>Foderstater!U$67</f>
-        <v>straw</v>
+        <f>Foderstater!U$69</f>
+        <v>wheat</v>
       </c>
       <c r="H192" t="s">
         <v>326</v>
       </c>
       <c r="I192" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E192,Foderstater!$U$63:$U$100,0),MATCH(A192&amp;C192&amp;D192,Foderstater!$X$62:$AI$62,0))</f>
-        <v>3.0977656304266756</v>
+        <v>5.0974881237730667</v>
       </c>
       <c r="J192" s="159"/>
       <c r="K192" s="159"/>
@@ -21366,15 +21420,15 @@
         <v>18</v>
       </c>
       <c r="E193" t="str">
-        <f>Foderstater!U$68</f>
-        <v>grazing</v>
+        <f>Foderstater!U$70</f>
+        <v>barley</v>
       </c>
       <c r="H193" t="s">
         <v>326</v>
       </c>
       <c r="I193" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E193,Foderstater!$U$63:$U$100,0),MATCH(A193&amp;C193&amp;D193,Foderstater!$X$62:$AI$62,0))</f>
-        <v>9.9407806910823222</v>
+        <v>8.404170018075888</v>
       </c>
       <c r="J193" s="159"/>
       <c r="K193" s="159"/>
@@ -21393,15 +21447,15 @@
         <v>18</v>
       </c>
       <c r="E194" t="str">
-        <f>Foderstater!U$69</f>
-        <v>wheat</v>
+        <f>Foderstater!U$71</f>
+        <v>oats</v>
       </c>
       <c r="H194" t="s">
         <v>326</v>
       </c>
       <c r="I194" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E194,Foderstater!$U$63:$U$100,0),MATCH(A194&amp;C194&amp;D194,Foderstater!$X$62:$AI$62,0))</f>
-        <v>5.0974881237730667</v>
+        <v>2.0416884227683041</v>
       </c>
       <c r="J194" s="159"/>
       <c r="K194" s="159"/>
@@ -21420,15 +21474,15 @@
         <v>18</v>
       </c>
       <c r="E195" t="str">
-        <f>Foderstater!U$70</f>
-        <v>barley</v>
+        <f>Foderstater!U$72</f>
+        <v>triticale</v>
       </c>
       <c r="H195" t="s">
         <v>326</v>
       </c>
       <c r="I195" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E195,Foderstater!$U$63:$U$100,0),MATCH(A195&amp;C195&amp;D195,Foderstater!$X$62:$AI$62,0))</f>
-        <v>8.404170018075888</v>
+        <v>2.6355687688154275</v>
       </c>
       <c r="J195" s="159"/>
       <c r="K195" s="159"/>
@@ -21447,15 +21501,15 @@
         <v>18</v>
       </c>
       <c r="E196" t="str">
-        <f>Foderstater!U$71</f>
-        <v>oats</v>
+        <f>Foderstater!U$73</f>
+        <v>rye</v>
       </c>
       <c r="H196" t="s">
         <v>326</v>
       </c>
       <c r="I196" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E196,Foderstater!$U$63:$U$100,0),MATCH(A196&amp;C196&amp;D196,Foderstater!$X$62:$AI$62,0))</f>
-        <v>2.0416884227683041</v>
+        <v>1.7420276725880934E-2</v>
       </c>
       <c r="J196" s="159"/>
       <c r="K196" s="159"/>
@@ -21474,15 +21528,15 @@
         <v>18</v>
       </c>
       <c r="E197" t="str">
-        <f>Foderstater!U$72</f>
-        <v>triticale</v>
+        <f>Foderstater!U$74</f>
+        <v>maize</v>
       </c>
       <c r="H197" t="s">
         <v>326</v>
       </c>
       <c r="I197" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E197,Foderstater!$U$63:$U$100,0),MATCH(A197&amp;C197&amp;D197,Foderstater!$X$62:$AI$62,0))</f>
-        <v>2.6355687688154275</v>
+        <v>0.6150281680723525</v>
       </c>
       <c r="J197" s="159"/>
       <c r="K197" s="159"/>
@@ -21501,15 +21555,15 @@
         <v>18</v>
       </c>
       <c r="E198" t="str">
-        <f>Foderstater!U$73</f>
-        <v>rye</v>
+        <f>Foderstater!U$75</f>
+        <v>peas</v>
       </c>
       <c r="H198" t="s">
         <v>326</v>
       </c>
       <c r="I198" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E198,Foderstater!$U$63:$U$100,0),MATCH(A198&amp;C198&amp;D198,Foderstater!$X$62:$AI$62,0))</f>
-        <v>1.7420276725880934E-2</v>
+        <v>9.6119233524986178E-2</v>
       </c>
       <c r="J198" s="159"/>
       <c r="K198" s="159"/>
@@ -21528,15 +21582,15 @@
         <v>18</v>
       </c>
       <c r="E199" t="str">
-        <f>Foderstater!U$74</f>
-        <v>maize</v>
+        <f>Foderstater!U$76</f>
+        <v>broad beans</v>
       </c>
       <c r="H199" t="s">
         <v>326</v>
       </c>
       <c r="I199" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E199,Foderstater!$U$63:$U$100,0),MATCH(A199&amp;C199&amp;D199,Foderstater!$X$62:$AI$62,0))</f>
-        <v>0.6150281680723525</v>
+        <v>0.33029420131428044</v>
       </c>
       <c r="J199" s="159"/>
       <c r="K199" s="159"/>
@@ -21555,15 +21609,15 @@
         <v>18</v>
       </c>
       <c r="E200" t="str">
-        <f>Foderstater!U$75</f>
-        <v>peas</v>
+        <f>Foderstater!U$77</f>
+        <v>rapeseed</v>
       </c>
       <c r="H200" t="s">
         <v>326</v>
       </c>
       <c r="I200" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E200,Foderstater!$U$63:$U$100,0),MATCH(A200&amp;C200&amp;D200,Foderstater!$X$62:$AI$62,0))</f>
-        <v>9.6119233524986178E-2</v>
+        <v>5.2287040112895822</v>
       </c>
       <c r="J200" s="159"/>
       <c r="K200" s="159"/>
@@ -21582,15 +21636,15 @@
         <v>18</v>
       </c>
       <c r="E201" t="str">
-        <f>Foderstater!U$76</f>
-        <v>broad beans</v>
+        <f>Foderstater!U$78</f>
+        <v>linseed</v>
       </c>
       <c r="H201" t="s">
         <v>326</v>
       </c>
       <c r="I201" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E201,Foderstater!$U$63:$U$100,0),MATCH(A201&amp;C201&amp;D201,Foderstater!$X$62:$AI$62,0))</f>
-        <v>0.33029420131428044</v>
+        <v>3.8569994694707295E-3</v>
       </c>
       <c r="J201" s="159"/>
       <c r="K201" s="159"/>
@@ -21609,15 +21663,15 @@
         <v>18</v>
       </c>
       <c r="E202" t="str">
-        <f>Foderstater!U$77</f>
-        <v>rapeseed</v>
+        <f>Foderstater!U$79</f>
+        <v>vegetable oils</v>
       </c>
       <c r="H202" t="s">
         <v>326</v>
       </c>
       <c r="I202" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E202,Foderstater!$U$63:$U$100,0),MATCH(A202&amp;C202&amp;D202,Foderstater!$X$62:$AI$62,0))</f>
-        <v>5.2287040112895822</v>
+        <v>9.957591958992984E-2</v>
       </c>
       <c r="J202" s="159"/>
       <c r="K202" s="159"/>
@@ -21636,15 +21690,15 @@
         <v>18</v>
       </c>
       <c r="E203" t="str">
-        <f>Foderstater!U$78</f>
-        <v>linseed</v>
+        <f>Foderstater!U$80</f>
+        <v>soybeans</v>
       </c>
       <c r="H203" t="s">
         <v>326</v>
       </c>
       <c r="I203" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E203,Foderstater!$U$63:$U$100,0),MATCH(A203&amp;C203&amp;D203,Foderstater!$X$62:$AI$62,0))</f>
-        <v>3.8569994694707295E-3</v>
+        <v>9.7308622107391843E-2</v>
       </c>
       <c r="J203" s="159"/>
       <c r="K203" s="159"/>
@@ -21663,15 +21717,15 @@
         <v>18</v>
       </c>
       <c r="E204" t="str">
-        <f>Foderstater!U$79</f>
-        <v>vegetable oils</v>
+        <f>Foderstater!U$81</f>
+        <v>soybean meal</v>
       </c>
       <c r="H204" t="s">
         <v>326</v>
       </c>
       <c r="I204" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E204,Foderstater!$U$63:$U$100,0),MATCH(A204&amp;C204&amp;D204,Foderstater!$X$62:$AI$62,0))</f>
-        <v>9.957591958992984E-2</v>
+        <v>0.88887815787688529</v>
       </c>
       <c r="J204" s="159"/>
       <c r="K204" s="159"/>
@@ -21690,15 +21744,15 @@
         <v>18</v>
       </c>
       <c r="E205" t="str">
-        <f>Foderstater!U$80</f>
-        <v>soybeans</v>
+        <f>Foderstater!U$82</f>
+        <v>soybean protein concentrate</v>
       </c>
       <c r="H205" t="s">
         <v>326</v>
       </c>
       <c r="I205" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E205,Foderstater!$U$63:$U$100,0),MATCH(A205&amp;C205&amp;D205,Foderstater!$X$62:$AI$62,0))</f>
-        <v>9.7308622107391843E-2</v>
+        <v>0</v>
       </c>
       <c r="J205" s="159"/>
       <c r="K205" s="159"/>
@@ -21717,15 +21771,15 @@
         <v>18</v>
       </c>
       <c r="E206" t="str">
-        <f>Foderstater!U$81</f>
-        <v>soybean meal</v>
+        <f>Foderstater!U$83</f>
+        <v>rapeseed meal</v>
       </c>
       <c r="H206" t="s">
         <v>326</v>
       </c>
       <c r="I206" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E206,Foderstater!$U$63:$U$100,0),MATCH(A206&amp;C206&amp;D206,Foderstater!$X$62:$AI$62,0))</f>
-        <v>0.88887815787688529</v>
+        <v>6.8653684247374684</v>
       </c>
       <c r="J206" s="159"/>
       <c r="K206" s="159"/>
@@ -21744,18 +21798,16 @@
         <v>18</v>
       </c>
       <c r="E207" t="str">
-        <f>Foderstater!U$82</f>
-        <v>soybean protein concentrate</v>
+        <f>Foderstater!U$84</f>
+        <v>sunflower seed meal</v>
       </c>
       <c r="H207" t="s">
         <v>326</v>
       </c>
       <c r="I207" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E207,Foderstater!$U$63:$U$100,0),MATCH(A207&amp;C207&amp;D207,Foderstater!$X$62:$AI$62,0))</f>
-        <v>0</v>
-      </c>
-      <c r="J207" s="159"/>
-      <c r="K207" s="159"/>
+        <v>9.4838419579113625E-2</v>
+      </c>
     </row>
     <row r="208" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
@@ -21771,18 +21823,16 @@
         <v>18</v>
       </c>
       <c r="E208" t="str">
-        <f>Foderstater!U$83</f>
-        <v>rapeseed meal</v>
+        <f>Foderstater!U$85</f>
+        <v>palm kernel expeller</v>
       </c>
       <c r="H208" t="s">
         <v>326</v>
       </c>
       <c r="I208" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E208,Foderstater!$U$63:$U$100,0),MATCH(A208&amp;C208&amp;D208,Foderstater!$X$62:$AI$62,0))</f>
-        <v>6.8653684247374684</v>
-      </c>
-      <c r="J208" s="159"/>
-      <c r="K208" s="159"/>
+        <v>0.61625238331975196</v>
+      </c>
     </row>
     <row r="209" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
@@ -21798,15 +21848,15 @@
         <v>18</v>
       </c>
       <c r="E209" t="str">
-        <f>Foderstater!U$84</f>
-        <v>sunflower seed meal</v>
+        <f>Foderstater!U$86</f>
+        <v>luzern meal</v>
       </c>
       <c r="H209" t="s">
         <v>326</v>
       </c>
       <c r="I209" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E209,Foderstater!$U$63:$U$100,0),MATCH(A209&amp;C209&amp;D209,Foderstater!$X$62:$AI$62,0))</f>
-        <v>9.4838419579113625E-2</v>
+        <v>0.18745720825786316</v>
       </c>
     </row>
     <row r="210" spans="1:9" x14ac:dyDescent="0.25">
@@ -21823,15 +21873,15 @@
         <v>18</v>
       </c>
       <c r="E210" t="str">
-        <f>Foderstater!U$85</f>
-        <v>palm kernel expeller</v>
+        <f>Foderstater!U$87</f>
+        <v>wheat bran</v>
       </c>
       <c r="H210" t="s">
         <v>326</v>
       </c>
       <c r="I210" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E210,Foderstater!$U$63:$U$100,0),MATCH(A210&amp;C210&amp;D210,Foderstater!$X$62:$AI$62,0))</f>
-        <v>0.61625238331975196</v>
+        <v>2.0423714635193808</v>
       </c>
     </row>
     <row r="211" spans="1:9" x14ac:dyDescent="0.25">
@@ -21848,15 +21898,15 @@
         <v>18</v>
       </c>
       <c r="E211" t="str">
-        <f>Foderstater!U$86</f>
-        <v>luzern meal</v>
+        <f>Foderstater!U$88</f>
+        <v>wheat bran, fine</v>
       </c>
       <c r="H211" t="s">
         <v>326</v>
       </c>
       <c r="I211" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E211,Foderstater!$U$63:$U$100,0),MATCH(A211&amp;C211&amp;D211,Foderstater!$X$62:$AI$62,0))</f>
-        <v>0.18745720825786316</v>
+        <v>5.3539448640650723E-3</v>
       </c>
     </row>
     <row r="212" spans="1:9" x14ac:dyDescent="0.25">
@@ -21873,15 +21923,15 @@
         <v>18</v>
       </c>
       <c r="E212" t="str">
-        <f>Foderstater!U$87</f>
-        <v>wheat bran</v>
+        <f>Foderstater!U$89</f>
+        <v>oat hulls</v>
       </c>
       <c r="H212" t="s">
         <v>326</v>
       </c>
       <c r="I212" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E212,Foderstater!$U$63:$U$100,0),MATCH(A212&amp;C212&amp;D212,Foderstater!$X$62:$AI$62,0))</f>
-        <v>2.0423714635193808</v>
+        <v>0.24598378379417407</v>
       </c>
     </row>
     <row r="213" spans="1:9" x14ac:dyDescent="0.25">
@@ -21898,15 +21948,15 @@
         <v>18</v>
       </c>
       <c r="E213" t="str">
-        <f>Foderstater!U$88</f>
-        <v>wheat bran, fine</v>
+        <f>Foderstater!U$90</f>
+        <v>oat bran</v>
       </c>
       <c r="H213" t="s">
         <v>326</v>
       </c>
       <c r="I213" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E213,Foderstater!$U$63:$U$100,0),MATCH(A213&amp;C213&amp;D213,Foderstater!$X$62:$AI$62,0))</f>
-        <v>5.3539448640650723E-3</v>
+        <v>2.77620480868788E-2</v>
       </c>
     </row>
     <row r="214" spans="1:9" x14ac:dyDescent="0.25">
@@ -21923,15 +21973,15 @@
         <v>18</v>
       </c>
       <c r="E214" t="str">
-        <f>Foderstater!U$89</f>
-        <v>oat hulls</v>
+        <f>Foderstater!U$91</f>
+        <v>rye bran</v>
       </c>
       <c r="H214" t="s">
         <v>326</v>
       </c>
       <c r="I214" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E214,Foderstater!$U$63:$U$100,0),MATCH(A214&amp;C214&amp;D214,Foderstater!$X$62:$AI$62,0))</f>
-        <v>0.24598378379417407</v>
+        <v>8.5618457243544915E-2</v>
       </c>
     </row>
     <row r="215" spans="1:9" x14ac:dyDescent="0.25">
@@ -21948,15 +21998,15 @@
         <v>18</v>
       </c>
       <c r="E215" t="str">
-        <f>Foderstater!U$90</f>
-        <v>oat bran</v>
+        <f>Foderstater!U$92</f>
+        <v>wheat distillers grain, dry</v>
       </c>
       <c r="H215" t="s">
         <v>326</v>
       </c>
       <c r="I215" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E215,Foderstater!$U$63:$U$100,0),MATCH(A215&amp;C215&amp;D215,Foderstater!$X$62:$AI$62,0))</f>
-        <v>2.77620480868788E-2</v>
+        <v>2.1953552977488813</v>
       </c>
     </row>
     <row r="216" spans="1:9" x14ac:dyDescent="0.25">
@@ -21973,15 +22023,15 @@
         <v>18</v>
       </c>
       <c r="E216" t="str">
-        <f>Foderstater!U$91</f>
-        <v>rye bran</v>
+        <f>Foderstater!U$93</f>
+        <v>barley brewers grain</v>
       </c>
       <c r="H216" t="s">
         <v>326</v>
       </c>
       <c r="I216" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E216,Foderstater!$U$63:$U$100,0),MATCH(A216&amp;C216&amp;D216,Foderstater!$X$62:$AI$62,0))</f>
-        <v>8.5618457243544915E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="217" spans="1:9" x14ac:dyDescent="0.25">
@@ -21998,15 +22048,15 @@
         <v>18</v>
       </c>
       <c r="E217" t="str">
-        <f>Foderstater!U$92</f>
-        <v>wheat distillers grain, dry</v>
+        <f>Foderstater!U$94</f>
+        <v>maize gluten meal</v>
       </c>
       <c r="H217" t="s">
         <v>326</v>
       </c>
       <c r="I217" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E217,Foderstater!$U$63:$U$100,0),MATCH(A217&amp;C217&amp;D217,Foderstater!$X$62:$AI$62,0))</f>
-        <v>2.1953552977488813</v>
+        <v>6.6336745025503241E-2</v>
       </c>
     </row>
     <row r="218" spans="1:9" x14ac:dyDescent="0.25">
@@ -22023,15 +22073,15 @@
         <v>18</v>
       </c>
       <c r="E218" t="str">
-        <f>Foderstater!U$93</f>
-        <v>barley brewers grain</v>
+        <f>Foderstater!U$95</f>
+        <v>sugar beet molasses</v>
       </c>
       <c r="H218" t="s">
         <v>326</v>
       </c>
       <c r="I218" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E218,Foderstater!$U$63:$U$100,0),MATCH(A218&amp;C218&amp;D218,Foderstater!$X$62:$AI$62,0))</f>
-        <v>0</v>
+        <v>0.73563427238161927</v>
       </c>
     </row>
     <row r="219" spans="1:9" x14ac:dyDescent="0.25">
@@ -22048,15 +22098,15 @@
         <v>18</v>
       </c>
       <c r="E219" t="str">
-        <f>Foderstater!U$94</f>
-        <v>maize gluten meal</v>
+        <f>Foderstater!U$96</f>
+        <v>sugar beet pulp</v>
       </c>
       <c r="H219" t="s">
         <v>326</v>
       </c>
       <c r="I219" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E219,Foderstater!$U$63:$U$100,0),MATCH(A219&amp;C219&amp;D219,Foderstater!$X$62:$AI$62,0))</f>
-        <v>6.6336745025503241E-2</v>
+        <v>1.4194645139923689</v>
       </c>
     </row>
     <row r="220" spans="1:9" x14ac:dyDescent="0.25">
@@ -22073,15 +22123,15 @@
         <v>18</v>
       </c>
       <c r="E220" t="str">
-        <f>Foderstater!U$95</f>
-        <v>sugar beet molasses</v>
+        <f>Foderstater!U$97</f>
+        <v>whey powder</v>
       </c>
       <c r="H220" t="s">
         <v>326</v>
       </c>
       <c r="I220" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E220,Foderstater!$U$63:$U$100,0),MATCH(A220&amp;C220&amp;D220,Foderstater!$X$62:$AI$62,0))</f>
-        <v>0.73563427238161927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="221" spans="1:9" x14ac:dyDescent="0.25">
@@ -22098,15 +22148,15 @@
         <v>18</v>
       </c>
       <c r="E221" t="str">
-        <f>Foderstater!U$96</f>
-        <v>sugar beet pulp</v>
+        <f>Foderstater!U$98</f>
+        <v>potatoe protein</v>
       </c>
       <c r="H221" t="s">
         <v>326</v>
       </c>
       <c r="I221" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E221,Foderstater!$U$63:$U$100,0),MATCH(A221&amp;C221&amp;D221,Foderstater!$X$62:$AI$62,0))</f>
-        <v>1.4194645139923689</v>
+        <v>6.4986728649744927E-3</v>
       </c>
     </row>
     <row r="222" spans="1:9" x14ac:dyDescent="0.25">
@@ -22123,8 +22173,8 @@
         <v>18</v>
       </c>
       <c r="E222" t="str">
-        <f>Foderstater!U$97</f>
-        <v>whey powder</v>
+        <f>Foderstater!U$99</f>
+        <v>fish meal</v>
       </c>
       <c r="H222" t="s">
         <v>326</v>
@@ -22148,102 +22198,94 @@
         <v>18</v>
       </c>
       <c r="E223" t="str">
-        <f>Foderstater!U$98</f>
-        <v>potatoe protein</v>
+        <f>Foderstater!U$100</f>
+        <v>minerals</v>
       </c>
       <c r="H223" t="s">
         <v>326</v>
       </c>
       <c r="I223" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E223,Foderstater!$U$63:$U$100,0),MATCH(A223&amp;C223&amp;D223,Foderstater!$X$62:$AI$62,0))</f>
-        <v>6.4986728649744927E-3</v>
-      </c>
-    </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A224" t="s">
+        <v>0.83716818155279793</v>
+      </c>
+    </row>
+    <row r="225" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A225" s="81" t="s">
+        <v>90</v>
+      </c>
+      <c r="B225" s="48"/>
+      <c r="C225" s="48"/>
+      <c r="D225" s="49"/>
+      <c r="E225" s="49"/>
+      <c r="F225" s="49"/>
+      <c r="G225" s="49"/>
+      <c r="H225" s="49"/>
+      <c r="I225" s="162"/>
+      <c r="J225" s="49"/>
+      <c r="K225" s="49"/>
+      <c r="L225" s="49"/>
+    </row>
+    <row r="226" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A226" s="159" t="s">
         <v>2</v>
       </c>
-      <c r="B224" t="s">
-        <v>1</v>
-      </c>
-      <c r="C224" t="s">
-        <v>430</v>
-      </c>
-      <c r="D224" t="s">
-        <v>18</v>
-      </c>
-      <c r="E224" t="str">
-        <f>Foderstater!U$99</f>
-        <v>fish meal</v>
-      </c>
-      <c r="H224" t="s">
+      <c r="B226" s="159"/>
+      <c r="C226" s="159"/>
+      <c r="D226" s="159" t="s">
+        <v>20</v>
+      </c>
+      <c r="H226" s="159" t="s">
         <v>326</v>
       </c>
-      <c r="I224" s="13">
-        <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E224,Foderstater!$U$63:$U$100,0),MATCH(A224&amp;C224&amp;D224,Foderstater!$X$62:$AI$62,0))</f>
+      <c r="I226" s="159">
         <v>0</v>
       </c>
-    </row>
-    <row r="225" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A225" t="s">
+      <c r="J226" s="159"/>
+      <c r="K226" s="159" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="227" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A227" t="s">
         <v>2</v>
       </c>
-      <c r="B225" t="s">
-        <v>1</v>
-      </c>
-      <c r="C225" t="s">
-        <v>430</v>
-      </c>
-      <c r="D225" t="s">
-        <v>18</v>
-      </c>
-      <c r="E225" t="str">
-        <f>Foderstater!U$100</f>
-        <v>minerals</v>
-      </c>
-      <c r="H225" t="s">
+      <c r="D227" t="s">
+        <v>20</v>
+      </c>
+      <c r="E227" t="str">
+        <f>Foderstater!U$63</f>
+        <v>ley silage, 1st cut</v>
+      </c>
+      <c r="H227" t="s">
         <v>326</v>
       </c>
-      <c r="I225" s="13">
-        <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E225,Foderstater!$U$63:$U$100,0),MATCH(A225&amp;C225&amp;D225,Foderstater!$X$62:$AI$62,0))</f>
-        <v>0.83716818155279793</v>
-      </c>
-    </row>
-    <row r="227" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A227" s="81" t="s">
-        <v>90</v>
-      </c>
-      <c r="B227" s="48"/>
-      <c r="C227" s="48"/>
-      <c r="D227" s="49"/>
-      <c r="E227" s="49"/>
-      <c r="F227" s="49"/>
-      <c r="G227" s="49"/>
-      <c r="H227" s="49"/>
-      <c r="I227" s="162"/>
-      <c r="J227" s="49"/>
-      <c r="K227" s="49"/>
-      <c r="L227" s="49"/>
+      <c r="I227" s="13">
+        <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E227,Foderstater!$U$63:$U$100,0),MATCH(A227&amp;C227&amp;D227,Foderstater!$X$62:$AI$62,0))</f>
+        <v>69.98809662916166</v>
+      </c>
+      <c r="J227" s="159"/>
+      <c r="K227" s="159"/>
     </row>
     <row r="228" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A228" s="159" t="s">
+      <c r="A228" t="s">
         <v>2</v>
       </c>
-      <c r="B228" s="159"/>
-      <c r="C228" s="159"/>
-      <c r="D228" s="159" t="s">
+      <c r="D228" t="s">
         <v>20</v>
       </c>
-      <c r="H228" s="159" t="s">
+      <c r="E228" t="str">
+        <f>Foderstater!U$64</f>
+        <v>ley silage, regrowth</v>
+      </c>
+      <c r="H228" t="s">
         <v>326</v>
       </c>
-      <c r="I228" s="159">
+      <c r="I228" s="13">
+        <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E228,Foderstater!$U$63:$U$100,0),MATCH(A228&amp;C228&amp;D228,Foderstater!$X$62:$AI$62,0))</f>
         <v>0</v>
       </c>
       <c r="J228" s="159"/>
-      <c r="K228" s="159" t="s">
-        <v>424</v>
-      </c>
+      <c r="K228" s="159"/>
     </row>
     <row r="229" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
@@ -22253,15 +22295,15 @@
         <v>20</v>
       </c>
       <c r="E229" t="str">
-        <f>Foderstater!U$63</f>
-        <v>ley silage, 1st cut</v>
+        <f>Foderstater!U$65</f>
+        <v>other silage</v>
       </c>
       <c r="H229" t="s">
         <v>326</v>
       </c>
       <c r="I229" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E229,Foderstater!$U$63:$U$100,0),MATCH(A229&amp;C229&amp;D229,Foderstater!$X$62:$AI$62,0))</f>
-        <v>69.98809662916166</v>
+        <v>0</v>
       </c>
       <c r="J229" s="159"/>
       <c r="K229" s="159"/>
@@ -22274,8 +22316,8 @@
         <v>20</v>
       </c>
       <c r="E230" t="str">
-        <f>Foderstater!U$64</f>
-        <v>ley silage, regrowth</v>
+        <f>Foderstater!U$66</f>
+        <v>maize silage</v>
       </c>
       <c r="H230" t="s">
         <v>326</v>
@@ -22295,8 +22337,8 @@
         <v>20</v>
       </c>
       <c r="E231" t="str">
-        <f>Foderstater!U$65</f>
-        <v>other silage</v>
+        <f>Foderstater!U$67</f>
+        <v>straw</v>
       </c>
       <c r="H231" t="s">
         <v>326</v>
@@ -22316,15 +22358,15 @@
         <v>20</v>
       </c>
       <c r="E232" t="str">
-        <f>Foderstater!U$66</f>
-        <v>maize silage</v>
+        <f>Foderstater!U$68</f>
+        <v>grazing</v>
       </c>
       <c r="H232" t="s">
         <v>326</v>
       </c>
       <c r="I232" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E232,Foderstater!$U$63:$U$100,0),MATCH(A232&amp;C232&amp;D232,Foderstater!$X$62:$AI$62,0))</f>
-        <v>0</v>
+        <v>13.62395305250616</v>
       </c>
       <c r="J232" s="159"/>
       <c r="K232" s="159"/>
@@ -22337,15 +22379,15 @@
         <v>20</v>
       </c>
       <c r="E233" t="str">
-        <f>Foderstater!U$67</f>
-        <v>straw</v>
+        <f>Foderstater!U$69</f>
+        <v>wheat</v>
       </c>
       <c r="H233" t="s">
         <v>326</v>
       </c>
       <c r="I233" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E233,Foderstater!$U$63:$U$100,0),MATCH(A233&amp;C233&amp;D233,Foderstater!$X$62:$AI$62,0))</f>
-        <v>0</v>
+        <v>3.3926452557375897</v>
       </c>
       <c r="J233" s="159"/>
       <c r="K233" s="159"/>
@@ -22358,15 +22400,15 @@
         <v>20</v>
       </c>
       <c r="E234" t="str">
-        <f>Foderstater!U$68</f>
-        <v>grazing</v>
+        <f>Foderstater!U$70</f>
+        <v>barley</v>
       </c>
       <c r="H234" t="s">
         <v>326</v>
       </c>
       <c r="I234" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E234,Foderstater!$U$63:$U$100,0),MATCH(A234&amp;C234&amp;D234,Foderstater!$X$62:$AI$62,0))</f>
-        <v>13.62395305250616</v>
+        <v>5.969609310362638</v>
       </c>
       <c r="J234" s="159"/>
       <c r="K234" s="159"/>
@@ -22379,15 +22421,15 @@
         <v>20</v>
       </c>
       <c r="E235" t="str">
-        <f>Foderstater!U$69</f>
-        <v>wheat</v>
+        <f>Foderstater!U$71</f>
+        <v>oats</v>
       </c>
       <c r="H235" t="s">
         <v>326</v>
       </c>
       <c r="I235" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E235,Foderstater!$U$63:$U$100,0),MATCH(A235&amp;C235&amp;D235,Foderstater!$X$62:$AI$62,0))</f>
-        <v>3.3926452557375897</v>
+        <v>1.380886004165597</v>
       </c>
       <c r="J235" s="159"/>
       <c r="K235" s="159"/>
@@ -22400,15 +22442,15 @@
         <v>20</v>
       </c>
       <c r="E236" t="str">
-        <f>Foderstater!U$70</f>
-        <v>barley</v>
+        <f>Foderstater!U$72</f>
+        <v>triticale</v>
       </c>
       <c r="H236" t="s">
         <v>326</v>
       </c>
       <c r="I236" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E236,Foderstater!$U$63:$U$100,0),MATCH(A236&amp;C236&amp;D236,Foderstater!$X$62:$AI$62,0))</f>
-        <v>5.969609310362638</v>
+        <v>2.0121854590151322</v>
       </c>
       <c r="J236" s="159"/>
       <c r="K236" s="159"/>
@@ -22421,15 +22463,15 @@
         <v>20</v>
       </c>
       <c r="E237" t="str">
-        <f>Foderstater!U$71</f>
-        <v>oats</v>
+        <f>Foderstater!U$73</f>
+        <v>rye</v>
       </c>
       <c r="H237" t="s">
         <v>326</v>
       </c>
       <c r="I237" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E237,Foderstater!$U$63:$U$100,0),MATCH(A237&amp;C237&amp;D237,Foderstater!$X$62:$AI$62,0))</f>
-        <v>1.380886004165597</v>
+        <v>8.4111477233144716E-3</v>
       </c>
       <c r="J237" s="159"/>
       <c r="K237" s="159"/>
@@ -22442,15 +22484,15 @@
         <v>20</v>
       </c>
       <c r="E238" t="str">
-        <f>Foderstater!U$72</f>
-        <v>triticale</v>
+        <f>Foderstater!U$74</f>
+        <v>maize</v>
       </c>
       <c r="H238" t="s">
         <v>326</v>
       </c>
       <c r="I238" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E238,Foderstater!$U$63:$U$100,0),MATCH(A238&amp;C238&amp;D238,Foderstater!$X$62:$AI$62,0))</f>
-        <v>2.0121854590151322</v>
+        <v>3.654322610609205E-2</v>
       </c>
       <c r="J238" s="159"/>
       <c r="K238" s="159"/>
@@ -22463,15 +22505,15 @@
         <v>20</v>
       </c>
       <c r="E239" t="str">
-        <f>Foderstater!U$73</f>
-        <v>rye</v>
+        <f>Foderstater!U$75</f>
+        <v>peas</v>
       </c>
       <c r="H239" t="s">
         <v>326</v>
       </c>
       <c r="I239" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E239,Foderstater!$U$63:$U$100,0),MATCH(A239&amp;C239&amp;D239,Foderstater!$X$62:$AI$62,0))</f>
-        <v>8.4111477233144716E-3</v>
+        <v>0.83995755602664501</v>
       </c>
       <c r="J239" s="159"/>
       <c r="K239" s="159"/>
@@ -22484,15 +22526,15 @@
         <v>20</v>
       </c>
       <c r="E240" t="str">
-        <f>Foderstater!U$74</f>
-        <v>maize</v>
+        <f>Foderstater!U$76</f>
+        <v>broad beans</v>
       </c>
       <c r="H240" t="s">
         <v>326</v>
       </c>
       <c r="I240" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E240,Foderstater!$U$63:$U$100,0),MATCH(A240&amp;C240&amp;D240,Foderstater!$X$62:$AI$62,0))</f>
-        <v>3.654322610609205E-2</v>
+        <v>0.81150854085068547</v>
       </c>
       <c r="J240" s="159"/>
       <c r="K240" s="159"/>
@@ -22505,15 +22547,15 @@
         <v>20</v>
       </c>
       <c r="E241" t="str">
-        <f>Foderstater!U$75</f>
-        <v>peas</v>
+        <f>Foderstater!U$77</f>
+        <v>rapeseed</v>
       </c>
       <c r="H241" t="s">
         <v>326</v>
       </c>
       <c r="I241" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E241,Foderstater!$U$63:$U$100,0),MATCH(A241&amp;C241&amp;D241,Foderstater!$X$62:$AI$62,0))</f>
-        <v>0.83995755602664501</v>
+        <v>0.3106747346633848</v>
       </c>
       <c r="J241" s="159"/>
       <c r="K241" s="159"/>
@@ -22526,15 +22568,15 @@
         <v>20</v>
       </c>
       <c r="E242" t="str">
-        <f>Foderstater!U$76</f>
-        <v>broad beans</v>
+        <f>Foderstater!U$78</f>
+        <v>linseed</v>
       </c>
       <c r="H242" t="s">
         <v>326</v>
       </c>
       <c r="I242" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E242,Foderstater!$U$63:$U$100,0),MATCH(A242&amp;C242&amp;D242,Foderstater!$X$62:$AI$62,0))</f>
-        <v>0.81150854085068547</v>
+        <v>2.2917194857222345E-4</v>
       </c>
       <c r="J242" s="159"/>
       <c r="K242" s="159"/>
@@ -22547,15 +22589,15 @@
         <v>20</v>
       </c>
       <c r="E243" t="str">
-        <f>Foderstater!U$77</f>
-        <v>rapeseed</v>
+        <f>Foderstater!U$79</f>
+        <v>vegetable oils</v>
       </c>
       <c r="H243" t="s">
         <v>326</v>
       </c>
       <c r="I243" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E243,Foderstater!$U$63:$U$100,0),MATCH(A243&amp;C243&amp;D243,Foderstater!$X$62:$AI$62,0))</f>
-        <v>0.3106747346633848</v>
+        <v>5.9165181908688962E-3</v>
       </c>
       <c r="J243" s="159"/>
       <c r="K243" s="159"/>
@@ -22568,15 +22610,15 @@
         <v>20</v>
       </c>
       <c r="E244" t="str">
-        <f>Foderstater!U$78</f>
-        <v>linseed</v>
+        <f>Foderstater!U$80</f>
+        <v>soybeans</v>
       </c>
       <c r="H244" t="s">
         <v>326</v>
       </c>
       <c r="I244" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E244,Foderstater!$U$63:$U$100,0),MATCH(A244&amp;C244&amp;D244,Foderstater!$X$62:$AI$62,0))</f>
-        <v>2.2917194857222345E-4</v>
+        <v>5.7818018171232116E-3</v>
       </c>
       <c r="J244" s="159"/>
       <c r="K244" s="159"/>
@@ -22589,15 +22631,15 @@
         <v>20</v>
       </c>
       <c r="E245" t="str">
-        <f>Foderstater!U$79</f>
-        <v>vegetable oils</v>
+        <f>Foderstater!U$81</f>
+        <v>soybean meal</v>
       </c>
       <c r="H245" t="s">
         <v>326</v>
       </c>
       <c r="I245" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E245,Foderstater!$U$63:$U$100,0),MATCH(A245&amp;C245&amp;D245,Foderstater!$X$62:$AI$62,0))</f>
-        <v>5.9165181908688962E-3</v>
+        <v>5.2814614338509994E-2</v>
       </c>
       <c r="J245" s="159"/>
       <c r="K245" s="159"/>
@@ -22610,15 +22652,15 @@
         <v>20</v>
       </c>
       <c r="E246" t="str">
-        <f>Foderstater!U$80</f>
-        <v>soybeans</v>
+        <f>Foderstater!U$82</f>
+        <v>soybean protein concentrate</v>
       </c>
       <c r="H246" t="s">
         <v>326</v>
       </c>
       <c r="I246" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E246,Foderstater!$U$63:$U$100,0),MATCH(A246&amp;C246&amp;D246,Foderstater!$X$62:$AI$62,0))</f>
-        <v>5.7818018171232116E-3</v>
+        <v>0</v>
       </c>
       <c r="J246" s="159"/>
       <c r="K246" s="159"/>
@@ -22631,15 +22673,15 @@
         <v>20</v>
       </c>
       <c r="E247" t="str">
-        <f>Foderstater!U$81</f>
-        <v>soybean meal</v>
+        <f>Foderstater!U$83</f>
+        <v>rapeseed meal</v>
       </c>
       <c r="H247" t="s">
         <v>326</v>
       </c>
       <c r="I247" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E247,Foderstater!$U$63:$U$100,0),MATCH(A247&amp;C247&amp;D247,Foderstater!$X$62:$AI$62,0))</f>
-        <v>5.2814614338509994E-2</v>
+        <v>0.40792068342679916</v>
       </c>
       <c r="J247" s="159"/>
       <c r="K247" s="159"/>
@@ -22652,18 +22694,16 @@
         <v>20</v>
       </c>
       <c r="E248" t="str">
-        <f>Foderstater!U$82</f>
-        <v>soybean protein concentrate</v>
+        <f>Foderstater!U$84</f>
+        <v>sunflower seed meal</v>
       </c>
       <c r="H248" t="s">
         <v>326</v>
       </c>
       <c r="I248" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E248,Foderstater!$U$63:$U$100,0),MATCH(A248&amp;C248&amp;D248,Foderstater!$X$62:$AI$62,0))</f>
-        <v>0</v>
-      </c>
-      <c r="J248" s="159"/>
-      <c r="K248" s="159"/>
+        <v>5.6350294021269417E-3</v>
+      </c>
     </row>
     <row r="249" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
@@ -22673,18 +22713,16 @@
         <v>20</v>
       </c>
       <c r="E249" t="str">
-        <f>Foderstater!U$83</f>
-        <v>rapeseed meal</v>
+        <f>Foderstater!U$85</f>
+        <v>palm kernel expeller</v>
       </c>
       <c r="H249" t="s">
         <v>326</v>
       </c>
       <c r="I249" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E249,Foderstater!$U$63:$U$100,0),MATCH(A249&amp;C249&amp;D249,Foderstater!$X$62:$AI$62,0))</f>
-        <v>0.40792068342679916</v>
-      </c>
-      <c r="J249" s="159"/>
-      <c r="K249" s="159"/>
+        <v>3.6615965497408809E-2</v>
+      </c>
     </row>
     <row r="250" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
@@ -22694,15 +22732,15 @@
         <v>20</v>
       </c>
       <c r="E250" t="str">
-        <f>Foderstater!U$84</f>
-        <v>sunflower seed meal</v>
+        <f>Foderstater!U$86</f>
+        <v>luzern meal</v>
       </c>
       <c r="H250" t="s">
         <v>326</v>
       </c>
       <c r="I250" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E250,Foderstater!$U$63:$U$100,0),MATCH(A250&amp;C250&amp;D250,Foderstater!$X$62:$AI$62,0))</f>
-        <v>5.6350294021269417E-3</v>
+        <v>1.1138174643373414E-2</v>
       </c>
     </row>
     <row r="251" spans="1:11" x14ac:dyDescent="0.25">
@@ -22713,15 +22751,15 @@
         <v>20</v>
       </c>
       <c r="E251" t="str">
-        <f>Foderstater!U$85</f>
-        <v>palm kernel expeller</v>
+        <f>Foderstater!U$87</f>
+        <v>wheat bran</v>
       </c>
       <c r="H251" t="s">
         <v>326</v>
       </c>
       <c r="I251" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E251,Foderstater!$U$63:$U$100,0),MATCH(A251&amp;C251&amp;D251,Foderstater!$X$62:$AI$62,0))</f>
-        <v>3.6615965497408809E-2</v>
+        <v>0.12135190883686281</v>
       </c>
     </row>
     <row r="252" spans="1:11" x14ac:dyDescent="0.25">
@@ -22732,15 +22770,15 @@
         <v>20</v>
       </c>
       <c r="E252" t="str">
-        <f>Foderstater!U$86</f>
-        <v>luzern meal</v>
+        <f>Foderstater!U$88</f>
+        <v>wheat bran, fine</v>
       </c>
       <c r="H252" t="s">
         <v>326</v>
       </c>
       <c r="I252" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E252,Foderstater!$U$63:$U$100,0),MATCH(A252&amp;C252&amp;D252,Foderstater!$X$62:$AI$62,0))</f>
-        <v>1.1138174643373414E-2</v>
+        <v>3.1811619025563673E-4</v>
       </c>
     </row>
     <row r="253" spans="1:11" x14ac:dyDescent="0.25">
@@ -22751,15 +22789,15 @@
         <v>20</v>
       </c>
       <c r="E253" t="str">
-        <f>Foderstater!U$87</f>
-        <v>wheat bran</v>
+        <f>Foderstater!U$89</f>
+        <v>oat hulls</v>
       </c>
       <c r="H253" t="s">
         <v>326</v>
       </c>
       <c r="I253" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E253,Foderstater!$U$63:$U$100,0),MATCH(A253&amp;C253&amp;D253,Foderstater!$X$62:$AI$62,0))</f>
-        <v>0.12135190883686281</v>
+        <v>1.4615657454838853E-2</v>
       </c>
     </row>
     <row r="254" spans="1:11" x14ac:dyDescent="0.25">
@@ -22770,15 +22808,15 @@
         <v>20</v>
       </c>
       <c r="E254" t="str">
-        <f>Foderstater!U$88</f>
-        <v>wheat bran, fine</v>
+        <f>Foderstater!U$90</f>
+        <v>oat bran</v>
       </c>
       <c r="H254" t="s">
         <v>326</v>
       </c>
       <c r="I254" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E254,Foderstater!$U$63:$U$100,0),MATCH(A254&amp;C254&amp;D254,Foderstater!$X$62:$AI$62,0))</f>
-        <v>3.1811619025563673E-4</v>
+        <v>1.6495420097371271E-3</v>
       </c>
     </row>
     <row r="255" spans="1:11" x14ac:dyDescent="0.25">
@@ -22789,15 +22827,15 @@
         <v>20</v>
       </c>
       <c r="E255" t="str">
-        <f>Foderstater!U$89</f>
-        <v>oat hulls</v>
+        <f>Foderstater!U$91</f>
+        <v>rye bran</v>
       </c>
       <c r="H255" t="s">
         <v>326</v>
       </c>
       <c r="I255" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E255,Foderstater!$U$63:$U$100,0),MATCH(A255&amp;C255&amp;D255,Foderstater!$X$62:$AI$62,0))</f>
-        <v>1.4615657454838853E-2</v>
+        <v>5.0872054392434975E-3</v>
       </c>
     </row>
     <row r="256" spans="1:11" x14ac:dyDescent="0.25">
@@ -22808,15 +22846,15 @@
         <v>20</v>
       </c>
       <c r="E256" t="str">
-        <f>Foderstater!U$90</f>
-        <v>oat bran</v>
+        <f>Foderstater!U$92</f>
+        <v>wheat distillers grain, dry</v>
       </c>
       <c r="H256" t="s">
         <v>326</v>
       </c>
       <c r="I256" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E256,Foderstater!$U$63:$U$100,0),MATCH(A256&amp;C256&amp;D256,Foderstater!$X$62:$AI$62,0))</f>
-        <v>1.6495420097371271E-3</v>
+        <v>0.13044177355370595</v>
       </c>
     </row>
     <row r="257" spans="1:12" x14ac:dyDescent="0.25">
@@ -22827,15 +22865,15 @@
         <v>20</v>
       </c>
       <c r="E257" t="str">
-        <f>Foderstater!U$91</f>
-        <v>rye bran</v>
+        <f>Foderstater!U$93</f>
+        <v>barley brewers grain</v>
       </c>
       <c r="H257" t="s">
         <v>326</v>
       </c>
       <c r="I257" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E257,Foderstater!$U$63:$U$100,0),MATCH(A257&amp;C257&amp;D257,Foderstater!$X$62:$AI$62,0))</f>
-        <v>5.0872054392434975E-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="258" spans="1:12" x14ac:dyDescent="0.25">
@@ -22846,15 +22884,15 @@
         <v>20</v>
       </c>
       <c r="E258" t="str">
-        <f>Foderstater!U$92</f>
-        <v>wheat distillers grain, dry</v>
+        <f>Foderstater!U$94</f>
+        <v>maize gluten meal</v>
       </c>
       <c r="H258" t="s">
         <v>326</v>
       </c>
       <c r="I258" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E258,Foderstater!$U$63:$U$100,0),MATCH(A258&amp;C258&amp;D258,Foderstater!$X$62:$AI$62,0))</f>
-        <v>0.13044177355370595</v>
+        <v>3.9415408894312009E-3</v>
       </c>
     </row>
     <row r="259" spans="1:12" x14ac:dyDescent="0.25">
@@ -22865,15 +22903,15 @@
         <v>20</v>
       </c>
       <c r="E259" t="str">
-        <f>Foderstater!U$93</f>
-        <v>barley brewers grain</v>
+        <f>Foderstater!U$95</f>
+        <v>sugar beet molasses</v>
       </c>
       <c r="H259" t="s">
         <v>326</v>
       </c>
       <c r="I259" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E259,Foderstater!$U$63:$U$100,0),MATCH(A259&amp;C259&amp;D259,Foderstater!$X$62:$AI$62,0))</f>
-        <v>0</v>
+        <v>4.3709298114406915E-2</v>
       </c>
     </row>
     <row r="260" spans="1:12" x14ac:dyDescent="0.25">
@@ -22884,15 +22922,15 @@
         <v>20</v>
       </c>
       <c r="E260" t="str">
-        <f>Foderstater!U$94</f>
-        <v>maize gluten meal</v>
+        <f>Foderstater!U$96</f>
+        <v>sugar beet pulp</v>
       </c>
       <c r="H260" t="s">
         <v>326</v>
       </c>
       <c r="I260" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E260,Foderstater!$U$63:$U$100,0),MATCH(A260&amp;C260&amp;D260,Foderstater!$X$62:$AI$62,0))</f>
-        <v>3.9415408894312009E-3</v>
+        <v>8.4340547924782114E-2</v>
       </c>
     </row>
     <row r="261" spans="1:12" x14ac:dyDescent="0.25">
@@ -22903,15 +22941,15 @@
         <v>20</v>
       </c>
       <c r="E261" t="str">
-        <f>Foderstater!U$95</f>
-        <v>sugar beet molasses</v>
+        <f>Foderstater!U$97</f>
+        <v>whey powder</v>
       </c>
       <c r="H261" t="s">
         <v>326</v>
       </c>
       <c r="I261" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E261,Foderstater!$U$63:$U$100,0),MATCH(A261&amp;C261&amp;D261,Foderstater!$X$62:$AI$62,0))</f>
-        <v>4.3709298114406915E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="262" spans="1:12" x14ac:dyDescent="0.25">
@@ -22922,15 +22960,15 @@
         <v>20</v>
       </c>
       <c r="E262" t="str">
-        <f>Foderstater!U$96</f>
-        <v>sugar beet pulp</v>
+        <f>Foderstater!U$98</f>
+        <v>potatoe protein</v>
       </c>
       <c r="H262" t="s">
         <v>326</v>
       </c>
       <c r="I262" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E262,Foderstater!$U$63:$U$100,0),MATCH(A262&amp;C262&amp;D262,Foderstater!$X$62:$AI$62,0))</f>
-        <v>8.4340547924782114E-2</v>
+        <v>3.8613267525390842E-4</v>
       </c>
     </row>
     <row r="263" spans="1:12" x14ac:dyDescent="0.25">
@@ -22941,8 +22979,8 @@
         <v>20</v>
       </c>
       <c r="E263" t="str">
-        <f>Foderstater!U$97</f>
-        <v>whey powder</v>
+        <f>Foderstater!U$99</f>
+        <v>fish meal</v>
       </c>
       <c r="H263" t="s">
         <v>326</v>
@@ -22960,96 +22998,94 @@
         <v>20</v>
       </c>
       <c r="E264" t="str">
-        <f>Foderstater!U$98</f>
-        <v>potatoe protein</v>
+        <f>Foderstater!U$100</f>
+        <v>minerals</v>
       </c>
       <c r="H264" t="s">
         <v>326</v>
       </c>
       <c r="I264" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E264,Foderstater!$U$63:$U$100,0),MATCH(A264&amp;C264&amp;D264,Foderstater!$X$62:$AI$62,0))</f>
-        <v>3.8613267525390842E-4</v>
-      </c>
-    </row>
-    <row r="265" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A265" t="s">
+        <v>0.69363540132779178</v>
+      </c>
+    </row>
+    <row r="266" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A266" s="81" t="s">
+        <v>580</v>
+      </c>
+      <c r="B266" s="48"/>
+      <c r="C266" s="48"/>
+      <c r="D266" s="49"/>
+      <c r="E266" s="49"/>
+      <c r="F266" s="49"/>
+      <c r="G266" s="49"/>
+      <c r="H266" s="49"/>
+      <c r="I266" s="162"/>
+      <c r="J266" s="49"/>
+      <c r="K266" s="49"/>
+      <c r="L266" s="49"/>
+    </row>
+    <row r="267" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A267" s="159" t="s">
         <v>2</v>
       </c>
-      <c r="D265" t="s">
-        <v>20</v>
-      </c>
-      <c r="E265" t="str">
-        <f>Foderstater!U$99</f>
-        <v>fish meal</v>
-      </c>
-      <c r="H265" t="s">
+      <c r="B267" s="159"/>
+      <c r="C267" s="159"/>
+      <c r="D267" s="159"/>
+      <c r="H267" s="159" t="s">
         <v>326</v>
       </c>
-      <c r="I265" s="13">
-        <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E265,Foderstater!$U$63:$U$100,0),MATCH(A265&amp;C265&amp;D265,Foderstater!$X$62:$AI$62,0))</f>
+      <c r="I267" s="256">
         <v>0</v>
       </c>
-    </row>
-    <row r="266" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A266" t="s">
+      <c r="J267" s="159"/>
+      <c r="K267" s="159" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="268" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A268" t="s">
         <v>2</v>
       </c>
-      <c r="D266" t="s">
-        <v>20</v>
-      </c>
-      <c r="E266" t="str">
-        <f>Foderstater!U$100</f>
-        <v>minerals</v>
-      </c>
-      <c r="H266" t="s">
+      <c r="E268" t="str">
+        <f>Foderstater!U$63</f>
+        <v>ley silage, 1st cut</v>
+      </c>
+      <c r="H268" t="s">
         <v>326</v>
       </c>
-      <c r="I266" s="13">
-        <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E266,Foderstater!$U$63:$U$100,0),MATCH(A266&amp;C266&amp;D266,Foderstater!$X$62:$AI$62,0))</f>
-        <v>0.69363540132779178</v>
-      </c>
-    </row>
-    <row r="268" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A268" s="81" t="s">
-        <v>580</v>
-      </c>
-      <c r="B268" s="48"/>
-      <c r="C268" s="48"/>
-      <c r="D268" s="49"/>
-      <c r="E268" s="49"/>
-      <c r="F268" s="49"/>
-      <c r="G268" s="49"/>
-      <c r="H268" s="49"/>
-      <c r="I268" s="162"/>
-      <c r="J268" s="49"/>
-      <c r="K268" s="49"/>
-      <c r="L268" s="49"/>
+      <c r="I268" s="13">
+        <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E268,Foderstater!$U$63:$U$100,0),MATCH(A268&amp;C268&amp;D268,Foderstater!$X$62:$AI$62,0))</f>
+        <v>0</v>
+      </c>
+      <c r="J268" s="159"/>
+      <c r="K268" s="159"/>
     </row>
     <row r="269" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A269" s="159" t="s">
+      <c r="A269" t="s">
         <v>2</v>
       </c>
-      <c r="B269" s="159"/>
-      <c r="C269" s="159"/>
-      <c r="D269" s="159"/>
-      <c r="H269" s="159" t="s">
+      <c r="E269" t="str">
+        <f>Foderstater!U$64</f>
+        <v>ley silage, regrowth</v>
+      </c>
+      <c r="H269" t="s">
         <v>326</v>
       </c>
-      <c r="I269" s="256">
-        <v>0</v>
+      <c r="I269" s="13">
+        <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E269,Foderstater!$U$63:$U$100,0),MATCH(A269&amp;C269&amp;D269,Foderstater!$X$62:$AI$62,0))</f>
+        <v>55.029062371648976</v>
       </c>
       <c r="J269" s="159"/>
-      <c r="K269" s="159" t="s">
-        <v>424</v>
-      </c>
+      <c r="K269" s="159"/>
     </row>
     <row r="270" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>2</v>
       </c>
       <c r="E270" t="str">
-        <f>Foderstater!U$63</f>
-        <v>ley silage, 1st cut</v>
+        <f>Foderstater!U$65</f>
+        <v>other silage</v>
       </c>
       <c r="H270" t="s">
         <v>326</v>
@@ -23066,15 +23102,15 @@
         <v>2</v>
       </c>
       <c r="E271" t="str">
-        <f>Foderstater!U$64</f>
-        <v>ley silage, regrowth</v>
+        <f>Foderstater!U$66</f>
+        <v>maize silage</v>
       </c>
       <c r="H271" t="s">
         <v>326</v>
       </c>
       <c r="I271" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E271,Foderstater!$U$63:$U$100,0),MATCH(A271&amp;C271&amp;D271,Foderstater!$X$62:$AI$62,0))</f>
-        <v>55.029062371648976</v>
+        <v>0</v>
       </c>
       <c r="J271" s="159"/>
       <c r="K271" s="159"/>
@@ -23084,8 +23120,8 @@
         <v>2</v>
       </c>
       <c r="E272" t="str">
-        <f>Foderstater!U$65</f>
-        <v>other silage</v>
+        <f>Foderstater!U$67</f>
+        <v>straw</v>
       </c>
       <c r="H272" t="s">
         <v>326</v>
@@ -23102,15 +23138,15 @@
         <v>2</v>
       </c>
       <c r="E273" t="str">
-        <f>Foderstater!U$66</f>
-        <v>maize silage</v>
+        <f>Foderstater!U$68</f>
+        <v>grazing</v>
       </c>
       <c r="H273" t="s">
         <v>326</v>
       </c>
       <c r="I273" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E273,Foderstater!$U$63:$U$100,0),MATCH(A273&amp;C273&amp;D273,Foderstater!$X$62:$AI$62,0))</f>
-        <v>0</v>
+        <v>38.614788214420173</v>
       </c>
       <c r="J273" s="159"/>
       <c r="K273" s="159"/>
@@ -23120,15 +23156,15 @@
         <v>2</v>
       </c>
       <c r="E274" t="str">
-        <f>Foderstater!U$67</f>
-        <v>straw</v>
+        <f>Foderstater!U$69</f>
+        <v>wheat</v>
       </c>
       <c r="H274" t="s">
         <v>326</v>
       </c>
       <c r="I274" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E274,Foderstater!$U$63:$U$100,0),MATCH(A274&amp;C274&amp;D274,Foderstater!$X$62:$AI$62,0))</f>
-        <v>0</v>
+        <v>1.3702995315856561</v>
       </c>
       <c r="J274" s="159"/>
       <c r="K274" s="159"/>
@@ -23138,15 +23174,15 @@
         <v>2</v>
       </c>
       <c r="E275" t="str">
-        <f>Foderstater!U$68</f>
-        <v>grazing</v>
+        <f>Foderstater!U$70</f>
+        <v>barley</v>
       </c>
       <c r="H275" t="s">
         <v>326</v>
       </c>
       <c r="I275" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E275,Foderstater!$U$63:$U$100,0),MATCH(A275&amp;C275&amp;D275,Foderstater!$X$62:$AI$62,0))</f>
-        <v>38.614788214420173</v>
+        <v>2.1464108702309166</v>
       </c>
       <c r="J275" s="159"/>
       <c r="K275" s="159"/>
@@ -23156,15 +23192,15 @@
         <v>2</v>
       </c>
       <c r="E276" t="str">
-        <f>Foderstater!U$69</f>
-        <v>wheat</v>
+        <f>Foderstater!U$71</f>
+        <v>oats</v>
       </c>
       <c r="H276" t="s">
         <v>326</v>
       </c>
       <c r="I276" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E276,Foderstater!$U$63:$U$100,0),MATCH(A276&amp;C276&amp;D276,Foderstater!$X$62:$AI$62,0))</f>
-        <v>1.3702995315856561</v>
+        <v>0.54223737074929057</v>
       </c>
       <c r="J276" s="159"/>
       <c r="K276" s="159"/>
@@ -23174,15 +23210,15 @@
         <v>2</v>
       </c>
       <c r="E277" t="str">
-        <f>Foderstater!U$70</f>
-        <v>barley</v>
+        <f>Foderstater!U$72</f>
+        <v>triticale</v>
       </c>
       <c r="H277" t="s">
         <v>326</v>
       </c>
       <c r="I277" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E277,Foderstater!$U$63:$U$100,0),MATCH(A277&amp;C277&amp;D277,Foderstater!$X$62:$AI$62,0))</f>
-        <v>2.1464108702309166</v>
+        <v>0.63111634374194048</v>
       </c>
       <c r="J277" s="159"/>
       <c r="K277" s="159"/>
@@ -23192,15 +23228,15 @@
         <v>2</v>
       </c>
       <c r="E278" t="str">
-        <f>Foderstater!U$71</f>
-        <v>oats</v>
+        <f>Foderstater!U$73</f>
+        <v>rye</v>
       </c>
       <c r="H278" t="s">
         <v>326</v>
       </c>
       <c r="I278" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E278,Foderstater!$U$63:$U$100,0),MATCH(A278&amp;C278&amp;D278,Foderstater!$X$62:$AI$62,0))</f>
-        <v>0.54223737074929057</v>
+        <v>5.6371722021104978E-3</v>
       </c>
       <c r="J278" s="159"/>
       <c r="K278" s="159"/>
@@ -23210,15 +23246,15 @@
         <v>2</v>
       </c>
       <c r="E279" t="str">
-        <f>Foderstater!U$72</f>
-        <v>triticale</v>
+        <f>Foderstater!U$74</f>
+        <v>maize</v>
       </c>
       <c r="H279" t="s">
         <v>326</v>
       </c>
       <c r="I279" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E279,Foderstater!$U$63:$U$100,0),MATCH(A279&amp;C279&amp;D279,Foderstater!$X$62:$AI$62,0))</f>
-        <v>0.63111634374194048</v>
+        <v>2.4491361364359067E-2</v>
       </c>
       <c r="J279" s="159"/>
       <c r="K279" s="159"/>
@@ -23228,15 +23264,15 @@
         <v>2</v>
       </c>
       <c r="E280" t="str">
-        <f>Foderstater!U$73</f>
-        <v>rye</v>
+        <f>Foderstater!U$75</f>
+        <v>peas</v>
       </c>
       <c r="H280" t="s">
         <v>326</v>
       </c>
       <c r="I280" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E280,Foderstater!$U$63:$U$100,0),MATCH(A280&amp;C280&amp;D280,Foderstater!$X$62:$AI$62,0))</f>
-        <v>5.6371722021104978E-3</v>
+        <v>3.3129545230803178E-2</v>
       </c>
       <c r="J280" s="159"/>
       <c r="K280" s="159"/>
@@ -23246,15 +23282,15 @@
         <v>2</v>
       </c>
       <c r="E281" t="str">
-        <f>Foderstater!U$74</f>
-        <v>maize</v>
+        <f>Foderstater!U$76</f>
+        <v>broad beans</v>
       </c>
       <c r="H281" t="s">
         <v>326</v>
       </c>
       <c r="I281" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E281,Foderstater!$U$63:$U$100,0),MATCH(A281&amp;C281&amp;D281,Foderstater!$X$62:$AI$62,0))</f>
-        <v>2.4491361364359067E-2</v>
+        <v>4.0966798466627027E-2</v>
       </c>
       <c r="J281" s="159"/>
       <c r="K281" s="159"/>
@@ -23264,15 +23300,15 @@
         <v>2</v>
       </c>
       <c r="E282" t="str">
-        <f>Foderstater!U$75</f>
-        <v>peas</v>
+        <f>Foderstater!U$77</f>
+        <v>rapeseed</v>
       </c>
       <c r="H282" t="s">
         <v>326</v>
       </c>
       <c r="I282" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E282,Foderstater!$U$63:$U$100,0),MATCH(A282&amp;C282&amp;D282,Foderstater!$X$62:$AI$62,0))</f>
-        <v>3.3129545230803178E-2</v>
+        <v>0.20821498275295594</v>
       </c>
       <c r="J282" s="159"/>
       <c r="K282" s="159"/>
@@ -23282,15 +23318,15 @@
         <v>2</v>
       </c>
       <c r="E283" t="str">
-        <f>Foderstater!U$76</f>
-        <v>broad beans</v>
+        <f>Foderstater!U$78</f>
+        <v>linseed</v>
       </c>
       <c r="H283" t="s">
         <v>326</v>
       </c>
       <c r="I283" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E283,Foderstater!$U$63:$U$100,0),MATCH(A283&amp;C283&amp;D283,Foderstater!$X$62:$AI$62,0))</f>
-        <v>4.0966798466627027E-2</v>
+        <v>1.5359161204765519E-4</v>
       </c>
       <c r="J283" s="159"/>
       <c r="K283" s="159"/>
@@ -23300,15 +23336,15 @@
         <v>2</v>
       </c>
       <c r="E284" t="str">
-        <f>Foderstater!U$77</f>
-        <v>rapeseed</v>
+        <f>Foderstater!U$79</f>
+        <v>vegetable oils</v>
       </c>
       <c r="H284" t="s">
         <v>326</v>
       </c>
       <c r="I284" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E284,Foderstater!$U$63:$U$100,0),MATCH(A284&amp;C284&amp;D284,Foderstater!$X$62:$AI$62,0))</f>
-        <v>0.20821498275295594</v>
+        <v>3.9652652617667341E-3</v>
       </c>
       <c r="J284" s="159"/>
       <c r="K284" s="159"/>
@@ -23318,15 +23354,15 @@
         <v>2</v>
       </c>
       <c r="E285" t="str">
-        <f>Foderstater!U$78</f>
-        <v>linseed</v>
+        <f>Foderstater!U$80</f>
+        <v>soybeans</v>
       </c>
       <c r="H285" t="s">
         <v>326</v>
       </c>
       <c r="I285" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E285,Foderstater!$U$63:$U$100,0),MATCH(A285&amp;C285&amp;D285,Foderstater!$X$62:$AI$62,0))</f>
-        <v>1.5359161204765519E-4</v>
+        <v>3.8749780117707201E-3</v>
       </c>
       <c r="J285" s="159"/>
       <c r="K285" s="159"/>
@@ -23336,15 +23372,15 @@
         <v>2</v>
       </c>
       <c r="E286" t="str">
-        <f>Foderstater!U$79</f>
-        <v>vegetable oils</v>
+        <f>Foderstater!U$81</f>
+        <v>soybean meal</v>
       </c>
       <c r="H286" t="s">
         <v>326</v>
       </c>
       <c r="I286" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E286,Foderstater!$U$63:$U$100,0),MATCH(A286&amp;C286&amp;D286,Foderstater!$X$62:$AI$62,0))</f>
-        <v>3.9652652617667341E-3</v>
+        <v>3.5396486378307765E-2</v>
       </c>
       <c r="J286" s="159"/>
       <c r="K286" s="159"/>
@@ -23354,15 +23390,15 @@
         <v>2</v>
       </c>
       <c r="E287" t="str">
-        <f>Foderstater!U$80</f>
-        <v>soybeans</v>
+        <f>Foderstater!U$82</f>
+        <v>soybean protein concentrate</v>
       </c>
       <c r="H287" t="s">
         <v>326</v>
       </c>
       <c r="I287" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E287,Foderstater!$U$63:$U$100,0),MATCH(A287&amp;C287&amp;D287,Foderstater!$X$62:$AI$62,0))</f>
-        <v>3.8749780117707201E-3</v>
+        <v>0</v>
       </c>
       <c r="J287" s="159"/>
       <c r="K287" s="159"/>
@@ -23372,270 +23408,266 @@
         <v>2</v>
       </c>
       <c r="E288" t="str">
-        <f>Foderstater!U$81</f>
-        <v>soybean meal</v>
+        <f>Foderstater!U$83</f>
+        <v>rapeseed meal</v>
       </c>
       <c r="H288" t="s">
         <v>326</v>
       </c>
       <c r="I288" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E288,Foderstater!$U$63:$U$100,0),MATCH(A288&amp;C288&amp;D288,Foderstater!$X$62:$AI$62,0))</f>
-        <v>3.5396486378307765E-2</v>
+        <v>0.27338946038309825</v>
       </c>
       <c r="J288" s="159"/>
       <c r="K288" s="159"/>
     </row>
-    <row r="289" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>2</v>
       </c>
       <c r="E289" t="str">
-        <f>Foderstater!U$82</f>
-        <v>soybean protein concentrate</v>
+        <f>Foderstater!U$84</f>
+        <v>sunflower seed meal</v>
       </c>
       <c r="H289" t="s">
         <v>326</v>
       </c>
       <c r="I289" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E289,Foderstater!$U$63:$U$100,0),MATCH(A289&amp;C289&amp;D289,Foderstater!$X$62:$AI$62,0))</f>
-        <v>0</v>
-      </c>
-      <c r="J289" s="159"/>
-      <c r="K289" s="159"/>
-    </row>
-    <row r="290" spans="1:11" x14ac:dyDescent="0.25">
+        <v>3.7766107728313516E-3</v>
+      </c>
+    </row>
+    <row r="290" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>2</v>
       </c>
       <c r="E290" t="str">
-        <f>Foderstater!U$83</f>
-        <v>rapeseed meal</v>
+        <f>Foderstater!U$85</f>
+        <v>palm kernel expeller</v>
       </c>
       <c r="H290" t="s">
         <v>326</v>
       </c>
       <c r="I290" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E290,Foderstater!$U$63:$U$100,0),MATCH(A290&amp;C290&amp;D290,Foderstater!$X$62:$AI$62,0))</f>
-        <v>0.27338946038309825</v>
-      </c>
-      <c r="J290" s="159"/>
-      <c r="K290" s="159"/>
-    </row>
-    <row r="291" spans="1:11" x14ac:dyDescent="0.25">
+        <v>2.454011148600925E-2</v>
+      </c>
+    </row>
+    <row r="291" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>2</v>
       </c>
       <c r="E291" t="str">
-        <f>Foderstater!U$84</f>
-        <v>sunflower seed meal</v>
+        <f>Foderstater!U$86</f>
+        <v>luzern meal</v>
       </c>
       <c r="H291" t="s">
         <v>326</v>
       </c>
       <c r="I291" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E291,Foderstater!$U$63:$U$100,0),MATCH(A291&amp;C291&amp;D291,Foderstater!$X$62:$AI$62,0))</f>
-        <v>3.7766107728313516E-3</v>
-      </c>
-    </row>
-    <row r="292" spans="1:11" x14ac:dyDescent="0.25">
+        <v>7.4648324517994124E-3</v>
+      </c>
+    </row>
+    <row r="292" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>2</v>
       </c>
       <c r="E292" t="str">
-        <f>Foderstater!U$85</f>
-        <v>palm kernel expeller</v>
+        <f>Foderstater!U$87</f>
+        <v>wheat bran</v>
       </c>
       <c r="H292" t="s">
         <v>326</v>
       </c>
       <c r="I292" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E292,Foderstater!$U$63:$U$100,0),MATCH(A292&amp;C292&amp;D292,Foderstater!$X$62:$AI$62,0))</f>
-        <v>2.454011148600925E-2</v>
-      </c>
-    </row>
-    <row r="293" spans="1:11" x14ac:dyDescent="0.25">
+        <v>8.1330352250506319E-2</v>
+      </c>
+    </row>
+    <row r="293" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>2</v>
       </c>
       <c r="E293" t="str">
-        <f>Foderstater!U$86</f>
-        <v>luzern meal</v>
+        <f>Foderstater!U$88</f>
+        <v>wheat bran, fine</v>
       </c>
       <c r="H293" t="s">
         <v>326</v>
       </c>
       <c r="I293" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E293,Foderstater!$U$63:$U$100,0),MATCH(A293&amp;C293&amp;D293,Foderstater!$X$62:$AI$62,0))</f>
-        <v>7.4648324517994124E-3</v>
-      </c>
-    </row>
-    <row r="294" spans="1:11" x14ac:dyDescent="0.25">
+        <v>2.1320226486804789E-4</v>
+      </c>
+    </row>
+    <row r="294" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>2</v>
       </c>
       <c r="E294" t="str">
-        <f>Foderstater!U$87</f>
-        <v>wheat bran</v>
+        <f>Foderstater!U$89</f>
+        <v>oat hulls</v>
       </c>
       <c r="H294" t="s">
         <v>326</v>
       </c>
       <c r="I294" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E294,Foderstater!$U$63:$U$100,0),MATCH(A294&amp;C294&amp;D294,Foderstater!$X$62:$AI$62,0))</f>
-        <v>8.1330352250506319E-2</v>
-      </c>
-    </row>
-    <row r="295" spans="1:11" x14ac:dyDescent="0.25">
+        <v>9.7954501133788105E-3</v>
+      </c>
+    </row>
+    <row r="295" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>2</v>
       </c>
       <c r="E295" t="str">
-        <f>Foderstater!U$88</f>
-        <v>wheat bran, fine</v>
+        <f>Foderstater!U$90</f>
+        <v>oat bran</v>
       </c>
       <c r="H295" t="s">
         <v>326</v>
       </c>
       <c r="I295" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E295,Foderstater!$U$63:$U$100,0),MATCH(A295&amp;C295&amp;D295,Foderstater!$X$62:$AI$62,0))</f>
-        <v>2.1320226486804789E-4</v>
-      </c>
-    </row>
-    <row r="296" spans="1:11" x14ac:dyDescent="0.25">
+        <v>1.1055271729123049E-3</v>
+      </c>
+    </row>
+    <row r="296" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>2</v>
       </c>
       <c r="E296" t="str">
-        <f>Foderstater!U$89</f>
-        <v>oat hulls</v>
+        <f>Foderstater!U$91</f>
+        <v>rye bran</v>
       </c>
       <c r="H296" t="s">
         <v>326</v>
       </c>
       <c r="I296" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E296,Foderstater!$U$63:$U$100,0),MATCH(A296&amp;C296&amp;D296,Foderstater!$X$62:$AI$62,0))</f>
-        <v>9.7954501133788105E-3</v>
-      </c>
-    </row>
-    <row r="297" spans="1:11" x14ac:dyDescent="0.25">
+        <v>3.4094577852959427E-3</v>
+      </c>
+    </row>
+    <row r="297" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>2</v>
       </c>
       <c r="E297" t="str">
-        <f>Foderstater!U$90</f>
-        <v>oat bran</v>
+        <f>Foderstater!U$92</f>
+        <v>wheat distillers grain, dry</v>
       </c>
       <c r="H297" t="s">
         <v>326</v>
       </c>
       <c r="I297" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E297,Foderstater!$U$63:$U$100,0),MATCH(A297&amp;C297&amp;D297,Foderstater!$X$62:$AI$62,0))</f>
-        <v>1.1055271729123049E-3</v>
-      </c>
-    </row>
-    <row r="298" spans="1:11" x14ac:dyDescent="0.25">
+        <v>8.7422402276057576E-2</v>
+      </c>
+    </row>
+    <row r="298" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>2</v>
       </c>
       <c r="E298" t="str">
-        <f>Foderstater!U$91</f>
-        <v>rye bran</v>
+        <f>Foderstater!U$93</f>
+        <v>barley brewers grain</v>
       </c>
       <c r="H298" t="s">
         <v>326</v>
       </c>
       <c r="I298" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E298,Foderstater!$U$63:$U$100,0),MATCH(A298&amp;C298&amp;D298,Foderstater!$X$62:$AI$62,0))</f>
-        <v>3.4094577852959427E-3</v>
-      </c>
-    </row>
-    <row r="299" spans="1:11" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="299" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>2</v>
       </c>
       <c r="E299" t="str">
-        <f>Foderstater!U$92</f>
-        <v>wheat distillers grain, dry</v>
+        <f>Foderstater!U$94</f>
+        <v>maize gluten meal</v>
       </c>
       <c r="H299" t="s">
         <v>326</v>
       </c>
       <c r="I299" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E299,Foderstater!$U$63:$U$100,0),MATCH(A299&amp;C299&amp;D299,Foderstater!$X$62:$AI$62,0))</f>
-        <v>8.7422402276057576E-2</v>
-      </c>
-    </row>
-    <row r="300" spans="1:11" x14ac:dyDescent="0.25">
+        <v>2.6416305439262745E-3</v>
+      </c>
+    </row>
+    <row r="300" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>2</v>
       </c>
       <c r="E300" t="str">
-        <f>Foderstater!U$93</f>
-        <v>barley brewers grain</v>
+        <f>Foderstater!U$95</f>
+        <v>sugar beet molasses</v>
       </c>
       <c r="H300" t="s">
         <v>326</v>
       </c>
       <c r="I300" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E300,Foderstater!$U$63:$U$100,0),MATCH(A300&amp;C300&amp;D300,Foderstater!$X$62:$AI$62,0))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="301" spans="1:11" x14ac:dyDescent="0.25">
+        <v>2.929408071401712E-2</v>
+      </c>
+    </row>
+    <row r="301" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>2</v>
       </c>
       <c r="E301" t="str">
-        <f>Foderstater!U$94</f>
-        <v>maize gluten meal</v>
+        <f>Foderstater!U$96</f>
+        <v>sugar beet pulp</v>
       </c>
       <c r="H301" t="s">
         <v>326</v>
       </c>
       <c r="I301" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E301,Foderstater!$U$63:$U$100,0),MATCH(A301&amp;C301&amp;D301,Foderstater!$X$62:$AI$62,0))</f>
-        <v>2.6416305439262745E-3</v>
-      </c>
-    </row>
-    <row r="302" spans="1:11" x14ac:dyDescent="0.25">
+        <v>5.6525245770502136E-2</v>
+      </c>
+    </row>
+    <row r="302" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>2</v>
       </c>
       <c r="E302" t="str">
-        <f>Foderstater!U$95</f>
-        <v>sugar beet molasses</v>
+        <f>Foderstater!U$97</f>
+        <v>whey powder</v>
       </c>
       <c r="H302" t="s">
         <v>326</v>
       </c>
       <c r="I302" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E302,Foderstater!$U$63:$U$100,0),MATCH(A302&amp;C302&amp;D302,Foderstater!$X$62:$AI$62,0))</f>
-        <v>2.929408071401712E-2</v>
-      </c>
-    </row>
-    <row r="303" spans="1:11" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="303" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>2</v>
       </c>
       <c r="E303" t="str">
-        <f>Foderstater!U$96</f>
-        <v>sugar beet pulp</v>
+        <f>Foderstater!U$98</f>
+        <v>potatoe protein</v>
       </c>
       <c r="H303" t="s">
         <v>326</v>
       </c>
       <c r="I303" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E303,Foderstater!$U$63:$U$100,0),MATCH(A303&amp;C303&amp;D303,Foderstater!$X$62:$AI$62,0))</f>
-        <v>5.6525245770502136E-2</v>
-      </c>
-    </row>
-    <row r="304" spans="1:11" x14ac:dyDescent="0.25">
+        <v>2.5878708291312121E-4</v>
+      </c>
+    </row>
+    <row r="304" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>2</v>
       </c>
       <c r="E304" t="str">
-        <f>Foderstater!U$97</f>
-        <v>whey powder</v>
+        <f>Foderstater!U$99</f>
+        <v>fish meal</v>
       </c>
       <c r="H304" t="s">
         <v>326</v>
@@ -23650,84 +23682,94 @@
         <v>2</v>
       </c>
       <c r="E305" t="str">
-        <f>Foderstater!U$98</f>
-        <v>potatoe protein</v>
+        <f>Foderstater!U$100</f>
+        <v>minerals</v>
       </c>
       <c r="H305" t="s">
         <v>326</v>
       </c>
       <c r="I305" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E305,Foderstater!$U$63:$U$100,0),MATCH(A305&amp;C305&amp;D305,Foderstater!$X$62:$AI$62,0))</f>
-        <v>2.5878708291312121E-4</v>
-      </c>
-    </row>
-    <row r="306" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A306" t="s">
+        <v>0.72908796527420217</v>
+      </c>
+    </row>
+    <row r="307" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A307" s="81" t="s">
+        <v>86</v>
+      </c>
+      <c r="B307" s="48"/>
+      <c r="C307" s="48"/>
+      <c r="D307" s="49"/>
+      <c r="E307" s="49"/>
+      <c r="F307" s="49"/>
+      <c r="G307" s="49"/>
+      <c r="H307" s="49"/>
+      <c r="I307" s="162"/>
+      <c r="J307" s="49"/>
+      <c r="K307" s="49"/>
+      <c r="L307" s="49"/>
+    </row>
+    <row r="308" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A308" s="159" t="s">
         <v>2</v>
       </c>
-      <c r="E306" t="str">
-        <f>Foderstater!U$99</f>
-        <v>fish meal</v>
-      </c>
-      <c r="H306" t="s">
+      <c r="B308" s="159"/>
+      <c r="C308" s="159"/>
+      <c r="D308" s="159" t="s">
+        <v>35</v>
+      </c>
+      <c r="H308" s="159" t="s">
         <v>326</v>
       </c>
-      <c r="I306" s="13">
-        <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E306,Foderstater!$U$63:$U$100,0),MATCH(A306&amp;C306&amp;D306,Foderstater!$X$62:$AI$62,0))</f>
+      <c r="I308" s="159">
         <v>0</v>
       </c>
-    </row>
-    <row r="307" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A307" t="s">
+      <c r="J308" s="159"/>
+      <c r="K308" s="159" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="309" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A309" t="s">
         <v>2</v>
       </c>
-      <c r="E307" t="str">
-        <f>Foderstater!U$100</f>
-        <v>minerals</v>
-      </c>
-      <c r="H307" t="s">
+      <c r="D309" s="110" t="s">
+        <v>35</v>
+      </c>
+      <c r="E309" t="str">
+        <f>Foderstater!U$63</f>
+        <v>ley silage, 1st cut</v>
+      </c>
+      <c r="H309" t="s">
         <v>326</v>
       </c>
-      <c r="I307" s="13">
-        <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E307,Foderstater!$U$63:$U$100,0),MATCH(A307&amp;C307&amp;D307,Foderstater!$X$62:$AI$62,0))</f>
-        <v>0.72908796527420217</v>
-      </c>
-    </row>
-    <row r="309" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A309" s="81" t="s">
-        <v>86</v>
-      </c>
-      <c r="B309" s="48"/>
-      <c r="C309" s="48"/>
-      <c r="D309" s="49"/>
-      <c r="E309" s="49"/>
-      <c r="F309" s="49"/>
-      <c r="G309" s="49"/>
-      <c r="H309" s="49"/>
-      <c r="I309" s="162"/>
-      <c r="J309" s="49"/>
-      <c r="K309" s="49"/>
-      <c r="L309" s="49"/>
+      <c r="I309" s="13">
+        <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E309,Foderstater!$U$63:$U$100,0),MATCH(A309&amp;C309&amp;D309,Foderstater!$X$62:$AI$62,0))</f>
+        <v>65.065884609325579</v>
+      </c>
+      <c r="J309" s="159"/>
+      <c r="K309" s="159"/>
     </row>
     <row r="310" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A310" s="159" t="s">
+      <c r="A310" t="s">
         <v>2</v>
       </c>
-      <c r="B310" s="159"/>
-      <c r="C310" s="159"/>
-      <c r="D310" s="159" t="s">
+      <c r="D310" s="110" t="s">
         <v>35</v>
       </c>
-      <c r="H310" s="159" t="s">
+      <c r="E310" t="str">
+        <f>Foderstater!U$64</f>
+        <v>ley silage, regrowth</v>
+      </c>
+      <c r="H310" t="s">
         <v>326</v>
       </c>
-      <c r="I310" s="159">
+      <c r="I310" s="13">
+        <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E310,Foderstater!$U$63:$U$100,0),MATCH(A310&amp;C310&amp;D310,Foderstater!$X$62:$AI$62,0))</f>
         <v>0</v>
       </c>
       <c r="J310" s="159"/>
-      <c r="K310" s="159" t="s">
-        <v>424</v>
-      </c>
+      <c r="K310" s="159"/>
     </row>
     <row r="311" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
@@ -23737,15 +23779,15 @@
         <v>35</v>
       </c>
       <c r="E311" t="str">
-        <f>Foderstater!U$63</f>
-        <v>ley silage, 1st cut</v>
+        <f>Foderstater!U$65</f>
+        <v>other silage</v>
       </c>
       <c r="H311" t="s">
         <v>326</v>
       </c>
       <c r="I311" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E311,Foderstater!$U$63:$U$100,0),MATCH(A311&amp;C311&amp;D311,Foderstater!$X$62:$AI$62,0))</f>
-        <v>65.065884609325579</v>
+        <v>0</v>
       </c>
       <c r="J311" s="159"/>
       <c r="K311" s="159"/>
@@ -23758,8 +23800,8 @@
         <v>35</v>
       </c>
       <c r="E312" t="str">
-        <f>Foderstater!U$64</f>
-        <v>ley silage, regrowth</v>
+        <f>Foderstater!U$66</f>
+        <v>maize silage</v>
       </c>
       <c r="H312" t="s">
         <v>326</v>
@@ -23779,8 +23821,8 @@
         <v>35</v>
       </c>
       <c r="E313" t="str">
-        <f>Foderstater!U$65</f>
-        <v>other silage</v>
+        <f>Foderstater!U$67</f>
+        <v>straw</v>
       </c>
       <c r="H313" t="s">
         <v>326</v>
@@ -23800,8 +23842,8 @@
         <v>35</v>
       </c>
       <c r="E314" t="str">
-        <f>Foderstater!U$66</f>
-        <v>maize silage</v>
+        <f>Foderstater!U$68</f>
+        <v>grazing</v>
       </c>
       <c r="H314" t="s">
         <v>326</v>
@@ -23821,15 +23863,15 @@
         <v>35</v>
       </c>
       <c r="E315" t="str">
-        <f>Foderstater!U$67</f>
-        <v>straw</v>
+        <f>Foderstater!U$69</f>
+        <v>wheat</v>
       </c>
       <c r="H315" t="s">
         <v>326</v>
       </c>
       <c r="I315" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E315,Foderstater!$U$63:$U$100,0),MATCH(A315&amp;C315&amp;D315,Foderstater!$X$62:$AI$62,0))</f>
-        <v>0</v>
+        <v>7.597272449205918</v>
       </c>
       <c r="J315" s="159"/>
       <c r="K315" s="159"/>
@@ -23842,15 +23884,15 @@
         <v>35</v>
       </c>
       <c r="E316" t="str">
-        <f>Foderstater!U$68</f>
-        <v>grazing</v>
+        <f>Foderstater!U$70</f>
+        <v>barley</v>
       </c>
       <c r="H316" t="s">
         <v>326</v>
       </c>
       <c r="I316" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E316,Foderstater!$U$63:$U$100,0),MATCH(A316&amp;C316&amp;D316,Foderstater!$X$62:$AI$62,0))</f>
-        <v>0</v>
+        <v>13.591338970365666</v>
       </c>
       <c r="J316" s="159"/>
       <c r="K316" s="159"/>
@@ -23863,15 +23905,15 @@
         <v>35</v>
       </c>
       <c r="E317" t="str">
-        <f>Foderstater!U$69</f>
-        <v>wheat</v>
+        <f>Foderstater!U$71</f>
+        <v>oats</v>
       </c>
       <c r="H317" t="s">
         <v>326</v>
       </c>
       <c r="I317" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E317,Foderstater!$U$63:$U$100,0),MATCH(A317&amp;C317&amp;D317,Foderstater!$X$62:$AI$62,0))</f>
-        <v>7.597272449205918</v>
+        <v>3.1053519716836115</v>
       </c>
       <c r="J317" s="159"/>
       <c r="K317" s="159"/>
@@ -23884,15 +23926,15 @@
         <v>35</v>
       </c>
       <c r="E318" t="str">
-        <f>Foderstater!U$70</f>
-        <v>barley</v>
+        <f>Foderstater!U$72</f>
+        <v>triticale</v>
       </c>
       <c r="H318" t="s">
         <v>326</v>
       </c>
       <c r="I318" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E318,Foderstater!$U$63:$U$100,0),MATCH(A318&amp;C318&amp;D318,Foderstater!$X$62:$AI$62,0))</f>
-        <v>13.591338970365666</v>
+        <v>4.6592010515149394</v>
       </c>
       <c r="J318" s="159"/>
       <c r="K318" s="159"/>
@@ -23905,15 +23947,15 @@
         <v>35</v>
       </c>
       <c r="E319" t="str">
-        <f>Foderstater!U$71</f>
-        <v>oats</v>
+        <f>Foderstater!U$73</f>
+        <v>rye</v>
       </c>
       <c r="H319" t="s">
         <v>326</v>
       </c>
       <c r="I319" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E319,Foderstater!$U$63:$U$100,0),MATCH(A319&amp;C319&amp;D319,Foderstater!$X$62:$AI$62,0))</f>
-        <v>3.1053519716836115</v>
+        <v>1.6945393347994473E-2</v>
       </c>
       <c r="J319" s="159"/>
       <c r="K319" s="159"/>
@@ -23926,15 +23968,15 @@
         <v>35</v>
       </c>
       <c r="E320" t="str">
-        <f>Foderstater!U$72</f>
-        <v>triticale</v>
+        <f>Foderstater!U$74</f>
+        <v>maize</v>
       </c>
       <c r="H320" t="s">
         <v>326</v>
       </c>
       <c r="I320" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E320,Foderstater!$U$63:$U$100,0),MATCH(A320&amp;C320&amp;D320,Foderstater!$X$62:$AI$62,0))</f>
-        <v>4.6592010515149394</v>
+        <v>7.3621265603978081E-2</v>
       </c>
       <c r="J320" s="159"/>
       <c r="K320" s="159"/>
@@ -23947,15 +23989,15 @@
         <v>35</v>
       </c>
       <c r="E321" t="str">
-        <f>Foderstater!U$73</f>
-        <v>rye</v>
+        <f>Foderstater!U$75</f>
+        <v>peas</v>
       </c>
       <c r="H321" t="s">
         <v>326</v>
       </c>
       <c r="I321" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E321,Foderstater!$U$63:$U$100,0),MATCH(A321&amp;C321&amp;D321,Foderstater!$X$62:$AI$62,0))</f>
-        <v>1.6945393347994473E-2</v>
+        <v>1.3794797059070938</v>
       </c>
       <c r="J321" s="159"/>
       <c r="K321" s="159"/>
@@ -23968,15 +24010,15 @@
         <v>35</v>
       </c>
       <c r="E322" t="str">
-        <f>Foderstater!U$74</f>
-        <v>maize</v>
+        <f>Foderstater!U$76</f>
+        <v>broad beans</v>
       </c>
       <c r="H322" t="s">
         <v>326</v>
       </c>
       <c r="I322" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E322,Foderstater!$U$63:$U$100,0),MATCH(A322&amp;C322&amp;D322,Foderstater!$X$62:$AI$62,0))</f>
-        <v>7.3621265603978081E-2</v>
+        <v>1.338045660068792</v>
       </c>
       <c r="J322" s="159"/>
       <c r="K322" s="159"/>
@@ -23989,15 +24031,15 @@
         <v>35</v>
       </c>
       <c r="E323" t="str">
-        <f>Foderstater!U$75</f>
-        <v>peas</v>
+        <f>Foderstater!U$77</f>
+        <v>rapeseed</v>
       </c>
       <c r="H323" t="s">
         <v>326</v>
       </c>
       <c r="I323" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E323,Foderstater!$U$63:$U$100,0),MATCH(A323&amp;C323&amp;D323,Foderstater!$X$62:$AI$62,0))</f>
-        <v>1.3794797059070938</v>
+        <v>0.62589622193442496</v>
       </c>
       <c r="J323" s="159"/>
       <c r="K323" s="159"/>
@@ -24010,15 +24052,15 @@
         <v>35</v>
       </c>
       <c r="E324" t="str">
-        <f>Foderstater!U$76</f>
-        <v>broad beans</v>
+        <f>Foderstater!U$78</f>
+        <v>linseed</v>
       </c>
       <c r="H324" t="s">
         <v>326</v>
       </c>
       <c r="I324" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E324,Foderstater!$U$63:$U$100,0),MATCH(A324&amp;C324&amp;D324,Foderstater!$X$62:$AI$62,0))</f>
-        <v>1.338045660068792</v>
+        <v>4.6169784916729557E-4</v>
       </c>
       <c r="J324" s="159"/>
       <c r="K324" s="159"/>
@@ -24031,15 +24073,15 @@
         <v>35</v>
       </c>
       <c r="E325" t="str">
-        <f>Foderstater!U$77</f>
-        <v>rapeseed</v>
+        <f>Foderstater!U$79</f>
+        <v>vegetable oils</v>
       </c>
       <c r="H325" t="s">
         <v>326</v>
       </c>
       <c r="I325" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E325,Foderstater!$U$63:$U$100,0),MATCH(A325&amp;C325&amp;D325,Foderstater!$X$62:$AI$62,0))</f>
-        <v>0.62589622193442496</v>
+        <v>1.1919625156141098E-2</v>
       </c>
       <c r="J325" s="159"/>
       <c r="K325" s="159"/>
@@ -24052,15 +24094,15 @@
         <v>35</v>
       </c>
       <c r="E326" t="str">
-        <f>Foderstater!U$78</f>
-        <v>linseed</v>
+        <f>Foderstater!U$80</f>
+        <v>soybeans</v>
       </c>
       <c r="H326" t="s">
         <v>326</v>
       </c>
       <c r="I326" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E326,Foderstater!$U$63:$U$100,0),MATCH(A326&amp;C326&amp;D326,Foderstater!$X$62:$AI$62,0))</f>
-        <v>4.6169784916729557E-4</v>
+        <v>1.1648220822436621E-2</v>
       </c>
       <c r="J326" s="159"/>
       <c r="K326" s="159"/>
@@ -24073,15 +24115,15 @@
         <v>35</v>
       </c>
       <c r="E327" t="str">
-        <f>Foderstater!U$79</f>
-        <v>vegetable oils</v>
+        <f>Foderstater!U$81</f>
+        <v>soybean meal</v>
       </c>
       <c r="H327" t="s">
         <v>326</v>
       </c>
       <c r="I327" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E327,Foderstater!$U$63:$U$100,0),MATCH(A327&amp;C327&amp;D327,Foderstater!$X$62:$AI$62,0))</f>
-        <v>1.1919625156141098E-2</v>
+        <v>0.10640217529505162</v>
       </c>
       <c r="J327" s="159"/>
       <c r="K327" s="159"/>
@@ -24094,15 +24136,15 @@
         <v>35</v>
       </c>
       <c r="E328" t="str">
-        <f>Foderstater!U$80</f>
-        <v>soybeans</v>
+        <f>Foderstater!U$82</f>
+        <v>soybean protein concentrate</v>
       </c>
       <c r="H328" t="s">
         <v>326</v>
       </c>
       <c r="I328" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E328,Foderstater!$U$63:$U$100,0),MATCH(A328&amp;C328&amp;D328,Foderstater!$X$62:$AI$62,0))</f>
-        <v>1.1648220822436621E-2</v>
+        <v>0</v>
       </c>
       <c r="J328" s="159"/>
       <c r="K328" s="159"/>
@@ -24115,15 +24157,15 @@
         <v>35</v>
       </c>
       <c r="E329" t="str">
-        <f>Foderstater!U$81</f>
-        <v>soybean meal</v>
+        <f>Foderstater!U$83</f>
+        <v>rapeseed meal</v>
       </c>
       <c r="H329" t="s">
         <v>326</v>
       </c>
       <c r="I329" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E329,Foderstater!$U$63:$U$100,0),MATCH(A329&amp;C329&amp;D329,Foderstater!$X$62:$AI$62,0))</f>
-        <v>0.10640217529505162</v>
+        <v>0.82181132264384626</v>
       </c>
       <c r="J329" s="159"/>
       <c r="K329" s="159"/>
@@ -24136,18 +24178,16 @@
         <v>35</v>
       </c>
       <c r="E330" t="str">
-        <f>Foderstater!U$82</f>
-        <v>soybean protein concentrate</v>
+        <f>Foderstater!U$84</f>
+        <v>sunflower seed meal</v>
       </c>
       <c r="H330" t="s">
         <v>326</v>
       </c>
       <c r="I330" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E330,Foderstater!$U$63:$U$100,0),MATCH(A330&amp;C330&amp;D330,Foderstater!$X$62:$AI$62,0))</f>
-        <v>0</v>
-      </c>
-      <c r="J330" s="159"/>
-      <c r="K330" s="159"/>
+        <v>1.1352527964985915E-2</v>
+      </c>
     </row>
     <row r="331" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
@@ -24157,18 +24197,16 @@
         <v>35</v>
       </c>
       <c r="E331" t="str">
-        <f>Foderstater!U$83</f>
-        <v>rapeseed meal</v>
+        <f>Foderstater!U$85</f>
+        <v>palm kernel expeller</v>
       </c>
       <c r="H331" t="s">
         <v>326</v>
       </c>
       <c r="I331" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E331,Foderstater!$U$63:$U$100,0),MATCH(A331&amp;C331&amp;D331,Foderstater!$X$62:$AI$62,0))</f>
-        <v>0.82181132264384626</v>
-      </c>
-      <c r="J331" s="159"/>
-      <c r="K331" s="159"/>
+        <v>7.3767808934127849E-2</v>
+      </c>
     </row>
     <row r="332" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
@@ -24178,15 +24216,15 @@
         <v>35</v>
       </c>
       <c r="E332" t="str">
-        <f>Foderstater!U$84</f>
-        <v>sunflower seed meal</v>
+        <f>Foderstater!U$86</f>
+        <v>luzern meal</v>
       </c>
       <c r="H332" t="s">
         <v>326</v>
       </c>
       <c r="I332" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E332,Foderstater!$U$63:$U$100,0),MATCH(A332&amp;C332&amp;D332,Foderstater!$X$62:$AI$62,0))</f>
-        <v>1.1352527964985915E-2</v>
+        <v>2.2439357471687103E-2</v>
       </c>
     </row>
     <row r="333" spans="1:11" x14ac:dyDescent="0.25">
@@ -24197,15 +24235,15 @@
         <v>35</v>
       </c>
       <c r="E333" t="str">
-        <f>Foderstater!U$85</f>
-        <v>palm kernel expeller</v>
+        <f>Foderstater!U$87</f>
+        <v>wheat bran</v>
       </c>
       <c r="H333" t="s">
         <v>326</v>
       </c>
       <c r="I333" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E333,Foderstater!$U$63:$U$100,0),MATCH(A333&amp;C333&amp;D333,Foderstater!$X$62:$AI$62,0))</f>
-        <v>7.3767808934127849E-2</v>
+        <v>0.24447981374416825</v>
       </c>
     </row>
     <row r="334" spans="1:11" x14ac:dyDescent="0.25">
@@ -24216,15 +24254,15 @@
         <v>35</v>
       </c>
       <c r="E334" t="str">
-        <f>Foderstater!U$86</f>
-        <v>luzern meal</v>
+        <f>Foderstater!U$88</f>
+        <v>wheat bran, fine</v>
       </c>
       <c r="H334" t="s">
         <v>326</v>
       </c>
       <c r="I334" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E334,Foderstater!$U$63:$U$100,0),MATCH(A334&amp;C334&amp;D334,Foderstater!$X$62:$AI$62,0))</f>
-        <v>2.2439357471687103E-2</v>
+        <v>6.4088803948898038E-4</v>
       </c>
     </row>
     <row r="335" spans="1:11" x14ac:dyDescent="0.25">
@@ -24235,15 +24273,15 @@
         <v>35</v>
       </c>
       <c r="E335" t="str">
-        <f>Foderstater!U$87</f>
-        <v>wheat bran</v>
+        <f>Foderstater!U$89</f>
+        <v>oat hulls</v>
       </c>
       <c r="H335" t="s">
         <v>326</v>
       </c>
       <c r="I335" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E335,Foderstater!$U$63:$U$100,0),MATCH(A335&amp;C335&amp;D335,Foderstater!$X$62:$AI$62,0))</f>
-        <v>0.24447981374416825</v>
+        <v>2.9445216367475335E-2</v>
       </c>
     </row>
     <row r="336" spans="1:11" x14ac:dyDescent="0.25">
@@ -24254,15 +24292,15 @@
         <v>35</v>
       </c>
       <c r="E336" t="str">
-        <f>Foderstater!U$88</f>
-        <v>wheat bran, fine</v>
+        <f>Foderstater!U$90</f>
+        <v>oat bran</v>
       </c>
       <c r="H336" t="s">
         <v>326</v>
       </c>
       <c r="I336" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E336,Foderstater!$U$63:$U$100,0),MATCH(A336&amp;C336&amp;D336,Foderstater!$X$62:$AI$62,0))</f>
-        <v>6.4088803948898038E-4</v>
+        <v>3.3232252147418258E-3</v>
       </c>
     </row>
     <row r="337" spans="1:11" x14ac:dyDescent="0.25">
@@ -24273,15 +24311,15 @@
         <v>35</v>
       </c>
       <c r="E337" t="str">
-        <f>Foderstater!U$89</f>
-        <v>oat hulls</v>
+        <f>Foderstater!U$91</f>
+        <v>rye bran</v>
       </c>
       <c r="H337" t="s">
         <v>326</v>
       </c>
       <c r="I337" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E337,Foderstater!$U$63:$U$100,0),MATCH(A337&amp;C337&amp;D337,Foderstater!$X$62:$AI$62,0))</f>
-        <v>2.9445216367475335E-2</v>
+        <v>1.0248862586385358E-2</v>
       </c>
     </row>
     <row r="338" spans="1:11" x14ac:dyDescent="0.25">
@@ -24292,15 +24330,15 @@
         <v>35</v>
       </c>
       <c r="E338" t="str">
-        <f>Foderstater!U$90</f>
-        <v>oat bran</v>
+        <f>Foderstater!U$92</f>
+        <v>wheat distillers grain, dry</v>
       </c>
       <c r="H338" t="s">
         <v>326</v>
       </c>
       <c r="I338" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E338,Foderstater!$U$63:$U$100,0),MATCH(A338&amp;C338&amp;D338,Foderstater!$X$62:$AI$62,0))</f>
-        <v>3.3232252147418258E-3</v>
+        <v>0.2627925741632976</v>
       </c>
     </row>
     <row r="339" spans="1:11" x14ac:dyDescent="0.25">
@@ -24311,15 +24349,15 @@
         <v>35</v>
       </c>
       <c r="E339" t="str">
-        <f>Foderstater!U$91</f>
-        <v>rye bran</v>
+        <f>Foderstater!U$93</f>
+        <v>barley brewers grain</v>
       </c>
       <c r="H339" t="s">
         <v>326</v>
       </c>
       <c r="I339" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E339,Foderstater!$U$63:$U$100,0),MATCH(A339&amp;C339&amp;D339,Foderstater!$X$62:$AI$62,0))</f>
-        <v>1.0248862586385358E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="340" spans="1:11" x14ac:dyDescent="0.25">
@@ -24330,15 +24368,15 @@
         <v>35</v>
       </c>
       <c r="E340" t="str">
-        <f>Foderstater!U$92</f>
-        <v>wheat distillers grain, dry</v>
+        <f>Foderstater!U$94</f>
+        <v>maize gluten meal</v>
       </c>
       <c r="H340" t="s">
         <v>326</v>
       </c>
       <c r="I340" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E340,Foderstater!$U$63:$U$100,0),MATCH(A340&amp;C340&amp;D340,Foderstater!$X$62:$AI$62,0))</f>
-        <v>0.2627925741632976</v>
+        <v>7.940766583314298E-3</v>
       </c>
     </row>
     <row r="341" spans="1:11" x14ac:dyDescent="0.25">
@@ -24349,15 +24387,15 @@
         <v>35</v>
       </c>
       <c r="E341" t="str">
-        <f>Foderstater!U$93</f>
-        <v>barley brewers grain</v>
+        <f>Foderstater!U$95</f>
+        <v>sugar beet molasses</v>
       </c>
       <c r="H341" t="s">
         <v>326</v>
       </c>
       <c r="I341" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E341,Foderstater!$U$63:$U$100,0),MATCH(A341&amp;C341&amp;D341,Foderstater!$X$62:$AI$62,0))</f>
-        <v>0</v>
+        <v>8.8058285727207697E-2</v>
       </c>
     </row>
     <row r="342" spans="1:11" x14ac:dyDescent="0.25">
@@ -24368,15 +24406,15 @@
         <v>35</v>
       </c>
       <c r="E342" t="str">
-        <f>Foderstater!U$94</f>
-        <v>maize gluten meal</v>
+        <f>Foderstater!U$96</f>
+        <v>sugar beet pulp</v>
       </c>
       <c r="H342" t="s">
         <v>326</v>
       </c>
       <c r="I342" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E342,Foderstater!$U$63:$U$100,0),MATCH(A342&amp;C342&amp;D342,Foderstater!$X$62:$AI$62,0))</f>
-        <v>7.940766583314298E-3</v>
+        <v>0.16991542733333806</v>
       </c>
     </row>
     <row r="343" spans="1:11" x14ac:dyDescent="0.25">
@@ -24387,15 +24425,15 @@
         <v>35</v>
       </c>
       <c r="E343" t="str">
-        <f>Foderstater!U$95</f>
-        <v>sugar beet molasses</v>
+        <f>Foderstater!U$97</f>
+        <v>whey powder</v>
       </c>
       <c r="H343" t="s">
         <v>326</v>
       </c>
       <c r="I343" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E343,Foderstater!$U$63:$U$100,0),MATCH(A343&amp;C343&amp;D343,Foderstater!$X$62:$AI$62,0))</f>
-        <v>8.8058285727207697E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="344" spans="1:11" x14ac:dyDescent="0.25">
@@ -24406,15 +24444,15 @@
         <v>35</v>
       </c>
       <c r="E344" t="str">
-        <f>Foderstater!U$96</f>
-        <v>sugar beet pulp</v>
+        <f>Foderstater!U$98</f>
+        <v>potatoe protein</v>
       </c>
       <c r="H344" t="s">
         <v>326</v>
       </c>
       <c r="I344" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E344,Foderstater!$U$63:$U$100,0),MATCH(A344&amp;C344&amp;D344,Foderstater!$X$62:$AI$62,0))</f>
-        <v>0.16991542733333806</v>
+        <v>7.7791643684418715E-4</v>
       </c>
     </row>
     <row r="345" spans="1:11" x14ac:dyDescent="0.25">
@@ -24425,8 +24463,8 @@
         <v>35</v>
       </c>
       <c r="E345" t="str">
-        <f>Foderstater!U$97</f>
-        <v>whey powder</v>
+        <f>Foderstater!U$99</f>
+        <v>fish meal</v>
       </c>
       <c r="H345" t="s">
         <v>326</v>
@@ -24444,88 +24482,104 @@
         <v>35</v>
       </c>
       <c r="E346" t="str">
-        <f>Foderstater!U$98</f>
-        <v>potatoe protein</v>
+        <f>Foderstater!U$100</f>
+        <v>minerals</v>
       </c>
       <c r="H346" t="s">
         <v>326</v>
       </c>
       <c r="I346" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E346,Foderstater!$U$63:$U$100,0),MATCH(A346&amp;C346&amp;D346,Foderstater!$X$62:$AI$62,0))</f>
-        <v>7.7791643684418715E-4</v>
+        <v>0.66953698870828937</v>
       </c>
     </row>
     <row r="347" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A347" t="s">
+      <c r="A347" s="159"/>
+      <c r="B347" s="159"/>
+      <c r="C347" s="159"/>
+      <c r="D347" s="159"/>
+      <c r="H347" s="159"/>
+      <c r="I347" s="159"/>
+      <c r="J347" s="159"/>
+      <c r="K347" s="159"/>
+    </row>
+    <row r="348" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A348" s="159" t="s">
         <v>2</v>
       </c>
-      <c r="D347" s="110" t="s">
+      <c r="B348" s="159" t="s">
+        <v>1</v>
+      </c>
+      <c r="C348" s="159" t="s">
+        <v>430</v>
+      </c>
+      <c r="D348" s="159" t="s">
         <v>35</v>
       </c>
-      <c r="E347" t="str">
-        <f>Foderstater!U$99</f>
-        <v>fish meal</v>
-      </c>
-      <c r="H347" t="s">
+      <c r="H348" s="159" t="s">
         <v>326</v>
       </c>
-      <c r="I347" s="13">
-        <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E347,Foderstater!$U$63:$U$100,0),MATCH(A347&amp;C347&amp;D347,Foderstater!$X$62:$AI$62,0))</f>
+      <c r="I348" s="159">
         <v>0</v>
       </c>
-    </row>
-    <row r="348" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A348" t="s">
+      <c r="J348" s="159"/>
+      <c r="K348" s="159" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="349" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A349" t="s">
         <v>2</v>
       </c>
-      <c r="D348" s="110" t="s">
+      <c r="B349" t="s">
+        <v>1</v>
+      </c>
+      <c r="C349" t="s">
+        <v>430</v>
+      </c>
+      <c r="D349" s="110" t="s">
         <v>35</v>
       </c>
-      <c r="E348" t="str">
-        <f>Foderstater!U$100</f>
-        <v>minerals</v>
-      </c>
-      <c r="H348" t="s">
+      <c r="E349" t="str">
+        <f>Foderstater!U$63</f>
+        <v>ley silage, 1st cut</v>
+      </c>
+      <c r="H349" t="s">
         <v>326</v>
       </c>
-      <c r="I348" s="13">
-        <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E348,Foderstater!$U$63:$U$100,0),MATCH(A348&amp;C348&amp;D348,Foderstater!$X$62:$AI$62,0))</f>
-        <v>0.66953698870828937</v>
-      </c>
-    </row>
-    <row r="349" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A349" s="159"/>
-      <c r="B349" s="159"/>
-      <c r="C349" s="159"/>
-      <c r="D349" s="159"/>
-      <c r="H349" s="159"/>
-      <c r="I349" s="159"/>
+      <c r="I349" s="13">
+        <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E349,Foderstater!$U$63:$U$100,0),MATCH(A349&amp;C349&amp;D349,Foderstater!$X$62:$AI$62,0))</f>
+        <v>56.668911580722877</v>
+      </c>
       <c r="J349" s="159"/>
       <c r="K349" s="159"/>
     </row>
     <row r="350" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A350" s="159" t="s">
+      <c r="A350" t="s">
         <v>2</v>
       </c>
-      <c r="B350" s="159" t="s">
+      <c r="B350" t="s">
         <v>1</v>
       </c>
-      <c r="C350" s="159" t="s">
+      <c r="C350" t="s">
         <v>430</v>
       </c>
-      <c r="D350" s="159" t="s">
+      <c r="D350" s="110" t="s">
         <v>35</v>
       </c>
-      <c r="H350" s="159" t="s">
+      <c r="E350" t="str">
+        <f>Foderstater!U$64</f>
+        <v>ley silage, regrowth</v>
+      </c>
+      <c r="H350" t="s">
         <v>326</v>
       </c>
-      <c r="I350" s="159">
+      <c r="I350" s="13">
+        <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E350,Foderstater!$U$63:$U$100,0),MATCH(A350&amp;C350&amp;D350,Foderstater!$X$62:$AI$62,0))</f>
         <v>0</v>
       </c>
       <c r="J350" s="159"/>
-      <c r="K350" s="159" t="s">
-        <v>424</v>
-      </c>
+      <c r="K350" s="159"/>
     </row>
     <row r="351" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
@@ -24541,15 +24595,15 @@
         <v>35</v>
       </c>
       <c r="E351" t="str">
-        <f>Foderstater!U$63</f>
-        <v>ley silage, 1st cut</v>
+        <f>Foderstater!U$65</f>
+        <v>other silage</v>
       </c>
       <c r="H351" t="s">
         <v>326</v>
       </c>
       <c r="I351" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E351,Foderstater!$U$63:$U$100,0),MATCH(A351&amp;C351&amp;D351,Foderstater!$X$62:$AI$62,0))</f>
-        <v>56.668911580722877</v>
+        <v>0</v>
       </c>
       <c r="J351" s="159"/>
       <c r="K351" s="159"/>
@@ -24568,15 +24622,15 @@
         <v>35</v>
       </c>
       <c r="E352" t="str">
-        <f>Foderstater!U$64</f>
-        <v>ley silage, regrowth</v>
+        <f>Foderstater!U$66</f>
+        <v>maize silage</v>
       </c>
       <c r="H352" t="s">
         <v>326</v>
       </c>
       <c r="I352" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E352,Foderstater!$U$63:$U$100,0),MATCH(A352&amp;C352&amp;D352,Foderstater!$X$62:$AI$62,0))</f>
-        <v>0</v>
+        <v>13.226790925693349</v>
       </c>
       <c r="J352" s="159"/>
       <c r="K352" s="159"/>
@@ -24595,8 +24649,8 @@
         <v>35</v>
       </c>
       <c r="E353" t="str">
-        <f>Foderstater!U$65</f>
-        <v>other silage</v>
+        <f>Foderstater!U$67</f>
+        <v>straw</v>
       </c>
       <c r="H353" t="s">
         <v>326</v>
@@ -24622,15 +24676,15 @@
         <v>35</v>
       </c>
       <c r="E354" t="str">
-        <f>Foderstater!U$66</f>
-        <v>maize silage</v>
+        <f>Foderstater!U$68</f>
+        <v>grazing</v>
       </c>
       <c r="H354" t="s">
         <v>326</v>
       </c>
       <c r="I354" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E354,Foderstater!$U$63:$U$100,0),MATCH(A354&amp;C354&amp;D354,Foderstater!$X$62:$AI$62,0))</f>
-        <v>13.226790925693349</v>
+        <v>0</v>
       </c>
       <c r="J354" s="159"/>
       <c r="K354" s="159"/>
@@ -24649,15 +24703,15 @@
         <v>35</v>
       </c>
       <c r="E355" t="str">
-        <f>Foderstater!U$67</f>
-        <v>straw</v>
+        <f>Foderstater!U$69</f>
+        <v>wheat</v>
       </c>
       <c r="H355" t="s">
         <v>326</v>
       </c>
       <c r="I355" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E355,Foderstater!$U$63:$U$100,0),MATCH(A355&amp;C355&amp;D355,Foderstater!$X$62:$AI$62,0))</f>
-        <v>0</v>
+        <v>6.3615760162052783</v>
       </c>
       <c r="J355" s="159"/>
       <c r="K355" s="159"/>
@@ -24676,15 +24730,15 @@
         <v>35</v>
       </c>
       <c r="E356" t="str">
-        <f>Foderstater!U$68</f>
-        <v>grazing</v>
+        <f>Foderstater!U$70</f>
+        <v>barley</v>
       </c>
       <c r="H356" t="s">
         <v>326</v>
       </c>
       <c r="I356" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E356,Foderstater!$U$63:$U$100,0),MATCH(A356&amp;C356&amp;D356,Foderstater!$X$62:$AI$62,0))</f>
-        <v>0</v>
+        <v>12.896189928777954</v>
       </c>
       <c r="J356" s="159"/>
       <c r="K356" s="159"/>
@@ -24703,15 +24757,15 @@
         <v>35</v>
       </c>
       <c r="E357" t="str">
-        <f>Foderstater!U$69</f>
-        <v>wheat</v>
+        <f>Foderstater!U$71</f>
+        <v>oats</v>
       </c>
       <c r="H357" t="s">
         <v>326</v>
       </c>
       <c r="I357" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E357,Foderstater!$U$63:$U$100,0),MATCH(A357&amp;C357&amp;D357,Foderstater!$X$62:$AI$62,0))</f>
-        <v>6.3615760162052783</v>
+        <v>2.68903535703005</v>
       </c>
       <c r="J357" s="159"/>
       <c r="K357" s="159"/>
@@ -24730,15 +24784,15 @@
         <v>35</v>
       </c>
       <c r="E358" t="str">
-        <f>Foderstater!U$70</f>
-        <v>barley</v>
+        <f>Foderstater!U$72</f>
+        <v>triticale</v>
       </c>
       <c r="H358" t="s">
         <v>326</v>
       </c>
       <c r="I358" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E358,Foderstater!$U$63:$U$100,0),MATCH(A358&amp;C358&amp;D358,Foderstater!$X$62:$AI$62,0))</f>
-        <v>12.896189928777954</v>
+        <v>4.9410321920692617</v>
       </c>
       <c r="J358" s="159"/>
       <c r="K358" s="159"/>
@@ -24757,15 +24811,15 @@
         <v>35</v>
       </c>
       <c r="E359" t="str">
-        <f>Foderstater!U$71</f>
-        <v>oats</v>
+        <f>Foderstater!U$73</f>
+        <v>rye</v>
       </c>
       <c r="H359" t="s">
         <v>326</v>
       </c>
       <c r="I359" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E359,Foderstater!$U$63:$U$100,0),MATCH(A359&amp;C359&amp;D359,Foderstater!$X$62:$AI$62,0))</f>
-        <v>2.68903535703005</v>
+        <v>1.3668084713412143E-3</v>
       </c>
       <c r="J359" s="159"/>
       <c r="K359" s="159"/>
@@ -24784,15 +24838,15 @@
         <v>35</v>
       </c>
       <c r="E360" t="str">
-        <f>Foderstater!U$72</f>
-        <v>triticale</v>
+        <f>Foderstater!U$74</f>
+        <v>maize</v>
       </c>
       <c r="H360" t="s">
         <v>326</v>
       </c>
       <c r="I360" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E360,Foderstater!$U$63:$U$100,0),MATCH(A360&amp;C360&amp;D360,Foderstater!$X$62:$AI$62,0))</f>
-        <v>4.9410321920692617</v>
+        <v>4.8255588786707375E-2</v>
       </c>
       <c r="J360" s="159"/>
       <c r="K360" s="159"/>
@@ -24811,15 +24865,15 @@
         <v>35</v>
       </c>
       <c r="E361" t="str">
-        <f>Foderstater!U$73</f>
-        <v>rye</v>
+        <f>Foderstater!U$75</f>
+        <v>peas</v>
       </c>
       <c r="H361" t="s">
         <v>326</v>
       </c>
       <c r="I361" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E361,Foderstater!$U$63:$U$100,0),MATCH(A361&amp;C361&amp;D361,Foderstater!$X$62:$AI$62,0))</f>
-        <v>1.3668084713412143E-3</v>
+        <v>0.43086866195785822</v>
       </c>
       <c r="J361" s="159"/>
       <c r="K361" s="159"/>
@@ -24838,15 +24892,15 @@
         <v>35</v>
       </c>
       <c r="E362" t="str">
-        <f>Foderstater!U$74</f>
-        <v>maize</v>
+        <f>Foderstater!U$76</f>
+        <v>broad beans</v>
       </c>
       <c r="H362" t="s">
         <v>326</v>
       </c>
       <c r="I362" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E362,Foderstater!$U$63:$U$100,0),MATCH(A362&amp;C362&amp;D362,Foderstater!$X$62:$AI$62,0))</f>
-        <v>4.8255588786707375E-2</v>
+        <v>0.42774566708132739</v>
       </c>
       <c r="J362" s="159"/>
       <c r="K362" s="159"/>
@@ -24865,15 +24919,15 @@
         <v>35</v>
       </c>
       <c r="E363" t="str">
-        <f>Foderstater!U$75</f>
-        <v>peas</v>
+        <f>Foderstater!U$77</f>
+        <v>rapeseed</v>
       </c>
       <c r="H363" t="s">
         <v>326</v>
       </c>
       <c r="I363" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E363,Foderstater!$U$63:$U$100,0),MATCH(A363&amp;C363&amp;D363,Foderstater!$X$62:$AI$62,0))</f>
-        <v>0.43086866195785822</v>
+        <v>0.41024818659446338</v>
       </c>
       <c r="J363" s="159"/>
       <c r="K363" s="159"/>
@@ -24892,15 +24946,15 @@
         <v>35</v>
       </c>
       <c r="E364" t="str">
-        <f>Foderstater!U$76</f>
-        <v>broad beans</v>
+        <f>Foderstater!U$78</f>
+        <v>linseed</v>
       </c>
       <c r="H364" t="s">
         <v>326</v>
       </c>
       <c r="I364" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E364,Foderstater!$U$63:$U$100,0),MATCH(A364&amp;C364&amp;D364,Foderstater!$X$62:$AI$62,0))</f>
-        <v>0.42774566708132739</v>
+        <v>3.0262318054907772E-4</v>
       </c>
       <c r="J364" s="159"/>
       <c r="K364" s="159"/>
@@ -24919,15 +24973,15 @@
         <v>35</v>
       </c>
       <c r="E365" t="str">
-        <f>Foderstater!U$77</f>
-        <v>rapeseed</v>
+        <f>Foderstater!U$79</f>
+        <v>vegetable oils</v>
       </c>
       <c r="H365" t="s">
         <v>326</v>
       </c>
       <c r="I365" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E365,Foderstater!$U$63:$U$100,0),MATCH(A365&amp;C365&amp;D365,Foderstater!$X$62:$AI$62,0))</f>
-        <v>0.41024818659446338</v>
+        <v>7.8128041579790201E-3</v>
       </c>
       <c r="J365" s="159"/>
       <c r="K365" s="159"/>
@@ -24946,15 +25000,15 @@
         <v>35</v>
       </c>
       <c r="E366" t="str">
-        <f>Foderstater!U$78</f>
-        <v>linseed</v>
+        <f>Foderstater!U$80</f>
+        <v>soybeans</v>
       </c>
       <c r="H366" t="s">
         <v>326</v>
       </c>
       <c r="I366" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E366,Foderstater!$U$63:$U$100,0),MATCH(A366&amp;C366&amp;D366,Foderstater!$X$62:$AI$62,0))</f>
-        <v>3.0262318054907772E-4</v>
+        <v>7.6349102327017302E-3</v>
       </c>
       <c r="J366" s="159"/>
       <c r="K366" s="159"/>
@@ -24973,15 +25027,15 @@
         <v>35</v>
       </c>
       <c r="E367" t="str">
-        <f>Foderstater!U$79</f>
-        <v>vegetable oils</v>
+        <f>Foderstater!U$81</f>
+        <v>soybean meal</v>
       </c>
       <c r="H367" t="s">
         <v>326</v>
       </c>
       <c r="I367" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E367,Foderstater!$U$63:$U$100,0),MATCH(A367&amp;C367&amp;D367,Foderstater!$X$62:$AI$62,0))</f>
-        <v>7.8128041579790201E-3</v>
+        <v>6.9742072143510206E-2</v>
       </c>
       <c r="J367" s="159"/>
       <c r="K367" s="159"/>
@@ -25000,15 +25054,15 @@
         <v>35</v>
       </c>
       <c r="E368" t="str">
-        <f>Foderstater!U$80</f>
-        <v>soybeans</v>
+        <f>Foderstater!U$82</f>
+        <v>soybean protein concentrate</v>
       </c>
       <c r="H368" t="s">
         <v>326</v>
       </c>
       <c r="I368" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E368,Foderstater!$U$63:$U$100,0),MATCH(A368&amp;C368&amp;D368,Foderstater!$X$62:$AI$62,0))</f>
-        <v>7.6349102327017302E-3</v>
+        <v>0</v>
       </c>
       <c r="J368" s="159"/>
       <c r="K368" s="159"/>
@@ -25027,15 +25081,15 @@
         <v>35</v>
       </c>
       <c r="E369" t="str">
-        <f>Foderstater!U$81</f>
-        <v>soybean meal</v>
+        <f>Foderstater!U$83</f>
+        <v>rapeseed meal</v>
       </c>
       <c r="H369" t="s">
         <v>326</v>
       </c>
       <c r="I369" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E369,Foderstater!$U$63:$U$100,0),MATCH(A369&amp;C369&amp;D369,Foderstater!$X$62:$AI$62,0))</f>
-        <v>6.9742072143510206E-2</v>
+        <v>0.53866215040479692</v>
       </c>
       <c r="J369" s="159"/>
       <c r="K369" s="159"/>
@@ -25054,18 +25108,16 @@
         <v>35</v>
       </c>
       <c r="E370" t="str">
-        <f>Foderstater!U$82</f>
-        <v>soybean protein concentrate</v>
+        <f>Foderstater!U$84</f>
+        <v>sunflower seed meal</v>
       </c>
       <c r="H370" t="s">
         <v>326</v>
       </c>
       <c r="I370" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E370,Foderstater!$U$63:$U$100,0),MATCH(A370&amp;C370&amp;D370,Foderstater!$X$62:$AI$62,0))</f>
-        <v>0</v>
-      </c>
-      <c r="J370" s="159"/>
-      <c r="K370" s="159"/>
+        <v>7.441096219600373E-3</v>
+      </c>
     </row>
     <row r="371" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
@@ -25081,18 +25133,16 @@
         <v>35</v>
       </c>
       <c r="E371" t="str">
-        <f>Foderstater!U$83</f>
-        <v>rapeseed meal</v>
+        <f>Foderstater!U$85</f>
+        <v>palm kernel expeller</v>
       </c>
       <c r="H371" t="s">
         <v>326</v>
       </c>
       <c r="I371" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E371,Foderstater!$U$63:$U$100,0),MATCH(A371&amp;C371&amp;D371,Foderstater!$X$62:$AI$62,0))</f>
-        <v>0.53866215040479692</v>
-      </c>
-      <c r="J371" s="159"/>
-      <c r="K371" s="159"/>
+        <v>4.8351641667911303E-2</v>
+      </c>
     </row>
     <row r="372" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
@@ -25108,15 +25158,15 @@
         <v>35</v>
       </c>
       <c r="E372" t="str">
-        <f>Foderstater!U$84</f>
-        <v>sunflower seed meal</v>
+        <f>Foderstater!U$86</f>
+        <v>luzern meal</v>
       </c>
       <c r="H372" t="s">
         <v>326</v>
       </c>
       <c r="I372" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E372,Foderstater!$U$63:$U$100,0),MATCH(A372&amp;C372&amp;D372,Foderstater!$X$62:$AI$62,0))</f>
-        <v>7.441096219600373E-3</v>
+        <v>1.4708038471063079E-2</v>
       </c>
     </row>
     <row r="373" spans="1:11" x14ac:dyDescent="0.25">
@@ -25133,15 +25183,15 @@
         <v>35</v>
       </c>
       <c r="E373" t="str">
-        <f>Foderstater!U$85</f>
-        <v>palm kernel expeller</v>
+        <f>Foderstater!U$87</f>
+        <v>wheat bran</v>
       </c>
       <c r="H373" t="s">
         <v>326</v>
       </c>
       <c r="I373" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E373,Foderstater!$U$63:$U$100,0),MATCH(A373&amp;C373&amp;D373,Foderstater!$X$62:$AI$62,0))</f>
-        <v>4.8351641667911303E-2</v>
+        <v>0.16024605474932127</v>
       </c>
     </row>
     <row r="374" spans="1:11" x14ac:dyDescent="0.25">
@@ -25158,15 +25208,15 @@
         <v>35</v>
       </c>
       <c r="E374" t="str">
-        <f>Foderstater!U$86</f>
-        <v>luzern meal</v>
+        <f>Foderstater!U$88</f>
+        <v>wheat bran, fine</v>
       </c>
       <c r="H374" t="s">
         <v>326</v>
       </c>
       <c r="I374" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E374,Foderstater!$U$63:$U$100,0),MATCH(A374&amp;C374&amp;D374,Foderstater!$X$62:$AI$62,0))</f>
-        <v>1.4708038471063079E-2</v>
+        <v>4.2007468138700703E-4</v>
       </c>
     </row>
     <row r="375" spans="1:11" x14ac:dyDescent="0.25">
@@ -25183,15 +25233,15 @@
         <v>35</v>
       </c>
       <c r="E375" t="str">
-        <f>Foderstater!U$87</f>
-        <v>wheat bran</v>
+        <f>Foderstater!U$89</f>
+        <v>oat hulls</v>
       </c>
       <c r="H375" t="s">
         <v>326</v>
       </c>
       <c r="I375" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E375,Foderstater!$U$63:$U$100,0),MATCH(A375&amp;C375&amp;D375,Foderstater!$X$62:$AI$62,0))</f>
-        <v>0.16024605474932127</v>
+        <v>1.9300079142998843E-2</v>
       </c>
     </row>
     <row r="376" spans="1:11" x14ac:dyDescent="0.25">
@@ -25208,15 +25258,15 @@
         <v>35</v>
       </c>
       <c r="E376" t="str">
-        <f>Foderstater!U$88</f>
-        <v>wheat bran, fine</v>
+        <f>Foderstater!U$90</f>
+        <v>oat bran</v>
       </c>
       <c r="H376" t="s">
         <v>326</v>
       </c>
       <c r="I376" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E376,Foderstater!$U$63:$U$100,0),MATCH(A376&amp;C376&amp;D376,Foderstater!$X$62:$AI$62,0))</f>
-        <v>4.2007468138700703E-4</v>
+        <v>2.178231902054312E-3</v>
       </c>
     </row>
     <row r="377" spans="1:11" x14ac:dyDescent="0.25">
@@ -25233,15 +25283,15 @@
         <v>35</v>
       </c>
       <c r="E377" t="str">
-        <f>Foderstater!U$89</f>
-        <v>oat hulls</v>
+        <f>Foderstater!U$91</f>
+        <v>rye bran</v>
       </c>
       <c r="H377" t="s">
         <v>326</v>
       </c>
       <c r="I377" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E377,Foderstater!$U$63:$U$100,0),MATCH(A377&amp;C377&amp;D377,Foderstater!$X$62:$AI$62,0))</f>
-        <v>1.9300079142998843E-2</v>
+        <v>6.7176907982054394E-3</v>
       </c>
     </row>
     <row r="378" spans="1:11" x14ac:dyDescent="0.25">
@@ -25258,15 +25308,15 @@
         <v>35</v>
       </c>
       <c r="E378" t="str">
-        <f>Foderstater!U$90</f>
-        <v>oat bran</v>
+        <f>Foderstater!U$92</f>
+        <v>wheat distillers grain, dry</v>
       </c>
       <c r="H378" t="s">
         <v>326</v>
       </c>
       <c r="I378" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E378,Foderstater!$U$63:$U$100,0),MATCH(A378&amp;C378&amp;D378,Foderstater!$X$62:$AI$62,0))</f>
-        <v>2.178231902054312E-3</v>
+        <v>0.17224928546106344</v>
       </c>
     </row>
     <row r="379" spans="1:11" x14ac:dyDescent="0.25">
@@ -25283,15 +25333,15 @@
         <v>35</v>
       </c>
       <c r="E379" t="str">
-        <f>Foderstater!U$91</f>
-        <v>rye bran</v>
+        <f>Foderstater!U$93</f>
+        <v>barley brewers grain</v>
       </c>
       <c r="H379" t="s">
         <v>326</v>
       </c>
       <c r="I379" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E379,Foderstater!$U$63:$U$100,0),MATCH(A379&amp;C379&amp;D379,Foderstater!$X$62:$AI$62,0))</f>
-        <v>6.7176907982054394E-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="380" spans="1:11" x14ac:dyDescent="0.25">
@@ -25308,15 +25358,15 @@
         <v>35</v>
       </c>
       <c r="E380" t="str">
-        <f>Foderstater!U$92</f>
-        <v>wheat distillers grain, dry</v>
+        <f>Foderstater!U$94</f>
+        <v>maize gluten meal</v>
       </c>
       <c r="H380" t="s">
         <v>326</v>
       </c>
       <c r="I380" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E380,Foderstater!$U$63:$U$100,0),MATCH(A380&amp;C380&amp;D380,Foderstater!$X$62:$AI$62,0))</f>
-        <v>0.17224928546106344</v>
+        <v>5.2048326492629164E-3</v>
       </c>
     </row>
     <row r="381" spans="1:11" x14ac:dyDescent="0.25">
@@ -25333,15 +25383,15 @@
         <v>35</v>
       </c>
       <c r="E381" t="str">
-        <f>Foderstater!U$93</f>
-        <v>barley brewers grain</v>
+        <f>Foderstater!U$95</f>
+        <v>sugar beet molasses</v>
       </c>
       <c r="H381" t="s">
         <v>326</v>
       </c>
       <c r="I381" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E381,Foderstater!$U$63:$U$100,0),MATCH(A381&amp;C381&amp;D381,Foderstater!$X$62:$AI$62,0))</f>
-        <v>0</v>
+        <v>5.7718437607039867E-2</v>
       </c>
     </row>
     <row r="382" spans="1:11" x14ac:dyDescent="0.25">
@@ -25358,15 +25408,15 @@
         <v>35</v>
       </c>
       <c r="E382" t="str">
-        <f>Foderstater!U$94</f>
-        <v>maize gluten meal</v>
+        <f>Foderstater!U$96</f>
+        <v>sugar beet pulp</v>
       </c>
       <c r="H382" t="s">
         <v>326</v>
       </c>
       <c r="I382" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E382,Foderstater!$U$63:$U$100,0),MATCH(A382&amp;C382&amp;D382,Foderstater!$X$62:$AI$62,0))</f>
-        <v>5.2048326492629164E-3</v>
+        <v>0.11137229063707067</v>
       </c>
     </row>
     <row r="383" spans="1:11" x14ac:dyDescent="0.25">
@@ -25383,15 +25433,15 @@
         <v>35</v>
       </c>
       <c r="E383" t="str">
-        <f>Foderstater!U$95</f>
-        <v>sugar beet molasses</v>
+        <f>Foderstater!U$97</f>
+        <v>whey powder</v>
       </c>
       <c r="H383" t="s">
         <v>326</v>
       </c>
       <c r="I383" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E383,Foderstater!$U$63:$U$100,0),MATCH(A383&amp;C383&amp;D383,Foderstater!$X$62:$AI$62,0))</f>
-        <v>5.7718437607039867E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="384" spans="1:11" x14ac:dyDescent="0.25">
@@ -25408,15 +25458,15 @@
         <v>35</v>
       </c>
       <c r="E384" t="str">
-        <f>Foderstater!U$96</f>
-        <v>sugar beet pulp</v>
+        <f>Foderstater!U$98</f>
+        <v>potatoe protein</v>
       </c>
       <c r="H384" t="s">
         <v>326</v>
       </c>
       <c r="I384" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E384,Foderstater!$U$63:$U$100,0),MATCH(A384&amp;C384&amp;D384,Foderstater!$X$62:$AI$62,0))</f>
-        <v>0.11137229063707067</v>
+        <v>5.0989093136080688E-4</v>
       </c>
     </row>
     <row r="385" spans="1:12" x14ac:dyDescent="0.25">
@@ -25433,8 +25483,8 @@
         <v>35</v>
       </c>
       <c r="E385" t="str">
-        <f>Foderstater!U$97</f>
-        <v>whey powder</v>
+        <f>Foderstater!U$99</f>
+        <v>fish meal</v>
       </c>
       <c r="H385" t="s">
         <v>326</v>
@@ -25458,118 +25508,110 @@
         <v>35</v>
       </c>
       <c r="E386" t="str">
-        <f>Foderstater!U$98</f>
-        <v>potatoe protein</v>
+        <f>Foderstater!U$100</f>
+        <v>minerals</v>
       </c>
       <c r="H386" t="s">
         <v>326</v>
       </c>
       <c r="I386" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E386,Foderstater!$U$63:$U$100,0),MATCH(A386&amp;C386&amp;D386,Foderstater!$X$62:$AI$62,0))</f>
-        <v>5.0989093136080688E-4</v>
-      </c>
-    </row>
-    <row r="387" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A387" t="s">
-        <v>2</v>
-      </c>
-      <c r="B387" t="s">
-        <v>1</v>
-      </c>
-      <c r="C387" t="s">
-        <v>430</v>
-      </c>
-      <c r="D387" s="110" t="s">
-        <v>35</v>
-      </c>
-      <c r="E387" t="str">
-        <f>Foderstater!U$99</f>
-        <v>fish meal</v>
-      </c>
-      <c r="H387" t="s">
+        <v>0.66740688157168271</v>
+      </c>
+    </row>
+    <row r="388" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A388" s="100" t="s">
+        <v>304</v>
+      </c>
+      <c r="B388" s="100"/>
+      <c r="C388" s="100"/>
+      <c r="D388" s="101"/>
+      <c r="E388" s="101"/>
+      <c r="F388" s="101"/>
+      <c r="G388" s="101"/>
+      <c r="H388" s="101"/>
+      <c r="I388" s="101"/>
+      <c r="J388" s="101"/>
+      <c r="K388" s="101"/>
+      <c r="L388" s="101"/>
+    </row>
+    <row r="389" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A389" s="91" t="s">
+        <v>74</v>
+      </c>
+      <c r="B389" s="163"/>
+      <c r="C389" s="163"/>
+      <c r="D389" s="90"/>
+      <c r="E389" s="90"/>
+      <c r="F389" s="90"/>
+      <c r="G389" s="90"/>
+      <c r="H389" s="90"/>
+      <c r="I389" s="164"/>
+      <c r="J389" s="90"/>
+      <c r="K389" s="90"/>
+      <c r="L389" s="90"/>
+    </row>
+    <row r="390" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A390" s="159" t="s">
+        <v>38</v>
+      </c>
+      <c r="B390" s="159"/>
+      <c r="C390" s="159"/>
+      <c r="D390" s="159" t="s">
+        <v>18</v>
+      </c>
+      <c r="H390" s="159" t="s">
         <v>326</v>
       </c>
-      <c r="I387" s="13">
-        <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E387,Foderstater!$U$63:$U$100,0),MATCH(A387&amp;C387&amp;D387,Foderstater!$X$62:$AI$62,0))</f>
+      <c r="I390" s="159">
         <v>0</v>
       </c>
-    </row>
-    <row r="388" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A388" t="s">
-        <v>2</v>
-      </c>
-      <c r="B388" t="s">
-        <v>1</v>
-      </c>
-      <c r="C388" t="s">
-        <v>430</v>
-      </c>
-      <c r="D388" s="110" t="s">
-        <v>35</v>
-      </c>
-      <c r="E388" t="str">
-        <f>Foderstater!U$100</f>
-        <v>minerals</v>
-      </c>
-      <c r="H388" t="s">
+      <c r="J390" s="159"/>
+      <c r="K390" s="159" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="391" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A391" t="s">
+        <v>38</v>
+      </c>
+      <c r="D391" t="s">
+        <v>18</v>
+      </c>
+      <c r="E391" t="str">
+        <f>Foderstater!U$63</f>
+        <v>ley silage, 1st cut</v>
+      </c>
+      <c r="H391" t="s">
         <v>326</v>
       </c>
-      <c r="I388" s="13">
-        <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E388,Foderstater!$U$63:$U$100,0),MATCH(A388&amp;C388&amp;D388,Foderstater!$X$62:$AI$62,0))</f>
-        <v>0.66740688157168271</v>
-      </c>
-    </row>
-    <row r="390" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A390" s="100" t="s">
-        <v>304</v>
-      </c>
-      <c r="B390" s="100"/>
-      <c r="C390" s="100"/>
-      <c r="D390" s="101"/>
-      <c r="E390" s="101"/>
-      <c r="F390" s="101"/>
-      <c r="G390" s="101"/>
-      <c r="H390" s="101"/>
-      <c r="I390" s="101"/>
-      <c r="J390" s="101"/>
-      <c r="K390" s="101"/>
-      <c r="L390" s="101"/>
-    </row>
-    <row r="391" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A391" s="91" t="s">
-        <v>74</v>
-      </c>
-      <c r="B391" s="163"/>
-      <c r="C391" s="163"/>
-      <c r="D391" s="90"/>
-      <c r="E391" s="90"/>
-      <c r="F391" s="90"/>
-      <c r="G391" s="90"/>
-      <c r="H391" s="90"/>
-      <c r="I391" s="164"/>
-      <c r="J391" s="90"/>
-      <c r="K391" s="90"/>
-      <c r="L391" s="90"/>
+      <c r="I391" s="13">
+        <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E391,Foderstater!$U$63:$U$100,0),MATCH(A391&amp;C391&amp;D391,Foderstater!$X$62:$AI$62,0))</f>
+        <v>0</v>
+      </c>
+      <c r="J391" s="159"/>
+      <c r="K391" s="159"/>
     </row>
     <row r="392" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A392" s="159" t="s">
+      <c r="A392" t="s">
         <v>38</v>
       </c>
-      <c r="B392" s="159"/>
-      <c r="C392" s="159"/>
-      <c r="D392" s="159" t="s">
+      <c r="D392" t="s">
         <v>18</v>
       </c>
-      <c r="H392" s="159" t="s">
+      <c r="E392" t="str">
+        <f>Foderstater!U$64</f>
+        <v>ley silage, regrowth</v>
+      </c>
+      <c r="H392" t="s">
         <v>326</v>
       </c>
-      <c r="I392" s="159">
-        <v>0</v>
+      <c r="I392" s="13">
+        <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E392,Foderstater!$U$63:$U$100,0),MATCH(A392&amp;C392&amp;D392,Foderstater!$X$62:$AI$62,0))</f>
+        <v>19.638470390756044</v>
       </c>
       <c r="J392" s="159"/>
-      <c r="K392" s="159" t="s">
-        <v>424</v>
-      </c>
+      <c r="K392" s="159"/>
     </row>
     <row r="393" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
@@ -25579,15 +25621,15 @@
         <v>18</v>
       </c>
       <c r="E393" t="str">
-        <f>Foderstater!U$63</f>
-        <v>ley silage, 1st cut</v>
+        <f>Foderstater!U$65</f>
+        <v>other silage</v>
       </c>
       <c r="H393" t="s">
         <v>326</v>
       </c>
       <c r="I393" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E393,Foderstater!$U$63:$U$100,0),MATCH(A393&amp;C393&amp;D393,Foderstater!$X$62:$AI$62,0))</f>
-        <v>0</v>
+        <v>20.321711421281208</v>
       </c>
       <c r="J393" s="159"/>
       <c r="K393" s="159"/>
@@ -25600,15 +25642,15 @@
         <v>18</v>
       </c>
       <c r="E394" t="str">
-        <f>Foderstater!U$64</f>
-        <v>ley silage, regrowth</v>
+        <f>Foderstater!U$66</f>
+        <v>maize silage</v>
       </c>
       <c r="H394" t="s">
         <v>326</v>
       </c>
       <c r="I394" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E394,Foderstater!$U$63:$U$100,0),MATCH(A394&amp;C394&amp;D394,Foderstater!$X$62:$AI$62,0))</f>
-        <v>19.638470390756044</v>
+        <v>0</v>
       </c>
       <c r="J394" s="159"/>
       <c r="K394" s="159"/>
@@ -25621,15 +25663,15 @@
         <v>18</v>
       </c>
       <c r="E395" t="str">
-        <f>Foderstater!U$65</f>
-        <v>other silage</v>
+        <f>Foderstater!U$67</f>
+        <v>straw</v>
       </c>
       <c r="H395" t="s">
         <v>326</v>
       </c>
       <c r="I395" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E395,Foderstater!$U$63:$U$100,0),MATCH(A395&amp;C395&amp;D395,Foderstater!$X$62:$AI$62,0))</f>
-        <v>20.321711421281208</v>
+        <v>1.1297448457337229</v>
       </c>
       <c r="J395" s="159"/>
       <c r="K395" s="159"/>
@@ -25642,15 +25684,15 @@
         <v>18</v>
       </c>
       <c r="E396" t="str">
-        <f>Foderstater!U$66</f>
-        <v>maize silage</v>
+        <f>Foderstater!U$68</f>
+        <v>grazing</v>
       </c>
       <c r="H396" t="s">
         <v>326</v>
       </c>
       <c r="I396" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E396,Foderstater!$U$63:$U$100,0),MATCH(A396&amp;C396&amp;D396,Foderstater!$X$62:$AI$62,0))</f>
-        <v>0</v>
+        <v>58.050981669759572</v>
       </c>
       <c r="J396" s="159"/>
       <c r="K396" s="159"/>
@@ -25663,15 +25705,15 @@
         <v>18</v>
       </c>
       <c r="E397" t="str">
-        <f>Foderstater!U$67</f>
-        <v>straw</v>
+        <f>Foderstater!U$69</f>
+        <v>wheat</v>
       </c>
       <c r="H397" t="s">
         <v>326</v>
       </c>
       <c r="I397" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E397,Foderstater!$U$63:$U$100,0),MATCH(A397&amp;C397&amp;D397,Foderstater!$X$62:$AI$62,0))</f>
-        <v>1.1297448457337229</v>
+        <v>0</v>
       </c>
       <c r="J397" s="159"/>
       <c r="K397" s="159"/>
@@ -25684,15 +25726,15 @@
         <v>18</v>
       </c>
       <c r="E398" t="str">
-        <f>Foderstater!U$68</f>
-        <v>grazing</v>
+        <f>Foderstater!U$70</f>
+        <v>barley</v>
       </c>
       <c r="H398" t="s">
         <v>326</v>
       </c>
       <c r="I398" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E398,Foderstater!$U$63:$U$100,0),MATCH(A398&amp;C398&amp;D398,Foderstater!$X$62:$AI$62,0))</f>
-        <v>58.050981669759572</v>
+        <v>0</v>
       </c>
       <c r="J398" s="159"/>
       <c r="K398" s="159"/>
@@ -25705,8 +25747,8 @@
         <v>18</v>
       </c>
       <c r="E399" t="str">
-        <f>Foderstater!U$69</f>
-        <v>wheat</v>
+        <f>Foderstater!U$71</f>
+        <v>oats</v>
       </c>
       <c r="H399" t="s">
         <v>326</v>
@@ -25726,8 +25768,8 @@
         <v>18</v>
       </c>
       <c r="E400" t="str">
-        <f>Foderstater!U$70</f>
-        <v>barley</v>
+        <f>Foderstater!U$72</f>
+        <v>triticale</v>
       </c>
       <c r="H400" t="s">
         <v>326</v>
@@ -25747,8 +25789,8 @@
         <v>18</v>
       </c>
       <c r="E401" t="str">
-        <f>Foderstater!U$71</f>
-        <v>oats</v>
+        <f>Foderstater!U$73</f>
+        <v>rye</v>
       </c>
       <c r="H401" t="s">
         <v>326</v>
@@ -25768,8 +25810,8 @@
         <v>18</v>
       </c>
       <c r="E402" t="str">
-        <f>Foderstater!U$72</f>
-        <v>triticale</v>
+        <f>Foderstater!U$74</f>
+        <v>maize</v>
       </c>
       <c r="H402" t="s">
         <v>326</v>
@@ -25789,8 +25831,8 @@
         <v>18</v>
       </c>
       <c r="E403" t="str">
-        <f>Foderstater!U$73</f>
-        <v>rye</v>
+        <f>Foderstater!U$75</f>
+        <v>peas</v>
       </c>
       <c r="H403" t="s">
         <v>326</v>
@@ -25810,8 +25852,8 @@
         <v>18</v>
       </c>
       <c r="E404" t="str">
-        <f>Foderstater!U$74</f>
-        <v>maize</v>
+        <f>Foderstater!U$76</f>
+        <v>broad beans</v>
       </c>
       <c r="H404" t="s">
         <v>326</v>
@@ -25831,8 +25873,8 @@
         <v>18</v>
       </c>
       <c r="E405" t="str">
-        <f>Foderstater!U$75</f>
-        <v>peas</v>
+        <f>Foderstater!U$77</f>
+        <v>rapeseed</v>
       </c>
       <c r="H405" t="s">
         <v>326</v>
@@ -25852,8 +25894,8 @@
         <v>18</v>
       </c>
       <c r="E406" t="str">
-        <f>Foderstater!U$76</f>
-        <v>broad beans</v>
+        <f>Foderstater!U$78</f>
+        <v>linseed</v>
       </c>
       <c r="H406" t="s">
         <v>326</v>
@@ -25873,8 +25915,8 @@
         <v>18</v>
       </c>
       <c r="E407" t="str">
-        <f>Foderstater!U$77</f>
-        <v>rapeseed</v>
+        <f>Foderstater!U$79</f>
+        <v>vegetable oils</v>
       </c>
       <c r="H407" t="s">
         <v>326</v>
@@ -25894,8 +25936,8 @@
         <v>18</v>
       </c>
       <c r="E408" t="str">
-        <f>Foderstater!U$78</f>
-        <v>linseed</v>
+        <f>Foderstater!U$80</f>
+        <v>soybeans</v>
       </c>
       <c r="H408" t="s">
         <v>326</v>
@@ -25915,8 +25957,8 @@
         <v>18</v>
       </c>
       <c r="E409" t="str">
-        <f>Foderstater!U$79</f>
-        <v>vegetable oils</v>
+        <f>Foderstater!U$81</f>
+        <v>soybean meal</v>
       </c>
       <c r="H409" t="s">
         <v>326</v>
@@ -25936,8 +25978,8 @@
         <v>18</v>
       </c>
       <c r="E410" t="str">
-        <f>Foderstater!U$80</f>
-        <v>soybeans</v>
+        <f>Foderstater!U$82</f>
+        <v>soybean protein concentrate</v>
       </c>
       <c r="H410" t="s">
         <v>326</v>
@@ -25957,8 +25999,8 @@
         <v>18</v>
       </c>
       <c r="E411" t="str">
-        <f>Foderstater!U$81</f>
-        <v>soybean meal</v>
+        <f>Foderstater!U$83</f>
+        <v>rapeseed meal</v>
       </c>
       <c r="H411" t="s">
         <v>326</v>
@@ -25978,8 +26020,8 @@
         <v>18</v>
       </c>
       <c r="E412" t="str">
-        <f>Foderstater!U$82</f>
-        <v>soybean protein concentrate</v>
+        <f>Foderstater!U$84</f>
+        <v>sunflower seed meal</v>
       </c>
       <c r="H412" t="s">
         <v>326</v>
@@ -25988,8 +26030,6 @@
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E412,Foderstater!$U$63:$U$100,0),MATCH(A412&amp;C412&amp;D412,Foderstater!$X$62:$AI$62,0))</f>
         <v>0</v>
       </c>
-      <c r="J412" s="159"/>
-      <c r="K412" s="159"/>
     </row>
     <row r="413" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
@@ -25999,8 +26039,8 @@
         <v>18</v>
       </c>
       <c r="E413" t="str">
-        <f>Foderstater!U$83</f>
-        <v>rapeseed meal</v>
+        <f>Foderstater!U$85</f>
+        <v>palm kernel expeller</v>
       </c>
       <c r="H413" t="s">
         <v>326</v>
@@ -26009,8 +26049,6 @@
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E413,Foderstater!$U$63:$U$100,0),MATCH(A413&amp;C413&amp;D413,Foderstater!$X$62:$AI$62,0))</f>
         <v>0</v>
       </c>
-      <c r="J413" s="159"/>
-      <c r="K413" s="159"/>
     </row>
     <row r="414" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
@@ -26020,8 +26058,8 @@
         <v>18</v>
       </c>
       <c r="E414" t="str">
-        <f>Foderstater!U$84</f>
-        <v>sunflower seed meal</v>
+        <f>Foderstater!U$86</f>
+        <v>luzern meal</v>
       </c>
       <c r="H414" t="s">
         <v>326</v>
@@ -26039,8 +26077,8 @@
         <v>18</v>
       </c>
       <c r="E415" t="str">
-        <f>Foderstater!U$85</f>
-        <v>palm kernel expeller</v>
+        <f>Foderstater!U$87</f>
+        <v>wheat bran</v>
       </c>
       <c r="H415" t="s">
         <v>326</v>
@@ -26058,8 +26096,8 @@
         <v>18</v>
       </c>
       <c r="E416" t="str">
-        <f>Foderstater!U$86</f>
-        <v>luzern meal</v>
+        <f>Foderstater!U$88</f>
+        <v>wheat bran, fine</v>
       </c>
       <c r="H416" t="s">
         <v>326</v>
@@ -26077,8 +26115,8 @@
         <v>18</v>
       </c>
       <c r="E417" t="str">
-        <f>Foderstater!U$87</f>
-        <v>wheat bran</v>
+        <f>Foderstater!U$89</f>
+        <v>oat hulls</v>
       </c>
       <c r="H417" t="s">
         <v>326</v>
@@ -26096,8 +26134,8 @@
         <v>18</v>
       </c>
       <c r="E418" t="str">
-        <f>Foderstater!U$88</f>
-        <v>wheat bran, fine</v>
+        <f>Foderstater!U$90</f>
+        <v>oat bran</v>
       </c>
       <c r="H418" t="s">
         <v>326</v>
@@ -26115,8 +26153,8 @@
         <v>18</v>
       </c>
       <c r="E419" t="str">
-        <f>Foderstater!U$89</f>
-        <v>oat hulls</v>
+        <f>Foderstater!U$91</f>
+        <v>rye bran</v>
       </c>
       <c r="H419" t="s">
         <v>326</v>
@@ -26134,8 +26172,8 @@
         <v>18</v>
       </c>
       <c r="E420" t="str">
-        <f>Foderstater!U$90</f>
-        <v>oat bran</v>
+        <f>Foderstater!U$92</f>
+        <v>wheat distillers grain, dry</v>
       </c>
       <c r="H420" t="s">
         <v>326</v>
@@ -26153,8 +26191,8 @@
         <v>18</v>
       </c>
       <c r="E421" t="str">
-        <f>Foderstater!U$91</f>
-        <v>rye bran</v>
+        <f>Foderstater!U$93</f>
+        <v>barley brewers grain</v>
       </c>
       <c r="H421" t="s">
         <v>326</v>
@@ -26172,8 +26210,8 @@
         <v>18</v>
       </c>
       <c r="E422" t="str">
-        <f>Foderstater!U$92</f>
-        <v>wheat distillers grain, dry</v>
+        <f>Foderstater!U$94</f>
+        <v>maize gluten meal</v>
       </c>
       <c r="H422" t="s">
         <v>326</v>
@@ -26191,8 +26229,8 @@
         <v>18</v>
       </c>
       <c r="E423" t="str">
-        <f>Foderstater!U$93</f>
-        <v>barley brewers grain</v>
+        <f>Foderstater!U$95</f>
+        <v>sugar beet molasses</v>
       </c>
       <c r="H423" t="s">
         <v>326</v>
@@ -26210,8 +26248,8 @@
         <v>18</v>
       </c>
       <c r="E424" t="str">
-        <f>Foderstater!U$94</f>
-        <v>maize gluten meal</v>
+        <f>Foderstater!U$96</f>
+        <v>sugar beet pulp</v>
       </c>
       <c r="H424" t="s">
         <v>326</v>
@@ -26229,8 +26267,8 @@
         <v>18</v>
       </c>
       <c r="E425" t="str">
-        <f>Foderstater!U$95</f>
-        <v>sugar beet molasses</v>
+        <f>Foderstater!U$97</f>
+        <v>whey powder</v>
       </c>
       <c r="H425" t="s">
         <v>326</v>
@@ -26248,8 +26286,8 @@
         <v>18</v>
       </c>
       <c r="E426" t="str">
-        <f>Foderstater!U$96</f>
-        <v>sugar beet pulp</v>
+        <f>Foderstater!U$98</f>
+        <v>potatoe protein</v>
       </c>
       <c r="H426" t="s">
         <v>326</v>
@@ -26267,8 +26305,8 @@
         <v>18</v>
       </c>
       <c r="E427" t="str">
-        <f>Foderstater!U$97</f>
-        <v>whey powder</v>
+        <f>Foderstater!U$99</f>
+        <v>fish meal</v>
       </c>
       <c r="H427" t="s">
         <v>326</v>
@@ -26286,90 +26324,94 @@
         <v>18</v>
       </c>
       <c r="E428" t="str">
-        <f>Foderstater!U$98</f>
-        <v>potatoe protein</v>
+        <f>Foderstater!U$100</f>
+        <v>minerals</v>
       </c>
       <c r="H428" t="s">
         <v>326</v>
       </c>
       <c r="I428" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E428,Foderstater!$U$63:$U$100,0),MATCH(A428&amp;C428&amp;D428,Foderstater!$X$62:$AI$62,0))</f>
+        <v>0.85909167246946194</v>
+      </c>
+    </row>
+    <row r="430" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A430" s="91" t="s">
+        <v>445</v>
+      </c>
+      <c r="B430" s="163"/>
+      <c r="C430" s="163"/>
+      <c r="D430" s="90"/>
+      <c r="E430" s="90"/>
+      <c r="F430" s="90"/>
+      <c r="G430" s="90"/>
+      <c r="H430" s="90"/>
+      <c r="I430" s="164"/>
+      <c r="J430" s="90"/>
+      <c r="K430" s="90"/>
+      <c r="L430" s="90"/>
+    </row>
+    <row r="431" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A431" s="159" t="s">
+        <v>38</v>
+      </c>
+      <c r="B431" s="159"/>
+      <c r="C431" s="159"/>
+      <c r="D431" s="159" t="s">
+        <v>20</v>
+      </c>
+      <c r="H431" s="159" t="s">
+        <v>326</v>
+      </c>
+      <c r="I431" s="159">
         <v>0</v>
       </c>
-    </row>
-    <row r="429" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A429" t="s">
+      <c r="J431" s="159"/>
+      <c r="K431" s="159" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="432" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A432" t="s">
         <v>38</v>
       </c>
-      <c r="D429" t="s">
-        <v>18</v>
-      </c>
-      <c r="E429" t="str">
-        <f>Foderstater!U$99</f>
-        <v>fish meal</v>
-      </c>
-      <c r="H429" t="s">
+      <c r="D432" t="s">
+        <v>20</v>
+      </c>
+      <c r="E432" t="str">
+        <f>Foderstater!U$63</f>
+        <v>ley silage, 1st cut</v>
+      </c>
+      <c r="H432" t="s">
         <v>326</v>
       </c>
-      <c r="I429" s="13">
-        <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E429,Foderstater!$U$63:$U$100,0),MATCH(A429&amp;C429&amp;D429,Foderstater!$X$62:$AI$62,0))</f>
+      <c r="I432" s="13">
+        <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E432,Foderstater!$U$63:$U$100,0),MATCH(A432&amp;C432&amp;D432,Foderstater!$X$62:$AI$62,0))</f>
+        <v>55.38698659192309</v>
+      </c>
+      <c r="J432" s="159"/>
+      <c r="K432" s="159"/>
+    </row>
+    <row r="433" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A433" t="s">
+        <v>38</v>
+      </c>
+      <c r="D433" t="s">
+        <v>20</v>
+      </c>
+      <c r="E433" t="str">
+        <f>Foderstater!U$64</f>
+        <v>ley silage, regrowth</v>
+      </c>
+      <c r="H433" t="s">
+        <v>326</v>
+      </c>
+      <c r="I433" s="13">
+        <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E433,Foderstater!$U$63:$U$100,0),MATCH(A433&amp;C433&amp;D433,Foderstater!$X$62:$AI$62,0))</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="430" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A430" t="s">
-        <v>38</v>
-      </c>
-      <c r="D430" t="s">
-        <v>18</v>
-      </c>
-      <c r="E430" t="str">
-        <f>Foderstater!U$100</f>
-        <v>minerals</v>
-      </c>
-      <c r="H430" t="s">
-        <v>326</v>
-      </c>
-      <c r="I430" s="13">
-        <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E430,Foderstater!$U$63:$U$100,0),MATCH(A430&amp;C430&amp;D430,Foderstater!$X$62:$AI$62,0))</f>
-        <v>0.85909167246946194</v>
-      </c>
-    </row>
-    <row r="432" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A432" s="91" t="s">
-        <v>445</v>
-      </c>
-      <c r="B432" s="163"/>
-      <c r="C432" s="163"/>
-      <c r="D432" s="90"/>
-      <c r="E432" s="90"/>
-      <c r="F432" s="90"/>
-      <c r="G432" s="90"/>
-      <c r="H432" s="90"/>
-      <c r="I432" s="164"/>
-      <c r="J432" s="90"/>
-      <c r="K432" s="90"/>
-      <c r="L432" s="90"/>
-    </row>
-    <row r="433" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A433" s="159" t="s">
-        <v>38</v>
-      </c>
-      <c r="B433" s="159"/>
-      <c r="C433" s="159"/>
-      <c r="D433" s="159" t="s">
-        <v>20</v>
-      </c>
-      <c r="H433" s="159" t="s">
-        <v>326</v>
-      </c>
-      <c r="I433" s="159">
-        <v>0</v>
-      </c>
       <c r="J433" s="159"/>
-      <c r="K433" s="159" t="s">
-        <v>424</v>
-      </c>
+      <c r="K433" s="159"/>
     </row>
     <row r="434" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
@@ -26379,15 +26421,15 @@
         <v>20</v>
       </c>
       <c r="E434" t="str">
-        <f>Foderstater!U$63</f>
-        <v>ley silage, 1st cut</v>
+        <f>Foderstater!U$65</f>
+        <v>other silage</v>
       </c>
       <c r="H434" t="s">
         <v>326</v>
       </c>
       <c r="I434" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E434,Foderstater!$U$63:$U$100,0),MATCH(A434&amp;C434&amp;D434,Foderstater!$X$62:$AI$62,0))</f>
-        <v>55.38698659192309</v>
+        <v>0</v>
       </c>
       <c r="J434" s="159"/>
       <c r="K434" s="159"/>
@@ -26400,8 +26442,8 @@
         <v>20</v>
       </c>
       <c r="E435" t="str">
-        <f>Foderstater!U$64</f>
-        <v>ley silage, regrowth</v>
+        <f>Foderstater!U$66</f>
+        <v>maize silage</v>
       </c>
       <c r="H435" t="s">
         <v>326</v>
@@ -26421,8 +26463,8 @@
         <v>20</v>
       </c>
       <c r="E436" t="str">
-        <f>Foderstater!U$65</f>
-        <v>other silage</v>
+        <f>Foderstater!U$67</f>
+        <v>straw</v>
       </c>
       <c r="H436" t="s">
         <v>326</v>
@@ -26442,15 +26484,15 @@
         <v>20</v>
       </c>
       <c r="E437" t="str">
-        <f>Foderstater!U$66</f>
-        <v>maize silage</v>
+        <f>Foderstater!U$68</f>
+        <v>grazing</v>
       </c>
       <c r="H437" t="s">
         <v>326</v>
       </c>
       <c r="I437" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E437,Foderstater!$U$63:$U$100,0),MATCH(A437&amp;C437&amp;D437,Foderstater!$X$62:$AI$62,0))</f>
-        <v>0</v>
+        <v>21.161076246926353</v>
       </c>
       <c r="J437" s="159"/>
       <c r="K437" s="159"/>
@@ -26463,15 +26505,15 @@
         <v>20</v>
       </c>
       <c r="E438" t="str">
-        <f>Foderstater!U$67</f>
-        <v>straw</v>
+        <f>Foderstater!U$69</f>
+        <v>wheat</v>
       </c>
       <c r="H438" t="s">
         <v>326</v>
       </c>
       <c r="I438" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E438,Foderstater!$U$63:$U$100,0),MATCH(A438&amp;C438&amp;D438,Foderstater!$X$62:$AI$62,0))</f>
-        <v>0</v>
+        <v>5.3749925447045763</v>
       </c>
       <c r="J438" s="159"/>
       <c r="K438" s="159"/>
@@ -26484,15 +26526,15 @@
         <v>20</v>
       </c>
       <c r="E439" t="str">
-        <f>Foderstater!U$68</f>
-        <v>grazing</v>
+        <f>Foderstater!U$70</f>
+        <v>barley</v>
       </c>
       <c r="H439" t="s">
         <v>326</v>
       </c>
       <c r="I439" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E439,Foderstater!$U$63:$U$100,0),MATCH(A439&amp;C439&amp;D439,Foderstater!$X$62:$AI$62,0))</f>
-        <v>21.161076246926353</v>
+        <v>9.8776139053089249</v>
       </c>
       <c r="J439" s="159"/>
       <c r="K439" s="159"/>
@@ -26505,15 +26547,15 @@
         <v>20</v>
       </c>
       <c r="E440" t="str">
-        <f>Foderstater!U$69</f>
-        <v>wheat</v>
+        <f>Foderstater!U$71</f>
+        <v>oats</v>
       </c>
       <c r="H440" t="s">
         <v>326</v>
       </c>
       <c r="I440" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E440,Foderstater!$U$63:$U$100,0),MATCH(A440&amp;C440&amp;D440,Foderstater!$X$62:$AI$62,0))</f>
-        <v>5.3749925447045763</v>
+        <v>2.2123443310104149</v>
       </c>
       <c r="J440" s="159"/>
       <c r="K440" s="159"/>
@@ -26526,15 +26568,15 @@
         <v>20</v>
       </c>
       <c r="E441" t="str">
-        <f>Foderstater!U$70</f>
-        <v>barley</v>
+        <f>Foderstater!U$72</f>
+        <v>triticale</v>
       </c>
       <c r="H441" t="s">
         <v>326</v>
       </c>
       <c r="I441" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E441,Foderstater!$U$63:$U$100,0),MATCH(A441&amp;C441&amp;D441,Foderstater!$X$62:$AI$62,0))</f>
-        <v>9.8776139053089249</v>
+        <v>3.4759922520526634</v>
       </c>
       <c r="J441" s="159"/>
       <c r="K441" s="159"/>
@@ -26547,15 +26589,15 @@
         <v>20</v>
       </c>
       <c r="E442" t="str">
-        <f>Foderstater!U$71</f>
-        <v>oats</v>
+        <f>Foderstater!U$73</f>
+        <v>rye</v>
       </c>
       <c r="H442" t="s">
         <v>326</v>
       </c>
       <c r="I442" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E442,Foderstater!$U$63:$U$100,0),MATCH(A442&amp;C442&amp;D442,Foderstater!$X$62:$AI$62,0))</f>
-        <v>2.2123443310104149</v>
+        <v>9.7729344009567475E-3</v>
       </c>
       <c r="J442" s="159"/>
       <c r="K442" s="159"/>
@@ -26568,15 +26610,15 @@
         <v>20</v>
       </c>
       <c r="E443" t="str">
-        <f>Foderstater!U$72</f>
-        <v>triticale</v>
+        <f>Foderstater!U$74</f>
+        <v>maize</v>
       </c>
       <c r="H443" t="s">
         <v>326</v>
       </c>
       <c r="I443" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E443,Foderstater!$U$63:$U$100,0),MATCH(A443&amp;C443&amp;D443,Foderstater!$X$62:$AI$62,0))</f>
-        <v>3.4759922520526634</v>
+        <v>4.2459669391401007E-2</v>
       </c>
       <c r="J443" s="159"/>
       <c r="K443" s="159"/>
@@ -26589,15 +26631,15 @@
         <v>20</v>
       </c>
       <c r="E444" t="str">
-        <f>Foderstater!U$73</f>
-        <v>rye</v>
+        <f>Foderstater!U$75</f>
+        <v>peas</v>
       </c>
       <c r="H444" t="s">
         <v>326</v>
       </c>
       <c r="I444" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E444,Foderstater!$U$63:$U$100,0),MATCH(A444&amp;C444&amp;D444,Foderstater!$X$62:$AI$62,0))</f>
-        <v>9.7729344009567475E-3</v>
+        <v>0.18818835539063533</v>
       </c>
       <c r="J444" s="159"/>
       <c r="K444" s="159"/>
@@ -26610,15 +26652,15 @@
         <v>20</v>
       </c>
       <c r="E445" t="str">
-        <f>Foderstater!U$74</f>
-        <v>maize</v>
+        <f>Foderstater!U$76</f>
+        <v>broad beans</v>
       </c>
       <c r="H445" t="s">
         <v>326</v>
       </c>
       <c r="I445" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E445,Foderstater!$U$63:$U$100,0),MATCH(A445&amp;C445&amp;D445,Foderstater!$X$62:$AI$62,0))</f>
-        <v>4.2459669391401007E-2</v>
+        <v>0.19513584282773944</v>
       </c>
       <c r="J445" s="159"/>
       <c r="K445" s="159"/>
@@ -26631,15 +26673,15 @@
         <v>20</v>
       </c>
       <c r="E446" t="str">
-        <f>Foderstater!U$75</f>
-        <v>peas</v>
+        <f>Foderstater!U$77</f>
+        <v>rapeseed</v>
       </c>
       <c r="H446" t="s">
         <v>326</v>
       </c>
       <c r="I446" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E446,Foderstater!$U$63:$U$100,0),MATCH(A446&amp;C446&amp;D446,Foderstater!$X$62:$AI$62,0))</f>
-        <v>0.18818835539063533</v>
+        <v>0.36097378167357463</v>
       </c>
       <c r="J446" s="159"/>
       <c r="K446" s="159"/>
@@ -26652,15 +26694,15 @@
         <v>20</v>
       </c>
       <c r="E447" t="str">
-        <f>Foderstater!U$76</f>
-        <v>broad beans</v>
+        <f>Foderstater!U$78</f>
+        <v>linseed</v>
       </c>
       <c r="H447" t="s">
         <v>326</v>
       </c>
       <c r="I447" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E447,Foderstater!$U$63:$U$100,0),MATCH(A447&amp;C447&amp;D447,Foderstater!$X$62:$AI$62,0))</f>
-        <v>0.19513584282773944</v>
+        <v>2.6627548268207211E-4</v>
       </c>
       <c r="J447" s="159"/>
       <c r="K447" s="159"/>
@@ -26673,15 +26715,15 @@
         <v>20</v>
       </c>
       <c r="E448" t="str">
-        <f>Foderstater!U$77</f>
-        <v>rapeseed</v>
+        <f>Foderstater!U$79</f>
+        <v>vegetable oils</v>
       </c>
       <c r="H448" t="s">
         <v>326</v>
       </c>
       <c r="I448" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E448,Foderstater!$U$63:$U$100,0),MATCH(A448&amp;C448&amp;D448,Foderstater!$X$62:$AI$62,0))</f>
-        <v>0.36097378167357463</v>
+        <v>6.874417863468929E-3</v>
       </c>
       <c r="J448" s="159"/>
       <c r="K448" s="159"/>
@@ -26694,15 +26736,15 @@
         <v>20</v>
       </c>
       <c r="E449" t="str">
-        <f>Foderstater!U$78</f>
-        <v>linseed</v>
+        <f>Foderstater!U$80</f>
+        <v>soybeans</v>
       </c>
       <c r="H449" t="s">
         <v>326</v>
       </c>
       <c r="I449" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E449,Foderstater!$U$63:$U$100,0),MATCH(A449&amp;C449&amp;D449,Foderstater!$X$62:$AI$62,0))</f>
-        <v>2.6627548268207211E-4</v>
+        <v>6.7178905586753141E-3</v>
       </c>
       <c r="J449" s="159"/>
       <c r="K449" s="159"/>
@@ -26715,15 +26757,15 @@
         <v>20</v>
       </c>
       <c r="E450" t="str">
-        <f>Foderstater!U$79</f>
-        <v>vegetable oils</v>
+        <f>Foderstater!U$81</f>
+        <v>soybean meal</v>
       </c>
       <c r="H450" t="s">
         <v>326</v>
       </c>
       <c r="I450" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E450,Foderstater!$U$63:$U$100,0),MATCH(A450&amp;C450&amp;D450,Foderstater!$X$62:$AI$62,0))</f>
-        <v>6.874417863468929E-3</v>
+        <v>6.1365437669271355E-2</v>
       </c>
       <c r="J450" s="159"/>
       <c r="K450" s="159"/>
@@ -26736,15 +26778,15 @@
         <v>20</v>
       </c>
       <c r="E451" t="str">
-        <f>Foderstater!U$80</f>
-        <v>soybeans</v>
+        <f>Foderstater!U$82</f>
+        <v>soybean protein concentrate</v>
       </c>
       <c r="H451" t="s">
         <v>326</v>
       </c>
       <c r="I451" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E451,Foderstater!$U$63:$U$100,0),MATCH(A451&amp;C451&amp;D451,Foderstater!$X$62:$AI$62,0))</f>
-        <v>6.7178905586753141E-3</v>
+        <v>0</v>
       </c>
       <c r="J451" s="159"/>
       <c r="K451" s="159"/>
@@ -26757,15 +26799,15 @@
         <v>20</v>
       </c>
       <c r="E452" t="str">
-        <f>Foderstater!U$81</f>
-        <v>soybean meal</v>
+        <f>Foderstater!U$83</f>
+        <v>rapeseed meal</v>
       </c>
       <c r="H452" t="s">
         <v>326</v>
       </c>
       <c r="I452" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E452,Foderstater!$U$63:$U$100,0),MATCH(A452&amp;C452&amp;D452,Foderstater!$X$62:$AI$62,0))</f>
-        <v>6.1365437669271355E-2</v>
+        <v>0.47396410229169195</v>
       </c>
       <c r="J452" s="159"/>
       <c r="K452" s="159"/>
@@ -26778,18 +26820,16 @@
         <v>20</v>
       </c>
       <c r="E453" t="str">
-        <f>Foderstater!U$82</f>
-        <v>soybean protein concentrate</v>
+        <f>Foderstater!U$84</f>
+        <v>sunflower seed meal</v>
       </c>
       <c r="H453" t="s">
         <v>326</v>
       </c>
       <c r="I453" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E453,Foderstater!$U$63:$U$100,0),MATCH(A453&amp;C453&amp;D453,Foderstater!$X$62:$AI$62,0))</f>
-        <v>0</v>
-      </c>
-      <c r="J453" s="159"/>
-      <c r="K453" s="159"/>
+        <v>6.5473553082180435E-3</v>
+      </c>
     </row>
     <row r="454" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
@@ -26799,18 +26839,16 @@
         <v>20</v>
       </c>
       <c r="E454" t="str">
-        <f>Foderstater!U$83</f>
-        <v>rapeseed meal</v>
+        <f>Foderstater!U$85</f>
+        <v>palm kernel expeller</v>
       </c>
       <c r="H454" t="s">
         <v>326</v>
       </c>
       <c r="I454" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E454,Foderstater!$U$63:$U$100,0),MATCH(A454&amp;C454&amp;D454,Foderstater!$X$62:$AI$62,0))</f>
-        <v>0.47396410229169195</v>
-      </c>
-      <c r="J454" s="159"/>
-      <c r="K454" s="159"/>
+        <v>4.2544185479227364E-2</v>
+      </c>
     </row>
     <row r="455" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
@@ -26820,15 +26858,15 @@
         <v>20</v>
       </c>
       <c r="E455" t="str">
-        <f>Foderstater!U$84</f>
-        <v>sunflower seed meal</v>
+        <f>Foderstater!U$86</f>
+        <v>luzern meal</v>
       </c>
       <c r="H455" t="s">
         <v>326</v>
       </c>
       <c r="I455" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E455,Foderstater!$U$63:$U$100,0),MATCH(A455&amp;C455&amp;D455,Foderstater!$X$62:$AI$62,0))</f>
-        <v>6.5473553082180435E-3</v>
+        <v>1.2941474067131715E-2</v>
       </c>
     </row>
     <row r="456" spans="1:11" x14ac:dyDescent="0.25">
@@ -26839,15 +26877,15 @@
         <v>20</v>
       </c>
       <c r="E456" t="str">
-        <f>Foderstater!U$85</f>
-        <v>palm kernel expeller</v>
+        <f>Foderstater!U$87</f>
+        <v>wheat bran</v>
       </c>
       <c r="H456" t="s">
         <v>326</v>
       </c>
       <c r="I456" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E456,Foderstater!$U$63:$U$100,0),MATCH(A456&amp;C456&amp;D456,Foderstater!$X$62:$AI$62,0))</f>
-        <v>4.2544185479227364E-2</v>
+        <v>0.14099909828075238</v>
       </c>
     </row>
     <row r="457" spans="1:11" x14ac:dyDescent="0.25">
@@ -26858,15 +26896,15 @@
         <v>20</v>
       </c>
       <c r="E457" t="str">
-        <f>Foderstater!U$86</f>
-        <v>luzern meal</v>
+        <f>Foderstater!U$88</f>
+        <v>wheat bran, fine</v>
       </c>
       <c r="H457" t="s">
         <v>326</v>
       </c>
       <c r="I457" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E457,Foderstater!$U$63:$U$100,0),MATCH(A457&amp;C457&amp;D457,Foderstater!$X$62:$AI$62,0))</f>
-        <v>1.2941474067131715E-2</v>
+        <v>3.6962002826714343E-4</v>
       </c>
     </row>
     <row r="458" spans="1:11" x14ac:dyDescent="0.25">
@@ -26877,15 +26915,15 @@
         <v>20</v>
       </c>
       <c r="E458" t="str">
-        <f>Foderstater!U$87</f>
-        <v>wheat bran</v>
+        <f>Foderstater!U$89</f>
+        <v>oat hulls</v>
       </c>
       <c r="H458" t="s">
         <v>326</v>
       </c>
       <c r="I458" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E458,Foderstater!$U$63:$U$100,0),MATCH(A458&amp;C458&amp;D458,Foderstater!$X$62:$AI$62,0))</f>
-        <v>0.14099909828075238</v>
+        <v>1.698197038402606E-2</v>
       </c>
     </row>
     <row r="459" spans="1:11" x14ac:dyDescent="0.25">
@@ -26896,15 +26934,15 @@
         <v>20</v>
       </c>
       <c r="E459" t="str">
-        <f>Foderstater!U$88</f>
-        <v>wheat bran, fine</v>
+        <f>Foderstater!U$90</f>
+        <v>oat bran</v>
       </c>
       <c r="H459" t="s">
         <v>326</v>
       </c>
       <c r="I459" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E459,Foderstater!$U$63:$U$100,0),MATCH(A459&amp;C459&amp;D459,Foderstater!$X$62:$AI$62,0))</f>
-        <v>3.6962002826714343E-4</v>
+        <v>1.9166071484036143E-3</v>
       </c>
     </row>
     <row r="460" spans="1:11" x14ac:dyDescent="0.25">
@@ -26915,15 +26953,15 @@
         <v>20</v>
       </c>
       <c r="E460" t="str">
-        <f>Foderstater!U$89</f>
-        <v>oat hulls</v>
+        <f>Foderstater!U$91</f>
+        <v>rye bran</v>
       </c>
       <c r="H460" t="s">
         <v>326</v>
       </c>
       <c r="I460" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E460,Foderstater!$U$63:$U$100,0),MATCH(A460&amp;C460&amp;D460,Foderstater!$X$62:$AI$62,0))</f>
-        <v>1.698197038402606E-2</v>
+        <v>5.9108372219059966E-3</v>
       </c>
     </row>
     <row r="461" spans="1:11" x14ac:dyDescent="0.25">
@@ -26934,15 +26972,15 @@
         <v>20</v>
       </c>
       <c r="E461" t="str">
-        <f>Foderstater!U$90</f>
-        <v>oat bran</v>
+        <f>Foderstater!U$92</f>
+        <v>wheat distillers grain, dry</v>
       </c>
       <c r="H461" t="s">
         <v>326</v>
       </c>
       <c r="I461" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E461,Foderstater!$U$63:$U$100,0),MATCH(A461&amp;C461&amp;D461,Foderstater!$X$62:$AI$62,0))</f>
-        <v>1.9166071484036143E-3</v>
+        <v>0.15156063572052919</v>
       </c>
     </row>
     <row r="462" spans="1:11" x14ac:dyDescent="0.25">
@@ -26953,15 +26991,15 @@
         <v>20</v>
       </c>
       <c r="E462" t="str">
-        <f>Foderstater!U$91</f>
-        <v>rye bran</v>
+        <f>Foderstater!U$93</f>
+        <v>barley brewers grain</v>
       </c>
       <c r="H462" t="s">
         <v>326</v>
       </c>
       <c r="I462" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E462,Foderstater!$U$63:$U$100,0),MATCH(A462&amp;C462&amp;D462,Foderstater!$X$62:$AI$62,0))</f>
-        <v>5.9108372219059966E-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="463" spans="1:11" x14ac:dyDescent="0.25">
@@ -26972,15 +27010,15 @@
         <v>20</v>
       </c>
       <c r="E463" t="str">
-        <f>Foderstater!U$92</f>
-        <v>wheat distillers grain, dry</v>
+        <f>Foderstater!U$94</f>
+        <v>maize gluten meal</v>
       </c>
       <c r="H463" t="s">
         <v>326</v>
       </c>
       <c r="I463" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E463,Foderstater!$U$63:$U$100,0),MATCH(A463&amp;C463&amp;D463,Foderstater!$X$62:$AI$62,0))</f>
-        <v>0.15156063572052919</v>
+        <v>4.5796866038063828E-3</v>
       </c>
     </row>
     <row r="464" spans="1:11" x14ac:dyDescent="0.25">
@@ -26991,15 +27029,15 @@
         <v>20</v>
       </c>
       <c r="E464" t="str">
-        <f>Foderstater!U$93</f>
-        <v>barley brewers grain</v>
+        <f>Foderstater!U$95</f>
+        <v>sugar beet molasses</v>
       </c>
       <c r="H464" t="s">
         <v>326</v>
       </c>
       <c r="I464" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E464,Foderstater!$U$63:$U$100,0),MATCH(A464&amp;C464&amp;D464,Foderstater!$X$62:$AI$62,0))</f>
-        <v>0</v>
+        <v>5.078594708304953E-2</v>
       </c>
     </row>
     <row r="465" spans="1:12" x14ac:dyDescent="0.25">
@@ -27010,15 +27048,15 @@
         <v>20</v>
       </c>
       <c r="E465" t="str">
-        <f>Foderstater!U$94</f>
-        <v>maize gluten meal</v>
+        <f>Foderstater!U$96</f>
+        <v>sugar beet pulp</v>
       </c>
       <c r="H465" t="s">
         <v>326</v>
       </c>
       <c r="I465" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E465,Foderstater!$U$63:$U$100,0),MATCH(A465&amp;C465&amp;D465,Foderstater!$X$62:$AI$62,0))</f>
-        <v>4.5796866038063828E-3</v>
+        <v>9.7995501841553825E-2</v>
       </c>
     </row>
     <row r="466" spans="1:12" x14ac:dyDescent="0.25">
@@ -27029,15 +27067,15 @@
         <v>20</v>
       </c>
       <c r="E466" t="str">
-        <f>Foderstater!U$95</f>
-        <v>sugar beet molasses</v>
+        <f>Foderstater!U$97</f>
+        <v>whey powder</v>
       </c>
       <c r="H466" t="s">
         <v>326</v>
       </c>
       <c r="I466" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E466,Foderstater!$U$63:$U$100,0),MATCH(A466&amp;C466&amp;D466,Foderstater!$X$62:$AI$62,0))</f>
-        <v>5.078594708304953E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="467" spans="1:12" x14ac:dyDescent="0.25">
@@ -27048,15 +27086,15 @@
         <v>20</v>
       </c>
       <c r="E467" t="str">
-        <f>Foderstater!U$96</f>
-        <v>sugar beet pulp</v>
+        <f>Foderstater!U$98</f>
+        <v>potatoe protein</v>
       </c>
       <c r="H467" t="s">
         <v>326</v>
       </c>
       <c r="I467" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E467,Foderstater!$U$63:$U$100,0),MATCH(A467&amp;C467&amp;D467,Foderstater!$X$62:$AI$62,0))</f>
-        <v>9.7995501841553825E-2</v>
+        <v>4.4864855896685517E-4</v>
       </c>
     </row>
     <row r="468" spans="1:12" x14ac:dyDescent="0.25">
@@ -27067,8 +27105,8 @@
         <v>20</v>
       </c>
       <c r="E468" t="str">
-        <f>Foderstater!U$97</f>
-        <v>whey powder</v>
+        <f>Foderstater!U$99</f>
+        <v>fish meal</v>
       </c>
       <c r="H468" t="s">
         <v>326</v>
@@ -27086,96 +27124,94 @@
         <v>20</v>
       </c>
       <c r="E469" t="str">
-        <f>Foderstater!U$98</f>
-        <v>potatoe protein</v>
+        <f>Foderstater!U$100</f>
+        <v>minerals</v>
       </c>
       <c r="H469" t="s">
         <v>326</v>
       </c>
       <c r="I469" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E469,Foderstater!$U$63:$U$100,0),MATCH(A469&amp;C469&amp;D469,Foderstater!$X$62:$AI$62,0))</f>
-        <v>4.4864855896685517E-4</v>
-      </c>
-    </row>
-    <row r="470" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A470" t="s">
+        <v>0.6316938527980368</v>
+      </c>
+    </row>
+    <row r="471" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A471" s="91" t="s">
+        <v>445</v>
+      </c>
+      <c r="B471" s="163"/>
+      <c r="C471" s="163"/>
+      <c r="D471" s="90"/>
+      <c r="E471" s="90"/>
+      <c r="F471" s="90"/>
+      <c r="G471" s="90"/>
+      <c r="H471" s="90"/>
+      <c r="I471" s="164"/>
+      <c r="J471" s="90"/>
+      <c r="K471" s="90"/>
+      <c r="L471" s="90"/>
+    </row>
+    <row r="472" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A472" s="159" t="s">
         <v>38</v>
       </c>
-      <c r="D470" t="s">
-        <v>20</v>
-      </c>
-      <c r="E470" t="str">
-        <f>Foderstater!U$99</f>
-        <v>fish meal</v>
-      </c>
-      <c r="H470" t="s">
+      <c r="B472" s="159"/>
+      <c r="C472" s="159"/>
+      <c r="D472" s="159"/>
+      <c r="H472" s="159" t="s">
         <v>326</v>
       </c>
-      <c r="I470" s="13">
-        <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E470,Foderstater!$U$63:$U$100,0),MATCH(A470&amp;C470&amp;D470,Foderstater!$X$62:$AI$62,0))</f>
+      <c r="I472" s="159">
         <v>0</v>
       </c>
-    </row>
-    <row r="471" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A471" t="s">
+      <c r="J472" s="159"/>
+      <c r="K472" s="159" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="473" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A473" t="s">
         <v>38</v>
       </c>
-      <c r="D471" t="s">
-        <v>20</v>
-      </c>
-      <c r="E471" t="str">
-        <f>Foderstater!U$100</f>
-        <v>minerals</v>
-      </c>
-      <c r="H471" t="s">
+      <c r="E473" t="str">
+        <f>Foderstater!U$63</f>
+        <v>ley silage, 1st cut</v>
+      </c>
+      <c r="H473" t="s">
         <v>326</v>
       </c>
-      <c r="I471" s="13">
-        <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E471,Foderstater!$U$63:$U$100,0),MATCH(A471&amp;C471&amp;D471,Foderstater!$X$62:$AI$62,0))</f>
-        <v>0.6316938527980368</v>
-      </c>
-    </row>
-    <row r="473" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A473" s="91" t="s">
-        <v>445</v>
-      </c>
-      <c r="B473" s="163"/>
-      <c r="C473" s="163"/>
-      <c r="D473" s="90"/>
-      <c r="E473" s="90"/>
-      <c r="F473" s="90"/>
-      <c r="G473" s="90"/>
-      <c r="H473" s="90"/>
-      <c r="I473" s="164"/>
-      <c r="J473" s="90"/>
-      <c r="K473" s="90"/>
-      <c r="L473" s="90"/>
+      <c r="I473" s="13">
+        <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E473,Foderstater!$U$63:$U$100,0),MATCH(A473&amp;C473&amp;D473,Foderstater!$X$62:$AI$62,0))</f>
+        <v>0</v>
+      </c>
+      <c r="J473" s="159"/>
+      <c r="K473" s="159"/>
     </row>
     <row r="474" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A474" s="159" t="s">
+      <c r="A474" t="s">
         <v>38</v>
       </c>
-      <c r="B474" s="159"/>
-      <c r="C474" s="159"/>
-      <c r="D474" s="159"/>
-      <c r="H474" s="159" t="s">
+      <c r="E474" t="str">
+        <f>Foderstater!U$64</f>
+        <v>ley silage, regrowth</v>
+      </c>
+      <c r="H474" t="s">
         <v>326</v>
       </c>
-      <c r="I474" s="159">
-        <v>0</v>
+      <c r="I474" s="13">
+        <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E474,Foderstater!$U$63:$U$100,0),MATCH(A474&amp;C474&amp;D474,Foderstater!$X$62:$AI$62,0))</f>
+        <v>68.854768967576106</v>
       </c>
       <c r="J474" s="159"/>
-      <c r="K474" s="159" t="s">
-        <v>424</v>
-      </c>
+      <c r="K474" s="159"/>
     </row>
     <row r="475" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
         <v>38</v>
       </c>
       <c r="E475" t="str">
-        <f>Foderstater!U$63</f>
-        <v>ley silage, 1st cut</v>
+        <f>Foderstater!U$65</f>
+        <v>other silage</v>
       </c>
       <c r="H475" t="s">
         <v>326</v>
@@ -27192,15 +27228,15 @@
         <v>38</v>
       </c>
       <c r="E476" t="str">
-        <f>Foderstater!U$64</f>
-        <v>ley silage, regrowth</v>
+        <f>Foderstater!U$66</f>
+        <v>maize silage</v>
       </c>
       <c r="H476" t="s">
         <v>326</v>
       </c>
       <c r="I476" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E476,Foderstater!$U$63:$U$100,0),MATCH(A476&amp;C476&amp;D476,Foderstater!$X$62:$AI$62,0))</f>
-        <v>68.854768967576106</v>
+        <v>0</v>
       </c>
       <c r="J476" s="159"/>
       <c r="K476" s="159"/>
@@ -27210,8 +27246,8 @@
         <v>38</v>
       </c>
       <c r="E477" t="str">
-        <f>Foderstater!U$65</f>
-        <v>other silage</v>
+        <f>Foderstater!U$67</f>
+        <v>straw</v>
       </c>
       <c r="H477" t="s">
         <v>326</v>
@@ -27228,15 +27264,15 @@
         <v>38</v>
       </c>
       <c r="E478" t="str">
-        <f>Foderstater!U$66</f>
-        <v>maize silage</v>
+        <f>Foderstater!U$68</f>
+        <v>grazing</v>
       </c>
       <c r="H478" t="s">
         <v>326</v>
       </c>
       <c r="I478" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E478,Foderstater!$U$63:$U$100,0),MATCH(A478&amp;C478&amp;D478,Foderstater!$X$62:$AI$62,0))</f>
-        <v>0</v>
+        <v>30.425854259446911</v>
       </c>
       <c r="J478" s="159"/>
       <c r="K478" s="159"/>
@@ -27246,8 +27282,8 @@
         <v>38</v>
       </c>
       <c r="E479" t="str">
-        <f>Foderstater!U$67</f>
-        <v>straw</v>
+        <f>Foderstater!U$69</f>
+        <v>wheat</v>
       </c>
       <c r="H479" t="s">
         <v>326</v>
@@ -27264,15 +27300,15 @@
         <v>38</v>
       </c>
       <c r="E480" t="str">
-        <f>Foderstater!U$68</f>
-        <v>grazing</v>
+        <f>Foderstater!U$70</f>
+        <v>barley</v>
       </c>
       <c r="H480" t="s">
         <v>326</v>
       </c>
       <c r="I480" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E480,Foderstater!$U$63:$U$100,0),MATCH(A480&amp;C480&amp;D480,Foderstater!$X$62:$AI$62,0))</f>
-        <v>30.425854259446911</v>
+        <v>0</v>
       </c>
       <c r="J480" s="159"/>
       <c r="K480" s="159"/>
@@ -27282,8 +27318,8 @@
         <v>38</v>
       </c>
       <c r="E481" t="str">
-        <f>Foderstater!U$69</f>
-        <v>wheat</v>
+        <f>Foderstater!U$71</f>
+        <v>oats</v>
       </c>
       <c r="H481" t="s">
         <v>326</v>
@@ -27300,8 +27336,8 @@
         <v>38</v>
       </c>
       <c r="E482" t="str">
-        <f>Foderstater!U$70</f>
-        <v>barley</v>
+        <f>Foderstater!U$72</f>
+        <v>triticale</v>
       </c>
       <c r="H482" t="s">
         <v>326</v>
@@ -27318,8 +27354,8 @@
         <v>38</v>
       </c>
       <c r="E483" t="str">
-        <f>Foderstater!U$71</f>
-        <v>oats</v>
+        <f>Foderstater!U$73</f>
+        <v>rye</v>
       </c>
       <c r="H483" t="s">
         <v>326</v>
@@ -27336,8 +27372,8 @@
         <v>38</v>
       </c>
       <c r="E484" t="str">
-        <f>Foderstater!U$72</f>
-        <v>triticale</v>
+        <f>Foderstater!U$74</f>
+        <v>maize</v>
       </c>
       <c r="H484" t="s">
         <v>326</v>
@@ -27354,8 +27390,8 @@
         <v>38</v>
       </c>
       <c r="E485" t="str">
-        <f>Foderstater!U$73</f>
-        <v>rye</v>
+        <f>Foderstater!U$75</f>
+        <v>peas</v>
       </c>
       <c r="H485" t="s">
         <v>326</v>
@@ -27372,8 +27408,8 @@
         <v>38</v>
       </c>
       <c r="E486" t="str">
-        <f>Foderstater!U$74</f>
-        <v>maize</v>
+        <f>Foderstater!U$76</f>
+        <v>broad beans</v>
       </c>
       <c r="H486" t="s">
         <v>326</v>
@@ -27390,8 +27426,8 @@
         <v>38</v>
       </c>
       <c r="E487" t="str">
-        <f>Foderstater!U$75</f>
-        <v>peas</v>
+        <f>Foderstater!U$77</f>
+        <v>rapeseed</v>
       </c>
       <c r="H487" t="s">
         <v>326</v>
@@ -27408,8 +27444,8 @@
         <v>38</v>
       </c>
       <c r="E488" t="str">
-        <f>Foderstater!U$76</f>
-        <v>broad beans</v>
+        <f>Foderstater!U$78</f>
+        <v>linseed</v>
       </c>
       <c r="H488" t="s">
         <v>326</v>
@@ -27426,8 +27462,8 @@
         <v>38</v>
       </c>
       <c r="E489" t="str">
-        <f>Foderstater!U$77</f>
-        <v>rapeseed</v>
+        <f>Foderstater!U$79</f>
+        <v>vegetable oils</v>
       </c>
       <c r="H489" t="s">
         <v>326</v>
@@ -27444,8 +27480,8 @@
         <v>38</v>
       </c>
       <c r="E490" t="str">
-        <f>Foderstater!U$78</f>
-        <v>linseed</v>
+        <f>Foderstater!U$80</f>
+        <v>soybeans</v>
       </c>
       <c r="H490" t="s">
         <v>326</v>
@@ -27462,8 +27498,8 @@
         <v>38</v>
       </c>
       <c r="E491" t="str">
-        <f>Foderstater!U$79</f>
-        <v>vegetable oils</v>
+        <f>Foderstater!U$81</f>
+        <v>soybean meal</v>
       </c>
       <c r="H491" t="s">
         <v>326</v>
@@ -27480,8 +27516,8 @@
         <v>38</v>
       </c>
       <c r="E492" t="str">
-        <f>Foderstater!U$80</f>
-        <v>soybeans</v>
+        <f>Foderstater!U$82</f>
+        <v>soybean protein concentrate</v>
       </c>
       <c r="H492" t="s">
         <v>326</v>
@@ -27498,8 +27534,8 @@
         <v>38</v>
       </c>
       <c r="E493" t="str">
-        <f>Foderstater!U$81</f>
-        <v>soybean meal</v>
+        <f>Foderstater!U$83</f>
+        <v>rapeseed meal</v>
       </c>
       <c r="H493" t="s">
         <v>326</v>
@@ -27516,8 +27552,8 @@
         <v>38</v>
       </c>
       <c r="E494" t="str">
-        <f>Foderstater!U$82</f>
-        <v>soybean protein concentrate</v>
+        <f>Foderstater!U$84</f>
+        <v>sunflower seed meal</v>
       </c>
       <c r="H494" t="s">
         <v>326</v>
@@ -27526,16 +27562,14 @@
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E494,Foderstater!$U$63:$U$100,0),MATCH(A494&amp;C494&amp;D494,Foderstater!$X$62:$AI$62,0))</f>
         <v>0</v>
       </c>
-      <c r="J494" s="159"/>
-      <c r="K494" s="159"/>
     </row>
     <row r="495" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
         <v>38</v>
       </c>
       <c r="E495" t="str">
-        <f>Foderstater!U$83</f>
-        <v>rapeseed meal</v>
+        <f>Foderstater!U$85</f>
+        <v>palm kernel expeller</v>
       </c>
       <c r="H495" t="s">
         <v>326</v>
@@ -27544,16 +27578,14 @@
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E495,Foderstater!$U$63:$U$100,0),MATCH(A495&amp;C495&amp;D495,Foderstater!$X$62:$AI$62,0))</f>
         <v>0</v>
       </c>
-      <c r="J495" s="159"/>
-      <c r="K495" s="159"/>
     </row>
     <row r="496" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
         <v>38</v>
       </c>
       <c r="E496" t="str">
-        <f>Foderstater!U$84</f>
-        <v>sunflower seed meal</v>
+        <f>Foderstater!U$86</f>
+        <v>luzern meal</v>
       </c>
       <c r="H496" t="s">
         <v>326</v>
@@ -27563,13 +27595,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="497" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
         <v>38</v>
       </c>
       <c r="E497" t="str">
-        <f>Foderstater!U$85</f>
-        <v>palm kernel expeller</v>
+        <f>Foderstater!U$87</f>
+        <v>wheat bran</v>
       </c>
       <c r="H497" t="s">
         <v>326</v>
@@ -27579,13 +27611,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="498" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
         <v>38</v>
       </c>
       <c r="E498" t="str">
-        <f>Foderstater!U$86</f>
-        <v>luzern meal</v>
+        <f>Foderstater!U$88</f>
+        <v>wheat bran, fine</v>
       </c>
       <c r="H498" t="s">
         <v>326</v>
@@ -27595,13 +27627,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="499" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
         <v>38</v>
       </c>
       <c r="E499" t="str">
-        <f>Foderstater!U$87</f>
-        <v>wheat bran</v>
+        <f>Foderstater!U$89</f>
+        <v>oat hulls</v>
       </c>
       <c r="H499" t="s">
         <v>326</v>
@@ -27611,13 +27643,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="500" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
         <v>38</v>
       </c>
       <c r="E500" t="str">
-        <f>Foderstater!U$88</f>
-        <v>wheat bran, fine</v>
+        <f>Foderstater!U$90</f>
+        <v>oat bran</v>
       </c>
       <c r="H500" t="s">
         <v>326</v>
@@ -27627,13 +27659,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="501" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
         <v>38</v>
       </c>
       <c r="E501" t="str">
-        <f>Foderstater!U$89</f>
-        <v>oat hulls</v>
+        <f>Foderstater!U$91</f>
+        <v>rye bran</v>
       </c>
       <c r="H501" t="s">
         <v>326</v>
@@ -27643,13 +27675,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="502" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
         <v>38</v>
       </c>
       <c r="E502" t="str">
-        <f>Foderstater!U$90</f>
-        <v>oat bran</v>
+        <f>Foderstater!U$92</f>
+        <v>wheat distillers grain, dry</v>
       </c>
       <c r="H502" t="s">
         <v>326</v>
@@ -27659,13 +27691,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="503" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
         <v>38</v>
       </c>
       <c r="E503" t="str">
-        <f>Foderstater!U$91</f>
-        <v>rye bran</v>
+        <f>Foderstater!U$93</f>
+        <v>barley brewers grain</v>
       </c>
       <c r="H503" t="s">
         <v>326</v>
@@ -27675,13 +27707,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="504" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
         <v>38</v>
       </c>
       <c r="E504" t="str">
-        <f>Foderstater!U$92</f>
-        <v>wheat distillers grain, dry</v>
+        <f>Foderstater!U$94</f>
+        <v>maize gluten meal</v>
       </c>
       <c r="H504" t="s">
         <v>326</v>
@@ -27691,13 +27723,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="505" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
         <v>38</v>
       </c>
       <c r="E505" t="str">
-        <f>Foderstater!U$93</f>
-        <v>barley brewers grain</v>
+        <f>Foderstater!U$95</f>
+        <v>sugar beet molasses</v>
       </c>
       <c r="H505" t="s">
         <v>326</v>
@@ -27707,13 +27739,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="506" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
         <v>38</v>
       </c>
       <c r="E506" t="str">
-        <f>Foderstater!U$94</f>
-        <v>maize gluten meal</v>
+        <f>Foderstater!U$96</f>
+        <v>sugar beet pulp</v>
       </c>
       <c r="H506" t="s">
         <v>326</v>
@@ -27723,13 +27755,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="507" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
         <v>38</v>
       </c>
       <c r="E507" t="str">
-        <f>Foderstater!U$95</f>
-        <v>sugar beet molasses</v>
+        <f>Foderstater!U$97</f>
+        <v>whey powder</v>
       </c>
       <c r="H507" t="s">
         <v>326</v>
@@ -27739,13 +27771,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="508" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
         <v>38</v>
       </c>
       <c r="E508" t="str">
-        <f>Foderstater!U$96</f>
-        <v>sugar beet pulp</v>
+        <f>Foderstater!U$98</f>
+        <v>potatoe protein</v>
       </c>
       <c r="H508" t="s">
         <v>326</v>
@@ -27755,13 +27787,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="509" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A509" t="s">
         <v>38</v>
       </c>
       <c r="E509" t="str">
-        <f>Foderstater!U$97</f>
-        <v>whey powder</v>
+        <f>Foderstater!U$99</f>
+        <v>fish meal</v>
       </c>
       <c r="H509" t="s">
         <v>326</v>
@@ -27771,91 +27803,101 @@
         <v>0</v>
       </c>
     </row>
-    <row r="510" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A510" t="s">
         <v>38</v>
       </c>
       <c r="E510" t="str">
-        <f>Foderstater!U$98</f>
-        <v>potatoe protein</v>
+        <f>Foderstater!U$100</f>
+        <v>minerals</v>
       </c>
       <c r="H510" t="s">
         <v>326</v>
       </c>
       <c r="I510" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E510,Foderstater!$U$63:$U$100,0),MATCH(A510&amp;C510&amp;D510,Foderstater!$X$62:$AI$62,0))</f>
+        <v>0.71937677297698155</v>
+      </c>
+    </row>
+    <row r="512" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A512" s="91" t="s">
+        <v>86</v>
+      </c>
+      <c r="B512" s="163"/>
+      <c r="C512" s="163"/>
+      <c r="D512" s="90"/>
+      <c r="E512" s="90"/>
+      <c r="F512" s="90"/>
+      <c r="G512" s="90"/>
+      <c r="H512" s="90"/>
+      <c r="I512" s="164"/>
+      <c r="J512" s="90"/>
+      <c r="K512" s="90"/>
+      <c r="L512" s="90"/>
+    </row>
+    <row r="513" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A513" s="159" t="s">
+        <v>38</v>
+      </c>
+      <c r="B513" s="159"/>
+      <c r="C513" s="159"/>
+      <c r="D513" s="159" t="s">
+        <v>35</v>
+      </c>
+      <c r="H513" s="159" t="s">
+        <v>326</v>
+      </c>
+      <c r="I513" s="159">
         <v>0</v>
       </c>
-    </row>
-    <row r="511" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A511" t="s">
+      <c r="J513" s="159"/>
+      <c r="K513" s="159" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="514" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A514" t="s">
         <v>38</v>
       </c>
-      <c r="E511" t="str">
-        <f>Foderstater!U$99</f>
-        <v>fish meal</v>
-      </c>
-      <c r="H511" t="s">
+      <c r="D514" t="s">
+        <v>35</v>
+      </c>
+      <c r="E514" t="str">
+        <f>Foderstater!U$63</f>
+        <v>ley silage, 1st cut</v>
+      </c>
+      <c r="H514" t="s">
         <v>326</v>
       </c>
-      <c r="I511" s="13">
-        <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E511,Foderstater!$U$63:$U$100,0),MATCH(A511&amp;C511&amp;D511,Foderstater!$X$62:$AI$62,0))</f>
+      <c r="I514" s="13">
+        <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E514,Foderstater!$U$63:$U$100,0),MATCH(A514&amp;C514&amp;D514,Foderstater!$X$62:$AI$62,0))</f>
+        <v>60.138713626619086</v>
+      </c>
+      <c r="J514" s="159"/>
+      <c r="K514" s="159"/>
+    </row>
+    <row r="515" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A515" t="s">
+        <v>38</v>
+      </c>
+      <c r="D515" t="s">
+        <v>35</v>
+      </c>
+      <c r="E515" t="str">
+        <f>Foderstater!U$64</f>
+        <v>ley silage, regrowth</v>
+      </c>
+      <c r="H515" t="s">
+        <v>326</v>
+      </c>
+      <c r="I515" s="13">
+        <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E515,Foderstater!$U$63:$U$100,0),MATCH(A515&amp;C515&amp;D515,Foderstater!$X$62:$AI$62,0))</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="512" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A512" t="s">
-        <v>38</v>
-      </c>
-      <c r="E512" t="str">
-        <f>Foderstater!U$100</f>
-        <v>minerals</v>
-      </c>
-      <c r="H512" t="s">
-        <v>326</v>
-      </c>
-      <c r="I512" s="13">
-        <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E512,Foderstater!$U$63:$U$100,0),MATCH(A512&amp;C512&amp;D512,Foderstater!$X$62:$AI$62,0))</f>
-        <v>0.71937677297698155</v>
-      </c>
-    </row>
-    <row r="514" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A514" s="91" t="s">
-        <v>86</v>
-      </c>
-      <c r="B514" s="163"/>
-      <c r="C514" s="163"/>
-      <c r="D514" s="90"/>
-      <c r="E514" s="90"/>
-      <c r="F514" s="90"/>
-      <c r="G514" s="90"/>
-      <c r="H514" s="90"/>
-      <c r="I514" s="164"/>
-      <c r="J514" s="90"/>
-      <c r="K514" s="90"/>
-      <c r="L514" s="90"/>
-    </row>
-    <row r="515" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A515" s="159" t="s">
-        <v>38</v>
-      </c>
-      <c r="B515" s="159"/>
-      <c r="C515" s="159"/>
-      <c r="D515" s="159" t="s">
-        <v>35</v>
-      </c>
-      <c r="H515" s="159" t="s">
-        <v>326</v>
-      </c>
-      <c r="I515" s="159">
-        <v>0</v>
-      </c>
       <c r="J515" s="159"/>
-      <c r="K515" s="159" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="516" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K515" s="159"/>
+    </row>
+    <row r="516" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
         <v>38</v>
       </c>
@@ -27863,20 +27905,20 @@
         <v>35</v>
       </c>
       <c r="E516" t="str">
-        <f>Foderstater!U$63</f>
-        <v>ley silage, 1st cut</v>
+        <f>Foderstater!U$65</f>
+        <v>other silage</v>
       </c>
       <c r="H516" t="s">
         <v>326</v>
       </c>
       <c r="I516" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E516,Foderstater!$U$63:$U$100,0),MATCH(A516&amp;C516&amp;D516,Foderstater!$X$62:$AI$62,0))</f>
-        <v>60.138713626619086</v>
+        <v>0</v>
       </c>
       <c r="J516" s="159"/>
       <c r="K516" s="159"/>
     </row>
-    <row r="517" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A517" t="s">
         <v>38</v>
       </c>
@@ -27884,8 +27926,8 @@
         <v>35</v>
       </c>
       <c r="E517" t="str">
-        <f>Foderstater!U$64</f>
-        <v>ley silage, regrowth</v>
+        <f>Foderstater!U$66</f>
+        <v>maize silage</v>
       </c>
       <c r="H517" t="s">
         <v>326</v>
@@ -27897,7 +27939,7 @@
       <c r="J517" s="159"/>
       <c r="K517" s="159"/>
     </row>
-    <row r="518" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A518" t="s">
         <v>38</v>
       </c>
@@ -27905,8 +27947,8 @@
         <v>35</v>
       </c>
       <c r="E518" t="str">
-        <f>Foderstater!U$65</f>
-        <v>other silage</v>
+        <f>Foderstater!U$67</f>
+        <v>straw</v>
       </c>
       <c r="H518" t="s">
         <v>326</v>
@@ -27918,7 +27960,7 @@
       <c r="J518" s="159"/>
       <c r="K518" s="159"/>
     </row>
-    <row r="519" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A519" t="s">
         <v>38</v>
       </c>
@@ -27926,8 +27968,8 @@
         <v>35</v>
       </c>
       <c r="E519" t="str">
-        <f>Foderstater!U$66</f>
-        <v>maize silage</v>
+        <f>Foderstater!U$68</f>
+        <v>grazing</v>
       </c>
       <c r="H519" t="s">
         <v>326</v>
@@ -27939,7 +27981,7 @@
       <c r="J519" s="159"/>
       <c r="K519" s="159"/>
     </row>
-    <row r="520" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A520" t="s">
         <v>38</v>
       </c>
@@ -27947,20 +27989,20 @@
         <v>35</v>
       </c>
       <c r="E520" t="str">
-        <f>Foderstater!U$67</f>
-        <v>straw</v>
+        <f>Foderstater!U$69</f>
+        <v>wheat</v>
       </c>
       <c r="H520" t="s">
         <v>326</v>
       </c>
       <c r="I520" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E520,Foderstater!$U$63:$U$100,0),MATCH(A520&amp;C520&amp;D520,Foderstater!$X$62:$AI$62,0))</f>
-        <v>0</v>
+        <v>8.7950802360888023</v>
       </c>
       <c r="J520" s="159"/>
       <c r="K520" s="159"/>
     </row>
-    <row r="521" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A521" t="s">
         <v>38</v>
       </c>
@@ -27968,20 +28010,20 @@
         <v>35</v>
       </c>
       <c r="E521" t="str">
-        <f>Foderstater!U$68</f>
-        <v>grazing</v>
+        <f>Foderstater!U$70</f>
+        <v>barley</v>
       </c>
       <c r="H521" t="s">
         <v>326</v>
       </c>
       <c r="I521" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E521,Foderstater!$U$63:$U$100,0),MATCH(A521&amp;C521&amp;D521,Foderstater!$X$62:$AI$62,0))</f>
-        <v>0</v>
+        <v>16.456273052444185</v>
       </c>
       <c r="J521" s="159"/>
       <c r="K521" s="159"/>
     </row>
-    <row r="522" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A522" t="s">
         <v>38</v>
       </c>
@@ -27989,20 +28031,20 @@
         <v>35</v>
       </c>
       <c r="E522" t="str">
-        <f>Foderstater!U$69</f>
-        <v>wheat</v>
+        <f>Foderstater!U$71</f>
+        <v>oats</v>
       </c>
       <c r="H522" t="s">
         <v>326</v>
       </c>
       <c r="I522" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E522,Foderstater!$U$63:$U$100,0),MATCH(A522&amp;C522&amp;D522,Foderstater!$X$62:$AI$62,0))</f>
-        <v>8.7950802360888023</v>
+        <v>3.6372465594215786</v>
       </c>
       <c r="J522" s="159"/>
       <c r="K522" s="159"/>
     </row>
-    <row r="523" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A523" t="s">
         <v>38</v>
       </c>
@@ -28010,20 +28052,20 @@
         <v>35</v>
       </c>
       <c r="E523" t="str">
-        <f>Foderstater!U$70</f>
-        <v>barley</v>
+        <f>Foderstater!U$72</f>
+        <v>triticale</v>
       </c>
       <c r="H523" t="s">
         <v>326</v>
       </c>
       <c r="I523" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E523,Foderstater!$U$63:$U$100,0),MATCH(A523&amp;C523&amp;D523,Foderstater!$X$62:$AI$62,0))</f>
-        <v>16.456273052444185</v>
+        <v>5.8891480485237606</v>
       </c>
       <c r="J523" s="159"/>
       <c r="K523" s="159"/>
     </row>
-    <row r="524" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A524" t="s">
         <v>38</v>
       </c>
@@ -28031,20 +28073,20 @@
         <v>35</v>
       </c>
       <c r="E524" t="str">
-        <f>Foderstater!U$71</f>
-        <v>oats</v>
+        <f>Foderstater!U$73</f>
+        <v>rye</v>
       </c>
       <c r="H524" t="s">
         <v>326</v>
       </c>
       <c r="I524" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E524,Foderstater!$U$63:$U$100,0),MATCH(A524&amp;C524&amp;D524,Foderstater!$X$62:$AI$62,0))</f>
-        <v>3.6372465594215786</v>
+        <v>1.3507533293838584E-2</v>
       </c>
       <c r="J524" s="159"/>
       <c r="K524" s="159"/>
     </row>
-    <row r="525" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A525" t="s">
         <v>38</v>
       </c>
@@ -28052,20 +28094,20 @@
         <v>35</v>
       </c>
       <c r="E525" t="str">
-        <f>Foderstater!U$72</f>
-        <v>triticale</v>
+        <f>Foderstater!U$74</f>
+        <v>maize</v>
       </c>
       <c r="H525" t="s">
         <v>326</v>
       </c>
       <c r="I525" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E525,Foderstater!$U$63:$U$100,0),MATCH(A525&amp;C525&amp;D525,Foderstater!$X$62:$AI$62,0))</f>
-        <v>5.8891480485237606</v>
+        <v>5.8685075988393134E-2</v>
       </c>
       <c r="J525" s="159"/>
       <c r="K525" s="159"/>
     </row>
-    <row r="526" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A526" t="s">
         <v>38</v>
       </c>
@@ -28073,20 +28115,20 @@
         <v>35</v>
       </c>
       <c r="E526" t="str">
-        <f>Foderstater!U$73</f>
-        <v>rye</v>
+        <f>Foderstater!U$75</f>
+        <v>peas</v>
       </c>
       <c r="H526" t="s">
         <v>326</v>
       </c>
       <c r="I526" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E526,Foderstater!$U$63:$U$100,0),MATCH(A526&amp;C526&amp;D526,Foderstater!$X$62:$AI$62,0))</f>
-        <v>1.3507533293838584E-2</v>
+        <v>1.230521308754674</v>
       </c>
       <c r="J526" s="159"/>
       <c r="K526" s="159"/>
     </row>
-    <row r="527" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A527" t="s">
         <v>38</v>
       </c>
@@ -28094,20 +28136,20 @@
         <v>35</v>
       </c>
       <c r="E527" t="str">
-        <f>Foderstater!U$74</f>
-        <v>maize</v>
+        <f>Foderstater!U$76</f>
+        <v>broad beans</v>
       </c>
       <c r="H527" t="s">
         <v>326</v>
       </c>
       <c r="I527" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E527,Foderstater!$U$63:$U$100,0),MATCH(A527&amp;C527&amp;D527,Foderstater!$X$62:$AI$62,0))</f>
-        <v>5.8685075988393134E-2</v>
+        <v>1.1908458068725807</v>
       </c>
       <c r="J527" s="159"/>
       <c r="K527" s="159"/>
     </row>
-    <row r="528" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A528" t="s">
         <v>38</v>
       </c>
@@ -28115,15 +28157,15 @@
         <v>35</v>
       </c>
       <c r="E528" t="str">
-        <f>Foderstater!U$75</f>
-        <v>peas</v>
+        <f>Foderstater!U$77</f>
+        <v>rapeseed</v>
       </c>
       <c r="H528" t="s">
         <v>326</v>
       </c>
       <c r="I528" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E528,Foderstater!$U$63:$U$100,0),MATCH(A528&amp;C528&amp;D528,Foderstater!$X$62:$AI$62,0))</f>
-        <v>1.230521308754674</v>
+        <v>0.49891518495011011</v>
       </c>
       <c r="J528" s="159"/>
       <c r="K528" s="159"/>
@@ -28136,15 +28178,15 @@
         <v>35</v>
       </c>
       <c r="E529" t="str">
-        <f>Foderstater!U$76</f>
-        <v>broad beans</v>
+        <f>Foderstater!U$78</f>
+        <v>linseed</v>
       </c>
       <c r="H529" t="s">
         <v>326</v>
       </c>
       <c r="I529" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E529,Foderstater!$U$63:$U$100,0),MATCH(A529&amp;C529&amp;D529,Foderstater!$X$62:$AI$62,0))</f>
-        <v>1.1908458068725807</v>
+        <v>3.6802917118822752E-4</v>
       </c>
       <c r="J529" s="159"/>
       <c r="K529" s="159"/>
@@ -28157,15 +28199,15 @@
         <v>35</v>
       </c>
       <c r="E530" t="str">
-        <f>Foderstater!U$77</f>
-        <v>rapeseed</v>
+        <f>Foderstater!U$79</f>
+        <v>vegetable oils</v>
       </c>
       <c r="H530" t="s">
         <v>326</v>
       </c>
       <c r="I530" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E530,Foderstater!$U$63:$U$100,0),MATCH(A530&amp;C530&amp;D530,Foderstater!$X$62:$AI$62,0))</f>
-        <v>0.49891518495011011</v>
+        <v>9.5013866211436822E-3</v>
       </c>
       <c r="J530" s="159"/>
       <c r="K530" s="159"/>
@@ -28178,15 +28220,15 @@
         <v>35</v>
       </c>
       <c r="E531" t="str">
-        <f>Foderstater!U$78</f>
-        <v>linseed</v>
+        <f>Foderstater!U$80</f>
+        <v>soybeans</v>
       </c>
       <c r="H531" t="s">
         <v>326</v>
       </c>
       <c r="I531" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E531,Foderstater!$U$63:$U$100,0),MATCH(A531&amp;C531&amp;D531,Foderstater!$X$62:$AI$62,0))</f>
-        <v>3.6802917118822752E-4</v>
+        <v>9.2850444567383218E-3</v>
       </c>
       <c r="J531" s="159"/>
       <c r="K531" s="159"/>
@@ -28199,15 +28241,15 @@
         <v>35</v>
       </c>
       <c r="E532" t="str">
-        <f>Foderstater!U$79</f>
-        <v>vegetable oils</v>
+        <f>Foderstater!U$81</f>
+        <v>soybean meal</v>
       </c>
       <c r="H532" t="s">
         <v>326</v>
       </c>
       <c r="I532" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E532,Foderstater!$U$63:$U$100,0),MATCH(A532&amp;C532&amp;D532,Foderstater!$X$62:$AI$62,0))</f>
-        <v>9.5013866211436822E-3</v>
+        <v>8.4815436019657742E-2</v>
       </c>
       <c r="J532" s="159"/>
       <c r="K532" s="159"/>
@@ -28220,15 +28262,15 @@
         <v>35</v>
       </c>
       <c r="E533" t="str">
-        <f>Foderstater!U$80</f>
-        <v>soybeans</v>
+        <f>Foderstater!U$82</f>
+        <v>soybean protein concentrate</v>
       </c>
       <c r="H533" t="s">
         <v>326</v>
       </c>
       <c r="I533" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E533,Foderstater!$U$63:$U$100,0),MATCH(A533&amp;C533&amp;D533,Foderstater!$X$62:$AI$62,0))</f>
-        <v>9.2850444567383218E-3</v>
+        <v>0</v>
       </c>
       <c r="J533" s="159"/>
       <c r="K533" s="159"/>
@@ -28241,15 +28283,15 @@
         <v>35</v>
       </c>
       <c r="E534" t="str">
-        <f>Foderstater!U$81</f>
-        <v>soybean meal</v>
+        <f>Foderstater!U$83</f>
+        <v>rapeseed meal</v>
       </c>
       <c r="H534" t="s">
         <v>326</v>
       </c>
       <c r="I534" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E534,Foderstater!$U$63:$U$100,0),MATCH(A534&amp;C534&amp;D534,Foderstater!$X$62:$AI$62,0))</f>
-        <v>8.4815436019657742E-2</v>
+        <v>0.65508327684698231</v>
       </c>
       <c r="J534" s="159"/>
       <c r="K534" s="159"/>
@@ -28262,18 +28304,16 @@
         <v>35</v>
       </c>
       <c r="E535" t="str">
-        <f>Foderstater!U$82</f>
-        <v>soybean protein concentrate</v>
+        <f>Foderstater!U$84</f>
+        <v>sunflower seed meal</v>
       </c>
       <c r="H535" t="s">
         <v>326</v>
       </c>
       <c r="I535" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E535,Foderstater!$U$63:$U$100,0),MATCH(A535&amp;C535&amp;D535,Foderstater!$X$62:$AI$62,0))</f>
-        <v>0</v>
-      </c>
-      <c r="J535" s="159"/>
-      <c r="K535" s="159"/>
+        <v>9.0493413936850002E-3</v>
+      </c>
     </row>
     <row r="536" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A536" t="s">
@@ -28283,18 +28323,16 @@
         <v>35</v>
       </c>
       <c r="E536" t="str">
-        <f>Foderstater!U$83</f>
-        <v>rapeseed meal</v>
+        <f>Foderstater!U$85</f>
+        <v>palm kernel expeller</v>
       </c>
       <c r="H536" t="s">
         <v>326</v>
       </c>
       <c r="I536" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E536,Foderstater!$U$63:$U$100,0),MATCH(A536&amp;C536&amp;D536,Foderstater!$X$62:$AI$62,0))</f>
-        <v>0.65508327684698231</v>
-      </c>
-      <c r="J536" s="159"/>
-      <c r="K536" s="159"/>
+        <v>5.880188879234155E-2</v>
+      </c>
     </row>
     <row r="537" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A537" t="s">
@@ -28304,15 +28342,15 @@
         <v>35</v>
       </c>
       <c r="E537" t="str">
-        <f>Foderstater!U$84</f>
-        <v>sunflower seed meal</v>
+        <f>Foderstater!U$86</f>
+        <v>luzern meal</v>
       </c>
       <c r="H537" t="s">
         <v>326</v>
       </c>
       <c r="I537" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E537,Foderstater!$U$63:$U$100,0),MATCH(A537&amp;C537&amp;D537,Foderstater!$X$62:$AI$62,0))</f>
-        <v>9.0493413936850002E-3</v>
+        <v>1.7886888897567656E-2</v>
       </c>
     </row>
     <row r="538" spans="1:11" x14ac:dyDescent="0.25">
@@ -28323,15 +28361,15 @@
         <v>35</v>
       </c>
       <c r="E538" t="str">
-        <f>Foderstater!U$85</f>
-        <v>palm kernel expeller</v>
+        <f>Foderstater!U$87</f>
+        <v>wheat bran</v>
       </c>
       <c r="H538" t="s">
         <v>326</v>
       </c>
       <c r="I538" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E538,Foderstater!$U$63:$U$100,0),MATCH(A538&amp;C538&amp;D538,Foderstater!$X$62:$AI$62,0))</f>
-        <v>5.880188879234155E-2</v>
+        <v>0.19488005713432707</v>
       </c>
     </row>
     <row r="539" spans="1:11" x14ac:dyDescent="0.25">
@@ -28342,15 +28380,15 @@
         <v>35</v>
       </c>
       <c r="E539" t="str">
-        <f>Foderstater!U$86</f>
-        <v>luzern meal</v>
+        <f>Foderstater!U$88</f>
+        <v>wheat bran, fine</v>
       </c>
       <c r="H539" t="s">
         <v>326</v>
       </c>
       <c r="I539" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E539,Foderstater!$U$63:$U$100,0),MATCH(A539&amp;C539&amp;D539,Foderstater!$X$62:$AI$62,0))</f>
-        <v>1.7886888897567656E-2</v>
+        <v>5.108654814463125E-4</v>
       </c>
     </row>
     <row r="540" spans="1:11" x14ac:dyDescent="0.25">
@@ -28361,15 +28399,15 @@
         <v>35</v>
       </c>
       <c r="E540" t="str">
-        <f>Foderstater!U$87</f>
-        <v>wheat bran</v>
+        <f>Foderstater!U$89</f>
+        <v>oat hulls</v>
       </c>
       <c r="H540" t="s">
         <v>326</v>
       </c>
       <c r="I540" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E540,Foderstater!$U$63:$U$100,0),MATCH(A540&amp;C540&amp;D540,Foderstater!$X$62:$AI$62,0))</f>
-        <v>0.19488005713432707</v>
+        <v>2.3471407966757316E-2</v>
       </c>
     </row>
     <row r="541" spans="1:11" x14ac:dyDescent="0.25">
@@ -28380,15 +28418,15 @@
         <v>35</v>
       </c>
       <c r="E541" t="str">
-        <f>Foderstater!U$88</f>
-        <v>wheat bran, fine</v>
+        <f>Foderstater!U$90</f>
+        <v>oat bran</v>
       </c>
       <c r="H541" t="s">
         <v>326</v>
       </c>
       <c r="I541" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E541,Foderstater!$U$63:$U$100,0),MATCH(A541&amp;C541&amp;D541,Foderstater!$X$62:$AI$62,0))</f>
-        <v>5.108654814463125E-4</v>
+        <v>2.6490134698680073E-3</v>
       </c>
     </row>
     <row r="542" spans="1:11" x14ac:dyDescent="0.25">
@@ -28399,15 +28437,15 @@
         <v>35</v>
       </c>
       <c r="E542" t="str">
-        <f>Foderstater!U$89</f>
-        <v>oat hulls</v>
+        <f>Foderstater!U$91</f>
+        <v>rye bran</v>
       </c>
       <c r="H542" t="s">
         <v>326</v>
       </c>
       <c r="I542" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E542,Foderstater!$U$63:$U$100,0),MATCH(A542&amp;C542&amp;D542,Foderstater!$X$62:$AI$62,0))</f>
-        <v>2.3471407966757316E-2</v>
+        <v>8.1695862566661028E-3</v>
       </c>
     </row>
     <row r="543" spans="1:11" x14ac:dyDescent="0.25">
@@ -28418,15 +28456,15 @@
         <v>35</v>
       </c>
       <c r="E543" t="str">
-        <f>Foderstater!U$90</f>
-        <v>oat bran</v>
+        <f>Foderstater!U$92</f>
+        <v>wheat distillers grain, dry</v>
       </c>
       <c r="H543" t="s">
         <v>326</v>
       </c>
       <c r="I543" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E543,Foderstater!$U$63:$U$100,0),MATCH(A543&amp;C543&amp;D543,Foderstater!$X$62:$AI$62,0))</f>
-        <v>2.6490134698680073E-3</v>
+        <v>0.20947754779055638</v>
       </c>
     </row>
     <row r="544" spans="1:11" x14ac:dyDescent="0.25">
@@ -28437,15 +28475,15 @@
         <v>35</v>
       </c>
       <c r="E544" t="str">
-        <f>Foderstater!U$91</f>
-        <v>rye bran</v>
+        <f>Foderstater!U$93</f>
+        <v>barley brewers grain</v>
       </c>
       <c r="H544" t="s">
         <v>326</v>
       </c>
       <c r="I544" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E544,Foderstater!$U$63:$U$100,0),MATCH(A544&amp;C544&amp;D544,Foderstater!$X$62:$AI$62,0))</f>
-        <v>8.1695862566661028E-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="545" spans="1:11" x14ac:dyDescent="0.25">
@@ -28456,15 +28494,15 @@
         <v>35</v>
       </c>
       <c r="E545" t="str">
-        <f>Foderstater!U$92</f>
-        <v>wheat distillers grain, dry</v>
+        <f>Foderstater!U$94</f>
+        <v>maize gluten meal</v>
       </c>
       <c r="H545" t="s">
         <v>326</v>
       </c>
       <c r="I545" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E545,Foderstater!$U$63:$U$100,0),MATCH(A545&amp;C545&amp;D545,Foderstater!$X$62:$AI$62,0))</f>
-        <v>0.20947754779055638</v>
+        <v>6.3297538628935548E-3</v>
       </c>
     </row>
     <row r="546" spans="1:11" x14ac:dyDescent="0.25">
@@ -28475,15 +28513,15 @@
         <v>35</v>
       </c>
       <c r="E546" t="str">
-        <f>Foderstater!U$93</f>
-        <v>barley brewers grain</v>
+        <f>Foderstater!U$95</f>
+        <v>sugar beet molasses</v>
       </c>
       <c r="H546" t="s">
         <v>326</v>
       </c>
       <c r="I546" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E546,Foderstater!$U$63:$U$100,0),MATCH(A546&amp;C546&amp;D546,Foderstater!$X$62:$AI$62,0))</f>
-        <v>0</v>
+        <v>7.0193131657187727E-2</v>
       </c>
     </row>
     <row r="547" spans="1:11" x14ac:dyDescent="0.25">
@@ -28494,15 +28532,15 @@
         <v>35</v>
       </c>
       <c r="E547" t="str">
-        <f>Foderstater!U$94</f>
-        <v>maize gluten meal</v>
+        <f>Foderstater!U$96</f>
+        <v>sugar beet pulp</v>
       </c>
       <c r="H547" t="s">
         <v>326</v>
       </c>
       <c r="I547" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E547,Foderstater!$U$63:$U$100,0),MATCH(A547&amp;C547&amp;D547,Foderstater!$X$62:$AI$62,0))</f>
-        <v>6.3297538628935548E-3</v>
+        <v>0.13544319950020575</v>
       </c>
     </row>
     <row r="548" spans="1:11" x14ac:dyDescent="0.25">
@@ -28513,15 +28551,15 @@
         <v>35</v>
       </c>
       <c r="E548" t="str">
-        <f>Foderstater!U$95</f>
-        <v>sugar beet molasses</v>
+        <f>Foderstater!U$97</f>
+        <v>whey powder</v>
       </c>
       <c r="H548" t="s">
         <v>326</v>
       </c>
       <c r="I548" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E548,Foderstater!$U$63:$U$100,0),MATCH(A548&amp;C548&amp;D548,Foderstater!$X$62:$AI$62,0))</f>
-        <v>7.0193131657187727E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="549" spans="1:11" x14ac:dyDescent="0.25">
@@ -28532,15 +28570,15 @@
         <v>35</v>
       </c>
       <c r="E549" t="str">
-        <f>Foderstater!U$96</f>
-        <v>sugar beet pulp</v>
+        <f>Foderstater!U$98</f>
+        <v>potatoe protein</v>
       </c>
       <c r="H549" t="s">
         <v>326</v>
       </c>
       <c r="I549" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E549,Foderstater!$U$63:$U$100,0),MATCH(A549&amp;C549&amp;D549,Foderstater!$X$62:$AI$62,0))</f>
-        <v>0.13544319950020575</v>
+        <v>6.2009373017834091E-4</v>
       </c>
     </row>
     <row r="550" spans="1:11" x14ac:dyDescent="0.25">
@@ -28551,8 +28589,8 @@
         <v>35</v>
       </c>
       <c r="E550" t="str">
-        <f>Foderstater!U$97</f>
-        <v>whey powder</v>
+        <f>Foderstater!U$99</f>
+        <v>fish meal</v>
       </c>
       <c r="H550" t="s">
         <v>326</v>
@@ -28570,82 +28608,98 @@
         <v>35</v>
       </c>
       <c r="E551" t="str">
-        <f>Foderstater!U$98</f>
-        <v>potatoe protein</v>
+        <f>Foderstater!U$100</f>
+        <v>minerals</v>
       </c>
       <c r="H551" t="s">
         <v>326</v>
       </c>
       <c r="I551" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E551,Foderstater!$U$63:$U$100,0),MATCH(A551&amp;C551&amp;D551,Foderstater!$X$62:$AI$62,0))</f>
-        <v>6.2009373017834091E-4</v>
+        <v>0.59452761799360676</v>
       </c>
     </row>
     <row r="552" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A552" t="s">
+      <c r="J552" s="159"/>
+      <c r="K552" s="159"/>
+    </row>
+    <row r="553" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A553" s="159" t="s">
         <v>38</v>
       </c>
-      <c r="D552" t="s">
+      <c r="B553" s="159" t="s">
+        <v>1</v>
+      </c>
+      <c r="C553" s="159" t="s">
+        <v>430</v>
+      </c>
+      <c r="D553" s="159" t="s">
         <v>35</v>
       </c>
-      <c r="E552" t="str">
-        <f>Foderstater!U$99</f>
-        <v>fish meal</v>
-      </c>
-      <c r="H552" t="s">
+      <c r="H553" s="159" t="s">
         <v>326</v>
       </c>
-      <c r="I552" s="13">
-        <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E552,Foderstater!$U$63:$U$100,0),MATCH(A552&amp;C552&amp;D552,Foderstater!$X$62:$AI$62,0))</f>
+      <c r="I553" s="159">
         <v>0</v>
       </c>
-    </row>
-    <row r="553" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A553" t="s">
+      <c r="J553" s="159"/>
+      <c r="K553" s="159" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="554" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A554" t="s">
         <v>38</v>
       </c>
-      <c r="D553" t="s">
+      <c r="B554" t="s">
+        <v>1</v>
+      </c>
+      <c r="C554" t="s">
+        <v>430</v>
+      </c>
+      <c r="D554" t="s">
         <v>35</v>
       </c>
-      <c r="E553" t="str">
-        <f>Foderstater!U$100</f>
-        <v>minerals</v>
-      </c>
-      <c r="H553" t="s">
+      <c r="E554" t="str">
+        <f>Foderstater!U$63</f>
+        <v>ley silage, 1st cut</v>
+      </c>
+      <c r="H554" t="s">
         <v>326</v>
       </c>
-      <c r="I553" s="13">
-        <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E553,Foderstater!$U$63:$U$100,0),MATCH(A553&amp;C553&amp;D553,Foderstater!$X$62:$AI$62,0))</f>
-        <v>0.59452761799360676</v>
-      </c>
-    </row>
-    <row r="554" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="I554" s="13">
+        <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E554,Foderstater!$U$63:$U$100,0),MATCH(A554&amp;C554&amp;D554,Foderstater!$X$62:$AI$62,0))</f>
+        <v>56.070538180908102</v>
+      </c>
       <c r="J554" s="159"/>
       <c r="K554" s="159"/>
     </row>
     <row r="555" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A555" s="159" t="s">
+      <c r="A555" t="s">
         <v>38</v>
       </c>
-      <c r="B555" s="159" t="s">
+      <c r="B555" t="s">
         <v>1</v>
       </c>
-      <c r="C555" s="159" t="s">
+      <c r="C555" t="s">
         <v>430</v>
       </c>
-      <c r="D555" s="159" t="s">
+      <c r="D555" t="s">
         <v>35</v>
       </c>
-      <c r="H555" s="159" t="s">
+      <c r="E555" t="str">
+        <f>Foderstater!U$64</f>
+        <v>ley silage, regrowth</v>
+      </c>
+      <c r="H555" t="s">
         <v>326</v>
       </c>
-      <c r="I555" s="159">
+      <c r="I555" s="13">
+        <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E555,Foderstater!$U$63:$U$100,0),MATCH(A555&amp;C555&amp;D555,Foderstater!$X$62:$AI$62,0))</f>
         <v>0</v>
       </c>
       <c r="J555" s="159"/>
-      <c r="K555" s="159" t="s">
-        <v>424</v>
-      </c>
+      <c r="K555" s="159"/>
     </row>
     <row r="556" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A556" t="s">
@@ -28661,15 +28715,15 @@
         <v>35</v>
       </c>
       <c r="E556" t="str">
-        <f>Foderstater!U$63</f>
-        <v>ley silage, 1st cut</v>
+        <f>Foderstater!U$65</f>
+        <v>other silage</v>
       </c>
       <c r="H556" t="s">
         <v>326</v>
       </c>
       <c r="I556" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E556,Foderstater!$U$63:$U$100,0),MATCH(A556&amp;C556&amp;D556,Foderstater!$X$62:$AI$62,0))</f>
-        <v>56.070538180908102</v>
+        <v>0</v>
       </c>
       <c r="J556" s="159"/>
       <c r="K556" s="159"/>
@@ -28688,15 +28742,15 @@
         <v>35</v>
       </c>
       <c r="E557" t="str">
-        <f>Foderstater!U$64</f>
-        <v>ley silage, regrowth</v>
+        <f>Foderstater!U$66</f>
+        <v>maize silage</v>
       </c>
       <c r="H557" t="s">
         <v>326</v>
       </c>
       <c r="I557" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E557,Foderstater!$U$63:$U$100,0),MATCH(A557&amp;C557&amp;D557,Foderstater!$X$62:$AI$62,0))</f>
-        <v>0</v>
+        <v>13.09114711176567</v>
       </c>
       <c r="J557" s="159"/>
       <c r="K557" s="159"/>
@@ -28715,8 +28769,8 @@
         <v>35</v>
       </c>
       <c r="E558" t="str">
-        <f>Foderstater!U$65</f>
-        <v>other silage</v>
+        <f>Foderstater!U$67</f>
+        <v>straw</v>
       </c>
       <c r="H558" t="s">
         <v>326</v>
@@ -28742,15 +28796,15 @@
         <v>35</v>
       </c>
       <c r="E559" t="str">
-        <f>Foderstater!U$66</f>
-        <v>maize silage</v>
+        <f>Foderstater!U$68</f>
+        <v>grazing</v>
       </c>
       <c r="H559" t="s">
         <v>326</v>
       </c>
       <c r="I559" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E559,Foderstater!$U$63:$U$100,0),MATCH(A559&amp;C559&amp;D559,Foderstater!$X$62:$AI$62,0))</f>
-        <v>13.09114711176567</v>
+        <v>0</v>
       </c>
       <c r="J559" s="159"/>
       <c r="K559" s="159"/>
@@ -28769,15 +28823,15 @@
         <v>35</v>
       </c>
       <c r="E560" t="str">
-        <f>Foderstater!U$67</f>
-        <v>straw</v>
+        <f>Foderstater!U$69</f>
+        <v>wheat</v>
       </c>
       <c r="H560" t="s">
         <v>326</v>
       </c>
       <c r="I560" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E560,Foderstater!$U$63:$U$100,0),MATCH(A560&amp;C560&amp;D560,Foderstater!$X$62:$AI$62,0))</f>
-        <v>0</v>
+        <v>6.338193642704308</v>
       </c>
       <c r="J560" s="159"/>
       <c r="K560" s="159"/>
@@ -28796,15 +28850,15 @@
         <v>35</v>
       </c>
       <c r="E561" t="str">
-        <f>Foderstater!U$68</f>
-        <v>grazing</v>
+        <f>Foderstater!U$70</f>
+        <v>barley</v>
       </c>
       <c r="H561" t="s">
         <v>326</v>
       </c>
       <c r="I561" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E561,Foderstater!$U$63:$U$100,0),MATCH(A561&amp;C561&amp;D561,Foderstater!$X$62:$AI$62,0))</f>
-        <v>0</v>
+        <v>13.009738603465815</v>
       </c>
       <c r="J561" s="159"/>
       <c r="K561" s="159"/>
@@ -28823,15 +28877,15 @@
         <v>35</v>
       </c>
       <c r="E562" t="str">
-        <f>Foderstater!U$69</f>
-        <v>wheat</v>
+        <f>Foderstater!U$71</f>
+        <v>oats</v>
       </c>
       <c r="H562" t="s">
         <v>326</v>
       </c>
       <c r="I562" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E562,Foderstater!$U$63:$U$100,0),MATCH(A562&amp;C562&amp;D562,Foderstater!$X$62:$AI$62,0))</f>
-        <v>6.338193642704308</v>
+        <v>2.6885792015166539</v>
       </c>
       <c r="J562" s="159"/>
       <c r="K562" s="159"/>
@@ -28850,15 +28904,15 @@
         <v>35</v>
       </c>
       <c r="E563" t="str">
-        <f>Foderstater!U$70</f>
-        <v>barley</v>
+        <f>Foderstater!U$72</f>
+        <v>triticale</v>
       </c>
       <c r="H563" t="s">
         <v>326</v>
       </c>
       <c r="I563" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E563,Foderstater!$U$63:$U$100,0),MATCH(A563&amp;C563&amp;D563,Foderstater!$X$62:$AI$62,0))</f>
-        <v>13.009738603465815</v>
+        <v>5.0332855432745562</v>
       </c>
       <c r="J563" s="159"/>
       <c r="K563" s="159"/>
@@ -28877,15 +28931,15 @@
         <v>35</v>
       </c>
       <c r="E564" t="str">
-        <f>Foderstater!U$71</f>
-        <v>oats</v>
+        <f>Foderstater!U$73</f>
+        <v>rye</v>
       </c>
       <c r="H564" t="s">
         <v>326</v>
       </c>
       <c r="I564" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E564,Foderstater!$U$63:$U$100,0),MATCH(A564&amp;C564&amp;D564,Foderstater!$X$62:$AI$62,0))</f>
-        <v>2.6885792015166539</v>
+        <v>0</v>
       </c>
       <c r="J564" s="159"/>
       <c r="K564" s="159"/>
@@ -28904,15 +28958,15 @@
         <v>35</v>
       </c>
       <c r="E565" t="str">
-        <f>Foderstater!U$72</f>
-        <v>triticale</v>
+        <f>Foderstater!U$74</f>
+        <v>maize</v>
       </c>
       <c r="H565" t="s">
         <v>326</v>
       </c>
       <c r="I565" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E565,Foderstater!$U$63:$U$100,0),MATCH(A565&amp;C565&amp;D565,Foderstater!$X$62:$AI$62,0))</f>
-        <v>5.0332855432745562</v>
+        <v>0</v>
       </c>
       <c r="J565" s="159"/>
       <c r="K565" s="159"/>
@@ -28931,15 +28985,15 @@
         <v>35</v>
       </c>
       <c r="E566" t="str">
-        <f>Foderstater!U$73</f>
-        <v>rye</v>
+        <f>Foderstater!U$75</f>
+        <v>peas</v>
       </c>
       <c r="H566" t="s">
         <v>326</v>
       </c>
       <c r="I566" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E566,Foderstater!$U$63:$U$100,0),MATCH(A566&amp;C566&amp;D566,Foderstater!$X$62:$AI$62,0))</f>
-        <v>0</v>
+        <v>1.6370482011197791</v>
       </c>
       <c r="J566" s="159"/>
       <c r="K566" s="159"/>
@@ -28958,15 +29012,15 @@
         <v>35</v>
       </c>
       <c r="E567" t="str">
-        <f>Foderstater!U$74</f>
-        <v>maize</v>
+        <f>Foderstater!U$76</f>
+        <v>broad beans</v>
       </c>
       <c r="H567" t="s">
         <v>326</v>
       </c>
       <c r="I567" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E567,Foderstater!$U$63:$U$100,0),MATCH(A567&amp;C567&amp;D567,Foderstater!$X$62:$AI$62,0))</f>
-        <v>0</v>
+        <v>1.5539189073731028</v>
       </c>
       <c r="J567" s="159"/>
       <c r="K567" s="159"/>
@@ -28985,15 +29039,15 @@
         <v>35</v>
       </c>
       <c r="E568" t="str">
-        <f>Foderstater!U$75</f>
-        <v>peas</v>
+        <f>Foderstater!U$77</f>
+        <v>rapeseed</v>
       </c>
       <c r="H568" t="s">
         <v>326</v>
       </c>
       <c r="I568" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E568,Foderstater!$U$63:$U$100,0),MATCH(A568&amp;C568&amp;D568,Foderstater!$X$62:$AI$62,0))</f>
-        <v>1.6370482011197791</v>
+        <v>0</v>
       </c>
       <c r="J568" s="159"/>
       <c r="K568" s="159"/>
@@ -29012,15 +29066,15 @@
         <v>35</v>
       </c>
       <c r="E569" t="str">
-        <f>Foderstater!U$76</f>
-        <v>broad beans</v>
+        <f>Foderstater!U$78</f>
+        <v>linseed</v>
       </c>
       <c r="H569" t="s">
         <v>326</v>
       </c>
       <c r="I569" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E569,Foderstater!$U$63:$U$100,0),MATCH(A569&amp;C569&amp;D569,Foderstater!$X$62:$AI$62,0))</f>
-        <v>1.5539189073731028</v>
+        <v>0</v>
       </c>
       <c r="J569" s="159"/>
       <c r="K569" s="159"/>
@@ -29039,8 +29093,8 @@
         <v>35</v>
       </c>
       <c r="E570" t="str">
-        <f>Foderstater!U$77</f>
-        <v>rapeseed</v>
+        <f>Foderstater!U$79</f>
+        <v>vegetable oils</v>
       </c>
       <c r="H570" t="s">
         <v>326</v>
@@ -29066,8 +29120,8 @@
         <v>35</v>
       </c>
       <c r="E571" t="str">
-        <f>Foderstater!U$78</f>
-        <v>linseed</v>
+        <f>Foderstater!U$80</f>
+        <v>soybeans</v>
       </c>
       <c r="H571" t="s">
         <v>326</v>
@@ -29093,8 +29147,8 @@
         <v>35</v>
       </c>
       <c r="E572" t="str">
-        <f>Foderstater!U$79</f>
-        <v>vegetable oils</v>
+        <f>Foderstater!U$81</f>
+        <v>soybean meal</v>
       </c>
       <c r="H572" t="s">
         <v>326</v>
@@ -29120,8 +29174,8 @@
         <v>35</v>
       </c>
       <c r="E573" t="str">
-        <f>Foderstater!U$80</f>
-        <v>soybeans</v>
+        <f>Foderstater!U$82</f>
+        <v>soybean protein concentrate</v>
       </c>
       <c r="H573" t="s">
         <v>326</v>
@@ -29147,8 +29201,8 @@
         <v>35</v>
       </c>
       <c r="E574" t="str">
-        <f>Foderstater!U$81</f>
-        <v>soybean meal</v>
+        <f>Foderstater!U$83</f>
+        <v>rapeseed meal</v>
       </c>
       <c r="H574" t="s">
         <v>326</v>
@@ -29174,8 +29228,8 @@
         <v>35</v>
       </c>
       <c r="E575" t="str">
-        <f>Foderstater!U$82</f>
-        <v>soybean protein concentrate</v>
+        <f>Foderstater!U$84</f>
+        <v>sunflower seed meal</v>
       </c>
       <c r="H575" t="s">
         <v>326</v>
@@ -29184,8 +29238,6 @@
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E575,Foderstater!$U$63:$U$100,0),MATCH(A575&amp;C575&amp;D575,Foderstater!$X$62:$AI$62,0))</f>
         <v>0</v>
       </c>
-      <c r="J575" s="159"/>
-      <c r="K575" s="159"/>
     </row>
     <row r="576" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A576" t="s">
@@ -29201,8 +29253,8 @@
         <v>35</v>
       </c>
       <c r="E576" t="str">
-        <f>Foderstater!U$83</f>
-        <v>rapeseed meal</v>
+        <f>Foderstater!U$85</f>
+        <v>palm kernel expeller</v>
       </c>
       <c r="H576" t="s">
         <v>326</v>
@@ -29211,8 +29263,6 @@
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E576,Foderstater!$U$63:$U$100,0),MATCH(A576&amp;C576&amp;D576,Foderstater!$X$62:$AI$62,0))</f>
         <v>0</v>
       </c>
-      <c r="J576" s="159"/>
-      <c r="K576" s="159"/>
     </row>
     <row r="577" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A577" t="s">
@@ -29228,8 +29278,8 @@
         <v>35</v>
       </c>
       <c r="E577" t="str">
-        <f>Foderstater!U$84</f>
-        <v>sunflower seed meal</v>
+        <f>Foderstater!U$86</f>
+        <v>luzern meal</v>
       </c>
       <c r="H577" t="s">
         <v>326</v>
@@ -29253,8 +29303,8 @@
         <v>35</v>
       </c>
       <c r="E578" t="str">
-        <f>Foderstater!U$85</f>
-        <v>palm kernel expeller</v>
+        <f>Foderstater!U$87</f>
+        <v>wheat bran</v>
       </c>
       <c r="H578" t="s">
         <v>326</v>
@@ -29278,8 +29328,8 @@
         <v>35</v>
       </c>
       <c r="E579" t="str">
-        <f>Foderstater!U$86</f>
-        <v>luzern meal</v>
+        <f>Foderstater!U$88</f>
+        <v>wheat bran, fine</v>
       </c>
       <c r="H579" t="s">
         <v>326</v>
@@ -29303,8 +29353,8 @@
         <v>35</v>
       </c>
       <c r="E580" t="str">
-        <f>Foderstater!U$87</f>
-        <v>wheat bran</v>
+        <f>Foderstater!U$89</f>
+        <v>oat hulls</v>
       </c>
       <c r="H580" t="s">
         <v>326</v>
@@ -29328,8 +29378,8 @@
         <v>35</v>
       </c>
       <c r="E581" t="str">
-        <f>Foderstater!U$88</f>
-        <v>wheat bran, fine</v>
+        <f>Foderstater!U$90</f>
+        <v>oat bran</v>
       </c>
       <c r="H581" t="s">
         <v>326</v>
@@ -29353,8 +29403,8 @@
         <v>35</v>
       </c>
       <c r="E582" t="str">
-        <f>Foderstater!U$89</f>
-        <v>oat hulls</v>
+        <f>Foderstater!U$91</f>
+        <v>rye bran</v>
       </c>
       <c r="H582" t="s">
         <v>326</v>
@@ -29378,8 +29428,8 @@
         <v>35</v>
       </c>
       <c r="E583" t="str">
-        <f>Foderstater!U$90</f>
-        <v>oat bran</v>
+        <f>Foderstater!U$92</f>
+        <v>wheat distillers grain, dry</v>
       </c>
       <c r="H583" t="s">
         <v>326</v>
@@ -29403,8 +29453,8 @@
         <v>35</v>
       </c>
       <c r="E584" t="str">
-        <f>Foderstater!U$91</f>
-        <v>rye bran</v>
+        <f>Foderstater!U$93</f>
+        <v>barley brewers grain</v>
       </c>
       <c r="H584" t="s">
         <v>326</v>
@@ -29428,8 +29478,8 @@
         <v>35</v>
       </c>
       <c r="E585" t="str">
-        <f>Foderstater!U$92</f>
-        <v>wheat distillers grain, dry</v>
+        <f>Foderstater!U$94</f>
+        <v>maize gluten meal</v>
       </c>
       <c r="H585" t="s">
         <v>326</v>
@@ -29453,8 +29503,8 @@
         <v>35</v>
       </c>
       <c r="E586" t="str">
-        <f>Foderstater!U$93</f>
-        <v>barley brewers grain</v>
+        <f>Foderstater!U$95</f>
+        <v>sugar beet molasses</v>
       </c>
       <c r="H586" t="s">
         <v>326</v>
@@ -29478,8 +29528,8 @@
         <v>35</v>
       </c>
       <c r="E587" t="str">
-        <f>Foderstater!U$94</f>
-        <v>maize gluten meal</v>
+        <f>Foderstater!U$96</f>
+        <v>sugar beet pulp</v>
       </c>
       <c r="H587" t="s">
         <v>326</v>
@@ -29503,8 +29553,8 @@
         <v>35</v>
       </c>
       <c r="E588" t="str">
-        <f>Foderstater!U$95</f>
-        <v>sugar beet molasses</v>
+        <f>Foderstater!U$97</f>
+        <v>whey powder</v>
       </c>
       <c r="H588" t="s">
         <v>326</v>
@@ -29528,8 +29578,8 @@
         <v>35</v>
       </c>
       <c r="E589" t="str">
-        <f>Foderstater!U$96</f>
-        <v>sugar beet pulp</v>
+        <f>Foderstater!U$98</f>
+        <v>potatoe protein</v>
       </c>
       <c r="H589" t="s">
         <v>326</v>
@@ -29553,8 +29603,8 @@
         <v>35</v>
       </c>
       <c r="E590" t="str">
-        <f>Foderstater!U$97</f>
-        <v>whey powder</v>
+        <f>Foderstater!U$99</f>
+        <v>fish meal</v>
       </c>
       <c r="H590" t="s">
         <v>326</v>
@@ -29578,89 +29628,85 @@
         <v>35</v>
       </c>
       <c r="E591" t="str">
-        <f>Foderstater!U$98</f>
-        <v>potatoe protein</v>
+        <f>Foderstater!U$100</f>
+        <v>minerals</v>
       </c>
       <c r="H591" t="s">
         <v>326</v>
       </c>
       <c r="I591" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E591,Foderstater!$U$63:$U$100,0),MATCH(A591&amp;C591&amp;D591,Foderstater!$X$62:$AI$62,0))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="592" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A592" t="s">
+        <v>0.57755060787201484</v>
+      </c>
+    </row>
+    <row r="593" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A593" s="158" t="s">
+        <v>305</v>
+      </c>
+      <c r="B593" s="158"/>
+      <c r="C593" s="158"/>
+      <c r="D593" s="95"/>
+      <c r="E593" s="95"/>
+      <c r="F593" s="95"/>
+      <c r="G593" s="95"/>
+      <c r="H593" s="95"/>
+      <c r="I593" s="95"/>
+      <c r="J593" s="95"/>
+      <c r="K593" s="95"/>
+      <c r="L593" s="95"/>
+    </row>
+    <row r="594" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A594" s="93" t="s">
+        <v>2</v>
+      </c>
+      <c r="D594" s="93" t="s">
+        <v>18</v>
+      </c>
+      <c r="E594" s="93"/>
+      <c r="F594" s="93"/>
+      <c r="G594" s="93"/>
+      <c r="H594" s="93" t="s">
+        <v>40</v>
+      </c>
+      <c r="I594" s="93">
+        <v>7.1</v>
+      </c>
+      <c r="J594" s="93" t="s">
+        <v>4</v>
+      </c>
+      <c r="K594" s="93"/>
+      <c r="L594" s="93" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="595" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A595" s="93" t="s">
         <v>38</v>
       </c>
-      <c r="B592" t="s">
-        <v>1</v>
-      </c>
-      <c r="C592" t="s">
-        <v>430</v>
-      </c>
-      <c r="D592" t="s">
-        <v>35</v>
-      </c>
-      <c r="E592" t="str">
-        <f>Foderstater!U$99</f>
-        <v>fish meal</v>
-      </c>
-      <c r="H592" t="s">
-        <v>326</v>
-      </c>
-      <c r="I592" s="13">
-        <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E592,Foderstater!$U$63:$U$100,0),MATCH(A592&amp;C592&amp;D592,Foderstater!$X$62:$AI$62,0))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="593" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A593" t="s">
-        <v>38</v>
-      </c>
-      <c r="B593" t="s">
-        <v>1</v>
-      </c>
-      <c r="C593" t="s">
-        <v>430</v>
-      </c>
-      <c r="D593" t="s">
-        <v>35</v>
-      </c>
-      <c r="E593" t="str">
-        <f>Foderstater!U$100</f>
-        <v>minerals</v>
-      </c>
-      <c r="H593" t="s">
-        <v>326</v>
-      </c>
-      <c r="I593" s="13">
-        <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E593,Foderstater!$U$63:$U$100,0),MATCH(A593&amp;C593&amp;D593,Foderstater!$X$62:$AI$62,0))</f>
-        <v>0.57755060787201484</v>
-      </c>
-    </row>
-    <row r="595" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A595" s="158" t="s">
-        <v>305</v>
-      </c>
-      <c r="B595" s="158"/>
-      <c r="C595" s="158"/>
-      <c r="D595" s="95"/>
-      <c r="E595" s="95"/>
-      <c r="F595" s="95"/>
-      <c r="G595" s="95"/>
-      <c r="H595" s="95"/>
-      <c r="I595" s="95"/>
-      <c r="J595" s="95"/>
-      <c r="K595" s="95"/>
-      <c r="L595" s="95"/>
+      <c r="D595" s="93" t="s">
+        <v>18</v>
+      </c>
+      <c r="E595" s="93"/>
+      <c r="F595" s="93"/>
+      <c r="G595" s="93"/>
+      <c r="H595" s="93" t="s">
+        <v>40</v>
+      </c>
+      <c r="I595" s="93">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="J595" s="93" t="s">
+        <v>4</v>
+      </c>
+      <c r="K595" s="93"/>
+      <c r="L595" s="93" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="596" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A596" s="93" t="s">
-        <v>2</v>
-      </c>
+      <c r="A596" s="93"/>
       <c r="D596" s="93" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="E596" s="93"/>
       <c r="F596" s="93"/>
@@ -29669,7 +29715,7 @@
         <v>40</v>
       </c>
       <c r="I596" s="93">
-        <v>7.1</v>
+        <v>5.7</v>
       </c>
       <c r="J596" s="93" t="s">
         <v>4</v>
@@ -29680,11 +29726,9 @@
       </c>
     </row>
     <row r="597" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A597" s="93" t="s">
-        <v>38</v>
-      </c>
+      <c r="A597" s="93"/>
       <c r="D597" s="93" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E597" s="93"/>
       <c r="F597" s="93"/>
@@ -29693,7 +29737,7 @@
         <v>40</v>
       </c>
       <c r="I597" s="93">
-        <v>5.0999999999999996</v>
+        <v>7.7</v>
       </c>
       <c r="J597" s="93" t="s">
         <v>4</v>
@@ -29706,7 +29750,7 @@
     <row r="598" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A598" s="93"/>
       <c r="D598" s="93" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E598" s="93"/>
       <c r="F598" s="93"/>
@@ -29715,12 +29759,14 @@
         <v>40</v>
       </c>
       <c r="I598" s="93">
-        <v>5.7</v>
+        <v>9.1</v>
       </c>
       <c r="J598" s="93" t="s">
         <v>4</v>
       </c>
-      <c r="K598" s="93"/>
+      <c r="K598" s="93" t="s">
+        <v>42</v>
+      </c>
       <c r="L598" s="93" t="s">
         <v>41</v>
       </c>
@@ -29728,7 +29774,7 @@
     <row r="599" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A599" s="93"/>
       <c r="D599" s="93" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="E599" s="93"/>
       <c r="F599" s="93"/>
@@ -29737,61 +29783,15 @@
         <v>40</v>
       </c>
       <c r="I599" s="93">
-        <v>7.7</v>
+        <v>9.1</v>
       </c>
       <c r="J599" s="93" t="s">
         <v>4</v>
       </c>
-      <c r="K599" s="93"/>
+      <c r="K599" s="93" t="s">
+        <v>42</v>
+      </c>
       <c r="L599" s="93" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="600" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A600" s="93"/>
-      <c r="D600" s="93" t="s">
-        <v>34</v>
-      </c>
-      <c r="E600" s="93"/>
-      <c r="F600" s="93"/>
-      <c r="G600" s="93"/>
-      <c r="H600" s="93" t="s">
-        <v>40</v>
-      </c>
-      <c r="I600" s="93">
-        <v>9.1</v>
-      </c>
-      <c r="J600" s="93" t="s">
-        <v>4</v>
-      </c>
-      <c r="K600" s="93" t="s">
-        <v>42</v>
-      </c>
-      <c r="L600" s="93" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="601" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A601" s="93"/>
-      <c r="D601" s="93" t="s">
-        <v>35</v>
-      </c>
-      <c r="E601" s="93"/>
-      <c r="F601" s="93"/>
-      <c r="G601" s="93"/>
-      <c r="H601" s="93" t="s">
-        <v>40</v>
-      </c>
-      <c r="I601" s="93">
-        <v>9.1</v>
-      </c>
-      <c r="J601" s="93" t="s">
-        <v>4</v>
-      </c>
-      <c r="K601" s="93" t="s">
-        <v>42</v>
-      </c>
-      <c r="L601" s="93" t="s">
         <v>41</v>
       </c>
     </row>
@@ -35996,49 +35996,49 @@
       </c>
       <c r="AB3" s="202"/>
       <c r="AC3" s="202"/>
-      <c r="AD3" s="261" t="s">
+      <c r="AD3" s="259" t="s">
         <v>540</v>
       </c>
-      <c r="AE3" s="262" t="s">
+      <c r="AE3" s="260" t="s">
         <v>542</v>
       </c>
-      <c r="AF3" s="261" t="s">
+      <c r="AF3" s="259" t="s">
         <v>544</v>
       </c>
-      <c r="AG3" s="262" t="s">
+      <c r="AG3" s="260" t="s">
         <v>546</v>
       </c>
-      <c r="AH3" s="261" t="s">
+      <c r="AH3" s="259" t="s">
         <v>547</v>
       </c>
-      <c r="AI3" s="262" t="s">
+      <c r="AI3" s="260" t="s">
         <v>549</v>
       </c>
-      <c r="AJ3" s="261" t="s">
+      <c r="AJ3" s="259" t="s">
         <v>550</v>
       </c>
-      <c r="AK3" s="262" t="s">
+      <c r="AK3" s="260" t="s">
         <v>551</v>
       </c>
-      <c r="AL3" s="261" t="s">
+      <c r="AL3" s="259" t="s">
         <v>553</v>
       </c>
-      <c r="AM3" s="262" t="s">
+      <c r="AM3" s="260" t="s">
         <v>554</v>
       </c>
-      <c r="AN3" s="261" t="s">
+      <c r="AN3" s="259" t="s">
         <v>574</v>
       </c>
-      <c r="AO3" s="262" t="s">
+      <c r="AO3" s="260" t="s">
         <v>556</v>
       </c>
-      <c r="AP3" s="261" t="s">
+      <c r="AP3" s="259" t="s">
         <v>557</v>
       </c>
-      <c r="AQ3" s="260" t="s">
+      <c r="AQ3" s="258" t="s">
         <v>578</v>
       </c>
-      <c r="AR3" s="259" t="s">
+      <c r="AR3" s="257" t="s">
         <v>573</v>
       </c>
     </row>
@@ -36089,21 +36089,21 @@
       <c r="AA4" s="201"/>
       <c r="AB4" s="202"/>
       <c r="AC4" s="202"/>
-      <c r="AD4" s="261"/>
-      <c r="AE4" s="262"/>
-      <c r="AF4" s="261"/>
-      <c r="AG4" s="262"/>
-      <c r="AH4" s="261"/>
-      <c r="AI4" s="262"/>
-      <c r="AJ4" s="261"/>
-      <c r="AK4" s="262"/>
-      <c r="AL4" s="261"/>
-      <c r="AM4" s="262"/>
-      <c r="AN4" s="261"/>
-      <c r="AO4" s="262"/>
-      <c r="AP4" s="261"/>
-      <c r="AQ4" s="260"/>
-      <c r="AR4" s="259"/>
+      <c r="AD4" s="259"/>
+      <c r="AE4" s="260"/>
+      <c r="AF4" s="259"/>
+      <c r="AG4" s="260"/>
+      <c r="AH4" s="259"/>
+      <c r="AI4" s="260"/>
+      <c r="AJ4" s="259"/>
+      <c r="AK4" s="260"/>
+      <c r="AL4" s="259"/>
+      <c r="AM4" s="260"/>
+      <c r="AN4" s="259"/>
+      <c r="AO4" s="260"/>
+      <c r="AP4" s="259"/>
+      <c r="AQ4" s="258"/>
+      <c r="AR4" s="257"/>
     </row>
     <row r="5" spans="2:44" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="209" t="s">
@@ -36184,21 +36184,21 @@
       <c r="AA5" s="201"/>
       <c r="AB5" s="202"/>
       <c r="AC5" s="202"/>
-      <c r="AD5" s="261"/>
-      <c r="AE5" s="262"/>
-      <c r="AF5" s="261"/>
-      <c r="AG5" s="262"/>
-      <c r="AH5" s="261"/>
-      <c r="AI5" s="262"/>
-      <c r="AJ5" s="261"/>
-      <c r="AK5" s="262"/>
-      <c r="AL5" s="261"/>
-      <c r="AM5" s="262"/>
-      <c r="AN5" s="261"/>
-      <c r="AO5" s="262"/>
-      <c r="AP5" s="261"/>
-      <c r="AQ5" s="260"/>
-      <c r="AR5" s="259" t="s">
+      <c r="AD5" s="259"/>
+      <c r="AE5" s="260"/>
+      <c r="AF5" s="259"/>
+      <c r="AG5" s="260"/>
+      <c r="AH5" s="259"/>
+      <c r="AI5" s="260"/>
+      <c r="AJ5" s="259"/>
+      <c r="AK5" s="260"/>
+      <c r="AL5" s="259"/>
+      <c r="AM5" s="260"/>
+      <c r="AN5" s="259"/>
+      <c r="AO5" s="260"/>
+      <c r="AP5" s="259"/>
+      <c r="AQ5" s="258"/>
+      <c r="AR5" s="257" t="s">
         <v>572</v>
       </c>
     </row>
@@ -37370,7 +37370,7 @@
         <v>3968</v>
       </c>
       <c r="E20" s="239">
-        <f t="shared" ref="D20:Z20" si="0">SUM(E6:E18)</f>
+        <f t="shared" ref="E20:Z20" si="0">SUM(E6:E18)</f>
         <v>4002</v>
       </c>
       <c r="F20" s="239">
@@ -37633,23 +37633,23 @@
       <c r="N23" s="169"/>
       <c r="O23" s="169"/>
       <c r="P23" s="169"/>
-      <c r="Q23" s="258" t="s">
+      <c r="Q23" s="262" t="s">
         <v>593</v>
       </c>
-      <c r="R23" s="258" t="s">
+      <c r="R23" s="262" t="s">
         <v>594</v>
       </c>
-      <c r="S23" s="258" t="s">
+      <c r="S23" s="262" t="s">
         <v>581</v>
       </c>
-      <c r="T23" s="257" t="s">
+      <c r="T23" s="261" t="s">
         <v>303</v>
       </c>
-      <c r="U23" s="257"/>
-      <c r="V23" s="257" t="s">
+      <c r="U23" s="261"/>
+      <c r="V23" s="261" t="s">
         <v>304</v>
       </c>
-      <c r="W23" s="257"/>
+      <c r="W23" s="261"/>
       <c r="X23" s="168" t="s">
         <v>479</v>
       </c>
@@ -37674,9 +37674,9 @@
       <c r="P24" s="170" t="s">
         <v>480</v>
       </c>
-      <c r="Q24" s="258"/>
-      <c r="R24" s="258"/>
-      <c r="S24" s="258"/>
+      <c r="Q24" s="262"/>
+      <c r="R24" s="262"/>
+      <c r="S24" s="262"/>
       <c r="T24" s="244" t="s">
         <v>480</v>
       </c>
@@ -44294,6 +44294,11 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="V23:W23"/>
+    <mergeCell ref="T23:U23"/>
+    <mergeCell ref="Q23:Q24"/>
+    <mergeCell ref="R23:R24"/>
+    <mergeCell ref="S23:S24"/>
     <mergeCell ref="AR3:AR5"/>
     <mergeCell ref="AQ3:AQ5"/>
     <mergeCell ref="AD3:AD5"/>
@@ -44309,11 +44314,6 @@
     <mergeCell ref="AN3:AN5"/>
     <mergeCell ref="AO3:AO5"/>
     <mergeCell ref="AP3:AP5"/>
-    <mergeCell ref="V23:W23"/>
-    <mergeCell ref="T23:U23"/>
-    <mergeCell ref="Q23:Q24"/>
-    <mergeCell ref="R23:R24"/>
-    <mergeCell ref="S23:S24"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/data/default/CattleHerd.xlsx
+++ b/data/default/CattleHerd.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="18360" windowHeight="6705" tabRatio="846" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="18360" windowHeight="6705" tabRatio="846" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="references" sheetId="13" r:id="rId1"/>
@@ -144,7 +144,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4205" uniqueCount="616">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4217" uniqueCount="624">
   <si>
     <t>value</t>
   </si>
@@ -1691,9 +1691,6 @@
     <t>Assumes same as dairy cows</t>
   </si>
   <si>
-    <t>Ahlgren et al. (2022) Miljöpåverkan av svensk nöt- och lammköttsproduktion</t>
-  </si>
-  <si>
     <t>Växa Husdjursstatistik 2020, tab 32</t>
   </si>
   <si>
@@ -1995,6 +1992,33 @@
   <si>
     <t>Set to give ~7 kg/calf/day</t>
   </si>
+  <si>
+    <t>Ahlgren, S., Behaderovic, D., Wirsenius, S., Carlsson, A., Hessle, A. Toräng, P., Seeman, A., den Braver, T. &amp;  et al. Kvarnbäck, O. (2022) Miljöpåverkan av svensk nöt- och lammköttsproduktion. RISE</t>
+  </si>
+  <si>
+    <t>Ahlgren et al. (2022)</t>
+  </si>
+  <si>
+    <t>agricultrual statistics</t>
+  </si>
+  <si>
+    <t>grazing factor:</t>
+  </si>
+  <si>
+    <t>ley factor:</t>
+  </si>
+  <si>
+    <t>Grazing share (% of roughage):</t>
+  </si>
+  <si>
+    <t>Grazing factor set to align 'Ley for fodder'</t>
+  </si>
+  <si>
+    <t>Einarsson et al 2022 share grazing of roughage for dairy cows</t>
+  </si>
+  <si>
+    <t>and 'Ley for grazing' areas better to</t>
+  </si>
 </sst>
 </file>
 
@@ -2007,7 +2031,7 @@
     <numFmt numFmtId="167" formatCode="0.000"/>
     <numFmt numFmtId="168" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="45" x14ac:knownFonts="1">
+  <fonts count="47" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2338,8 +2362,23 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="42">
+  <fills count="43">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2570,6 +2609,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2942,7 +2987,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="44" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="267">
+  <cellXfs count="275">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -3354,12 +3399,6 @@
     <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="43"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="38" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="40" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="40" fillId="41" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -3372,6 +3411,26 @@
     <xf numFmtId="0" fontId="40" fillId="40" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="38" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="40" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="46" fillId="42" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="46" fillId="42" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="45" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="44">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -15476,17 +15535,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:B3"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B2" s="109" t="s">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" s="109" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="3" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B3" t="s">
-        <v>604</v>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>615</v>
       </c>
     </row>
   </sheetData>
@@ -16747,7 +16811,7 @@
         <v>312</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="G1" s="6" t="s">
         <v>319</v>
@@ -16837,7 +16901,7 @@
         <v>1</v>
       </c>
       <c r="I5" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="J5" s="111">
         <v>8</v>
@@ -16846,7 +16910,7 @@
         <v>9</v>
       </c>
       <c r="L5" s="93" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="M5" t="s">
         <v>282</v>
@@ -16923,7 +16987,7 @@
         <v>5</v>
       </c>
       <c r="I9" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="J9" s="111">
         <v>8</v>
@@ -16932,7 +16996,7 @@
         <v>9</v>
       </c>
       <c r="L9" s="93" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="M9" t="s">
         <v>282</v>
@@ -17011,7 +17075,7 @@
         <v>41</v>
       </c>
       <c r="L13" s="260" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="14" spans="1:16" s="32" customFormat="1" x14ac:dyDescent="0.25">
@@ -17019,7 +17083,7 @@
         <v>38</v>
       </c>
       <c r="I14" s="32" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="J14" s="259">
         <v>0</v>
@@ -17402,7 +17466,7 @@
         <v>7</v>
       </c>
       <c r="M37" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.25">
@@ -18020,7 +18084,7 @@
         <v>10</v>
       </c>
       <c r="M66" t="s">
-        <v>515</v>
+        <v>616</v>
       </c>
     </row>
     <row r="67" spans="1:13" x14ac:dyDescent="0.25">
@@ -18043,7 +18107,7 @@
         <v>22</v>
       </c>
       <c r="M67" t="s">
-        <v>515</v>
+        <v>616</v>
       </c>
     </row>
     <row r="68" spans="1:13" x14ac:dyDescent="0.25">
@@ -18066,7 +18130,7 @@
         <v>24</v>
       </c>
       <c r="M68" t="s">
-        <v>515</v>
+        <v>616</v>
       </c>
     </row>
     <row r="69" spans="1:13" x14ac:dyDescent="0.25">
@@ -18089,7 +18153,7 @@
         <v>22</v>
       </c>
       <c r="M69" t="s">
-        <v>515</v>
+        <v>616</v>
       </c>
     </row>
     <row r="70" spans="1:13" x14ac:dyDescent="0.25">
@@ -18112,7 +18176,7 @@
         <v>24</v>
       </c>
       <c r="M70" t="s">
-        <v>515</v>
+        <v>616</v>
       </c>
     </row>
     <row r="71" spans="1:13" x14ac:dyDescent="0.25">
@@ -18135,7 +18199,7 @@
         <v>28</v>
       </c>
       <c r="M71" t="s">
-        <v>515</v>
+        <v>616</v>
       </c>
     </row>
     <row r="72" spans="1:13" x14ac:dyDescent="0.25">
@@ -18158,7 +18222,7 @@
         <v>24</v>
       </c>
       <c r="M72" t="s">
-        <v>515</v>
+        <v>616</v>
       </c>
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.25">
@@ -18181,7 +18245,7 @@
         <v>28</v>
       </c>
       <c r="M73" t="s">
-        <v>515</v>
+        <v>616</v>
       </c>
     </row>
     <row r="74" spans="1:13" x14ac:dyDescent="0.25">
@@ -18204,7 +18268,7 @@
         <v>24</v>
       </c>
       <c r="M74" t="s">
-        <v>515</v>
+        <v>616</v>
       </c>
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.25">
@@ -18244,7 +18308,7 @@
         <v>10</v>
       </c>
       <c r="M76" t="s">
-        <v>515</v>
+        <v>616</v>
       </c>
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.25">
@@ -18267,7 +18331,7 @@
         <v>22</v>
       </c>
       <c r="M77" t="s">
-        <v>515</v>
+        <v>616</v>
       </c>
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.25">
@@ -18290,7 +18354,7 @@
         <v>39</v>
       </c>
       <c r="M78" t="s">
-        <v>515</v>
+        <v>616</v>
       </c>
     </row>
     <row r="79" spans="1:13" x14ac:dyDescent="0.25">
@@ -18313,7 +18377,7 @@
         <v>22</v>
       </c>
       <c r="M79" t="s">
-        <v>515</v>
+        <v>616</v>
       </c>
     </row>
     <row r="80" spans="1:13" x14ac:dyDescent="0.25">
@@ -18336,7 +18400,7 @@
         <v>39</v>
       </c>
       <c r="M80" t="s">
-        <v>515</v>
+        <v>616</v>
       </c>
     </row>
     <row r="81" spans="1:13" x14ac:dyDescent="0.25">
@@ -18359,7 +18423,7 @@
         <v>28</v>
       </c>
       <c r="M81" t="s">
-        <v>515</v>
+        <v>616</v>
       </c>
     </row>
     <row r="82" spans="1:13" x14ac:dyDescent="0.25">
@@ -18382,7 +18446,7 @@
         <v>39</v>
       </c>
       <c r="M82" t="s">
-        <v>515</v>
+        <v>616</v>
       </c>
     </row>
     <row r="83" spans="1:13" x14ac:dyDescent="0.25">
@@ -18405,7 +18469,7 @@
         <v>28</v>
       </c>
       <c r="M83" t="s">
-        <v>515</v>
+        <v>616</v>
       </c>
     </row>
     <row r="84" spans="1:13" x14ac:dyDescent="0.25">
@@ -18428,7 +18492,7 @@
         <v>39</v>
       </c>
       <c r="M84" t="s">
-        <v>515</v>
+        <v>616</v>
       </c>
     </row>
     <row r="86" spans="1:13" x14ac:dyDescent="0.25">
@@ -19011,7 +19075,7 @@
     </row>
     <row r="118" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A118" s="257" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B118" s="158"/>
       <c r="C118" s="158"/>
@@ -19037,12 +19101,12 @@
       </c>
       <c r="E119" s="110"/>
       <c r="F119" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="G119" s="110"/>
       <c r="H119" s="110"/>
       <c r="I119" s="110" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="J119" s="110">
         <v>5</v>
@@ -19052,7 +19116,7 @@
       </c>
       <c r="L119" s="110"/>
       <c r="M119" s="110" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="120" spans="1:13" x14ac:dyDescent="0.25">
@@ -19066,12 +19130,12 @@
       </c>
       <c r="E120" s="110"/>
       <c r="F120" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="G120" s="110"/>
       <c r="H120" s="110"/>
       <c r="I120" s="110" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="J120" s="110">
         <v>5.4</v>
@@ -19081,7 +19145,7 @@
       </c>
       <c r="L120" s="110"/>
       <c r="M120" s="110" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="121" spans="1:13" x14ac:dyDescent="0.25">
@@ -19095,12 +19159,12 @@
       </c>
       <c r="E121" s="110"/>
       <c r="F121" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="G121" s="110"/>
       <c r="H121" s="110"/>
       <c r="I121" s="110" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="J121" s="110">
         <v>4.9000000000000004</v>
@@ -19110,7 +19174,7 @@
       </c>
       <c r="L121" s="110"/>
       <c r="M121" s="110" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="122" spans="1:13" x14ac:dyDescent="0.25">
@@ -19124,12 +19188,12 @@
       </c>
       <c r="E122" s="110"/>
       <c r="F122" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="G122" s="110"/>
       <c r="H122" s="110"/>
       <c r="I122" s="110" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="J122" s="110">
         <v>5.0999999999999996</v>
@@ -19139,7 +19203,7 @@
       </c>
       <c r="L122" s="110"/>
       <c r="M122" s="110" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="123" spans="1:13" x14ac:dyDescent="0.25">
@@ -19153,12 +19217,12 @@
       </c>
       <c r="E123" s="110"/>
       <c r="F123" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="G123" s="110"/>
       <c r="H123" s="110"/>
       <c r="I123" s="110" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="J123" s="110">
         <v>4.9000000000000004</v>
@@ -19168,7 +19232,7 @@
       </c>
       <c r="L123" s="110"/>
       <c r="M123" s="110" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="124" spans="1:13" x14ac:dyDescent="0.25">
@@ -19182,12 +19246,12 @@
       </c>
       <c r="E124" s="110"/>
       <c r="F124" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="G124" s="110"/>
       <c r="H124" s="110"/>
       <c r="I124" s="110" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="J124" s="110">
         <v>5</v>
@@ -19197,7 +19261,7 @@
       </c>
       <c r="L124" s="110"/>
       <c r="M124" s="110" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="125" spans="1:13" x14ac:dyDescent="0.25">
@@ -19211,12 +19275,12 @@
       </c>
       <c r="E125" s="110"/>
       <c r="F125" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="G125" s="110"/>
       <c r="H125" s="110"/>
       <c r="I125" s="110" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="J125" s="110">
         <v>5</v>
@@ -19226,7 +19290,7 @@
       </c>
       <c r="L125" s="110"/>
       <c r="M125" s="110" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="126" spans="1:13" x14ac:dyDescent="0.25">
@@ -19240,12 +19304,12 @@
       </c>
       <c r="E126" s="110"/>
       <c r="F126" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="G126" s="110"/>
       <c r="H126" s="110"/>
       <c r="I126" s="110" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="J126" s="110">
         <v>3.1</v>
@@ -19255,7 +19319,7 @@
       </c>
       <c r="L126" s="110"/>
       <c r="M126" s="110" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="127" spans="1:13" x14ac:dyDescent="0.25">
@@ -19280,12 +19344,12 @@
       <c r="D128" s="110"/>
       <c r="E128" s="110"/>
       <c r="F128" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="G128" s="110"/>
       <c r="H128" s="110"/>
       <c r="I128" s="110" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="J128" s="110">
         <v>6.5</v>
@@ -19294,10 +19358,10 @@
         <v>4</v>
       </c>
       <c r="L128" s="110" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="M128" s="110" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="129" spans="1:13" x14ac:dyDescent="0.25">
@@ -19307,12 +19371,12 @@
       <c r="D129" s="110"/>
       <c r="E129" s="110"/>
       <c r="F129" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="G129" s="110"/>
       <c r="H129" s="110"/>
       <c r="I129" s="110" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="J129" s="110">
         <v>6.8</v>
@@ -19322,7 +19386,7 @@
       </c>
       <c r="L129" s="110"/>
       <c r="M129" s="110" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="130" spans="1:13" x14ac:dyDescent="0.25">
@@ -19332,12 +19396,12 @@
       <c r="D130" s="110"/>
       <c r="E130" s="110"/>
       <c r="F130" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="G130" s="110"/>
       <c r="H130" s="110"/>
       <c r="I130" s="110" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="J130" s="110">
         <v>6.2</v>
@@ -19347,7 +19411,7 @@
       </c>
       <c r="L130" s="110"/>
       <c r="M130" s="110" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="131" spans="1:13" x14ac:dyDescent="0.25">
@@ -19357,12 +19421,12 @@
       <c r="D131" s="110"/>
       <c r="E131" s="110"/>
       <c r="F131" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="G131" s="110"/>
       <c r="H131" s="110"/>
       <c r="I131" s="110" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="J131" s="110">
         <v>6.3</v>
@@ -19372,7 +19436,7 @@
       </c>
       <c r="L131" s="110"/>
       <c r="M131" s="110" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="132" spans="1:13" x14ac:dyDescent="0.25">
@@ -19382,12 +19446,12 @@
       <c r="D132" s="110"/>
       <c r="E132" s="110"/>
       <c r="F132" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="G132" s="110"/>
       <c r="H132" s="110"/>
       <c r="I132" s="110" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="J132" s="110">
         <v>6.5</v>
@@ -19397,7 +19461,7 @@
       </c>
       <c r="L132" s="110"/>
       <c r="M132" s="110" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="133" spans="1:13" x14ac:dyDescent="0.25">
@@ -19407,12 +19471,12 @@
       <c r="D133" s="110"/>
       <c r="E133" s="110"/>
       <c r="F133" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="G133" s="110"/>
       <c r="H133" s="110"/>
       <c r="I133" s="110" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="J133" s="110">
         <v>6</v>
@@ -19422,7 +19486,7 @@
       </c>
       <c r="L133" s="110"/>
       <c r="M133" s="110" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="134" spans="1:13" x14ac:dyDescent="0.25">
@@ -19432,12 +19496,12 @@
       <c r="D134" s="110"/>
       <c r="E134" s="110"/>
       <c r="F134" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="G134" s="110"/>
       <c r="H134" s="110"/>
       <c r="I134" s="110" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="J134" s="110">
         <v>5.4</v>
@@ -19447,7 +19511,7 @@
       </c>
       <c r="L134" s="110"/>
       <c r="M134" s="110" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="135" spans="1:13" x14ac:dyDescent="0.25">
@@ -19457,12 +19521,12 @@
       <c r="D135" s="110"/>
       <c r="E135" s="110"/>
       <c r="F135" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="G135" s="110"/>
       <c r="H135" s="110"/>
       <c r="I135" s="110" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="J135" s="110">
         <v>4.2</v>
@@ -19472,7 +19536,7 @@
       </c>
       <c r="L135" s="110"/>
       <c r="M135" s="110" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="136" spans="1:13" x14ac:dyDescent="0.25">
@@ -19499,12 +19563,12 @@
       </c>
       <c r="E137" s="110"/>
       <c r="F137" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="G137" s="110"/>
       <c r="H137" s="110"/>
       <c r="I137" s="110" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="J137" s="110">
         <v>4</v>
@@ -19514,7 +19578,7 @@
       </c>
       <c r="L137" s="110"/>
       <c r="M137" s="110" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="138" spans="1:13" x14ac:dyDescent="0.25">
@@ -19526,12 +19590,12 @@
       </c>
       <c r="E138" s="110"/>
       <c r="F138" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="G138" s="110"/>
       <c r="H138" s="110"/>
       <c r="I138" s="110" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="J138" s="110">
         <v>4.3</v>
@@ -19541,7 +19605,7 @@
       </c>
       <c r="L138" s="110"/>
       <c r="M138" s="110" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="139" spans="1:13" x14ac:dyDescent="0.25">
@@ -19553,12 +19617,12 @@
       </c>
       <c r="E139" s="110"/>
       <c r="F139" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="G139" s="110"/>
       <c r="H139" s="110"/>
       <c r="I139" s="110" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="J139" s="110">
         <v>4</v>
@@ -19568,7 +19632,7 @@
       </c>
       <c r="L139" s="110"/>
       <c r="M139" s="110" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="140" spans="1:13" x14ac:dyDescent="0.25">
@@ -19580,12 +19644,12 @@
       </c>
       <c r="E140" s="110"/>
       <c r="F140" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="G140" s="110"/>
       <c r="H140" s="110"/>
       <c r="I140" s="110" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="J140" s="110">
         <v>4.3</v>
@@ -19595,7 +19659,7 @@
       </c>
       <c r="L140" s="110"/>
       <c r="M140" s="110" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="141" spans="1:13" x14ac:dyDescent="0.25">
@@ -19607,12 +19671,12 @@
       </c>
       <c r="E141" s="110"/>
       <c r="F141" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="G141" s="110"/>
       <c r="H141" s="110"/>
       <c r="I141" s="110" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="J141" s="110">
         <v>4.7</v>
@@ -19622,7 +19686,7 @@
       </c>
       <c r="L141" s="110"/>
       <c r="M141" s="110" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="142" spans="1:13" x14ac:dyDescent="0.25">
@@ -19634,12 +19698,12 @@
       </c>
       <c r="E142" s="110"/>
       <c r="F142" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="G142" s="110"/>
       <c r="H142" s="110"/>
       <c r="I142" s="110" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="J142" s="110">
         <v>3.8</v>
@@ -19649,7 +19713,7 @@
       </c>
       <c r="L142" s="110"/>
       <c r="M142" s="110" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="143" spans="1:13" x14ac:dyDescent="0.25">
@@ -19661,12 +19725,12 @@
       </c>
       <c r="E143" s="110"/>
       <c r="F143" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="G143" s="110"/>
       <c r="H143" s="110"/>
       <c r="I143" s="110" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="J143" s="110">
         <v>3.9</v>
@@ -19676,7 +19740,7 @@
       </c>
       <c r="L143" s="110"/>
       <c r="M143" s="110" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="144" spans="1:13" x14ac:dyDescent="0.25">
@@ -19688,12 +19752,12 @@
       </c>
       <c r="E144" s="110"/>
       <c r="F144" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="G144" s="110"/>
       <c r="H144" s="110"/>
       <c r="I144" s="110" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="J144" s="110">
         <v>3.2</v>
@@ -19703,7 +19767,7 @@
       </c>
       <c r="L144" s="110"/>
       <c r="M144" s="110" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="145" spans="1:13" x14ac:dyDescent="0.25">
@@ -19730,12 +19794,12 @@
       </c>
       <c r="E146" s="110"/>
       <c r="F146" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="G146" s="110"/>
       <c r="H146" s="110"/>
       <c r="I146" s="110" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="J146" s="110">
         <v>0</v>
@@ -19744,7 +19808,7 @@
         <v>4</v>
       </c>
       <c r="L146" s="110" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="M146" s="110"/>
     </row>
@@ -19757,12 +19821,12 @@
       </c>
       <c r="E147" s="110"/>
       <c r="F147" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="G147" s="110"/>
       <c r="H147" s="110"/>
       <c r="I147" s="110" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="J147" s="110">
         <v>0</v>
@@ -19782,12 +19846,12 @@
       </c>
       <c r="E148" s="110"/>
       <c r="F148" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="G148" s="110"/>
       <c r="H148" s="110"/>
       <c r="I148" s="110" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="J148" s="110">
         <v>0</v>
@@ -19807,12 +19871,12 @@
       </c>
       <c r="E149" s="110"/>
       <c r="F149" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="G149" s="110"/>
       <c r="H149" s="110"/>
       <c r="I149" s="110" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="J149" s="110">
         <v>0</v>
@@ -19832,12 +19896,12 @@
       </c>
       <c r="E150" s="110"/>
       <c r="F150" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="G150" s="110"/>
       <c r="H150" s="110"/>
       <c r="I150" s="110" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="J150" s="110">
         <v>0</v>
@@ -19857,12 +19921,12 @@
       </c>
       <c r="E151" s="110"/>
       <c r="F151" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="G151" s="110"/>
       <c r="H151" s="110"/>
       <c r="I151" s="110" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="J151" s="110">
         <v>0</v>
@@ -19882,12 +19946,12 @@
       </c>
       <c r="E152" s="110"/>
       <c r="F152" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="G152" s="110"/>
       <c r="H152" s="110"/>
       <c r="I152" s="110" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="J152" s="110">
         <v>0</v>
@@ -19907,12 +19971,12 @@
       </c>
       <c r="E153" s="110"/>
       <c r="F153" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="G153" s="110"/>
       <c r="H153" s="110"/>
       <c r="I153" s="110" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="J153" s="110">
         <v>0</v>
@@ -19947,12 +20011,12 @@
       </c>
       <c r="E155" s="110"/>
       <c r="F155" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="G155" s="110"/>
       <c r="H155" s="110"/>
       <c r="I155" s="110" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="J155" s="110">
         <v>0</v>
@@ -19961,7 +20025,7 @@
         <v>4</v>
       </c>
       <c r="L155" s="110" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="M155" s="110"/>
     </row>
@@ -19974,12 +20038,12 @@
       </c>
       <c r="E156" s="110"/>
       <c r="F156" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="G156" s="110"/>
       <c r="H156" s="110"/>
       <c r="I156" s="110" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="J156" s="110">
         <v>0</v>
@@ -19999,12 +20063,12 @@
       </c>
       <c r="E157" s="110"/>
       <c r="F157" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="G157" s="110"/>
       <c r="H157" s="110"/>
       <c r="I157" s="110" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="J157" s="110">
         <v>0</v>
@@ -20024,12 +20088,12 @@
       </c>
       <c r="E158" s="110"/>
       <c r="F158" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="G158" s="110"/>
       <c r="H158" s="110"/>
       <c r="I158" s="110" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="J158" s="110">
         <v>0</v>
@@ -20049,12 +20113,12 @@
       </c>
       <c r="E159" s="110"/>
       <c r="F159" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="G159" s="110"/>
       <c r="H159" s="110"/>
       <c r="I159" s="110" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="J159" s="110">
         <v>0</v>
@@ -20074,12 +20138,12 @@
       </c>
       <c r="E160" s="110"/>
       <c r="F160" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="G160" s="110"/>
       <c r="H160" s="110"/>
       <c r="I160" s="110" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="J160" s="110">
         <v>0</v>
@@ -20099,12 +20163,12 @@
       </c>
       <c r="E161" s="110"/>
       <c r="F161" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="G161" s="110"/>
       <c r="H161" s="110"/>
       <c r="I161" s="110" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="J161" s="110">
         <v>0</v>
@@ -20124,12 +20188,12 @@
       </c>
       <c r="E162" s="110"/>
       <c r="F162" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="G162" s="110"/>
       <c r="H162" s="110"/>
       <c r="I162" s="110" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="J162" s="110">
         <v>0</v>
@@ -20165,7 +20229,7 @@
       <c r="G164" s="110"/>
       <c r="H164" s="110"/>
       <c r="I164" s="110" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="J164" s="110">
         <v>0</v>
@@ -20174,7 +20238,7 @@
         <v>9</v>
       </c>
       <c r="L164" s="110" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="M164" s="110"/>
     </row>
@@ -20192,7 +20256,7 @@
       <c r="G165" s="110"/>
       <c r="H165" s="110"/>
       <c r="I165" s="110" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="J165" s="110">
         <v>38</v>
@@ -20202,7 +20266,7 @@
       </c>
       <c r="L165" s="110"/>
       <c r="M165" s="110" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="167" spans="1:13" x14ac:dyDescent="0.25">
@@ -20588,16 +20652,16 @@
         <v>38</v>
       </c>
       <c r="I188" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="J188" s="2">
         <v>78</v>
       </c>
       <c r="K188" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="L188" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="M188" t="s">
         <v>513</v>
@@ -20608,34 +20672,34 @@
         <v>2</v>
       </c>
       <c r="I189" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="J189" s="2">
         <v>81</v>
       </c>
       <c r="K189" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="L189" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="M189" s="258" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="190" spans="1:13" x14ac:dyDescent="0.25">
       <c r="I190" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="J190" s="13">
         <f>18.8*0.13</f>
         <v>2.4440000000000004</v>
       </c>
       <c r="K190" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="L190" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="191" spans="1:13" x14ac:dyDescent="0.25">
@@ -20745,7 +20809,7 @@
       </c>
       <c r="J198" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E198,Foderstater!$U$63:$U$100,0),MATCH(A198&amp;C198&amp;D198,Foderstater!$X$62:$AI$62,0))</f>
-        <v>38.609681277854051</v>
+        <v>41.480852339300604</v>
       </c>
       <c r="K198" s="159"/>
       <c r="L198" s="159"/>
@@ -20766,7 +20830,7 @@
       </c>
       <c r="J199" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E199,Foderstater!$U$63:$U$100,0),MATCH(A199&amp;C199&amp;D199,Foderstater!$X$62:$AI$62,0))</f>
-        <v>9.2377598080515053</v>
+        <v>9.9247167513786927</v>
       </c>
       <c r="K199" s="159"/>
       <c r="L199" s="159"/>
@@ -20850,7 +20914,7 @@
       </c>
       <c r="J203" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E203,Foderstater!$U$63:$U$100,0),MATCH(A203&amp;C203&amp;D203,Foderstater!$X$62:$AI$62,0))</f>
-        <v>10.166080013639251</v>
+        <v>6.6079520088655128</v>
       </c>
       <c r="K203" s="159"/>
       <c r="L203" s="159"/>
@@ -21539,7 +21603,7 @@
       </c>
       <c r="J238" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E238,Foderstater!$U$63:$U$100,0),MATCH(A238&amp;C238&amp;D238,Foderstater!$X$62:$AI$62,0))</f>
-        <v>20.561419371957058</v>
+        <v>22.93829412577864</v>
       </c>
       <c r="K238" s="159"/>
       <c r="L238" s="159"/>
@@ -21566,7 +21630,7 @@
       </c>
       <c r="J239" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E239,Foderstater!$U$63:$U$100,0),MATCH(A239&amp;C239&amp;D239,Foderstater!$X$62:$AI$62,0))</f>
-        <v>9.5364207102254017</v>
+        <v>10.638819198282629</v>
       </c>
       <c r="K239" s="159"/>
       <c r="L239" s="159"/>
@@ -21674,7 +21738,7 @@
       </c>
       <c r="J243" s="13">
         <f>INDEX(Foderstater!$X$63:$AI$100,MATCH(E243,Foderstater!$U$63:$U$100,0),MATCH(A243&amp;C243&amp;D243,Foderstater!$X$62:$AI$62,0))</f>
-        <v>9.9407806910823222</v>
+        <v>6.4615074492035101</v>
       </c>
       <c r="K243" s="159"/>
       <c r="L243" s="159"/>
@@ -23312,7 +23376,7 @@
     </row>
     <row r="318" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A318" s="81" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B318" s="48"/>
       <c r="C318" s="48"/>
@@ -35993,7 +36057,7 @@
       </c>
       <c r="Z2" s="219"/>
       <c r="AA2" s="197" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="AB2" s="198"/>
       <c r="AC2" s="198"/>
@@ -36015,7 +36079,7 @@
     </row>
     <row r="3" spans="2:44" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="230" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C3" s="231"/>
       <c r="D3" s="232" t="s">
@@ -36050,61 +36114,61 @@
       </c>
       <c r="Z3" s="220"/>
       <c r="AA3" s="241" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="AB3" s="202"/>
       <c r="AC3" s="202"/>
-      <c r="AD3" s="265" t="s">
-        <v>525</v>
-      </c>
-      <c r="AE3" s="266" t="s">
-        <v>527</v>
-      </c>
-      <c r="AF3" s="265" t="s">
-        <v>529</v>
-      </c>
-      <c r="AG3" s="266" t="s">
+      <c r="AD3" s="263" t="s">
+        <v>524</v>
+      </c>
+      <c r="AE3" s="264" t="s">
+        <v>526</v>
+      </c>
+      <c r="AF3" s="263" t="s">
+        <v>528</v>
+      </c>
+      <c r="AG3" s="264" t="s">
+        <v>530</v>
+      </c>
+      <c r="AH3" s="263" t="s">
         <v>531</v>
       </c>
-      <c r="AH3" s="265" t="s">
-        <v>532</v>
-      </c>
-      <c r="AI3" s="266" t="s">
+      <c r="AI3" s="264" t="s">
+        <v>533</v>
+      </c>
+      <c r="AJ3" s="263" t="s">
         <v>534</v>
       </c>
-      <c r="AJ3" s="265" t="s">
+      <c r="AK3" s="264" t="s">
         <v>535</v>
       </c>
-      <c r="AK3" s="266" t="s">
-        <v>536</v>
-      </c>
-      <c r="AL3" s="265" t="s">
+      <c r="AL3" s="263" t="s">
+        <v>537</v>
+      </c>
+      <c r="AM3" s="264" t="s">
         <v>538</v>
       </c>
-      <c r="AM3" s="266" t="s">
-        <v>539</v>
-      </c>
-      <c r="AN3" s="265" t="s">
-        <v>559</v>
-      </c>
-      <c r="AO3" s="266" t="s">
+      <c r="AN3" s="263" t="s">
+        <v>558</v>
+      </c>
+      <c r="AO3" s="264" t="s">
+        <v>540</v>
+      </c>
+      <c r="AP3" s="263" t="s">
         <v>541</v>
       </c>
-      <c r="AP3" s="265" t="s">
-        <v>542</v>
-      </c>
-      <c r="AQ3" s="264" t="s">
-        <v>563</v>
-      </c>
-      <c r="AR3" s="263" t="s">
-        <v>558</v>
+      <c r="AQ3" s="262" t="s">
+        <v>562</v>
+      </c>
+      <c r="AR3" s="261" t="s">
+        <v>557</v>
       </c>
     </row>
     <row r="4" spans="2:44" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="201"/>
       <c r="C4" s="202"/>
       <c r="D4" s="234" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="E4" s="234"/>
       <c r="F4" s="234"/>
@@ -36147,25 +36211,25 @@
       <c r="AA4" s="201"/>
       <c r="AB4" s="202"/>
       <c r="AC4" s="202"/>
-      <c r="AD4" s="265"/>
-      <c r="AE4" s="266"/>
-      <c r="AF4" s="265"/>
-      <c r="AG4" s="266"/>
-      <c r="AH4" s="265"/>
-      <c r="AI4" s="266"/>
-      <c r="AJ4" s="265"/>
-      <c r="AK4" s="266"/>
-      <c r="AL4" s="265"/>
-      <c r="AM4" s="266"/>
-      <c r="AN4" s="265"/>
-      <c r="AO4" s="266"/>
-      <c r="AP4" s="265"/>
-      <c r="AQ4" s="264"/>
-      <c r="AR4" s="263"/>
+      <c r="AD4" s="263"/>
+      <c r="AE4" s="264"/>
+      <c r="AF4" s="263"/>
+      <c r="AG4" s="264"/>
+      <c r="AH4" s="263"/>
+      <c r="AI4" s="264"/>
+      <c r="AJ4" s="263"/>
+      <c r="AK4" s="264"/>
+      <c r="AL4" s="263"/>
+      <c r="AM4" s="264"/>
+      <c r="AN4" s="263"/>
+      <c r="AO4" s="264"/>
+      <c r="AP4" s="263"/>
+      <c r="AQ4" s="262"/>
+      <c r="AR4" s="261"/>
     </row>
     <row r="5" spans="2:44" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="209" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="C5" s="210" t="s">
         <v>466</v>
@@ -36242,27 +36306,27 @@
       <c r="AA5" s="201"/>
       <c r="AB5" s="202"/>
       <c r="AC5" s="202"/>
-      <c r="AD5" s="265"/>
-      <c r="AE5" s="266"/>
-      <c r="AF5" s="265"/>
-      <c r="AG5" s="266"/>
-      <c r="AH5" s="265"/>
-      <c r="AI5" s="266"/>
-      <c r="AJ5" s="265"/>
-      <c r="AK5" s="266"/>
-      <c r="AL5" s="265"/>
-      <c r="AM5" s="266"/>
-      <c r="AN5" s="265"/>
-      <c r="AO5" s="266"/>
-      <c r="AP5" s="265"/>
-      <c r="AQ5" s="264"/>
-      <c r="AR5" s="263" t="s">
-        <v>557</v>
+      <c r="AD5" s="263"/>
+      <c r="AE5" s="264"/>
+      <c r="AF5" s="263"/>
+      <c r="AG5" s="264"/>
+      <c r="AH5" s="263"/>
+      <c r="AI5" s="264"/>
+      <c r="AJ5" s="263"/>
+      <c r="AK5" s="264"/>
+      <c r="AL5" s="263"/>
+      <c r="AM5" s="264"/>
+      <c r="AN5" s="263"/>
+      <c r="AO5" s="264"/>
+      <c r="AP5" s="263"/>
+      <c r="AQ5" s="262"/>
+      <c r="AR5" s="261" t="s">
+        <v>556</v>
       </c>
     </row>
     <row r="6" spans="2:44" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="201" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C6" s="236">
         <v>1</v>
@@ -36303,7 +36367,7 @@
         <v>1619.5499999999997</v>
       </c>
       <c r="AA6" s="201" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="AB6" s="202"/>
       <c r="AC6" s="202"/>
@@ -36402,55 +36466,55 @@
         <v>751.1500000000002</v>
       </c>
       <c r="AA7" s="201" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="AB7" s="202"/>
       <c r="AC7" s="202"/>
       <c r="AD7" s="207" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="AE7" s="208" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="AF7" s="207" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="AG7" s="208" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="AH7" s="207" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="AI7" s="208" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="AJ7" s="207" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="AK7" s="208" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="AL7" s="207" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="AM7" s="208" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="AN7" s="207" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="AO7" s="208" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="AP7" s="207" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="AQ7" s="205"/>
       <c r="AR7" s="206"/>
     </row>
     <row r="8" spans="2:44" x14ac:dyDescent="0.25">
       <c r="B8" s="201" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C8" s="236">
         <v>1</v>
@@ -36540,7 +36604,7 @@
       <c r="Y9" s="225"/>
       <c r="Z9" s="226"/>
       <c r="AA9" s="209" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="AB9" s="202"/>
       <c r="AC9" s="210" t="s">
@@ -36599,7 +36663,7 @@
         <v>1250.5</v>
       </c>
       <c r="AA10" s="201" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="AB10" s="202"/>
       <c r="AC10" s="236">
@@ -36655,7 +36719,7 @@
     </row>
     <row r="11" spans="2:44" x14ac:dyDescent="0.25">
       <c r="B11" s="201" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="C11" s="236">
         <v>1</v>
@@ -36692,7 +36756,7 @@
       <c r="Y11" s="225"/>
       <c r="Z11" s="226"/>
       <c r="AA11" s="201" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="AB11" s="202"/>
       <c r="AC11" s="236">
@@ -36722,7 +36786,7 @@
     </row>
     <row r="12" spans="2:44" x14ac:dyDescent="0.25">
       <c r="B12" s="201" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C12" s="236">
         <v>0.85</v>
@@ -36759,7 +36823,7 @@
         <v>244</v>
       </c>
       <c r="AA12" s="201" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="AB12" s="202"/>
       <c r="AC12" s="236">
@@ -36785,7 +36849,7 @@
     </row>
     <row r="13" spans="2:44" x14ac:dyDescent="0.25">
       <c r="B13" s="201" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C13" s="236">
         <v>1</v>
@@ -36844,7 +36908,7 @@
       <c r="Y13" s="225"/>
       <c r="Z13" s="226"/>
       <c r="AA13" s="201" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="AB13" s="202"/>
       <c r="AC13" s="236">
@@ -36870,7 +36934,7 @@
     </row>
     <row r="14" spans="2:44" x14ac:dyDescent="0.25">
       <c r="B14" s="201" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C14" s="236">
         <v>1</v>
@@ -36933,7 +36997,7 @@
         <v>782.99999999999989</v>
       </c>
       <c r="AA14" s="201" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="AB14" s="202"/>
       <c r="AC14" s="236">
@@ -36985,7 +37049,7 @@
     </row>
     <row r="15" spans="2:44" x14ac:dyDescent="0.25">
       <c r="B15" s="201" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C15" s="236">
         <v>0.86</v>
@@ -37032,7 +37096,7 @@
         <v>1159.4923144269196</v>
       </c>
       <c r="AA15" s="201" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="AB15" s="202"/>
       <c r="AC15" s="236">
@@ -37127,7 +37191,7 @@
       <c r="Y16" s="225"/>
       <c r="Z16" s="226"/>
       <c r="AA16" s="201" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="AB16" s="202"/>
       <c r="AC16" s="236">
@@ -37222,7 +37286,7 @@
         <v>2405.9342126196852</v>
       </c>
       <c r="AA17" s="201" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="AB17" s="202"/>
       <c r="AC17" s="236">
@@ -37387,7 +37451,7 @@
       <c r="Y19" s="225"/>
       <c r="Z19" s="226"/>
       <c r="AA19" s="201" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="AB19" s="202"/>
       <c r="AC19" s="255">
@@ -37516,7 +37580,7 @@
         <v>8279.5672923170714</v>
       </c>
       <c r="AA20" s="201" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="AB20" s="202"/>
       <c r="AC20" s="255">
@@ -37566,7 +37630,7 @@
       <c r="W21" s="42"/>
       <c r="X21" s="42"/>
       <c r="AA21" s="213" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="AB21" s="214"/>
       <c r="AC21" s="214"/>
@@ -37651,7 +37715,7 @@
       <c r="J22" s="165"/>
       <c r="K22" s="165"/>
       <c r="L22" s="174" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="M22" s="242"/>
       <c r="N22" s="242"/>
@@ -37691,29 +37755,29 @@
       <c r="N23" s="169"/>
       <c r="O23" s="169"/>
       <c r="P23" s="169"/>
-      <c r="Q23" s="262" t="s">
+      <c r="Q23" s="266" t="s">
+        <v>577</v>
+      </c>
+      <c r="R23" s="266" t="s">
         <v>578</v>
       </c>
-      <c r="R23" s="262" t="s">
-        <v>579</v>
-      </c>
-      <c r="S23" s="262" t="s">
-        <v>566</v>
-      </c>
-      <c r="T23" s="261" t="s">
+      <c r="S23" s="266" t="s">
+        <v>565</v>
+      </c>
+      <c r="T23" s="265" t="s">
         <v>293</v>
       </c>
-      <c r="U23" s="261"/>
-      <c r="V23" s="261" t="s">
+      <c r="U23" s="265"/>
+      <c r="V23" s="265" t="s">
         <v>294</v>
       </c>
-      <c r="W23" s="261"/>
+      <c r="W23" s="265"/>
       <c r="X23" s="168" t="s">
         <v>465</v>
       </c>
       <c r="Y23" s="165"/>
       <c r="Z23" s="174" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="AA23" s="83"/>
       <c r="AB23" s="83"/>
@@ -37732,9 +37796,9 @@
       <c r="P24" s="170" t="s">
         <v>466</v>
       </c>
-      <c r="Q24" s="262"/>
-      <c r="R24" s="262"/>
-      <c r="S24" s="262"/>
+      <c r="Q24" s="266"/>
+      <c r="R24" s="266"/>
+      <c r="S24" s="266"/>
       <c r="T24" s="244" t="s">
         <v>466</v>
       </c>
@@ -37751,7 +37815,7 @@
         <v>500</v>
       </c>
       <c r="Z24" s="174" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="AA24" s="169"/>
       <c r="AB24" s="169"/>
@@ -37856,7 +37920,7 @@
     </row>
     <row r="26" spans="2:44" x14ac:dyDescent="0.25">
       <c r="B26" s="174" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C26" s="174"/>
       <c r="D26" s="168"/>
@@ -38644,7 +38708,7 @@
         <v>0</v>
       </c>
       <c r="L34" s="169" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="M34" s="169"/>
       <c r="N34" s="169"/>
@@ -38940,7 +39004,7 @@
         <v>1</v>
       </c>
       <c r="L38" s="169" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="M38" s="169"/>
       <c r="N38" s="169"/>
@@ -39404,7 +39468,7 @@
         <v>0.40587012896078656</v>
       </c>
       <c r="L44" s="169" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="M44" s="169"/>
       <c r="N44" s="169"/>
@@ -39481,7 +39545,7 @@
         <v>0.2671631311304497</v>
       </c>
       <c r="L45" s="169" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="M45" s="169"/>
       <c r="N45" s="169"/>
@@ -39558,7 +39622,7 @@
         <v>0.14385536511797675</v>
       </c>
       <c r="L46" s="169" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="M46" s="169"/>
       <c r="N46" s="169"/>
@@ -39636,7 +39700,7 @@
         <v>0.46986991038291381</v>
       </c>
       <c r="L47" s="169" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="M47" s="169"/>
       <c r="N47" s="169"/>
@@ -39779,7 +39843,7 @@
         <v>0.15455308043620117</v>
       </c>
       <c r="L49" s="169" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="M49" s="169"/>
       <c r="N49" s="169"/>
@@ -39820,7 +39884,7 @@
     </row>
     <row r="50" spans="2:44" x14ac:dyDescent="0.25">
       <c r="L50" s="169" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="M50" s="169"/>
       <c r="N50" s="169"/>
@@ -39945,7 +40009,7 @@
     </row>
     <row r="53" spans="2:44" x14ac:dyDescent="0.25">
       <c r="L53" s="169" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="M53" s="169"/>
       <c r="N53" s="169"/>
@@ -40024,10 +40088,14 @@
         <f t="shared" si="11"/>
         <v>0.93</v>
       </c>
+      <c r="Z54" s="271"/>
+      <c r="AA54" s="272"/>
+      <c r="AB54" s="273"/>
+      <c r="AC54" s="274"/>
     </row>
     <row r="55" spans="2:44" x14ac:dyDescent="0.25">
       <c r="L55" s="169" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="M55" s="169"/>
       <c r="N55" s="169"/>
@@ -40100,16 +40168,40 @@
         <f t="shared" si="11"/>
         <v>0.93</v>
       </c>
+      <c r="Z56" s="268" t="s">
+        <v>621</v>
+      </c>
+      <c r="AA56" s="268"/>
+      <c r="AB56" s="268"/>
+      <c r="AC56" s="267"/>
+      <c r="AE56" t="s">
+        <v>622</v>
+      </c>
       <c r="AQ56" s="12"/>
       <c r="AR56" s="26"/>
     </row>
     <row r="57" spans="2:44" x14ac:dyDescent="0.25">
+      <c r="Z57" s="268" t="s">
+        <v>623</v>
+      </c>
+      <c r="AA57" s="268"/>
+      <c r="AB57" s="268"/>
+      <c r="AC57" s="267"/>
+      <c r="AE57" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG57">
+        <v>9</v>
+      </c>
+      <c r="AH57" t="s">
+        <v>9</v>
+      </c>
       <c r="AQ57" s="12"/>
       <c r="AR57" s="26"/>
     </row>
     <row r="58" spans="2:44" x14ac:dyDescent="0.25">
       <c r="S58" s="185" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="T58" s="12">
         <f>SUM(T25:T30)</f>
@@ -40127,12 +40219,28 @@
         <f>V58/SUM(V$58:V$59)</f>
         <v>0.68124800328654078</v>
       </c>
+      <c r="Z58" s="267" t="s">
+        <v>617</v>
+      </c>
+      <c r="AA58" s="268"/>
+      <c r="AB58" s="268"/>
+      <c r="AC58" s="267"/>
+      <c r="AE58" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG58">
+        <v>14</v>
+      </c>
+      <c r="AH58" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI58" s="2"/>
       <c r="AQ58" s="12"/>
       <c r="AR58" s="26"/>
     </row>
     <row r="59" spans="2:44" x14ac:dyDescent="0.25">
       <c r="S59" s="185" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="T59" s="12">
         <f>SUM(T31:T55)</f>
@@ -40153,8 +40261,100 @@
       <c r="AQ59" s="12"/>
       <c r="AR59" s="26"/>
     </row>
+    <row r="60" spans="2:44" x14ac:dyDescent="0.25">
+      <c r="W60" s="269" t="s">
+        <v>618</v>
+      </c>
+      <c r="X60" s="270">
+        <v>1</v>
+      </c>
+      <c r="Y60" s="270">
+        <v>1</v>
+      </c>
+      <c r="Z60" s="270">
+        <v>1</v>
+      </c>
+      <c r="AA60" s="270">
+        <v>1</v>
+      </c>
+      <c r="AB60" s="270">
+        <v>1</v>
+      </c>
+      <c r="AC60" s="270">
+        <v>1</v>
+      </c>
+      <c r="AD60" s="270">
+        <v>0.65</v>
+      </c>
+      <c r="AE60" s="270">
+        <v>1</v>
+      </c>
+      <c r="AF60" s="270">
+        <v>1</v>
+      </c>
+      <c r="AG60" s="270">
+        <v>1</v>
+      </c>
+      <c r="AH60" s="270">
+        <v>0.65</v>
+      </c>
+      <c r="AI60" s="270">
+        <v>1</v>
+      </c>
+    </row>
     <row r="61" spans="2:44" x14ac:dyDescent="0.25">
       <c r="T61" s="2"/>
+      <c r="W61" s="269" t="s">
+        <v>619</v>
+      </c>
+      <c r="X61" s="270">
+        <f>1+(D71*(1-X60))/SUM(D66:D67)</f>
+        <v>1</v>
+      </c>
+      <c r="Y61" s="270">
+        <f t="shared" ref="X61:AI61" si="14">1+(E71*(1-Y60))/SUM(E66:E67)</f>
+        <v>1</v>
+      </c>
+      <c r="Z61" s="270">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+      <c r="AA61" s="270">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+      <c r="AB61" s="270">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+      <c r="AC61" s="270">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+      <c r="AD61" s="270">
+        <f t="shared" si="14"/>
+        <v>1.0743640187232888</v>
+      </c>
+      <c r="AE61" s="270">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+      <c r="AF61" s="270">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+      <c r="AG61" s="270">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+      <c r="AH61" s="270">
+        <f t="shared" si="14"/>
+        <v>1.1155987682962838</v>
+      </c>
+      <c r="AI61" s="270">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="62" spans="2:44" x14ac:dyDescent="0.25">
       <c r="B62" s="6" t="s">
@@ -40261,25 +40461,26 @@
       <c r="O63" t="s">
         <v>416</v>
       </c>
+      <c r="Q63" s="4"/>
       <c r="T63" s="2"/>
       <c r="U63" s="110" t="str">
         <f>B66</f>
         <v>ley silage, 1st cut</v>
       </c>
       <c r="X63" s="13">
-        <f t="shared" ref="X63:X68" si="14">D66/D$116*100</f>
+        <f>X61*D66/D$116*100</f>
         <v>0</v>
       </c>
       <c r="Y63" s="13">
-        <f t="shared" ref="Y63:AI63" si="15">E66/E$116*100</f>
+        <f>Y61*E66/E$116*100</f>
         <v>55.38698659192309</v>
       </c>
       <c r="Z63" s="13">
-        <f t="shared" si="15"/>
+        <f>Z61*F66/F$116*100</f>
         <v>0</v>
       </c>
       <c r="AA63" s="13">
-        <f t="shared" si="15"/>
+        <f t="shared" ref="Y63:AI63" si="15">AA61*G66/G$116*100</f>
         <v>0</v>
       </c>
       <c r="AB63" s="13">
@@ -40292,7 +40493,7 @@
       </c>
       <c r="AD63" s="13">
         <f t="shared" si="15"/>
-        <v>38.609681277854051</v>
+        <v>41.480852339300604</v>
       </c>
       <c r="AE63" s="13">
         <f t="shared" si="15"/>
@@ -40308,7 +40509,7 @@
       </c>
       <c r="AH63" s="13">
         <f t="shared" si="15"/>
-        <v>20.561419371957058</v>
+        <v>22.93829412577864</v>
       </c>
       <c r="AI63" s="13">
         <f t="shared" si="15"/>
@@ -40362,51 +40563,51 @@
         <v>ley silage, regrowth</v>
       </c>
       <c r="X64" s="13">
-        <f t="shared" si="14"/>
+        <f>X61*D67/D$116*100</f>
         <v>19.638470390756044</v>
       </c>
       <c r="Y64" s="13">
-        <f t="shared" ref="Y64:AI64" si="17">E67/E$116*100</f>
+        <f>Y61*E67/E$116*100</f>
         <v>0</v>
       </c>
       <c r="Z64" s="13">
-        <f t="shared" si="17"/>
+        <f>Z61*F67/F$116*100</f>
         <v>68.854768967576106</v>
       </c>
       <c r="AA64" s="13">
-        <f t="shared" si="17"/>
+        <f>AA61*G67/G$116*100</f>
         <v>69.016974351370379</v>
       </c>
       <c r="AB64" s="13">
-        <f t="shared" si="17"/>
+        <f>AB61*H67/H$116*100</f>
         <v>0</v>
       </c>
       <c r="AC64" s="13">
-        <f t="shared" si="17"/>
+        <f>AC61*I67/I$116*100</f>
         <v>0</v>
       </c>
       <c r="AD64" s="13">
-        <f t="shared" si="17"/>
-        <v>9.2377598080515053</v>
+        <f>AD61*J67/J$116*100</f>
+        <v>9.9247167513786927</v>
       </c>
       <c r="AE64" s="13">
-        <f t="shared" si="17"/>
+        <f>AE61*K67/K$116*100</f>
         <v>0</v>
       </c>
       <c r="AF64" s="13">
-        <f t="shared" si="17"/>
+        <f>AF61*L67/L$116*100</f>
         <v>55.029062371648976</v>
       </c>
       <c r="AG64" s="13">
-        <f t="shared" si="17"/>
+        <f>AG61*M67/M$116*100</f>
         <v>0</v>
       </c>
       <c r="AH64" s="13">
-        <f t="shared" si="17"/>
-        <v>9.5364207102254017</v>
+        <f>AH61*N67/N$116*100</f>
+        <v>10.638819198282629</v>
       </c>
       <c r="AI64" s="13">
-        <f t="shared" si="17"/>
+        <f>AI61*O67/O$116*100</f>
         <v>0</v>
       </c>
     </row>
@@ -40421,7 +40622,7 @@
         <v>other silage</v>
       </c>
       <c r="X65" s="13">
-        <f t="shared" si="14"/>
+        <f t="shared" ref="X63:X68" si="17">D68/D$116*100</f>
         <v>20.321711421281208</v>
       </c>
       <c r="Y65" s="13">
@@ -40510,14 +40711,13 @@
         <f>N9*C9</f>
         <v>1868</v>
       </c>
-      <c r="Q66" s="2"/>
       <c r="T66" s="72"/>
       <c r="U66" s="110" t="str">
         <f t="shared" si="16"/>
         <v>maize silage</v>
       </c>
       <c r="X66" s="13">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="Y66" s="13">
@@ -40596,14 +40796,12 @@
         <f>Z7</f>
         <v>751.1500000000002</v>
       </c>
-      <c r="Q67" s="2"/>
-      <c r="T67" s="2"/>
       <c r="U67" s="110" t="str">
         <f t="shared" si="16"/>
         <v>straw</v>
       </c>
       <c r="X67" s="13">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>1.1297448457337229</v>
       </c>
       <c r="Y67" s="13">
@@ -40666,18 +40864,16 @@
       <c r="L68" s="12"/>
       <c r="M68" s="12"/>
       <c r="N68" s="12"/>
-      <c r="Q68" s="2"/>
-      <c r="T68" s="2"/>
       <c r="U68" s="110" t="str">
         <f t="shared" si="16"/>
         <v>grazing</v>
       </c>
       <c r="X68" s="13">
-        <f t="shared" si="14"/>
+        <f>X60*D71/D$116*100</f>
         <v>58.050981669759572</v>
       </c>
       <c r="Y68" s="13">
-        <f t="shared" ref="Y68:AI68" si="21">E71/E$116*100</f>
+        <f t="shared" ref="Y68:AI68" si="21">Y60*E71/E$116*100</f>
         <v>21.161076246926353</v>
       </c>
       <c r="Z68" s="13">
@@ -40698,7 +40894,7 @@
       </c>
       <c r="AD68" s="13">
         <f t="shared" si="21"/>
-        <v>10.166080013639251</v>
+        <v>6.6079520088655128</v>
       </c>
       <c r="AE68" s="13">
         <f t="shared" si="21"/>
@@ -40714,7 +40910,7 @@
       </c>
       <c r="AH68" s="13">
         <f t="shared" si="21"/>
-        <v>9.9407806910823222</v>
+        <v>6.4615074492035101</v>
       </c>
       <c r="AI68" s="13">
         <f t="shared" si="21"/>
@@ -40743,8 +40939,6 @@
         <f>N10*C10</f>
         <v>436</v>
       </c>
-      <c r="Q69" s="2"/>
-      <c r="T69" s="2"/>
       <c r="U69" s="110" t="str">
         <f t="shared" ref="U69:U100" si="22">B82</f>
         <v>wheat</v>
@@ -40819,8 +41013,6 @@
         <f>Z12</f>
         <v>244</v>
       </c>
-      <c r="Q70" s="2"/>
-      <c r="T70" s="2"/>
       <c r="U70" s="110" t="str">
         <f t="shared" si="22"/>
         <v>barley</v>
@@ -43833,7 +44025,7 @@
         <v>rye bran</v>
       </c>
       <c r="E104" s="13">
-        <f t="shared" si="46"/>
+        <f>E$81*$W47</f>
         <v>8.8218496845068217E-2</v>
       </c>
       <c r="H104" s="13">
@@ -43869,14 +44061,14 @@
       <c r="U104" s="6"/>
       <c r="V104" s="6"/>
       <c r="W104" s="185" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="X104" s="72">
-        <f t="shared" ref="X104:AI104" si="94">SUM(X63:X68)</f>
+        <f>SUM(X63:X68)</f>
         <v>99.140908327530553</v>
       </c>
       <c r="Y104" s="72">
-        <f t="shared" si="94"/>
+        <f t="shared" ref="X104:AI104" si="94">SUM(Y63:Y68)</f>
         <v>76.548062838849447</v>
       </c>
       <c r="Z104" s="72">
@@ -43897,7 +44089,7 @@
       </c>
       <c r="AD104" s="72">
         <f t="shared" si="94"/>
-        <v>61.18149494798412</v>
+        <v>61.181494947984113</v>
       </c>
       <c r="AE104" s="72">
         <f t="shared" si="94"/>
@@ -43959,6 +44151,57 @@
         <v>5.677922096367217</v>
       </c>
       <c r="Q105" s="2"/>
+      <c r="W105" s="185" t="s">
+        <v>620</v>
+      </c>
+      <c r="X105" s="72">
+        <f>X68/X104*100</f>
+        <v>58.5540143307718</v>
+      </c>
+      <c r="Y105" s="72">
+        <f t="shared" ref="Y105:AI105" si="97">Y68/Y104*100</f>
+        <v>27.644169508868021</v>
+      </c>
+      <c r="Z105" s="72">
+        <f t="shared" si="97"/>
+        <v>30.646316743875307</v>
+      </c>
+      <c r="AA105" s="72">
+        <f t="shared" si="97"/>
+        <v>30.495841704076714</v>
+      </c>
+      <c r="AB105" s="72">
+        <f t="shared" si="97"/>
+        <v>0</v>
+      </c>
+      <c r="AC105" s="72">
+        <f t="shared" si="97"/>
+        <v>0</v>
+      </c>
+      <c r="AD105" s="72">
+        <f t="shared" si="97"/>
+        <v>10.800572974693617</v>
+      </c>
+      <c r="AE105" s="72">
+        <f t="shared" si="97"/>
+        <v>16.294245990112653</v>
+      </c>
+      <c r="AF105" s="72">
+        <f t="shared" si="97"/>
+        <v>41.235797089451033</v>
+      </c>
+      <c r="AG105" s="72">
+        <f t="shared" si="97"/>
+        <v>0</v>
+      </c>
+      <c r="AH105" s="72">
+        <f t="shared" si="97"/>
+        <v>10.949399767651991</v>
+      </c>
+      <c r="AI105" s="72">
+        <f t="shared" si="97"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="106" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B106" t="str">
@@ -43979,23 +44222,23 @@
         <v>0</v>
       </c>
       <c r="K106" s="13">
-        <f t="shared" ref="K106:M106" si="97">K$81*$W49</f>
+        <f t="shared" ref="K106:M106" si="98">K$81*$W49</f>
         <v>0</v>
       </c>
       <c r="L106" s="13">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>0</v>
       </c>
       <c r="M106" s="13">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>0</v>
       </c>
       <c r="N106" s="13">
-        <f t="shared" ref="N106:O106" si="98">N$81*$U49</f>
+        <f t="shared" ref="N106:O106" si="99">N$81*$U49</f>
         <v>0</v>
       </c>
       <c r="O106" s="13">
-        <f t="shared" si="98"/>
+        <f t="shared" si="99"/>
         <v>0</v>
       </c>
       <c r="Q106" s="2"/>
@@ -44019,23 +44262,23 @@
         <v>3.3062241528984204</v>
       </c>
       <c r="K107" s="13">
-        <f t="shared" ref="K107:M107" si="99">K$81*$W50</f>
+        <f t="shared" ref="K107:M107" si="100">K$81*$W50</f>
         <v>5.3579732624603534E-2</v>
       </c>
       <c r="L107" s="13">
-        <f t="shared" si="99"/>
+        <f t="shared" si="100"/>
         <v>0.12681195334591416</v>
       </c>
       <c r="M107" s="13">
-        <f t="shared" si="99"/>
+        <f t="shared" si="100"/>
         <v>0.25884226195508947</v>
       </c>
       <c r="N107" s="13">
-        <f t="shared" ref="N107:O107" si="100">N$81*$U50</f>
+        <f t="shared" ref="N107:O107" si="101">N$81*$U50</f>
         <v>5.2251098750790144</v>
       </c>
       <c r="O107" s="13">
-        <f t="shared" si="100"/>
+        <f t="shared" si="101"/>
         <v>0.17156898055071318</v>
       </c>
       <c r="Q107" s="2"/>
@@ -44059,23 +44302,23 @@
         <v>36.664020794401559</v>
       </c>
       <c r="K108" s="13">
-        <f t="shared" ref="K108:M108" si="101">K$81*$W51</f>
+        <f t="shared" ref="K108:M108" si="102">K$81*$W51</f>
         <v>0.59416674135200243</v>
       </c>
       <c r="L108" s="13">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>1.4062676574355435</v>
       </c>
       <c r="M108" s="13">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>2.8704037100665714</v>
       </c>
       <c r="N108" s="13">
-        <f t="shared" ref="N108:O108" si="102">N$81*$U51</f>
+        <f t="shared" ref="N108:O108" si="103">N$81*$U51</f>
         <v>57.943299744206961</v>
       </c>
       <c r="O108" s="13">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>1.9025959462158974</v>
       </c>
       <c r="Q108" s="2"/>
@@ -44099,23 +44342,23 @@
         <v>70.746128085415293</v>
       </c>
       <c r="K109" s="13">
-        <f t="shared" ref="K109:M109" si="103">K$81*$W52</f>
+        <f t="shared" ref="K109:M109" si="104">K$81*$W52</f>
         <v>1.1464917234118837</v>
       </c>
       <c r="L109" s="13">
-        <f t="shared" si="103"/>
+        <f t="shared" si="104"/>
         <v>2.7135046746019542</v>
       </c>
       <c r="M109" s="13">
-        <f t="shared" si="103"/>
+        <f t="shared" si="104"/>
         <v>5.5386709948688679</v>
       </c>
       <c r="N109" s="13">
-        <f t="shared" ref="N109:O109" si="104">N$81*$U52</f>
+        <f t="shared" ref="N109:O109" si="105">N$81*$U52</f>
         <v>111.80617991633959</v>
       </c>
       <c r="O109" s="13">
-        <f t="shared" si="104"/>
+        <f t="shared" si="105"/>
         <v>3.6712093651860145</v>
       </c>
       <c r="Q109" s="2"/>
@@ -44139,23 +44382,23 @@
         <v>0</v>
       </c>
       <c r="K110" s="13">
-        <f t="shared" ref="K110:M110" si="105">K$81*$W53</f>
+        <f t="shared" ref="K110:M110" si="106">K$81*$W53</f>
         <v>0</v>
       </c>
       <c r="L110" s="13">
-        <f t="shared" si="105"/>
+        <f t="shared" si="106"/>
         <v>0</v>
       </c>
       <c r="M110" s="13">
-        <f t="shared" si="105"/>
+        <f t="shared" si="106"/>
         <v>0</v>
       </c>
       <c r="N110" s="13">
-        <f t="shared" ref="N110:O110" si="106">N$81*$U53</f>
+        <f t="shared" ref="N110:O110" si="107">N$81*$U53</f>
         <v>0</v>
       </c>
       <c r="O110" s="13">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>0</v>
       </c>
       <c r="Q110" s="2"/>
@@ -44179,23 +44422,23 @@
         <v>0.32389393208400408</v>
       </c>
       <c r="K111" s="13">
-        <f t="shared" ref="K111:M111" si="107">K$81*$W54</f>
+        <f t="shared" ref="K111:M111" si="108">K$81*$W54</f>
         <v>5.2489333684707425E-3</v>
       </c>
       <c r="L111" s="13">
-        <f t="shared" si="107"/>
+        <f t="shared" si="108"/>
         <v>1.2423120848734343E-2</v>
       </c>
       <c r="M111" s="13">
-        <f t="shared" si="107"/>
+        <f t="shared" si="108"/>
         <v>2.5357457370413061E-2</v>
       </c>
       <c r="N111" s="13">
-        <f t="shared" ref="N111:O111" si="108">N$81*$U54</f>
+        <f t="shared" ref="N111:O111" si="109">N$81*$U54</f>
         <v>0.51187738784336978</v>
       </c>
       <c r="O111" s="13">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>1.6807738726818816E-2</v>
       </c>
       <c r="Q111" s="2"/>
@@ -44219,23 +44462,23 @@
         <v>0</v>
       </c>
       <c r="K112" s="13">
-        <f t="shared" ref="K112:M112" si="109">K$81*$W55</f>
+        <f t="shared" ref="K112:M112" si="110">K$81*$W55</f>
         <v>0</v>
       </c>
       <c r="L112" s="13">
-        <f t="shared" si="109"/>
+        <f t="shared" si="110"/>
         <v>0</v>
       </c>
       <c r="M112" s="13">
-        <f t="shared" si="109"/>
+        <f t="shared" si="110"/>
         <v>0</v>
       </c>
       <c r="N112" s="13">
-        <f t="shared" ref="N112:O112" si="110">N$81*$U55</f>
+        <f t="shared" ref="N112:O112" si="111">N$81*$U55</f>
         <v>0</v>
       </c>
       <c r="O112" s="13">
-        <f t="shared" si="110"/>
+        <f t="shared" si="111"/>
         <v>0</v>
       </c>
       <c r="Q112" s="2"/>
@@ -44314,11 +44557,11 @@
         <v>3614.2395719012102</v>
       </c>
       <c r="G116" s="12">
-        <f t="shared" ref="G116:O116" si="111">SUM(G66:G71,G73:G77,G79:G80,G82:G113)</f>
+        <f t="shared" ref="G116:O116" si="112">SUM(G66:G71,G73:G77,G79:G80,G82:G113)</f>
         <v>3674.463258325256</v>
       </c>
       <c r="H116" s="12">
-        <f t="shared" si="111"/>
+        <f t="shared" si="112"/>
         <v>2068.2399000680466</v>
       </c>
       <c r="I116" s="12">
@@ -44326,32 +44569,37 @@
         <v>2077.7399999999998</v>
       </c>
       <c r="J116" s="12">
-        <f t="shared" si="111"/>
+        <f t="shared" si="112"/>
         <v>7702.0837820427678</v>
       </c>
       <c r="K116" s="12">
-        <f t="shared" si="111"/>
+        <f t="shared" si="112"/>
         <v>1359.3600606369851</v>
       </c>
       <c r="L116" s="12">
-        <f t="shared" si="111"/>
+        <f t="shared" si="112"/>
         <v>4800.5181359476801</v>
       </c>
       <c r="M116" s="12">
-        <f t="shared" si="111"/>
+        <f t="shared" si="112"/>
         <v>3259.6633994882459</v>
       </c>
       <c r="N116" s="12">
-        <f t="shared" si="111"/>
+        <f t="shared" si="112"/>
         <v>7876.6449470353336</v>
       </c>
       <c r="O116" s="12">
-        <f t="shared" si="111"/>
+        <f t="shared" si="112"/>
         <v>3296.3399999999992</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="V23:W23"/>
+    <mergeCell ref="T23:U23"/>
+    <mergeCell ref="Q23:Q24"/>
+    <mergeCell ref="R23:R24"/>
+    <mergeCell ref="S23:S24"/>
     <mergeCell ref="AR3:AR5"/>
     <mergeCell ref="AQ3:AQ5"/>
     <mergeCell ref="AD3:AD5"/>
@@ -44367,17 +44615,12 @@
     <mergeCell ref="AN3:AN5"/>
     <mergeCell ref="AO3:AO5"/>
     <mergeCell ref="AP3:AP5"/>
-    <mergeCell ref="V23:W23"/>
-    <mergeCell ref="T23:U23"/>
-    <mergeCell ref="Q23:Q24"/>
-    <mergeCell ref="R23:R24"/>
-    <mergeCell ref="S23:S24"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
     <ignoredError sqref="S39:S56 F67:G67 L71 E81 S25:S38" formulaRange="1"/>
-    <ignoredError sqref="V39:V56 AF62 J73:J76 N73:N76 V25:V38 F28" formula="1"/>
+    <ignoredError sqref="V39:V56 J73:J76 N73:N76 V25:V38 F28" formula="1"/>
   </ignoredErrors>
   <drawing r:id="rId2"/>
   <legacyDrawing r:id="rId3"/>

--- a/data/default/CattleHerd.xlsx
+++ b/data/default/CattleHerd.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="18360" windowHeight="6705" tabRatio="846" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="18360" windowHeight="6705" tabRatio="846" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="references" sheetId="13" r:id="rId1"/>
@@ -2046,7 +2046,7 @@
     <numFmt numFmtId="167" formatCode="0.000"/>
     <numFmt numFmtId="168" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="48" x14ac:knownFonts="1">
+  <fonts count="49" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2395,6 +2395,13 @@
     <font>
       <sz val="11"/>
       <color theme="7"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="2" tint="-0.249977111117893"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -3009,7 +3016,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="44" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="279">
+  <cellXfs count="281">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -3457,6 +3464,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="48" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="44">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -40654,54 +40665,54 @@
     </row>
     <row r="61" spans="2:44" x14ac:dyDescent="0.25">
       <c r="T61" s="2"/>
-      <c r="W61" s="263" t="s">
+      <c r="W61" s="279" t="s">
         <v>618</v>
       </c>
-      <c r="X61" s="264">
+      <c r="X61" s="280">
         <f>1+(D71*(1-X60))/SUM(D66:D67)</f>
         <v>1</v>
       </c>
-      <c r="Y61" s="264">
+      <c r="Y61" s="280">
         <f t="shared" ref="Y61:AI61" si="14">1+(E71*(1-Y60))/SUM(E66:E67)</f>
         <v>1</v>
       </c>
-      <c r="Z61" s="264">
+      <c r="Z61" s="280">
         <f t="shared" si="14"/>
         <v>1</v>
       </c>
-      <c r="AA61" s="264">
+      <c r="AA61" s="280">
         <f t="shared" si="14"/>
         <v>1</v>
       </c>
-      <c r="AB61" s="264">
+      <c r="AB61" s="280">
         <f t="shared" si="14"/>
         <v>1</v>
       </c>
-      <c r="AC61" s="264">
+      <c r="AC61" s="280">
         <f t="shared" si="14"/>
         <v>1</v>
       </c>
-      <c r="AD61" s="264">
+      <c r="AD61" s="280">
         <f t="shared" si="14"/>
         <v>1.0743640187232888</v>
       </c>
-      <c r="AE61" s="264">
+      <c r="AE61" s="280">
         <f t="shared" si="14"/>
         <v>1</v>
       </c>
-      <c r="AF61" s="264">
+      <c r="AF61" s="280">
         <f t="shared" si="14"/>
         <v>1</v>
       </c>
-      <c r="AG61" s="264">
+      <c r="AG61" s="280">
         <f t="shared" si="14"/>
         <v>1</v>
       </c>
-      <c r="AH61" s="264">
+      <c r="AH61" s="280">
         <f t="shared" si="14"/>
         <v>1.1155987682962838</v>
       </c>
-      <c r="AI61" s="264">
+      <c r="AI61" s="280">
         <f t="shared" si="14"/>
         <v>1</v>
       </c>

--- a/data/default/CattleHerd.xlsx
+++ b/data/default/CattleHerd.xlsx
@@ -56,7 +56,7 @@
   </definedNames>
   <calcPr calcId="162913"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId12"/>
+    <pivotCache cacheId="1" r:id="rId12"/>
   </pivotCaches>
 </workbook>
 </file>
@@ -144,7 +144,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4270" uniqueCount="635">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4273" uniqueCount="635">
   <si>
     <t>value</t>
   </si>
@@ -3034,7 +3034,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="44" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="282">
+  <cellXfs count="290">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -3468,6 +3468,19 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="2" fontId="48" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="38" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3486,7 +3499,6 @@
     <xf numFmtId="0" fontId="40" fillId="40" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="44">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -15103,7 +15115,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable2" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="L3:O43" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="12">
     <pivotField axis="axisRow" showAll="0">
@@ -17812,7 +17824,7 @@
       <c r="I51" s="110" t="s">
         <v>633</v>
       </c>
-      <c r="J51" s="281">
+      <c r="J51" s="275">
         <v>100</v>
       </c>
       <c r="K51" t="s">
@@ -18061,7 +18073,7 @@
       <c r="I61" s="110" t="s">
         <v>633</v>
       </c>
-      <c r="J61" s="281">
+      <c r="J61" s="275">
         <v>300</v>
       </c>
       <c r="K61" t="s">
@@ -18084,7 +18096,7 @@
       <c r="I62" s="110" t="s">
         <v>634</v>
       </c>
-      <c r="J62" s="281">
+      <c r="J62" s="275">
         <v>275</v>
       </c>
       <c r="K62" t="s">
@@ -36525,49 +36537,49 @@
       </c>
       <c r="AB3" s="202"/>
       <c r="AC3" s="202"/>
-      <c r="AD3" s="279" t="s">
+      <c r="AD3" s="288" t="s">
         <v>520</v>
       </c>
-      <c r="AE3" s="280" t="s">
+      <c r="AE3" s="289" t="s">
         <v>522</v>
       </c>
-      <c r="AF3" s="279" t="s">
+      <c r="AF3" s="288" t="s">
         <v>524</v>
       </c>
-      <c r="AG3" s="280" t="s">
+      <c r="AG3" s="289" t="s">
         <v>526</v>
       </c>
-      <c r="AH3" s="279" t="s">
+      <c r="AH3" s="288" t="s">
         <v>527</v>
       </c>
-      <c r="AI3" s="280" t="s">
+      <c r="AI3" s="289" t="s">
         <v>529</v>
       </c>
-      <c r="AJ3" s="279" t="s">
+      <c r="AJ3" s="288" t="s">
         <v>530</v>
       </c>
-      <c r="AK3" s="280" t="s">
+      <c r="AK3" s="289" t="s">
         <v>531</v>
       </c>
-      <c r="AL3" s="279" t="s">
+      <c r="AL3" s="288" t="s">
         <v>533</v>
       </c>
-      <c r="AM3" s="280" t="s">
+      <c r="AM3" s="289" t="s">
         <v>534</v>
       </c>
-      <c r="AN3" s="279" t="s">
+      <c r="AN3" s="288" t="s">
         <v>554</v>
       </c>
-      <c r="AO3" s="280" t="s">
+      <c r="AO3" s="289" t="s">
         <v>536</v>
       </c>
-      <c r="AP3" s="279" t="s">
+      <c r="AP3" s="288" t="s">
         <v>537</v>
       </c>
-      <c r="AQ3" s="278" t="s">
+      <c r="AQ3" s="287" t="s">
         <v>558</v>
       </c>
-      <c r="AR3" s="277" t="s">
+      <c r="AR3" s="286" t="s">
         <v>553</v>
       </c>
     </row>
@@ -36618,21 +36630,21 @@
       <c r="AA4" s="201"/>
       <c r="AB4" s="202"/>
       <c r="AC4" s="202"/>
-      <c r="AD4" s="279"/>
-      <c r="AE4" s="280"/>
-      <c r="AF4" s="279"/>
-      <c r="AG4" s="280"/>
-      <c r="AH4" s="279"/>
-      <c r="AI4" s="280"/>
-      <c r="AJ4" s="279"/>
-      <c r="AK4" s="280"/>
-      <c r="AL4" s="279"/>
-      <c r="AM4" s="280"/>
-      <c r="AN4" s="279"/>
-      <c r="AO4" s="280"/>
-      <c r="AP4" s="279"/>
-      <c r="AQ4" s="278"/>
-      <c r="AR4" s="277"/>
+      <c r="AD4" s="288"/>
+      <c r="AE4" s="289"/>
+      <c r="AF4" s="288"/>
+      <c r="AG4" s="289"/>
+      <c r="AH4" s="288"/>
+      <c r="AI4" s="289"/>
+      <c r="AJ4" s="288"/>
+      <c r="AK4" s="289"/>
+      <c r="AL4" s="288"/>
+      <c r="AM4" s="289"/>
+      <c r="AN4" s="288"/>
+      <c r="AO4" s="289"/>
+      <c r="AP4" s="288"/>
+      <c r="AQ4" s="287"/>
+      <c r="AR4" s="286"/>
     </row>
     <row r="5" spans="2:44" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="209" t="s">
@@ -36713,21 +36725,21 @@
       <c r="AA5" s="201"/>
       <c r="AB5" s="202"/>
       <c r="AC5" s="202"/>
-      <c r="AD5" s="279"/>
-      <c r="AE5" s="280"/>
-      <c r="AF5" s="279"/>
-      <c r="AG5" s="280"/>
-      <c r="AH5" s="279"/>
-      <c r="AI5" s="280"/>
-      <c r="AJ5" s="279"/>
-      <c r="AK5" s="280"/>
-      <c r="AL5" s="279"/>
-      <c r="AM5" s="280"/>
-      <c r="AN5" s="279"/>
-      <c r="AO5" s="280"/>
-      <c r="AP5" s="279"/>
-      <c r="AQ5" s="278"/>
-      <c r="AR5" s="277" t="s">
+      <c r="AD5" s="288"/>
+      <c r="AE5" s="289"/>
+      <c r="AF5" s="288"/>
+      <c r="AG5" s="289"/>
+      <c r="AH5" s="288"/>
+      <c r="AI5" s="289"/>
+      <c r="AJ5" s="288"/>
+      <c r="AK5" s="289"/>
+      <c r="AL5" s="288"/>
+      <c r="AM5" s="289"/>
+      <c r="AN5" s="288"/>
+      <c r="AO5" s="289"/>
+      <c r="AP5" s="288"/>
+      <c r="AQ5" s="287"/>
+      <c r="AR5" s="286" t="s">
         <v>552</v>
       </c>
     </row>
@@ -38162,23 +38174,23 @@
       <c r="N23" s="169"/>
       <c r="O23" s="169"/>
       <c r="P23" s="169"/>
-      <c r="Q23" s="276" t="s">
+      <c r="Q23" s="285" t="s">
         <v>573</v>
       </c>
-      <c r="R23" s="276" t="s">
+      <c r="R23" s="285" t="s">
         <v>574</v>
       </c>
-      <c r="S23" s="276" t="s">
+      <c r="S23" s="285" t="s">
         <v>561</v>
       </c>
-      <c r="T23" s="275" t="s">
+      <c r="T23" s="284" t="s">
         <v>292</v>
       </c>
-      <c r="U23" s="275"/>
-      <c r="V23" s="275" t="s">
+      <c r="U23" s="284"/>
+      <c r="V23" s="284" t="s">
         <v>293</v>
       </c>
-      <c r="W23" s="275"/>
+      <c r="W23" s="284"/>
       <c r="X23" s="168" t="s">
         <v>462</v>
       </c>
@@ -38203,9 +38215,9 @@
       <c r="P24" s="170" t="s">
         <v>463</v>
       </c>
-      <c r="Q24" s="276"/>
-      <c r="R24" s="276"/>
-      <c r="S24" s="276"/>
+      <c r="Q24" s="285"/>
+      <c r="R24" s="285"/>
+      <c r="S24" s="285"/>
       <c r="T24" s="244" t="s">
         <v>463</v>
       </c>
@@ -66797,13 +66809,13 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="F1:AE32"/>
+  <dimension ref="F1:AR32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="18" max="18" width="15.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="6:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="6:44" x14ac:dyDescent="0.25">
       <c r="F1" s="4" t="s">
         <v>332</v>
       </c>
@@ -66811,12 +66823,12 @@
         <v>333</v>
       </c>
     </row>
-    <row r="2" spans="6:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="6:44" x14ac:dyDescent="0.25">
       <c r="G2" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="3" spans="6:31" x14ac:dyDescent="0.25">
+    <row r="3" spans="6:44" x14ac:dyDescent="0.25">
       <c r="F3" t="s">
         <v>331</v>
       </c>
@@ -66830,7 +66842,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="4" spans="6:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="6:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F4">
         <v>400</v>
       </c>
@@ -66885,8 +66897,19 @@
       <c r="AE4" t="s">
         <v>338</v>
       </c>
-    </row>
-    <row r="5" spans="6:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AH4" s="15"/>
+      <c r="AI4" s="15"/>
+      <c r="AJ4" s="15"/>
+      <c r="AK4" s="15"/>
+      <c r="AL4" s="15"/>
+      <c r="AM4" s="15"/>
+      <c r="AN4" s="15"/>
+      <c r="AO4" s="15"/>
+      <c r="AP4" s="15"/>
+      <c r="AQ4" s="15"/>
+      <c r="AR4" s="15"/>
+    </row>
+    <row r="5" spans="6:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F5">
         <v>500</v>
       </c>
@@ -66944,8 +66967,19 @@
       <c r="AE5" s="125">
         <v>6</v>
       </c>
-    </row>
-    <row r="6" spans="6:31" x14ac:dyDescent="0.25">
+      <c r="AH5" s="15"/>
+      <c r="AI5" s="15"/>
+      <c r="AJ5" s="15"/>
+      <c r="AK5" s="15"/>
+      <c r="AL5" s="15"/>
+      <c r="AM5" s="15"/>
+      <c r="AN5" s="15"/>
+      <c r="AO5" s="15"/>
+      <c r="AP5" s="15"/>
+      <c r="AQ5" s="15"/>
+      <c r="AR5" s="15"/>
+    </row>
+    <row r="6" spans="6:44" x14ac:dyDescent="0.25">
       <c r="F6">
         <v>600</v>
       </c>
@@ -67009,8 +67043,19 @@
       <c r="AE6" s="128">
         <v>7</v>
       </c>
-    </row>
-    <row r="7" spans="6:31" x14ac:dyDescent="0.25">
+      <c r="AH6" s="15"/>
+      <c r="AI6" s="15"/>
+      <c r="AJ6" s="15"/>
+      <c r="AK6" s="15"/>
+      <c r="AL6" s="15"/>
+      <c r="AM6" s="15"/>
+      <c r="AN6" s="15"/>
+      <c r="AO6" s="15"/>
+      <c r="AP6" s="15"/>
+      <c r="AQ6" s="15"/>
+      <c r="AR6" s="15"/>
+    </row>
+    <row r="7" spans="6:44" x14ac:dyDescent="0.25">
       <c r="F7">
         <v>700</v>
       </c>
@@ -67076,8 +67121,19 @@
       <c r="AE7" s="128">
         <v>8.5</v>
       </c>
-    </row>
-    <row r="8" spans="6:31" x14ac:dyDescent="0.25">
+      <c r="AH7" s="282"/>
+      <c r="AI7" s="282"/>
+      <c r="AJ7" s="15"/>
+      <c r="AK7" s="15"/>
+      <c r="AL7" s="15"/>
+      <c r="AM7" s="15"/>
+      <c r="AN7" s="15"/>
+      <c r="AO7" s="15"/>
+      <c r="AP7" s="15"/>
+      <c r="AQ7" s="15"/>
+      <c r="AR7" s="15"/>
+    </row>
+    <row r="8" spans="6:44" x14ac:dyDescent="0.25">
       <c r="R8" s="116">
         <v>40</v>
       </c>
@@ -67094,10 +67150,10 @@
         <v>19</v>
       </c>
       <c r="W8" s="113"/>
-      <c r="X8" t="s">
+      <c r="X8" s="276" t="s">
         <v>368</v>
       </c>
-      <c r="Y8">
+      <c r="Y8" s="10">
         <v>0</v>
       </c>
       <c r="AB8" s="134">
@@ -67113,8 +67169,19 @@
       <c r="AE8" s="128">
         <v>10</v>
       </c>
-    </row>
-    <row r="9" spans="6:31" x14ac:dyDescent="0.25">
+      <c r="AH8" s="136"/>
+      <c r="AI8" s="136"/>
+      <c r="AJ8" s="15"/>
+      <c r="AK8" s="15"/>
+      <c r="AL8" s="15"/>
+      <c r="AM8" s="15"/>
+      <c r="AN8" s="15"/>
+      <c r="AO8" s="15"/>
+      <c r="AP8" s="15"/>
+      <c r="AQ8" s="15"/>
+      <c r="AR8" s="15"/>
+    </row>
+    <row r="9" spans="6:44" x14ac:dyDescent="0.25">
       <c r="R9" s="116">
         <v>50</v>
       </c>
@@ -67131,10 +67198,10 @@
         <v>21</v>
       </c>
       <c r="W9" s="113"/>
-      <c r="X9" t="s">
+      <c r="X9" s="14" t="s">
         <v>331</v>
       </c>
-      <c r="Y9" s="136">
+      <c r="Y9" s="280">
         <v>0.16</v>
       </c>
       <c r="AB9" s="134">
@@ -67150,8 +67217,19 @@
       <c r="AE9" s="128">
         <v>11.5</v>
       </c>
-    </row>
-    <row r="10" spans="6:31" x14ac:dyDescent="0.25">
+      <c r="AH9" s="136"/>
+      <c r="AI9" s="136"/>
+      <c r="AJ9" s="15"/>
+      <c r="AK9" s="15"/>
+      <c r="AL9" s="15"/>
+      <c r="AM9" s="15"/>
+      <c r="AN9" s="15"/>
+      <c r="AO9" s="15"/>
+      <c r="AP9" s="15"/>
+      <c r="AQ9" s="15"/>
+      <c r="AR9" s="15"/>
+    </row>
+    <row r="10" spans="6:44" x14ac:dyDescent="0.25">
       <c r="R10" s="116">
         <v>60</v>
       </c>
@@ -67168,10 +67246,10 @@
         <v>23</v>
       </c>
       <c r="W10" s="113"/>
-      <c r="X10" t="s">
+      <c r="X10" s="278" t="s">
         <v>337</v>
       </c>
-      <c r="Y10">
+      <c r="Y10" s="281">
         <v>12.5</v>
       </c>
       <c r="AB10" s="135">
@@ -67187,8 +67265,19 @@
       <c r="AE10" s="131">
         <v>13</v>
       </c>
-    </row>
-    <row r="11" spans="6:31" x14ac:dyDescent="0.25">
+      <c r="AH10" s="136"/>
+      <c r="AI10" s="136"/>
+      <c r="AJ10" s="15"/>
+      <c r="AK10" s="15"/>
+      <c r="AL10" s="15"/>
+      <c r="AM10" s="15"/>
+      <c r="AN10" s="15"/>
+      <c r="AO10" s="15"/>
+      <c r="AP10" s="15"/>
+      <c r="AQ10" s="15"/>
+      <c r="AR10" s="15"/>
+    </row>
+    <row r="11" spans="6:44" x14ac:dyDescent="0.25">
       <c r="R11" s="116">
         <v>70</v>
       </c>
@@ -67220,8 +67309,19 @@
       <c r="AE11" s="125">
         <v>8</v>
       </c>
-    </row>
-    <row r="12" spans="6:31" x14ac:dyDescent="0.25">
+      <c r="AH11" s="136"/>
+      <c r="AI11" s="136"/>
+      <c r="AJ11" s="15"/>
+      <c r="AK11" s="15"/>
+      <c r="AL11" s="15"/>
+      <c r="AM11" s="15"/>
+      <c r="AN11" s="15"/>
+      <c r="AO11" s="15"/>
+      <c r="AP11" s="15"/>
+      <c r="AQ11" s="15"/>
+      <c r="AR11" s="15"/>
+    </row>
+    <row r="12" spans="6:44" x14ac:dyDescent="0.25">
       <c r="R12" s="117">
         <v>80</v>
       </c>
@@ -67236,6 +67336,12 @@
       </c>
       <c r="V12" s="132">
         <v>28</v>
+      </c>
+      <c r="X12" s="276" t="s">
+        <v>368</v>
+      </c>
+      <c r="Y12" s="10">
+        <v>0</v>
       </c>
       <c r="AB12" s="134">
         <v>40</v>
@@ -67250,8 +67356,25 @@
       <c r="AE12" s="128">
         <v>9.5</v>
       </c>
-    </row>
-    <row r="13" spans="6:31" x14ac:dyDescent="0.25">
+      <c r="AH12" s="136"/>
+      <c r="AI12" s="136"/>
+      <c r="AJ12" s="15"/>
+      <c r="AK12" s="15"/>
+      <c r="AL12" s="15"/>
+      <c r="AM12" s="15"/>
+      <c r="AN12" s="15"/>
+      <c r="AO12" s="15"/>
+      <c r="AP12" s="15"/>
+      <c r="AQ12" s="15"/>
+      <c r="AR12" s="15"/>
+    </row>
+    <row r="13" spans="6:44" x14ac:dyDescent="0.25">
+      <c r="X13" s="14" t="s">
+        <v>367</v>
+      </c>
+      <c r="Y13" s="277">
+        <v>0.46328995179259302</v>
+      </c>
       <c r="AB13" s="134">
         <v>50</v>
       </c>
@@ -67265,8 +67388,19 @@
       <c r="AE13" s="128">
         <v>11</v>
       </c>
-    </row>
-    <row r="14" spans="6:31" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AH13" s="15"/>
+      <c r="AI13" s="15"/>
+      <c r="AJ13" s="15"/>
+      <c r="AK13" s="15"/>
+      <c r="AL13" s="15"/>
+      <c r="AM13" s="15"/>
+      <c r="AN13" s="15"/>
+      <c r="AO13" s="15"/>
+      <c r="AP13" s="15"/>
+      <c r="AQ13" s="15"/>
+      <c r="AR13" s="15"/>
+    </row>
+    <row r="14" spans="6:44" ht="15.75" x14ac:dyDescent="0.25">
       <c r="R14" s="140" t="s">
         <v>373</v>
       </c>
@@ -67274,6 +67408,13 @@
       <c r="T14" s="118"/>
       <c r="U14" s="118"/>
       <c r="V14" s="118"/>
+      <c r="X14" s="278" t="s">
+        <v>337</v>
+      </c>
+      <c r="Y14" s="279">
+        <f>0.0125625963867342*1000</f>
+        <v>12.562596386734201</v>
+      </c>
       <c r="AB14" s="134">
         <v>60</v>
       </c>
@@ -67287,8 +67428,19 @@
       <c r="AE14" s="128">
         <v>12.5</v>
       </c>
-    </row>
-    <row r="15" spans="6:31" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AH14" s="15"/>
+      <c r="AI14" s="15"/>
+      <c r="AJ14" s="15"/>
+      <c r="AK14" s="15"/>
+      <c r="AL14" s="15"/>
+      <c r="AM14" s="15"/>
+      <c r="AN14" s="15"/>
+      <c r="AO14" s="15"/>
+      <c r="AP14" s="15"/>
+      <c r="AQ14" s="15"/>
+      <c r="AR14" s="15"/>
+    </row>
+    <row r="15" spans="6:44" ht="15.75" x14ac:dyDescent="0.25">
       <c r="R15" s="119" t="s">
         <v>336</v>
       </c>
@@ -67311,8 +67463,19 @@
       <c r="AE15" s="128">
         <v>14</v>
       </c>
-    </row>
-    <row r="16" spans="6:31" x14ac:dyDescent="0.25">
+      <c r="AH15" s="283"/>
+      <c r="AI15" s="283"/>
+      <c r="AJ15" s="283"/>
+      <c r="AK15" s="283"/>
+      <c r="AL15" s="283"/>
+      <c r="AM15" s="283"/>
+      <c r="AN15" s="15"/>
+      <c r="AO15" s="15"/>
+      <c r="AP15" s="15"/>
+      <c r="AQ15" s="15"/>
+      <c r="AR15" s="15"/>
+    </row>
+    <row r="16" spans="6:44" x14ac:dyDescent="0.25">
       <c r="R16" s="120" t="s">
         <v>123</v>
       </c>
@@ -67341,26 +67504,37 @@
       <c r="AE16" s="131">
         <v>16</v>
       </c>
-    </row>
-    <row r="17" spans="18:31" x14ac:dyDescent="0.25">
+      <c r="AH16" s="136"/>
+      <c r="AI16" s="136"/>
+      <c r="AJ16" s="136"/>
+      <c r="AK16" s="136"/>
+      <c r="AL16" s="136"/>
+      <c r="AM16" s="136"/>
+      <c r="AN16" s="15"/>
+      <c r="AO16" s="15"/>
+      <c r="AP16" s="15"/>
+      <c r="AQ16" s="15"/>
+      <c r="AR16" s="15"/>
+    </row>
+    <row r="17" spans="18:44" x14ac:dyDescent="0.25">
       <c r="R17" s="114">
         <v>30</v>
       </c>
       <c r="S17" s="142">
-        <f t="shared" ref="S17:V22" si="2">($Y$8+$R17*$Y$9+S$16*$Y$10)/S7</f>
-        <v>0.79999999999999993</v>
+        <f>($Y$12+$R17^0.75*$Y$13+S$16*$Y$14)/S7</f>
+        <v>0.98978888297456324</v>
       </c>
       <c r="T17" s="143">
-        <f t="shared" si="2"/>
-        <v>0.99062499999999998</v>
+        <f t="shared" ref="T17:V17" si="2">($Y$12+$R17^0.75*$Y$13+T$16*$Y$14)/T7</f>
+        <v>1.1349227993163662</v>
       </c>
       <c r="U17" s="143">
         <f t="shared" si="2"/>
-        <v>1.0045454545454546</v>
+        <v>1.1109119537467711</v>
       </c>
       <c r="V17" s="144">
         <f t="shared" si="2"/>
-        <v>0.98857142857142866</v>
+        <v>1.0572188391189474</v>
       </c>
       <c r="AB17" s="133">
         <v>30</v>
@@ -67375,26 +67549,37 @@
       <c r="AE17" s="125">
         <v>11</v>
       </c>
-    </row>
-    <row r="18" spans="18:31" x14ac:dyDescent="0.25">
+      <c r="AH17" s="136"/>
+      <c r="AI17" s="136"/>
+      <c r="AJ17" s="136"/>
+      <c r="AK17" s="136"/>
+      <c r="AL17" s="136"/>
+      <c r="AM17" s="136"/>
+      <c r="AN17" s="15"/>
+      <c r="AO17" s="15"/>
+      <c r="AP17" s="15"/>
+      <c r="AQ17" s="15"/>
+      <c r="AR17" s="15"/>
+    </row>
+    <row r="18" spans="18:44" x14ac:dyDescent="0.25">
       <c r="R18" s="116">
         <v>40</v>
       </c>
       <c r="S18" s="145">
-        <f t="shared" si="2"/>
-        <v>0.91428571428571437</v>
+        <f t="shared" ref="S18:V18" si="3">($Y$12+$R18^0.75*$Y$13+S$16*$Y$14)/S8</f>
+        <v>1.0526883931215636</v>
       </c>
       <c r="T18" s="146">
-        <f>($Y$8+$R18*$Y$9+T$16*$Y$10)/T8</f>
-        <v>1.0026315789473685</v>
+        <f t="shared" si="3"/>
+        <v>1.1062597735299469</v>
       </c>
       <c r="U18" s="146">
-        <f t="shared" si="2"/>
-        <v>1.012</v>
+        <f t="shared" si="3"/>
+        <v>1.0920093556174435</v>
       </c>
       <c r="V18" s="147">
-        <f t="shared" si="2"/>
-        <v>0.99473684210526303</v>
+        <f t="shared" si="3"/>
+        <v>1.0490218493992181</v>
       </c>
       <c r="AB18" s="134">
         <v>40</v>
@@ -67409,26 +67594,37 @@
       <c r="AE18" s="128">
         <v>12.5</v>
       </c>
-    </row>
-    <row r="19" spans="18:31" x14ac:dyDescent="0.25">
+      <c r="AH18" s="136"/>
+      <c r="AI18" s="136"/>
+      <c r="AJ18" s="136"/>
+      <c r="AK18" s="136"/>
+      <c r="AL18" s="136"/>
+      <c r="AM18" s="136"/>
+      <c r="AN18" s="15"/>
+      <c r="AO18" s="15"/>
+      <c r="AP18" s="15"/>
+      <c r="AQ18" s="15"/>
+      <c r="AR18" s="15"/>
+    </row>
+    <row r="19" spans="18:44" x14ac:dyDescent="0.25">
       <c r="R19" s="116">
         <v>50</v>
       </c>
       <c r="S19" s="145">
-        <f t="shared" si="2"/>
-        <v>0.94117647058823528</v>
+        <f>($Y$12+$R19^0.75*$Y$13+S$16*$Y$14)/S9</f>
+        <v>1.0248527210041596</v>
       </c>
       <c r="T19" s="146">
-        <f t="shared" si="2"/>
-        <v>1.0113636363636365</v>
+        <f t="shared" ref="T19:V19" si="4">($Y$12+$R19^0.75*$Y$13+T$16*$Y$14)/T9</f>
+        <v>1.0774452022926277</v>
       </c>
       <c r="U19" s="146">
-        <f t="shared" si="2"/>
-        <v>1.0178571428571428</v>
+        <f t="shared" si="4"/>
+        <v>1.0708961658501754</v>
       </c>
       <c r="V19" s="147">
-        <f t="shared" si="2"/>
-        <v>0.97619047619047616</v>
+        <f t="shared" si="4"/>
+        <v>1.0130402150128361</v>
       </c>
       <c r="AB19" s="134">
         <v>50</v>
@@ -67443,26 +67639,37 @@
       <c r="AE19" s="128">
         <v>14</v>
       </c>
-    </row>
-    <row r="20" spans="18:31" x14ac:dyDescent="0.25">
+      <c r="AH19" s="15"/>
+      <c r="AI19" s="15"/>
+      <c r="AJ19" s="15"/>
+      <c r="AK19" s="15"/>
+      <c r="AL19" s="15"/>
+      <c r="AM19" s="15"/>
+      <c r="AN19" s="15"/>
+      <c r="AO19" s="15"/>
+      <c r="AP19" s="15"/>
+      <c r="AQ19" s="15"/>
+      <c r="AR19" s="15"/>
+    </row>
+    <row r="20" spans="18:44" x14ac:dyDescent="0.25">
       <c r="R20" s="116">
         <v>60</v>
       </c>
       <c r="S20" s="145">
-        <f t="shared" si="2"/>
-        <v>0.96</v>
+        <f t="shared" ref="S20:V20" si="5">($Y$12+$R20^0.75*$Y$13+S$16*$Y$14)/S10</f>
+        <v>0.99877190826154594</v>
       </c>
       <c r="T20" s="146">
-        <f t="shared" si="2"/>
-        <v>1.018</v>
+        <f t="shared" si="5"/>
+        <v>1.0502694543439208</v>
       </c>
       <c r="U20" s="146">
-        <f t="shared" si="2"/>
-        <v>1.0225806451612902</v>
+        <f t="shared" si="5"/>
+        <v>1.0496140178053264</v>
       </c>
       <c r="V20" s="147">
-        <f t="shared" si="2"/>
-        <v>0.96086956521739142</v>
+        <f t="shared" si="5"/>
+        <v>0.9804484986673766</v>
       </c>
       <c r="AB20" s="134">
         <v>60</v>
@@ -67477,26 +67684,37 @@
       <c r="AE20" s="128">
         <v>15.5</v>
       </c>
-    </row>
-    <row r="21" spans="18:31" x14ac:dyDescent="0.25">
+      <c r="AH20" s="283"/>
+      <c r="AI20" s="283"/>
+      <c r="AJ20" s="283"/>
+      <c r="AK20" s="283"/>
+      <c r="AL20" s="283"/>
+      <c r="AM20" s="283"/>
+      <c r="AN20" s="283"/>
+      <c r="AO20" s="283"/>
+      <c r="AP20" s="283"/>
+      <c r="AQ20" s="15"/>
+      <c r="AR20" s="15"/>
+    </row>
+    <row r="21" spans="18:44" x14ac:dyDescent="0.25">
       <c r="R21" s="116">
         <v>70</v>
       </c>
       <c r="S21" s="145">
-        <f t="shared" si="2"/>
-        <v>0.97391304347826091</v>
+        <f>($Y$12+$R21^0.75*$Y$13+S$16*$Y$14)/S11</f>
+        <v>0.97494153004629269</v>
       </c>
       <c r="T21" s="146">
-        <f t="shared" si="2"/>
-        <v>1.0232142857142859</v>
+        <f t="shared" ref="T21:V21" si="6">($Y$12+$R21^0.75*$Y$13+T$16*$Y$14)/T11</f>
+        <v>1.0251769065868512</v>
       </c>
       <c r="U21" s="146">
-        <f t="shared" si="2"/>
-        <v>0.99714285714285733</v>
+        <f t="shared" si="6"/>
+        <v>0.99960718793711234</v>
       </c>
       <c r="V21" s="147">
-        <f t="shared" si="2"/>
-        <v>0.94800000000000006</v>
+        <f t="shared" si="6"/>
+        <v>0.95097695929066273</v>
       </c>
       <c r="AB21" s="134">
         <v>70</v>
@@ -67511,26 +67729,37 @@
       <c r="AE21" s="128">
         <v>17.5</v>
       </c>
-    </row>
-    <row r="22" spans="18:31" x14ac:dyDescent="0.25">
+      <c r="AH21" s="136"/>
+      <c r="AI21" s="136"/>
+      <c r="AJ21" s="136"/>
+      <c r="AK21" s="136"/>
+      <c r="AL21" s="136"/>
+      <c r="AM21" s="136"/>
+      <c r="AN21" s="136"/>
+      <c r="AO21" s="136"/>
+      <c r="AP21" s="136"/>
+      <c r="AQ21" s="15"/>
+      <c r="AR21" s="15"/>
+    </row>
+    <row r="22" spans="18:44" x14ac:dyDescent="0.25">
       <c r="R22" s="117">
         <v>80</v>
       </c>
       <c r="S22" s="148">
-        <f t="shared" si="2"/>
-        <v>0.98461538461538467</v>
+        <f t="shared" ref="S22:V22" si="7">($Y$12+$R22^0.75*$Y$13+S$16*$Y$14)/S12</f>
+        <v>0.95329434970550908</v>
       </c>
       <c r="T22" s="149">
-        <f t="shared" si="2"/>
-        <v>0.99531250000000004</v>
+        <f t="shared" si="7"/>
+        <v>0.97084222767844797</v>
       </c>
       <c r="U22" s="149">
-        <f t="shared" si="2"/>
-        <v>0.97692307692307701</v>
+        <f t="shared" si="7"/>
+        <v>0.9576474225404471</v>
       </c>
       <c r="V22" s="150">
-        <f t="shared" si="2"/>
-        <v>0.90357142857142858</v>
+        <f t="shared" si="7"/>
+        <v>0.89126510474663634</v>
       </c>
       <c r="AB22" s="135">
         <v>80</v>
@@ -67545,8 +67774,19 @@
       <c r="AE22" s="131">
         <v>19.5</v>
       </c>
-    </row>
-    <row r="23" spans="18:31" x14ac:dyDescent="0.25">
+      <c r="AH22" s="136"/>
+      <c r="AI22" s="136"/>
+      <c r="AJ22" s="136"/>
+      <c r="AK22" s="136"/>
+      <c r="AL22" s="136"/>
+      <c r="AM22" s="136"/>
+      <c r="AN22" s="136"/>
+      <c r="AO22" s="136"/>
+      <c r="AP22" s="136"/>
+      <c r="AQ22" s="15"/>
+      <c r="AR22" s="15"/>
+    </row>
+    <row r="23" spans="18:44" x14ac:dyDescent="0.25">
       <c r="AB23" s="133">
         <v>30</v>
       </c>
@@ -67560,8 +67800,19 @@
       <c r="AE23" s="125">
         <v>17.5</v>
       </c>
-    </row>
-    <row r="24" spans="18:31" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AH23" s="136"/>
+      <c r="AI23" s="136"/>
+      <c r="AJ23" s="136"/>
+      <c r="AK23" s="136"/>
+      <c r="AL23" s="136"/>
+      <c r="AM23" s="136"/>
+      <c r="AN23" s="136"/>
+      <c r="AO23" s="136"/>
+      <c r="AP23" s="136"/>
+      <c r="AQ23" s="15"/>
+      <c r="AR23" s="15"/>
+    </row>
+    <row r="24" spans="18:44" ht="15.75" x14ac:dyDescent="0.25">
       <c r="R24" s="140" t="s">
         <v>372</v>
       </c>
@@ -67582,8 +67833,19 @@
       <c r="AE24" s="128">
         <v>19</v>
       </c>
-    </row>
-    <row r="25" spans="18:31" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AH24" s="15"/>
+      <c r="AI24" s="15"/>
+      <c r="AJ24" s="15"/>
+      <c r="AK24" s="15"/>
+      <c r="AL24" s="15"/>
+      <c r="AM24" s="15"/>
+      <c r="AN24" s="15"/>
+      <c r="AO24" s="15"/>
+      <c r="AP24" s="15"/>
+      <c r="AQ24" s="15"/>
+      <c r="AR24" s="15"/>
+    </row>
+    <row r="25" spans="18:44" ht="15.75" x14ac:dyDescent="0.25">
       <c r="R25" s="119" t="s">
         <v>336</v>
       </c>
@@ -67606,8 +67868,19 @@
       <c r="AE25" s="128">
         <v>21</v>
       </c>
-    </row>
-    <row r="26" spans="18:31" x14ac:dyDescent="0.25">
+      <c r="AH25" s="15"/>
+      <c r="AI25" s="15"/>
+      <c r="AJ25" s="15"/>
+      <c r="AK25" s="15"/>
+      <c r="AL25" s="15"/>
+      <c r="AM25" s="15"/>
+      <c r="AN25" s="15"/>
+      <c r="AO25" s="15"/>
+      <c r="AP25" s="15"/>
+      <c r="AQ25" s="15"/>
+      <c r="AR25" s="15"/>
+    </row>
+    <row r="26" spans="18:44" x14ac:dyDescent="0.25">
       <c r="R26" s="120" t="s">
         <v>123</v>
       </c>
@@ -67636,8 +67909,19 @@
       <c r="AE26" s="128">
         <v>23</v>
       </c>
-    </row>
-    <row r="27" spans="18:31" x14ac:dyDescent="0.25">
+      <c r="AH26" s="15"/>
+      <c r="AI26" s="15"/>
+      <c r="AJ26" s="15"/>
+      <c r="AK26" s="15"/>
+      <c r="AL26" s="15"/>
+      <c r="AM26" s="15"/>
+      <c r="AN26" s="15"/>
+      <c r="AO26" s="15"/>
+      <c r="AP26" s="15"/>
+      <c r="AQ26" s="15"/>
+      <c r="AR26" s="15"/>
+    </row>
+    <row r="27" spans="18:44" x14ac:dyDescent="0.25">
       <c r="R27" s="114">
         <v>30</v>
       </c>
@@ -67646,15 +67930,15 @@
         <v>1.0148066401910558</v>
       </c>
       <c r="T27" s="143">
-        <f t="shared" ref="T27:V27" si="3">(0.475*$R27^0.75 + T$26*$X$27)/T7</f>
+        <f t="shared" ref="T27:V27" si="8">(0.475*$R27^0.75 + T$26*$X$27)/T7</f>
         <v>1.1361049801432919</v>
       </c>
       <c r="U27" s="143">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>1.0989854401042123</v>
       </c>
       <c r="V27" s="144">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>1.0336479909226477</v>
       </c>
       <c r="X27">
@@ -67674,24 +67958,24 @@
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="18:31" x14ac:dyDescent="0.25">
+    <row r="28" spans="18:44" x14ac:dyDescent="0.25">
       <c r="R28" s="116">
         <v>40</v>
       </c>
       <c r="S28" s="145">
-        <f t="shared" ref="S28:V28" si="4">(0.475*$R28^0.75 + S$26*$X$27)/S8</f>
+        <f t="shared" ref="S28:V28" si="9">(0.475*$R28^0.75 + S$26*$X$27)/S8</f>
         <v>1.0792959890409974</v>
       </c>
       <c r="T28" s="146">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>1.1110602024512612</v>
       </c>
       <c r="U28" s="146">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>1.0844057538629586</v>
       </c>
       <c r="V28" s="147">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>1.0292143117519463</v>
       </c>
       <c r="X28">
@@ -67711,92 +67995,117 @@
         <v>28</v>
       </c>
     </row>
-    <row r="29" spans="18:31" x14ac:dyDescent="0.25">
+    <row r="29" spans="18:44" x14ac:dyDescent="0.25">
       <c r="R29" s="116">
         <v>50</v>
       </c>
       <c r="S29" s="145">
-        <f t="shared" ref="S29:V29" si="5">(0.475*$R29^0.75 + S$26*$X$27)/S9</f>
+        <f t="shared" ref="S29:V29" si="10">(0.475*$R29^0.75 + S$26*$X$27)/S9</f>
         <v>1.0507567465976686</v>
       </c>
       <c r="T29" s="146">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>1.0846756678254712</v>
       </c>
       <c r="U29" s="146">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>1.0665308818628703</v>
       </c>
       <c r="V29" s="147">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>0.99673487362286584</v>
       </c>
     </row>
-    <row r="30" spans="18:31" x14ac:dyDescent="0.25">
+    <row r="30" spans="18:44" x14ac:dyDescent="0.25">
       <c r="R30" s="116">
         <v>60</v>
       </c>
       <c r="S30" s="145">
-        <f t="shared" ref="S30:V30" si="6">(0.475*$R30^0.75 + S$26*$X$27)/S10</f>
+        <f t="shared" ref="S30:V30" si="11">(0.475*$R30^0.75 + S$26*$X$27)/S10</f>
         <v>1.0240167190947895</v>
       </c>
       <c r="T30" s="146">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>1.0592133752758317</v>
       </c>
       <c r="U30" s="146">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>1.0477527219966383</v>
       </c>
       <c r="V30" s="147">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>0.966963790910778</v>
       </c>
     </row>
-    <row r="31" spans="18:31" x14ac:dyDescent="0.25">
+    <row r="31" spans="18:44" x14ac:dyDescent="0.25">
       <c r="R31" s="116">
         <v>70</v>
       </c>
       <c r="S31" s="145">
-        <f t="shared" ref="S31:V31" si="7">(0.475*$R31^0.75 + S$26*$X$27)/S11</f>
+        <f t="shared" ref="S31:V31" si="12">(0.475*$R31^0.75 + S$26*$X$27)/S11</f>
         <v>0.99958400776909073</v>
       </c>
       <c r="T31" s="146">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>1.0353725778103244</v>
       </c>
       <c r="U31" s="146">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>0.99972663367683112</v>
       </c>
       <c r="V31" s="147">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>0.9398086435737818</v>
       </c>
     </row>
-    <row r="32" spans="18:31" x14ac:dyDescent="0.25">
+    <row r="32" spans="18:44" x14ac:dyDescent="0.25">
       <c r="R32" s="117">
         <v>80</v>
       </c>
       <c r="S32" s="148">
-        <f t="shared" ref="S32:V32" si="8">(0.475*$R32^0.75 + S$26*$X$27)/S12</f>
+        <f t="shared" ref="S32:V32" si="13">(0.475*$R32^0.75 + S$26*$X$27)/S12</f>
         <v>0.9773896765040011</v>
       </c>
       <c r="T32" s="149">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>0.98162911215950088</v>
       </c>
       <c r="U32" s="149">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>0.95928542536164174</v>
       </c>
       <c r="V32" s="150">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>0.88235949266257196</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="S17:V22">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="num" val="0.9"/>
+        <cfvo type="num" val="1"/>
+        <cfvo type="num" val="1.1000000000000001"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S27:V32">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="num" val="0.9"/>
+        <cfvo type="num" val="1"/>
+        <cfvo type="num" val="1.1000000000000001"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/data/default/CattleHerd.xlsx
+++ b/data/default/CattleHerd.xlsx
@@ -145,7 +145,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5596" uniqueCount="689">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5596" uniqueCount="690">
   <si>
     <t>value</t>
   </si>
@@ -2215,6 +2215,9 @@
   <si>
     <t>Spörndly (2003)</t>
   </si>
+  <si>
+    <t>g/kg DM</t>
+  </si>
 </sst>
 </file>
 
@@ -3713,13 +3716,13 @@
     <xf numFmtId="14" fontId="51" fillId="37" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="1" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="38" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="40" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="44">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -21050,7 +21053,7 @@
       <c r="J229" s="158" t="s">
         <v>680</v>
       </c>
-      <c r="K229" s="311">
+      <c r="K229" s="309">
         <v>0</v>
       </c>
       <c r="L229" s="158" t="s">
@@ -21064,7 +21067,7 @@
       <c r="J230" s="158" t="s">
         <v>682</v>
       </c>
-      <c r="K230" s="311">
+      <c r="K230" s="309">
         <v>0</v>
       </c>
       <c r="L230" s="158" t="s">
@@ -21078,7 +21081,7 @@
       <c r="J231" s="158" t="s">
         <v>683</v>
       </c>
-      <c r="K231" s="311">
+      <c r="K231" s="309">
         <v>0</v>
       </c>
       <c r="L231" s="158" t="s">
@@ -21092,7 +21095,7 @@
       <c r="J232" s="158" t="s">
         <v>685</v>
       </c>
-      <c r="K232" s="311">
+      <c r="K232" s="309">
         <v>0</v>
       </c>
       <c r="L232" s="158" t="s">
@@ -21309,10 +21312,10 @@
         <v>687</v>
       </c>
       <c r="K249" s="2">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="L249" t="s">
-        <v>311</v>
+        <v>689</v>
       </c>
       <c r="N249" t="s">
         <v>688</v>
@@ -43002,23 +43005,23 @@
       <c r="N24" s="168"/>
       <c r="O24" s="168"/>
       <c r="P24" s="168"/>
-      <c r="Q24" s="310" t="s">
+      <c r="Q24" s="311" t="s">
         <v>563</v>
       </c>
-      <c r="R24" s="310" t="s">
+      <c r="R24" s="311" t="s">
         <v>564</v>
       </c>
-      <c r="S24" s="310" t="s">
+      <c r="S24" s="311" t="s">
         <v>551</v>
       </c>
-      <c r="T24" s="309" t="s">
+      <c r="T24" s="310" t="s">
         <v>290</v>
       </c>
-      <c r="U24" s="309"/>
-      <c r="V24" s="309" t="s">
+      <c r="U24" s="310"/>
+      <c r="V24" s="310" t="s">
         <v>291</v>
       </c>
-      <c r="W24" s="309"/>
+      <c r="W24" s="310"/>
       <c r="X24" s="167" t="s">
         <v>455</v>
       </c>
@@ -43043,9 +43046,9 @@
       <c r="P25" s="169" t="s">
         <v>456</v>
       </c>
-      <c r="Q25" s="310"/>
-      <c r="R25" s="310"/>
-      <c r="S25" s="310"/>
+      <c r="Q25" s="311"/>
+      <c r="R25" s="311"/>
+      <c r="S25" s="311"/>
       <c r="T25" s="243" t="s">
         <v>456</v>
       </c>

--- a/data/default/CattleHerd.xlsx
+++ b/data/default/CattleHerd.xlsx
@@ -143,7 +143,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5616" uniqueCount="734">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5618" uniqueCount="735">
   <si>
     <t>value</t>
   </si>
@@ -2347,6 +2347,9 @@
   </si>
   <si>
     <t>% of LW</t>
+  </si>
+  <si>
+    <t>not applicable to dairy cows</t>
   </si>
 </sst>
 </file>
@@ -3866,14 +3869,14 @@
     <xf numFmtId="9" fontId="35" fillId="0" borderId="0" xfId="42" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="38" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="40" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="44">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -15619,6 +15622,9 @@
       <c r="L27" t="s">
         <v>4</v>
       </c>
+      <c r="M27" t="s">
+        <v>734</v>
+      </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
@@ -15840,18 +15846,22 @@
       <c r="J39" t="s">
         <v>3</v>
       </c>
-      <c r="K39">
-        <v>12.7</v>
+      <c r="K39" s="13">
+        <f>(1291*12.4 + 3095*12.5 + 2319*12.5 + 1051*12.7 + 1624*12.6) / (1291 + 3095 + 2319 + 1051 + 1624)</f>
+        <v>12.525959488272919</v>
       </c>
       <c r="L39" t="s">
         <v>4</v>
       </c>
+      <c r="M39" t="s">
+        <v>720</v>
+      </c>
       <c r="N39" t="s">
         <v>719</v>
       </c>
       <c r="O39" s="318">
         <f>(12/K39)*(1*(1-K44/100)+2*K44/100)*(1-K45/100)</f>
-        <v>0.96237372896491069</v>
+        <v>0.97574532069156117</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
@@ -16448,7 +16458,7 @@
       <c r="M64" s="109" t="s">
         <v>616</v>
       </c>
-      <c r="O64" s="321">
+      <c r="O64" s="319">
         <f>O63</f>
         <v>0.515625</v>
       </c>
@@ -16772,7 +16782,7 @@
       <c r="M75" s="109" t="s">
         <v>616</v>
       </c>
-      <c r="O75" s="321">
+      <c r="O75" s="319">
         <f>O74</f>
         <v>0.5625</v>
       </c>
@@ -19183,7 +19193,7 @@
       <c r="N185" s="255" t="s">
         <v>658</v>
       </c>
-      <c r="O185" s="322">
+      <c r="O185" s="320">
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
@@ -19208,7 +19218,7 @@
         <v>660</v>
       </c>
       <c r="N186" s="255"/>
-      <c r="O186" s="322">
+      <c r="O186" s="320">
         <v>0.03</v>
       </c>
     </row>
@@ -19232,7 +19242,7 @@
       <c r="M187" t="s">
         <v>660</v>
       </c>
-      <c r="O187" s="322">
+      <c r="O187" s="320">
         <v>0.03</v>
       </c>
     </row>
@@ -19256,7 +19266,7 @@
       <c r="M188" t="s">
         <v>660</v>
       </c>
-      <c r="O188" s="322">
+      <c r="O188" s="320">
         <v>0.03</v>
       </c>
     </row>
@@ -19280,7 +19290,7 @@
       <c r="M189" t="s">
         <v>660</v>
       </c>
-      <c r="O189" s="322">
+      <c r="O189" s="320">
         <v>0.03</v>
       </c>
     </row>
@@ -19304,7 +19314,7 @@
       <c r="M190" t="s">
         <v>660</v>
       </c>
-      <c r="O190" s="322">
+      <c r="O190" s="320">
         <v>0.03</v>
       </c>
     </row>
@@ -19328,7 +19338,7 @@
       <c r="M191" t="s">
         <v>660</v>
       </c>
-      <c r="O191" s="322">
+      <c r="O191" s="320">
         <v>0.03</v>
       </c>
     </row>
@@ -19352,7 +19362,7 @@
       <c r="M192" t="s">
         <v>660</v>
       </c>
-      <c r="O192" s="322">
+      <c r="O192" s="320">
         <v>0.03</v>
       </c>
     </row>
@@ -19376,7 +19386,7 @@
       <c r="M193" t="s">
         <v>660</v>
       </c>
-      <c r="O193" s="322">
+      <c r="O193" s="320">
         <v>0.03</v>
       </c>
     </row>
@@ -19400,7 +19410,7 @@
       <c r="M194" t="s">
         <v>660</v>
       </c>
-      <c r="O194" s="322">
+      <c r="O194" s="320">
         <v>0.03</v>
       </c>
     </row>
@@ -19424,7 +19434,7 @@
       <c r="M195" t="s">
         <v>660</v>
       </c>
-      <c r="O195" s="322">
+      <c r="O195" s="320">
         <v>0.03</v>
       </c>
     </row>
@@ -19448,7 +19458,7 @@
       <c r="M196" t="s">
         <v>660</v>
       </c>
-      <c r="O196" s="322">
+      <c r="O196" s="320">
         <v>0.03</v>
       </c>
     </row>
@@ -46068,23 +46078,23 @@
       <c r="N24" s="166"/>
       <c r="O24" s="166"/>
       <c r="P24" s="166"/>
-      <c r="Q24" s="320" t="s">
+      <c r="Q24" s="322" t="s">
         <v>560</v>
       </c>
-      <c r="R24" s="320" t="s">
+      <c r="R24" s="322" t="s">
         <v>561</v>
       </c>
-      <c r="S24" s="320" t="s">
+      <c r="S24" s="322" t="s">
         <v>548</v>
       </c>
-      <c r="T24" s="319" t="s">
+      <c r="T24" s="321" t="s">
         <v>287</v>
       </c>
-      <c r="U24" s="319"/>
-      <c r="V24" s="319" t="s">
+      <c r="U24" s="321"/>
+      <c r="V24" s="321" t="s">
         <v>288</v>
       </c>
-      <c r="W24" s="319"/>
+      <c r="W24" s="321"/>
       <c r="X24" s="165" t="s">
         <v>452</v>
       </c>
@@ -46129,9 +46139,9 @@
       <c r="P25" s="167" t="s">
         <v>453</v>
       </c>
-      <c r="Q25" s="320"/>
-      <c r="R25" s="320"/>
-      <c r="S25" s="320"/>
+      <c r="Q25" s="322"/>
+      <c r="R25" s="322"/>
+      <c r="S25" s="322"/>
       <c r="T25" s="241" t="s">
         <v>453</v>
       </c>
